--- a/बजेट माग estimate/Swasthya chauki/water tank 2082_2083.xlsx
+++ b/बजेट माग estimate/Swasthya chauki/water tank 2082_2083.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\082_083\ward1\बजेट माग estimate\Swasthya chauki\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\बजेट माग estimate\Swasthya chauki\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CB71DE-6F9E-4F38-8020-C2AA8868A1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="8400" activeTab="2"/>
+    <workbookView xWindow="-135" yWindow="0" windowWidth="15120" windowHeight="10905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESTIMATE" sheetId="25" r:id="rId1"/>
@@ -23,12 +24,12 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">ESTIMATE!$A$1:$L$71</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">me!$A$1:$L$108</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">me!$A$1:$L$112</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">ESTIMATE!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">me!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">WCR!$1:$11</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -44,12 +45,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>DELL</author>
   </authors>
   <commentList>
-    <comment ref="F10" authorId="0" shapeId="0">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -73,7 +74,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -102,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="153">
   <si>
     <t>S.N.</t>
   </si>
@@ -608,33 +609,54 @@
   <si>
     <t>d]lzgsf] k|of]u u/L ;'k/ :6«Sr/df l;d]G6 s+lqm6 ug]{ sfd -!M!=%M#_</t>
   </si>
+  <si>
+    <t>vat on diesel</t>
+  </si>
+  <si>
+    <t>vat on petrol</t>
+  </si>
+  <si>
+    <t>-at toilet of ward</t>
+  </si>
+  <si>
+    <t>-deduction for opening</t>
+  </si>
+  <si>
+    <t>e'O{+tNnfdf lrDgL e§fsf] O{+6fsf] uf/f] l;d]G6 d;nf -!M^_ df</t>
+  </si>
+  <si>
+    <t>-at water tank</t>
+  </si>
+  <si>
+    <t>-At shear wall</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="21">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="#."/>
-    <numFmt numFmtId="169" formatCode="0.00_)"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_ * #,##0_)&quot;$&quot;_ ;_ * \(#,##0\)&quot;$&quot;_ ;_ * &quot;-&quot;_)&quot;$&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="173" formatCode="General_)"/>
-    <numFmt numFmtId="174" formatCode="_ * #,##0_)_$_ ;_ * \(#,##0\)_$_ ;_ * &quot;-&quot;_)_$_ ;_ @_ "/>
-    <numFmt numFmtId="175" formatCode="_ * #,##0.00_)&quot;$&quot;_ ;_ * \(#,##0.00\)&quot;$&quot;_ ;_ * &quot;-&quot;??_)&quot;$&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_)_$_ ;_ * \(#,##0.00\)_$_ ;_ * &quot;-&quot;??_)_$_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="mmmm\ d\,\ yyyy"/>
-    <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#.##0\)"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="181" formatCode="_ &quot;\&quot;* #,##0_ ;_ &quot;\&quot;* \-#,##0_ ;_ &quot;\&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="182" formatCode="_ &quot;\&quot;* #,##0.00_ ;_ &quot;\&quot;* \-#,##0.00_ ;_ &quot;\&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="183" formatCode="0.0"/>
+    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#."/>
+    <numFmt numFmtId="168" formatCode="0.00_)"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_ * #,##0_)&quot;$&quot;_ ;_ * \(#,##0\)&quot;$&quot;_ ;_ * &quot;-&quot;_)&quot;$&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="172" formatCode="General_)"/>
+    <numFmt numFmtId="173" formatCode="_ * #,##0_)_$_ ;_ * \(#,##0\)_$_ ;_ * &quot;-&quot;_)_$_ ;_ @_ "/>
+    <numFmt numFmtId="174" formatCode="_ * #,##0.00_)&quot;$&quot;_ ;_ * \(#,##0.00\)&quot;$&quot;_ ;_ * &quot;-&quot;??_)&quot;$&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="175" formatCode="_ * #,##0.00_)_$_ ;_ * \(#,##0.00\)_$_ ;_ * &quot;-&quot;??_)_$_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="mmmm\ d\,\ yyyy"/>
+    <numFmt numFmtId="177" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#.##0\)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="_ &quot;\&quot;* #,##0_ ;_ &quot;\&quot;* \-#,##0_ ;_ &quot;\&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="181" formatCode="_ &quot;\&quot;* #,##0.00_ ;_ &quot;\&quot;* \-#,##0.00_ ;_ &quot;\&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="182" formatCode="0.0"/>
   </numFmts>
   <fonts count="86">
     <font>
@@ -1867,7 +1889,7 @@
   </borders>
   <cellStyleXfs count="759">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1895,35 +1917,35 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -1949,7 +1971,7 @@
     <xf numFmtId="10" fontId="5" fillId="24" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -1998,10 +2020,10 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -2370,41 +2392,41 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyNumberFormat="0" applyFont="0">
       <alignment horizontal="center" vertical="justify"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="167" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="174" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="175" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="5" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="15"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="14" fontId="34" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="38" fontId="29" fillId="0" borderId="16">
       <alignment vertical="center"/>
@@ -2418,11 +2440,11 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="175" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
@@ -2452,12 +2474,12 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="29" borderId="15"/>
     <xf numFmtId="0" fontId="45" fillId="27" borderId="15"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="175" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -2501,10 +2523,10 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="179" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="180" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="181" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -2653,41 +2675,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="57" fillId="0" borderId="0"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="57" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2697,7 +2719,7 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="49" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="49" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2707,14 +2729,14 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="49" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="49" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="49" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="49" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2763,24 +2785,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="65" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="65" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="65" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="48" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="48" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2824,15 +2846,15 @@
     <xf numFmtId="0" fontId="66" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="51" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="51" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="51" fillId="2" borderId="23" xfId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2866,18 +2888,10 @@
     <xf numFmtId="0" fontId="67" fillId="2" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="51" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="51" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="51" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="51" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2892,7 +2906,7 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="49" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="49" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2900,9 +2914,88 @@
     <xf numFmtId="0" fontId="70" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="67" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="67" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="78" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="83" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="83" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="51" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="33" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="33" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="33" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2920,6 +3013,21 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2932,920 +3040,854 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="51" fillId="33" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="51" fillId="33" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="52" fillId="33" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="78" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="83" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="78" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="78" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="83" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="78" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="78" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="78" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="78" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="78" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="78" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="78" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="52" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="52" fillId="33" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="52" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="52" fillId="33" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="2" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="justify"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="33" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="51" fillId="2" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="51" fillId="33" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="51" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="33" borderId="23" xfId="734" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="183" fontId="51" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="2" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="51" fillId="33" borderId="23" xfId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="759">
-    <cellStyle name="??" xfId="476"/>
-    <cellStyle name="?? [0.00]_PERSONAL" xfId="477"/>
-    <cellStyle name="???? [0.00]_PERSONAL" xfId="478"/>
-    <cellStyle name="????_PERSONAL" xfId="479"/>
-    <cellStyle name="??_PERSONAL" xfId="480"/>
-    <cellStyle name="20% - Accent1 10" xfId="457"/>
-    <cellStyle name="20% - Accent1 11" xfId="592"/>
-    <cellStyle name="20% - Accent1 12" xfId="638"/>
-    <cellStyle name="20% - Accent1 13" xfId="724"/>
-    <cellStyle name="20% - Accent1 2" xfId="2"/>
-    <cellStyle name="20% - Accent1 3" xfId="138"/>
-    <cellStyle name="20% - Accent1 4" xfId="209"/>
-    <cellStyle name="20% - Accent1 5" xfId="241"/>
-    <cellStyle name="20% - Accent1 6" xfId="267"/>
-    <cellStyle name="20% - Accent1 7" xfId="328"/>
-    <cellStyle name="20% - Accent1 8" xfId="370"/>
-    <cellStyle name="20% - Accent1 9" xfId="396"/>
-    <cellStyle name="20% - Accent2 10" xfId="467"/>
-    <cellStyle name="20% - Accent2 11" xfId="593"/>
-    <cellStyle name="20% - Accent2 12" xfId="639"/>
-    <cellStyle name="20% - Accent2 13" xfId="723"/>
-    <cellStyle name="20% - Accent2 2" xfId="3"/>
-    <cellStyle name="20% - Accent2 3" xfId="139"/>
-    <cellStyle name="20% - Accent2 4" xfId="222"/>
-    <cellStyle name="20% - Accent2 5" xfId="251"/>
-    <cellStyle name="20% - Accent2 6" xfId="268"/>
-    <cellStyle name="20% - Accent2 7" xfId="340"/>
-    <cellStyle name="20% - Accent2 8" xfId="380"/>
-    <cellStyle name="20% - Accent2 9" xfId="397"/>
-    <cellStyle name="20% - Accent3 10" xfId="456"/>
-    <cellStyle name="20% - Accent3 11" xfId="594"/>
-    <cellStyle name="20% - Accent3 12" xfId="640"/>
-    <cellStyle name="20% - Accent3 13" xfId="722"/>
-    <cellStyle name="20% - Accent3 2" xfId="4"/>
-    <cellStyle name="20% - Accent3 3" xfId="140"/>
-    <cellStyle name="20% - Accent3 4" xfId="208"/>
-    <cellStyle name="20% - Accent3 5" xfId="240"/>
-    <cellStyle name="20% - Accent3 6" xfId="269"/>
-    <cellStyle name="20% - Accent3 7" xfId="327"/>
-    <cellStyle name="20% - Accent3 8" xfId="369"/>
-    <cellStyle name="20% - Accent3 9" xfId="398"/>
-    <cellStyle name="20% - Accent4 10" xfId="455"/>
-    <cellStyle name="20% - Accent4 11" xfId="595"/>
-    <cellStyle name="20% - Accent4 12" xfId="641"/>
-    <cellStyle name="20% - Accent4 13" xfId="721"/>
-    <cellStyle name="20% - Accent4 2" xfId="5"/>
-    <cellStyle name="20% - Accent4 3" xfId="141"/>
-    <cellStyle name="20% - Accent4 4" xfId="207"/>
-    <cellStyle name="20% - Accent4 5" xfId="239"/>
-    <cellStyle name="20% - Accent4 6" xfId="270"/>
-    <cellStyle name="20% - Accent4 7" xfId="326"/>
-    <cellStyle name="20% - Accent4 8" xfId="368"/>
-    <cellStyle name="20% - Accent4 9" xfId="399"/>
-    <cellStyle name="20% - Accent5 10" xfId="452"/>
-    <cellStyle name="20% - Accent5 11" xfId="596"/>
-    <cellStyle name="20% - Accent5 12" xfId="642"/>
-    <cellStyle name="20% - Accent5 13" xfId="720"/>
-    <cellStyle name="20% - Accent5 2" xfId="6"/>
-    <cellStyle name="20% - Accent5 3" xfId="142"/>
-    <cellStyle name="20% - Accent5 4" xfId="204"/>
-    <cellStyle name="20% - Accent5 5" xfId="236"/>
-    <cellStyle name="20% - Accent5 6" xfId="271"/>
-    <cellStyle name="20% - Accent5 7" xfId="325"/>
-    <cellStyle name="20% - Accent5 8" xfId="365"/>
-    <cellStyle name="20% - Accent5 9" xfId="400"/>
-    <cellStyle name="20% - Accent6 10" xfId="451"/>
-    <cellStyle name="20% - Accent6 11" xfId="597"/>
-    <cellStyle name="20% - Accent6 12" xfId="643"/>
-    <cellStyle name="20% - Accent6 13" xfId="719"/>
-    <cellStyle name="20% - Accent6 2" xfId="7"/>
-    <cellStyle name="20% - Accent6 3" xfId="143"/>
-    <cellStyle name="20% - Accent6 4" xfId="231"/>
-    <cellStyle name="20% - Accent6 5" xfId="260"/>
-    <cellStyle name="20% - Accent6 6" xfId="272"/>
-    <cellStyle name="20% - Accent6 7" xfId="324"/>
-    <cellStyle name="20% - Accent6 8" xfId="389"/>
-    <cellStyle name="20% - Accent6 9" xfId="401"/>
-    <cellStyle name="40% - Accent1 10" xfId="466"/>
-    <cellStyle name="40% - Accent1 11" xfId="598"/>
-    <cellStyle name="40% - Accent1 12" xfId="644"/>
-    <cellStyle name="40% - Accent1 13" xfId="718"/>
-    <cellStyle name="40% - Accent1 2" xfId="8"/>
-    <cellStyle name="40% - Accent1 3" xfId="144"/>
-    <cellStyle name="40% - Accent1 4" xfId="203"/>
-    <cellStyle name="40% - Accent1 5" xfId="235"/>
-    <cellStyle name="40% - Accent1 6" xfId="273"/>
-    <cellStyle name="40% - Accent1 7" xfId="348"/>
-    <cellStyle name="40% - Accent1 8" xfId="364"/>
-    <cellStyle name="40% - Accent1 9" xfId="402"/>
-    <cellStyle name="40% - Accent2 10" xfId="450"/>
-    <cellStyle name="40% - Accent2 11" xfId="599"/>
-    <cellStyle name="40% - Accent2 12" xfId="645"/>
-    <cellStyle name="40% - Accent2 13" xfId="717"/>
-    <cellStyle name="40% - Accent2 2" xfId="9"/>
-    <cellStyle name="40% - Accent2 3" xfId="145"/>
-    <cellStyle name="40% - Accent2 4" xfId="221"/>
-    <cellStyle name="40% - Accent2 5" xfId="250"/>
-    <cellStyle name="40% - Accent2 6" xfId="274"/>
-    <cellStyle name="40% - Accent2 7" xfId="351"/>
-    <cellStyle name="40% - Accent2 8" xfId="379"/>
-    <cellStyle name="40% - Accent2 9" xfId="403"/>
-    <cellStyle name="40% - Accent3 10" xfId="449"/>
-    <cellStyle name="40% - Accent3 11" xfId="600"/>
-    <cellStyle name="40% - Accent3 12" xfId="646"/>
-    <cellStyle name="40% - Accent3 13" xfId="716"/>
-    <cellStyle name="40% - Accent3 2" xfId="10"/>
-    <cellStyle name="40% - Accent3 3" xfId="146"/>
-    <cellStyle name="40% - Accent3 4" xfId="202"/>
-    <cellStyle name="40% - Accent3 5" xfId="234"/>
-    <cellStyle name="40% - Accent3 6" xfId="275"/>
-    <cellStyle name="40% - Accent3 7" xfId="347"/>
-    <cellStyle name="40% - Accent3 8" xfId="363"/>
-    <cellStyle name="40% - Accent3 9" xfId="404"/>
-    <cellStyle name="40% - Accent4 10" xfId="469"/>
-    <cellStyle name="40% - Accent4 11" xfId="601"/>
-    <cellStyle name="40% - Accent4 12" xfId="647"/>
-    <cellStyle name="40% - Accent4 13" xfId="715"/>
-    <cellStyle name="40% - Accent4 2" xfId="11"/>
-    <cellStyle name="40% - Accent4 3" xfId="147"/>
-    <cellStyle name="40% - Accent4 4" xfId="201"/>
-    <cellStyle name="40% - Accent4 5" xfId="233"/>
-    <cellStyle name="40% - Accent4 6" xfId="276"/>
-    <cellStyle name="40% - Accent4 7" xfId="323"/>
-    <cellStyle name="40% - Accent4 8" xfId="362"/>
-    <cellStyle name="40% - Accent4 9" xfId="405"/>
-    <cellStyle name="40% - Accent5 10" xfId="448"/>
-    <cellStyle name="40% - Accent5 11" xfId="602"/>
-    <cellStyle name="40% - Accent5 12" xfId="648"/>
-    <cellStyle name="40% - Accent5 13" xfId="714"/>
-    <cellStyle name="40% - Accent5 2" xfId="12"/>
-    <cellStyle name="40% - Accent5 3" xfId="148"/>
-    <cellStyle name="40% - Accent5 4" xfId="224"/>
-    <cellStyle name="40% - Accent5 5" xfId="253"/>
-    <cellStyle name="40% - Accent5 6" xfId="277"/>
-    <cellStyle name="40% - Accent5 7" xfId="322"/>
-    <cellStyle name="40% - Accent5 8" xfId="382"/>
-    <cellStyle name="40% - Accent5 9" xfId="406"/>
-    <cellStyle name="40% - Accent6 10" xfId="465"/>
-    <cellStyle name="40% - Accent6 11" xfId="603"/>
-    <cellStyle name="40% - Accent6 12" xfId="649"/>
-    <cellStyle name="40% - Accent6 13" xfId="713"/>
-    <cellStyle name="40% - Accent6 2" xfId="13"/>
-    <cellStyle name="40% - Accent6 3" xfId="149"/>
-    <cellStyle name="40% - Accent6 4" xfId="200"/>
-    <cellStyle name="40% - Accent6 5" xfId="232"/>
-    <cellStyle name="40% - Accent6 6" xfId="278"/>
-    <cellStyle name="40% - Accent6 7" xfId="321"/>
-    <cellStyle name="40% - Accent6 8" xfId="361"/>
-    <cellStyle name="40% - Accent6 9" xfId="407"/>
-    <cellStyle name="60% - Accent1 10" xfId="447"/>
-    <cellStyle name="60% - Accent1 11" xfId="604"/>
-    <cellStyle name="60% - Accent1 12" xfId="650"/>
-    <cellStyle name="60% - Accent1 13" xfId="712"/>
-    <cellStyle name="60% - Accent1 2" xfId="14"/>
-    <cellStyle name="60% - Accent1 3" xfId="150"/>
-    <cellStyle name="60% - Accent1 4" xfId="220"/>
-    <cellStyle name="60% - Accent1 5" xfId="249"/>
-    <cellStyle name="60% - Accent1 6" xfId="279"/>
-    <cellStyle name="60% - Accent1 7" xfId="339"/>
-    <cellStyle name="60% - Accent1 8" xfId="378"/>
-    <cellStyle name="60% - Accent1 9" xfId="408"/>
-    <cellStyle name="60% - Accent2 10" xfId="446"/>
-    <cellStyle name="60% - Accent2 11" xfId="605"/>
-    <cellStyle name="60% - Accent2 12" xfId="651"/>
-    <cellStyle name="60% - Accent2 13" xfId="711"/>
-    <cellStyle name="60% - Accent2 2" xfId="15"/>
-    <cellStyle name="60% - Accent2 3" xfId="151"/>
-    <cellStyle name="60% - Accent2 4" xfId="199"/>
-    <cellStyle name="60% - Accent2 5" xfId="165"/>
-    <cellStyle name="60% - Accent2 6" xfId="280"/>
-    <cellStyle name="60% - Accent2 7" xfId="320"/>
-    <cellStyle name="60% - Accent2 8" xfId="360"/>
-    <cellStyle name="60% - Accent2 9" xfId="409"/>
-    <cellStyle name="60% - Accent3 10" xfId="445"/>
-    <cellStyle name="60% - Accent3 11" xfId="606"/>
-    <cellStyle name="60% - Accent3 12" xfId="652"/>
-    <cellStyle name="60% - Accent3 13" xfId="710"/>
-    <cellStyle name="60% - Accent3 2" xfId="16"/>
-    <cellStyle name="60% - Accent3 3" xfId="152"/>
-    <cellStyle name="60% - Accent3 4" xfId="198"/>
-    <cellStyle name="60% - Accent3 5" xfId="166"/>
-    <cellStyle name="60% - Accent3 6" xfId="281"/>
-    <cellStyle name="60% - Accent3 7" xfId="350"/>
-    <cellStyle name="60% - Accent3 8" xfId="359"/>
-    <cellStyle name="60% - Accent3 9" xfId="410"/>
-    <cellStyle name="60% - Accent4 10" xfId="444"/>
-    <cellStyle name="60% - Accent4 11" xfId="607"/>
-    <cellStyle name="60% - Accent4 12" xfId="653"/>
-    <cellStyle name="60% - Accent4 13" xfId="698"/>
-    <cellStyle name="60% - Accent4 2" xfId="17"/>
-    <cellStyle name="60% - Accent4 3" xfId="153"/>
-    <cellStyle name="60% - Accent4 4" xfId="197"/>
-    <cellStyle name="60% - Accent4 5" xfId="167"/>
-    <cellStyle name="60% - Accent4 6" xfId="282"/>
-    <cellStyle name="60% - Accent4 7" xfId="319"/>
-    <cellStyle name="60% - Accent4 8" xfId="358"/>
-    <cellStyle name="60% - Accent4 9" xfId="411"/>
-    <cellStyle name="60% - Accent5 10" xfId="471"/>
-    <cellStyle name="60% - Accent5 11" xfId="608"/>
-    <cellStyle name="60% - Accent5 12" xfId="654"/>
-    <cellStyle name="60% - Accent5 13" xfId="688"/>
-    <cellStyle name="60% - Accent5 2" xfId="18"/>
-    <cellStyle name="60% - Accent5 3" xfId="154"/>
-    <cellStyle name="60% - Accent5 4" xfId="196"/>
-    <cellStyle name="60% - Accent5 5" xfId="213"/>
-    <cellStyle name="60% - Accent5 6" xfId="283"/>
-    <cellStyle name="60% - Accent5 7" xfId="349"/>
-    <cellStyle name="60% - Accent5 8" xfId="357"/>
-    <cellStyle name="60% - Accent5 9" xfId="412"/>
-    <cellStyle name="60% - Accent6 10" xfId="474"/>
-    <cellStyle name="60% - Accent6 11" xfId="609"/>
-    <cellStyle name="60% - Accent6 12" xfId="655"/>
-    <cellStyle name="60% - Accent6 13" xfId="693"/>
-    <cellStyle name="60% - Accent6 2" xfId="19"/>
-    <cellStyle name="60% - Accent6 3" xfId="155"/>
-    <cellStyle name="60% - Accent6 4" xfId="227"/>
-    <cellStyle name="60% - Accent6 5" xfId="256"/>
-    <cellStyle name="60% - Accent6 6" xfId="284"/>
-    <cellStyle name="60% - Accent6 7" xfId="318"/>
-    <cellStyle name="60% - Accent6 8" xfId="385"/>
-    <cellStyle name="60% - Accent6 9" xfId="413"/>
-    <cellStyle name="Accent1 10" xfId="470"/>
-    <cellStyle name="Accent1 11" xfId="610"/>
-    <cellStyle name="Accent1 12" xfId="656"/>
-    <cellStyle name="Accent1 13" xfId="687"/>
-    <cellStyle name="Accent1 2" xfId="20"/>
-    <cellStyle name="Accent1 3" xfId="156"/>
-    <cellStyle name="Accent1 4" xfId="229"/>
-    <cellStyle name="Accent1 5" xfId="258"/>
-    <cellStyle name="Accent1 6" xfId="285"/>
-    <cellStyle name="Accent1 7" xfId="317"/>
-    <cellStyle name="Accent1 8" xfId="387"/>
-    <cellStyle name="Accent1 9" xfId="414"/>
-    <cellStyle name="Accent2 10" xfId="443"/>
-    <cellStyle name="Accent2 11" xfId="611"/>
-    <cellStyle name="Accent2 12" xfId="657"/>
-    <cellStyle name="Accent2 13" xfId="686"/>
-    <cellStyle name="Accent2 2" xfId="21"/>
-    <cellStyle name="Accent2 3" xfId="157"/>
-    <cellStyle name="Accent2 4" xfId="226"/>
-    <cellStyle name="Accent2 5" xfId="255"/>
-    <cellStyle name="Accent2 6" xfId="286"/>
-    <cellStyle name="Accent2 7" xfId="345"/>
-    <cellStyle name="Accent2 8" xfId="384"/>
-    <cellStyle name="Accent2 9" xfId="415"/>
-    <cellStyle name="Accent3 10" xfId="442"/>
-    <cellStyle name="Accent3 11" xfId="612"/>
-    <cellStyle name="Accent3 12" xfId="658"/>
-    <cellStyle name="Accent3 13" xfId="683"/>
-    <cellStyle name="Accent3 2" xfId="22"/>
-    <cellStyle name="Accent3 3" xfId="158"/>
-    <cellStyle name="Accent3 4" xfId="195"/>
-    <cellStyle name="Accent3 5" xfId="168"/>
-    <cellStyle name="Accent3 6" xfId="287"/>
-    <cellStyle name="Accent3 7" xfId="344"/>
-    <cellStyle name="Accent3 8" xfId="356"/>
-    <cellStyle name="Accent3 9" xfId="416"/>
-    <cellStyle name="Accent4 10" xfId="441"/>
-    <cellStyle name="Accent4 11" xfId="613"/>
-    <cellStyle name="Accent4 12" xfId="659"/>
-    <cellStyle name="Accent4 13" xfId="709"/>
-    <cellStyle name="Accent4 2" xfId="23"/>
-    <cellStyle name="Accent4 3" xfId="159"/>
-    <cellStyle name="Accent4 4" xfId="194"/>
-    <cellStyle name="Accent4 5" xfId="169"/>
-    <cellStyle name="Accent4 6" xfId="288"/>
-    <cellStyle name="Accent4 7" xfId="316"/>
-    <cellStyle name="Accent4 8" xfId="355"/>
-    <cellStyle name="Accent4 9" xfId="417"/>
-    <cellStyle name="Accent5 10" xfId="464"/>
-    <cellStyle name="Accent5 11" xfId="614"/>
-    <cellStyle name="Accent5 12" xfId="660"/>
-    <cellStyle name="Accent5 13" xfId="682"/>
-    <cellStyle name="Accent5 2" xfId="24"/>
-    <cellStyle name="Accent5 3" xfId="160"/>
-    <cellStyle name="Accent5 4" xfId="193"/>
-    <cellStyle name="Accent5 5" xfId="170"/>
-    <cellStyle name="Accent5 6" xfId="289"/>
-    <cellStyle name="Accent5 7" xfId="315"/>
-    <cellStyle name="Accent5 8" xfId="354"/>
-    <cellStyle name="Accent5 9" xfId="418"/>
-    <cellStyle name="Accent6 10" xfId="440"/>
-    <cellStyle name="Accent6 11" xfId="615"/>
-    <cellStyle name="Accent6 12" xfId="661"/>
-    <cellStyle name="Accent6 13" xfId="692"/>
-    <cellStyle name="Accent6 2" xfId="25"/>
-    <cellStyle name="Accent6 3" xfId="161"/>
-    <cellStyle name="Accent6 4" xfId="219"/>
-    <cellStyle name="Accent6 5" xfId="248"/>
-    <cellStyle name="Accent6 6" xfId="290"/>
-    <cellStyle name="Accent6 7" xfId="314"/>
-    <cellStyle name="Accent6 8" xfId="377"/>
-    <cellStyle name="Accent6 9" xfId="419"/>
-    <cellStyle name="as" xfId="481"/>
-    <cellStyle name="Bad 10" xfId="473"/>
-    <cellStyle name="Bad 11" xfId="616"/>
-    <cellStyle name="Bad 12" xfId="662"/>
-    <cellStyle name="Bad 13" xfId="681"/>
-    <cellStyle name="Bad 2" xfId="26"/>
-    <cellStyle name="Bad 3" xfId="162"/>
-    <cellStyle name="Bad 4" xfId="192"/>
-    <cellStyle name="Bad 5" xfId="214"/>
-    <cellStyle name="Bad 6" xfId="291"/>
-    <cellStyle name="Bad 7" xfId="343"/>
-    <cellStyle name="Bad 8" xfId="353"/>
-    <cellStyle name="Bad 9" xfId="420"/>
-    <cellStyle name="Calc Currency (0)" xfId="482"/>
-    <cellStyle name="Calc Currency (2)" xfId="483"/>
-    <cellStyle name="Calc Percent (0)" xfId="484"/>
-    <cellStyle name="Calc Percent (1)" xfId="485"/>
-    <cellStyle name="Calc Percent (2)" xfId="486"/>
-    <cellStyle name="Calc Units (0)" xfId="487"/>
-    <cellStyle name="Calc Units (1)" xfId="488"/>
-    <cellStyle name="Calc Units (2)" xfId="489"/>
-    <cellStyle name="Calculation 10" xfId="439"/>
-    <cellStyle name="Calculation 11" xfId="617"/>
-    <cellStyle name="Calculation 12" xfId="663"/>
-    <cellStyle name="Calculation 13" xfId="680"/>
-    <cellStyle name="Calculation 2" xfId="27"/>
-    <cellStyle name="Calculation 3" xfId="163"/>
-    <cellStyle name="Calculation 4" xfId="228"/>
-    <cellStyle name="Calculation 5" xfId="257"/>
-    <cellStyle name="Calculation 6" xfId="292"/>
-    <cellStyle name="Calculation 7" xfId="313"/>
-    <cellStyle name="Calculation 8" xfId="386"/>
-    <cellStyle name="Calculation 9" xfId="421"/>
-    <cellStyle name="Check Cell 10" xfId="472"/>
-    <cellStyle name="Check Cell 11" xfId="618"/>
-    <cellStyle name="Check Cell 12" xfId="664"/>
-    <cellStyle name="Check Cell 13" xfId="708"/>
-    <cellStyle name="Check Cell 2" xfId="28"/>
-    <cellStyle name="Check Cell 3" xfId="164"/>
-    <cellStyle name="Check Cell 4" xfId="191"/>
-    <cellStyle name="Check Cell 5" xfId="171"/>
-    <cellStyle name="Check Cell 6" xfId="293"/>
-    <cellStyle name="Check Cell 7" xfId="312"/>
-    <cellStyle name="Check Cell 8" xfId="352"/>
-    <cellStyle name="Check Cell 9" xfId="422"/>
+    <cellStyle name="??" xfId="476" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="?? [0.00]_PERSONAL" xfId="477" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="???? [0.00]_PERSONAL" xfId="478" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="????_PERSONAL" xfId="479" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="??_PERSONAL" xfId="480" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Accent1 10" xfId="457" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="20% - Accent1 11" xfId="592" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="20% - Accent1 12" xfId="638" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="20% - Accent1 13" xfId="724" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="20% - Accent1 3" xfId="138" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="20% - Accent1 4" xfId="209" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="20% - Accent1 5" xfId="241" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="20% - Accent1 6" xfId="267" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="20% - Accent1 7" xfId="328" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="20% - Accent1 8" xfId="370" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="20% - Accent1 9" xfId="396" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="20% - Accent2 10" xfId="467" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="20% - Accent2 11" xfId="593" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="20% - Accent2 12" xfId="639" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="20% - Accent2 13" xfId="723" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="20% - Accent2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="20% - Accent2 3" xfId="139" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="20% - Accent2 4" xfId="222" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="20% - Accent2 5" xfId="251" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="20% - Accent2 6" xfId="268" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="20% - Accent2 7" xfId="340" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="20% - Accent2 8" xfId="380" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="20% - Accent2 9" xfId="397" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="20% - Accent3 10" xfId="456" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="20% - Accent3 11" xfId="594" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="20% - Accent3 12" xfId="640" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="20% - Accent3 13" xfId="722" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="20% - Accent3 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="20% - Accent3 3" xfId="140" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="20% - Accent3 4" xfId="208" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="20% - Accent3 5" xfId="240" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="20% - Accent3 6" xfId="269" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="20% - Accent3 7" xfId="327" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="20% - Accent3 8" xfId="369" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="20% - Accent3 9" xfId="398" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="20% - Accent4 10" xfId="455" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="20% - Accent4 11" xfId="595" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="20% - Accent4 12" xfId="641" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="20% - Accent4 13" xfId="721" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="20% - Accent4 2" xfId="5" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="20% - Accent4 3" xfId="141" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="20% - Accent4 4" xfId="207" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="20% - Accent4 5" xfId="239" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="20% - Accent4 6" xfId="270" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="20% - Accent4 7" xfId="326" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="20% - Accent4 8" xfId="368" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="20% - Accent4 9" xfId="399" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="20% - Accent5 10" xfId="452" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="20% - Accent5 11" xfId="596" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="20% - Accent5 12" xfId="642" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="20% - Accent5 13" xfId="720" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="20% - Accent5 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="20% - Accent5 3" xfId="142" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="20% - Accent5 4" xfId="204" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="20% - Accent5 5" xfId="236" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="20% - Accent5 6" xfId="271" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="20% - Accent5 7" xfId="325" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="20% - Accent5 8" xfId="365" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="20% - Accent5 9" xfId="400" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="20% - Accent6 10" xfId="451" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="20% - Accent6 11" xfId="597" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="20% - Accent6 12" xfId="643" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="20% - Accent6 13" xfId="719" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="20% - Accent6 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="20% - Accent6 3" xfId="143" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="20% - Accent6 4" xfId="231" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="20% - Accent6 5" xfId="260" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="20% - Accent6 6" xfId="272" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="20% - Accent6 7" xfId="324" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="20% - Accent6 8" xfId="389" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="20% - Accent6 9" xfId="401" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="40% - Accent1 10" xfId="466" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="40% - Accent1 11" xfId="598" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="40% - Accent1 12" xfId="644" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="40% - Accent1 13" xfId="718" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="40% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="40% - Accent1 3" xfId="144" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="40% - Accent1 4" xfId="203" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="40% - Accent1 5" xfId="235" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="40% - Accent1 6" xfId="273" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="40% - Accent1 7" xfId="348" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="40% - Accent1 8" xfId="364" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="40% - Accent1 9" xfId="402" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="40% - Accent2 10" xfId="450" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="40% - Accent2 11" xfId="599" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="40% - Accent2 12" xfId="645" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="40% - Accent2 13" xfId="717" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="40% - Accent2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="40% - Accent2 3" xfId="145" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="40% - Accent2 4" xfId="221" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="40% - Accent2 5" xfId="250" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="40% - Accent2 6" xfId="274" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="40% - Accent2 7" xfId="351" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="40% - Accent2 8" xfId="379" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="40% - Accent2 9" xfId="403" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="40% - Accent3 10" xfId="449" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="40% - Accent3 11" xfId="600" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="40% - Accent3 12" xfId="646" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="40% - Accent3 13" xfId="716" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="40% - Accent3 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="40% - Accent3 3" xfId="146" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="40% - Accent3 4" xfId="202" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="40% - Accent3 5" xfId="234" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
+    <cellStyle name="40% - Accent3 6" xfId="275" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="40% - Accent3 7" xfId="347" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="40% - Accent3 8" xfId="363" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="40% - Accent3 9" xfId="404" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="40% - Accent4 10" xfId="469" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
+    <cellStyle name="40% - Accent4 11" xfId="601" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
+    <cellStyle name="40% - Accent4 12" xfId="647" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
+    <cellStyle name="40% - Accent4 13" xfId="715" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
+    <cellStyle name="40% - Accent4 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
+    <cellStyle name="40% - Accent4 3" xfId="147" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
+    <cellStyle name="40% - Accent4 4" xfId="201" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
+    <cellStyle name="40% - Accent4 5" xfId="233" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
+    <cellStyle name="40% - Accent4 6" xfId="276" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
+    <cellStyle name="40% - Accent4 7" xfId="323" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
+    <cellStyle name="40% - Accent4 8" xfId="362" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
+    <cellStyle name="40% - Accent4 9" xfId="405" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
+    <cellStyle name="40% - Accent5 10" xfId="448" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
+    <cellStyle name="40% - Accent5 11" xfId="602" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
+    <cellStyle name="40% - Accent5 12" xfId="648" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
+    <cellStyle name="40% - Accent5 13" xfId="714" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
+    <cellStyle name="40% - Accent5 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
+    <cellStyle name="40% - Accent5 3" xfId="148" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
+    <cellStyle name="40% - Accent5 4" xfId="224" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
+    <cellStyle name="40% - Accent5 5" xfId="253" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
+    <cellStyle name="40% - Accent5 6" xfId="277" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
+    <cellStyle name="40% - Accent5 7" xfId="322" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
+    <cellStyle name="40% - Accent5 8" xfId="382" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
+    <cellStyle name="40% - Accent5 9" xfId="406" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
+    <cellStyle name="40% - Accent6 10" xfId="465" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
+    <cellStyle name="40% - Accent6 11" xfId="603" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
+    <cellStyle name="40% - Accent6 12" xfId="649" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
+    <cellStyle name="40% - Accent6 13" xfId="713" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
+    <cellStyle name="40% - Accent6 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
+    <cellStyle name="40% - Accent6 3" xfId="149" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
+    <cellStyle name="40% - Accent6 4" xfId="200" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
+    <cellStyle name="40% - Accent6 5" xfId="232" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
+    <cellStyle name="40% - Accent6 6" xfId="278" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
+    <cellStyle name="40% - Accent6 7" xfId="321" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
+    <cellStyle name="40% - Accent6 8" xfId="361" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
+    <cellStyle name="40% - Accent6 9" xfId="407" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
+    <cellStyle name="60% - Accent1 10" xfId="447" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
+    <cellStyle name="60% - Accent1 11" xfId="604" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
+    <cellStyle name="60% - Accent1 12" xfId="650" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
+    <cellStyle name="60% - Accent1 13" xfId="712" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
+    <cellStyle name="60% - Accent1 2" xfId="14" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
+    <cellStyle name="60% - Accent1 3" xfId="150" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
+    <cellStyle name="60% - Accent1 4" xfId="220" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
+    <cellStyle name="60% - Accent1 5" xfId="249" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
+    <cellStyle name="60% - Accent1 6" xfId="279" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
+    <cellStyle name="60% - Accent1 7" xfId="339" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
+    <cellStyle name="60% - Accent1 8" xfId="378" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
+    <cellStyle name="60% - Accent1 9" xfId="408" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
+    <cellStyle name="60% - Accent2 10" xfId="446" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
+    <cellStyle name="60% - Accent2 11" xfId="605" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
+    <cellStyle name="60% - Accent2 12" xfId="651" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
+    <cellStyle name="60% - Accent2 13" xfId="711" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="15" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
+    <cellStyle name="60% - Accent2 3" xfId="151" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
+    <cellStyle name="60% - Accent2 4" xfId="199" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
+    <cellStyle name="60% - Accent2 5" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
+    <cellStyle name="60% - Accent2 6" xfId="280" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
+    <cellStyle name="60% - Accent2 7" xfId="320" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
+    <cellStyle name="60% - Accent2 8" xfId="360" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
+    <cellStyle name="60% - Accent2 9" xfId="409" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
+    <cellStyle name="60% - Accent3 10" xfId="445" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
+    <cellStyle name="60% - Accent3 11" xfId="606" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
+    <cellStyle name="60% - Accent3 12" xfId="652" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
+    <cellStyle name="60% - Accent3 13" xfId="710" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="16" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
+    <cellStyle name="60% - Accent3 3" xfId="152" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
+    <cellStyle name="60% - Accent3 4" xfId="198" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
+    <cellStyle name="60% - Accent3 5" xfId="166" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
+    <cellStyle name="60% - Accent3 6" xfId="281" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
+    <cellStyle name="60% - Accent3 7" xfId="350" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
+    <cellStyle name="60% - Accent3 8" xfId="359" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
+    <cellStyle name="60% - Accent3 9" xfId="410" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
+    <cellStyle name="60% - Accent4 10" xfId="444" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
+    <cellStyle name="60% - Accent4 11" xfId="607" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
+    <cellStyle name="60% - Accent4 12" xfId="653" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
+    <cellStyle name="60% - Accent4 13" xfId="698" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="17" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
+    <cellStyle name="60% - Accent4 3" xfId="153" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
+    <cellStyle name="60% - Accent4 4" xfId="197" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
+    <cellStyle name="60% - Accent4 5" xfId="167" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
+    <cellStyle name="60% - Accent4 6" xfId="282" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
+    <cellStyle name="60% - Accent4 7" xfId="319" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
+    <cellStyle name="60% - Accent4 8" xfId="358" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
+    <cellStyle name="60% - Accent4 9" xfId="411" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
+    <cellStyle name="60% - Accent5 10" xfId="471" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
+    <cellStyle name="60% - Accent5 11" xfId="608" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
+    <cellStyle name="60% - Accent5 12" xfId="654" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
+    <cellStyle name="60% - Accent5 13" xfId="688" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="18" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
+    <cellStyle name="60% - Accent5 3" xfId="154" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
+    <cellStyle name="60% - Accent5 4" xfId="196" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
+    <cellStyle name="60% - Accent5 5" xfId="213" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
+    <cellStyle name="60% - Accent5 6" xfId="283" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
+    <cellStyle name="60% - Accent5 7" xfId="349" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
+    <cellStyle name="60% - Accent5 8" xfId="357" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
+    <cellStyle name="60% - Accent5 9" xfId="412" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
+    <cellStyle name="60% - Accent6 10" xfId="474" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
+    <cellStyle name="60% - Accent6 11" xfId="609" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
+    <cellStyle name="60% - Accent6 12" xfId="655" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
+    <cellStyle name="60% - Accent6 13" xfId="693" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="19" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
+    <cellStyle name="60% - Accent6 3" xfId="155" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
+    <cellStyle name="60% - Accent6 4" xfId="227" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
+    <cellStyle name="60% - Accent6 5" xfId="256" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
+    <cellStyle name="60% - Accent6 6" xfId="284" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
+    <cellStyle name="60% - Accent6 7" xfId="318" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
+    <cellStyle name="60% - Accent6 8" xfId="385" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
+    <cellStyle name="60% - Accent6 9" xfId="413" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
+    <cellStyle name="Accent1 10" xfId="470" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
+    <cellStyle name="Accent1 11" xfId="610" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
+    <cellStyle name="Accent1 12" xfId="656" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
+    <cellStyle name="Accent1 13" xfId="687" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
+    <cellStyle name="Accent1 2" xfId="20" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
+    <cellStyle name="Accent1 3" xfId="156" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
+    <cellStyle name="Accent1 4" xfId="229" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
+    <cellStyle name="Accent1 5" xfId="258" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
+    <cellStyle name="Accent1 6" xfId="285" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
+    <cellStyle name="Accent1 7" xfId="317" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
+    <cellStyle name="Accent1 8" xfId="387" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
+    <cellStyle name="Accent1 9" xfId="414" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
+    <cellStyle name="Accent2 10" xfId="443" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
+    <cellStyle name="Accent2 11" xfId="611" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
+    <cellStyle name="Accent2 12" xfId="657" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
+    <cellStyle name="Accent2 13" xfId="686" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
+    <cellStyle name="Accent2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
+    <cellStyle name="Accent2 3" xfId="157" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
+    <cellStyle name="Accent2 4" xfId="226" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
+    <cellStyle name="Accent2 5" xfId="255" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
+    <cellStyle name="Accent2 6" xfId="286" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
+    <cellStyle name="Accent2 7" xfId="345" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
+    <cellStyle name="Accent2 8" xfId="384" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
+    <cellStyle name="Accent2 9" xfId="415" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
+    <cellStyle name="Accent3 10" xfId="442" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
+    <cellStyle name="Accent3 11" xfId="612" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
+    <cellStyle name="Accent3 12" xfId="658" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
+    <cellStyle name="Accent3 13" xfId="683" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
+    <cellStyle name="Accent3 2" xfId="22" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
+    <cellStyle name="Accent3 3" xfId="158" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
+    <cellStyle name="Accent3 4" xfId="195" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
+    <cellStyle name="Accent3 5" xfId="168" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
+    <cellStyle name="Accent3 6" xfId="287" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
+    <cellStyle name="Accent3 7" xfId="344" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
+    <cellStyle name="Accent3 8" xfId="356" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
+    <cellStyle name="Accent3 9" xfId="416" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
+    <cellStyle name="Accent4 10" xfId="441" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
+    <cellStyle name="Accent4 11" xfId="613" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
+    <cellStyle name="Accent4 12" xfId="659" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
+    <cellStyle name="Accent4 13" xfId="709" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
+    <cellStyle name="Accent4 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
+    <cellStyle name="Accent4 3" xfId="159" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
+    <cellStyle name="Accent4 4" xfId="194" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
+    <cellStyle name="Accent4 5" xfId="169" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
+    <cellStyle name="Accent4 6" xfId="288" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
+    <cellStyle name="Accent4 7" xfId="316" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
+    <cellStyle name="Accent4 8" xfId="355" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
+    <cellStyle name="Accent4 9" xfId="417" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
+    <cellStyle name="Accent5 10" xfId="464" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
+    <cellStyle name="Accent5 11" xfId="614" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
+    <cellStyle name="Accent5 12" xfId="660" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
+    <cellStyle name="Accent5 13" xfId="682" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
+    <cellStyle name="Accent5 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
+    <cellStyle name="Accent5 3" xfId="160" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
+    <cellStyle name="Accent5 4" xfId="193" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
+    <cellStyle name="Accent5 5" xfId="170" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
+    <cellStyle name="Accent5 6" xfId="289" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
+    <cellStyle name="Accent5 7" xfId="315" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
+    <cellStyle name="Accent5 8" xfId="354" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
+    <cellStyle name="Accent5 9" xfId="418" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
+    <cellStyle name="Accent6 10" xfId="440" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
+    <cellStyle name="Accent6 11" xfId="615" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
+    <cellStyle name="Accent6 12" xfId="661" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
+    <cellStyle name="Accent6 13" xfId="692" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
+    <cellStyle name="Accent6 2" xfId="25" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
+    <cellStyle name="Accent6 3" xfId="161" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
+    <cellStyle name="Accent6 4" xfId="219" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
+    <cellStyle name="Accent6 5" xfId="248" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
+    <cellStyle name="Accent6 6" xfId="290" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
+    <cellStyle name="Accent6 7" xfId="314" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
+    <cellStyle name="Accent6 8" xfId="377" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
+    <cellStyle name="Accent6 9" xfId="419" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
+    <cellStyle name="as" xfId="481" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
+    <cellStyle name="Bad 10" xfId="473" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
+    <cellStyle name="Bad 11" xfId="616" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
+    <cellStyle name="Bad 12" xfId="662" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
+    <cellStyle name="Bad 13" xfId="681" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
+    <cellStyle name="Bad 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
+    <cellStyle name="Bad 3" xfId="162" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
+    <cellStyle name="Bad 4" xfId="192" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
+    <cellStyle name="Bad 5" xfId="214" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
+    <cellStyle name="Bad 6" xfId="291" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
+    <cellStyle name="Bad 7" xfId="343" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
+    <cellStyle name="Bad 8" xfId="353" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
+    <cellStyle name="Bad 9" xfId="420" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
+    <cellStyle name="Calc Currency (0)" xfId="482" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
+    <cellStyle name="Calc Currency (2)" xfId="483" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
+    <cellStyle name="Calc Percent (0)" xfId="484" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
+    <cellStyle name="Calc Percent (1)" xfId="485" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
+    <cellStyle name="Calc Percent (2)" xfId="486" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
+    <cellStyle name="Calc Units (0)" xfId="487" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
+    <cellStyle name="Calc Units (1)" xfId="488" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
+    <cellStyle name="Calc Units (2)" xfId="489" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
+    <cellStyle name="Calculation 10" xfId="439" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
+    <cellStyle name="Calculation 11" xfId="617" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
+    <cellStyle name="Calculation 12" xfId="663" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
+    <cellStyle name="Calculation 13" xfId="680" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
+    <cellStyle name="Calculation 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
+    <cellStyle name="Calculation 3" xfId="163" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
+    <cellStyle name="Calculation 4" xfId="228" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
+    <cellStyle name="Calculation 5" xfId="257" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
+    <cellStyle name="Calculation 6" xfId="292" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
+    <cellStyle name="Calculation 7" xfId="313" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
+    <cellStyle name="Calculation 8" xfId="386" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
+    <cellStyle name="Calculation 9" xfId="421" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
+    <cellStyle name="Check Cell 10" xfId="472" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
+    <cellStyle name="Check Cell 11" xfId="618" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
+    <cellStyle name="Check Cell 12" xfId="664" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
+    <cellStyle name="Check Cell 13" xfId="708" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
+    <cellStyle name="Check Cell 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
+    <cellStyle name="Check Cell 3" xfId="164" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
+    <cellStyle name="Check Cell 4" xfId="191" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
+    <cellStyle name="Check Cell 5" xfId="171" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
+    <cellStyle name="Check Cell 6" xfId="293" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
+    <cellStyle name="Check Cell 7" xfId="312" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
+    <cellStyle name="Check Cell 8" xfId="352" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
+    <cellStyle name="Check Cell 9" xfId="422" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [00]" xfId="490"/>
-    <cellStyle name="Comma 10" xfId="732"/>
-    <cellStyle name="Comma 11" xfId="731"/>
-    <cellStyle name="Comma 12" xfId="752"/>
-    <cellStyle name="Comma 13" xfId="753"/>
-    <cellStyle name="Comma 14" xfId="754"/>
-    <cellStyle name="Comma 15" xfId="758"/>
-    <cellStyle name="Comma 2" xfId="29"/>
-    <cellStyle name="Comma 2 2" xfId="30"/>
-    <cellStyle name="Comma 2 2 2" xfId="491"/>
-    <cellStyle name="Comma 2 2 2 2" xfId="739"/>
-    <cellStyle name="Comma 2 2 2 2 2" xfId="749"/>
-    <cellStyle name="Comma 2 3" xfId="31"/>
-    <cellStyle name="Comma 2 3 2" xfId="109"/>
-    <cellStyle name="Comma 2 4" xfId="492"/>
-    <cellStyle name="Comma 2 5" xfId="737"/>
-    <cellStyle name="Comma 3" xfId="32"/>
-    <cellStyle name="Comma 3 2" xfId="33"/>
-    <cellStyle name="Comma 3 2 2" xfId="493"/>
-    <cellStyle name="Comma 3 3" xfId="34"/>
-    <cellStyle name="Comma 3 4" xfId="110"/>
-    <cellStyle name="Comma 3 5" xfId="745"/>
-    <cellStyle name="Comma 4" xfId="35"/>
-    <cellStyle name="Comma 4 2" xfId="36"/>
-    <cellStyle name="Comma 4 3" xfId="111"/>
-    <cellStyle name="Comma 4 4" xfId="747"/>
-    <cellStyle name="Comma 5" xfId="37"/>
-    <cellStyle name="Comma 5 2" xfId="494"/>
-    <cellStyle name="Comma 6" xfId="112"/>
-    <cellStyle name="Comma 6 2" xfId="495"/>
-    <cellStyle name="Comma 7" xfId="496"/>
-    <cellStyle name="Comma 7 2" xfId="497"/>
-    <cellStyle name="Comma 8" xfId="498"/>
-    <cellStyle name="Comma 9" xfId="730"/>
-    <cellStyle name="Comma0" xfId="499"/>
-    <cellStyle name="Comma0 - Modelo1" xfId="500"/>
-    <cellStyle name="Comma0 - Style1" xfId="501"/>
-    <cellStyle name="Comma1 - Modelo2" xfId="502"/>
-    <cellStyle name="Comma1 - Style2" xfId="503"/>
-    <cellStyle name="ContentsHyperlink" xfId="124"/>
-    <cellStyle name="Currency [00]" xfId="504"/>
-    <cellStyle name="Currency0" xfId="505"/>
-    <cellStyle name="Custom - Style1" xfId="506"/>
-    <cellStyle name="Data   - Style2" xfId="507"/>
-    <cellStyle name="Date" xfId="508"/>
-    <cellStyle name="Date Short" xfId="509"/>
-    <cellStyle name="DELTA" xfId="510"/>
-    <cellStyle name="Dia" xfId="511"/>
-    <cellStyle name="Encabez1" xfId="512"/>
-    <cellStyle name="Encabez2" xfId="513"/>
-    <cellStyle name="Enter Currency (0)" xfId="514"/>
-    <cellStyle name="Enter Currency (2)" xfId="515"/>
-    <cellStyle name="Enter Units (0)" xfId="516"/>
-    <cellStyle name="Enter Units (1)" xfId="517"/>
-    <cellStyle name="Enter Units (2)" xfId="518"/>
-    <cellStyle name="Explanatory Text 10" xfId="437"/>
-    <cellStyle name="Explanatory Text 11" xfId="619"/>
-    <cellStyle name="Explanatory Text 12" xfId="665"/>
-    <cellStyle name="Explanatory Text 13" xfId="707"/>
-    <cellStyle name="Explanatory Text 2" xfId="38"/>
-    <cellStyle name="Explanatory Text 3" xfId="172"/>
-    <cellStyle name="Explanatory Text 4" xfId="190"/>
-    <cellStyle name="Explanatory Text 5" xfId="173"/>
-    <cellStyle name="Explanatory Text 6" xfId="296"/>
-    <cellStyle name="Explanatory Text 7" xfId="311"/>
-    <cellStyle name="Explanatory Text 8" xfId="294"/>
-    <cellStyle name="Explanatory Text 9" xfId="423"/>
-    <cellStyle name="F2" xfId="39"/>
-    <cellStyle name="F3" xfId="40"/>
-    <cellStyle name="F4" xfId="41"/>
-    <cellStyle name="F5" xfId="42"/>
-    <cellStyle name="F6" xfId="43"/>
-    <cellStyle name="F7" xfId="44"/>
-    <cellStyle name="F8" xfId="45"/>
-    <cellStyle name="Fijo" xfId="519"/>
-    <cellStyle name="Financiero" xfId="520"/>
-    <cellStyle name="Fixed" xfId="521"/>
-    <cellStyle name="Formulas" xfId="522"/>
-    <cellStyle name="General" xfId="46"/>
-    <cellStyle name="Good 10" xfId="463"/>
-    <cellStyle name="Good 11" xfId="620"/>
-    <cellStyle name="Good 12" xfId="666"/>
-    <cellStyle name="Good 13" xfId="679"/>
-    <cellStyle name="Good 2" xfId="47"/>
-    <cellStyle name="Good 3" xfId="174"/>
-    <cellStyle name="Good 4" xfId="225"/>
-    <cellStyle name="Good 5" xfId="254"/>
-    <cellStyle name="Good 6" xfId="299"/>
-    <cellStyle name="Good 7" xfId="310"/>
-    <cellStyle name="Good 8" xfId="383"/>
-    <cellStyle name="Good 9" xfId="424"/>
-    <cellStyle name="Grey" xfId="48"/>
-    <cellStyle name="Grey 2" xfId="523"/>
-    <cellStyle name="Header1" xfId="524"/>
-    <cellStyle name="Header2" xfId="525"/>
-    <cellStyle name="Heading 1 10" xfId="436"/>
-    <cellStyle name="Heading 1 11" xfId="621"/>
-    <cellStyle name="Heading 1 12" xfId="667"/>
-    <cellStyle name="Heading 1 13" xfId="697"/>
-    <cellStyle name="Heading 1 2" xfId="49"/>
-    <cellStyle name="Heading 1 3" xfId="175"/>
-    <cellStyle name="Heading 1 4" xfId="189"/>
-    <cellStyle name="Heading 1 5" xfId="179"/>
-    <cellStyle name="Heading 1 6" xfId="300"/>
-    <cellStyle name="Heading 1 7" xfId="341"/>
-    <cellStyle name="Heading 1 8" xfId="334"/>
-    <cellStyle name="Heading 1 9" xfId="425"/>
-    <cellStyle name="Heading 2 10" xfId="435"/>
-    <cellStyle name="Heading 2 11" xfId="622"/>
-    <cellStyle name="Heading 2 12" xfId="668"/>
-    <cellStyle name="Heading 2 13" xfId="678"/>
-    <cellStyle name="Heading 2 2" xfId="50"/>
-    <cellStyle name="Heading 2 3" xfId="176"/>
-    <cellStyle name="Heading 2 4" xfId="188"/>
-    <cellStyle name="Heading 2 5" xfId="180"/>
-    <cellStyle name="Heading 2 6" xfId="301"/>
-    <cellStyle name="Heading 2 7" xfId="338"/>
-    <cellStyle name="Heading 2 8" xfId="295"/>
-    <cellStyle name="Heading 2 9" xfId="426"/>
-    <cellStyle name="Heading 3 10" xfId="434"/>
-    <cellStyle name="Heading 3 11" xfId="623"/>
-    <cellStyle name="Heading 3 12" xfId="669"/>
-    <cellStyle name="Heading 3 13" xfId="706"/>
-    <cellStyle name="Heading 3 2" xfId="51"/>
-    <cellStyle name="Heading 3 3" xfId="177"/>
-    <cellStyle name="Heading 3 4" xfId="218"/>
-    <cellStyle name="Heading 3 5" xfId="247"/>
-    <cellStyle name="Heading 3 6" xfId="302"/>
-    <cellStyle name="Heading 3 7" xfId="337"/>
-    <cellStyle name="Heading 3 8" xfId="376"/>
-    <cellStyle name="Heading 3 9" xfId="427"/>
-    <cellStyle name="Heading 4 10" xfId="462"/>
-    <cellStyle name="Heading 4 11" xfId="624"/>
-    <cellStyle name="Heading 4 12" xfId="670"/>
-    <cellStyle name="Heading 4 13" xfId="696"/>
-    <cellStyle name="Heading 4 2" xfId="52"/>
-    <cellStyle name="Heading 4 3" xfId="178"/>
-    <cellStyle name="Heading 4 4" xfId="187"/>
-    <cellStyle name="Heading 4 5" xfId="215"/>
-    <cellStyle name="Heading 4 6" xfId="303"/>
-    <cellStyle name="Heading 4 7" xfId="342"/>
-    <cellStyle name="Heading 4 8" xfId="335"/>
-    <cellStyle name="Heading 4 9" xfId="428"/>
-    <cellStyle name="HEADING1" xfId="526"/>
-    <cellStyle name="HEADING2" xfId="527"/>
-    <cellStyle name="Hyperlink 2" xfId="53"/>
-    <cellStyle name="Hyperlink 2 2" xfId="54"/>
-    <cellStyle name="Hyperlink 2 3" xfId="55"/>
-    <cellStyle name="Hyperlink 2 4" xfId="113"/>
-    <cellStyle name="Hyperlink 3" xfId="528"/>
-    <cellStyle name="Input [yellow]" xfId="57"/>
-    <cellStyle name="Input [yellow] 2" xfId="529"/>
-    <cellStyle name="Input 10" xfId="433"/>
-    <cellStyle name="Input 11" xfId="625"/>
-    <cellStyle name="Input 12" xfId="671"/>
-    <cellStyle name="Input 13" xfId="695"/>
-    <cellStyle name="Input 2" xfId="56"/>
-    <cellStyle name="Input 3" xfId="181"/>
-    <cellStyle name="Input 4" xfId="217"/>
-    <cellStyle name="Input 5" xfId="246"/>
-    <cellStyle name="Input 6" xfId="305"/>
-    <cellStyle name="Input 7" xfId="308"/>
-    <cellStyle name="Input 8" xfId="375"/>
-    <cellStyle name="Input 9" xfId="429"/>
-    <cellStyle name="Item" xfId="530"/>
-    <cellStyle name="Labels - Style3" xfId="531"/>
-    <cellStyle name="Labels - Style3 2" xfId="532"/>
-    <cellStyle name="Link Currency (0)" xfId="533"/>
-    <cellStyle name="Link Currency (2)" xfId="534"/>
-    <cellStyle name="Link Units (0)" xfId="535"/>
-    <cellStyle name="Link Units (1)" xfId="536"/>
-    <cellStyle name="Link Units (2)" xfId="537"/>
-    <cellStyle name="Linked Cell 10" xfId="546"/>
-    <cellStyle name="Linked Cell 11" xfId="626"/>
-    <cellStyle name="Linked Cell 12" xfId="672"/>
-    <cellStyle name="Linked Cell 13" xfId="705"/>
-    <cellStyle name="Linked Cell 2" xfId="58"/>
-    <cellStyle name="Linked Cell 3" xfId="182"/>
-    <cellStyle name="Linked Cell 4" xfId="223"/>
-    <cellStyle name="Linked Cell 5" xfId="252"/>
-    <cellStyle name="Linked Cell 6" xfId="306"/>
-    <cellStyle name="Linked Cell 7" xfId="336"/>
-    <cellStyle name="Linked Cell 8" xfId="381"/>
-    <cellStyle name="Linked Cell 9" xfId="430"/>
-    <cellStyle name="Millares [0]_10 AVERIAS MASIVAS + ANT" xfId="538"/>
-    <cellStyle name="Neutral 10" xfId="461"/>
-    <cellStyle name="Neutral 11" xfId="627"/>
-    <cellStyle name="Neutral 12" xfId="673"/>
-    <cellStyle name="Neutral 13" xfId="694"/>
-    <cellStyle name="Neutral 2" xfId="59"/>
-    <cellStyle name="Neutral 3" xfId="183"/>
-    <cellStyle name="Neutral 4" xfId="186"/>
-    <cellStyle name="Neutral 5" xfId="184"/>
-    <cellStyle name="Neutral 6" xfId="307"/>
-    <cellStyle name="Neutral 7" xfId="304"/>
-    <cellStyle name="Neutral 8" xfId="297"/>
-    <cellStyle name="Neutral 9" xfId="431"/>
+    <cellStyle name="Comma [00]" xfId="490" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
+    <cellStyle name="Comma 10" xfId="732" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
+    <cellStyle name="Comma 11" xfId="731" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
+    <cellStyle name="Comma 12" xfId="752" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
+    <cellStyle name="Comma 13" xfId="753" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
+    <cellStyle name="Comma 14" xfId="754" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
+    <cellStyle name="Comma 15" xfId="758" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
+    <cellStyle name="Comma 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
+    <cellStyle name="Comma 2 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
+    <cellStyle name="Comma 2 2 2" xfId="491" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
+    <cellStyle name="Comma 2 2 2 2" xfId="739" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
+    <cellStyle name="Comma 2 2 2 2 2" xfId="749" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
+    <cellStyle name="Comma 2 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
+    <cellStyle name="Comma 2 3 2" xfId="109" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
+    <cellStyle name="Comma 2 4" xfId="492" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
+    <cellStyle name="Comma 2 5" xfId="737" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
+    <cellStyle name="Comma 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
+    <cellStyle name="Comma 3 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
+    <cellStyle name="Comma 3 2 2" xfId="493" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
+    <cellStyle name="Comma 3 3" xfId="34" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
+    <cellStyle name="Comma 3 4" xfId="110" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
+    <cellStyle name="Comma 3 5" xfId="745" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
+    <cellStyle name="Comma 4" xfId="35" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
+    <cellStyle name="Comma 4 2" xfId="36" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
+    <cellStyle name="Comma 4 3" xfId="111" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
+    <cellStyle name="Comma 4 4" xfId="747" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
+    <cellStyle name="Comma 5" xfId="37" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
+    <cellStyle name="Comma 5 2" xfId="494" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
+    <cellStyle name="Comma 6" xfId="112" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
+    <cellStyle name="Comma 6 2" xfId="495" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
+    <cellStyle name="Comma 7" xfId="496" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
+    <cellStyle name="Comma 7 2" xfId="497" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
+    <cellStyle name="Comma 8" xfId="498" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
+    <cellStyle name="Comma 9" xfId="730" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
+    <cellStyle name="Comma0" xfId="499" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
+    <cellStyle name="Comma0 - Modelo1" xfId="500" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
+    <cellStyle name="Comma0 - Style1" xfId="501" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
+    <cellStyle name="Comma1 - Modelo2" xfId="502" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
+    <cellStyle name="Comma1 - Style2" xfId="503" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
+    <cellStyle name="ContentsHyperlink" xfId="124" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
+    <cellStyle name="Currency [00]" xfId="504" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
+    <cellStyle name="Currency0" xfId="505" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
+    <cellStyle name="Custom - Style1" xfId="506" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
+    <cellStyle name="Data   - Style2" xfId="507" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
+    <cellStyle name="Date" xfId="508" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
+    <cellStyle name="Date Short" xfId="509" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
+    <cellStyle name="DELTA" xfId="510" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
+    <cellStyle name="Dia" xfId="511" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
+    <cellStyle name="Encabez1" xfId="512" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
+    <cellStyle name="Encabez2" xfId="513" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
+    <cellStyle name="Enter Currency (0)" xfId="514" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
+    <cellStyle name="Enter Currency (2)" xfId="515" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
+    <cellStyle name="Enter Units (0)" xfId="516" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
+    <cellStyle name="Enter Units (1)" xfId="517" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
+    <cellStyle name="Enter Units (2)" xfId="518" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
+    <cellStyle name="Explanatory Text 10" xfId="437" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
+    <cellStyle name="Explanatory Text 11" xfId="619" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
+    <cellStyle name="Explanatory Text 12" xfId="665" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
+    <cellStyle name="Explanatory Text 13" xfId="707" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
+    <cellStyle name="Explanatory Text 2" xfId="38" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
+    <cellStyle name="Explanatory Text 3" xfId="172" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
+    <cellStyle name="Explanatory Text 4" xfId="190" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
+    <cellStyle name="Explanatory Text 5" xfId="173" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
+    <cellStyle name="Explanatory Text 6" xfId="296" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
+    <cellStyle name="Explanatory Text 7" xfId="311" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
+    <cellStyle name="Explanatory Text 8" xfId="294" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
+    <cellStyle name="Explanatory Text 9" xfId="423" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
+    <cellStyle name="F2" xfId="39" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
+    <cellStyle name="F3" xfId="40" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
+    <cellStyle name="F4" xfId="41" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
+    <cellStyle name="F5" xfId="42" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
+    <cellStyle name="F6" xfId="43" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
+    <cellStyle name="F7" xfId="44" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
+    <cellStyle name="F8" xfId="45" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
+    <cellStyle name="Fijo" xfId="519" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
+    <cellStyle name="Financiero" xfId="520" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
+    <cellStyle name="Fixed" xfId="521" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
+    <cellStyle name="Formulas" xfId="522" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
+    <cellStyle name="General" xfId="46" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
+    <cellStyle name="Good 10" xfId="463" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
+    <cellStyle name="Good 11" xfId="620" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
+    <cellStyle name="Good 12" xfId="666" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
+    <cellStyle name="Good 13" xfId="679" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
+    <cellStyle name="Good 2" xfId="47" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
+    <cellStyle name="Good 3" xfId="174" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
+    <cellStyle name="Good 4" xfId="225" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
+    <cellStyle name="Good 5" xfId="254" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
+    <cellStyle name="Good 6" xfId="299" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
+    <cellStyle name="Good 7" xfId="310" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
+    <cellStyle name="Good 8" xfId="383" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
+    <cellStyle name="Good 9" xfId="424" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
+    <cellStyle name="Grey" xfId="48" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
+    <cellStyle name="Grey 2" xfId="523" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
+    <cellStyle name="Header1" xfId="524" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
+    <cellStyle name="Header2" xfId="525" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
+    <cellStyle name="Heading 1 10" xfId="436" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
+    <cellStyle name="Heading 1 11" xfId="621" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
+    <cellStyle name="Heading 1 12" xfId="667" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
+    <cellStyle name="Heading 1 13" xfId="697" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
+    <cellStyle name="Heading 1 2" xfId="49" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
+    <cellStyle name="Heading 1 3" xfId="175" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
+    <cellStyle name="Heading 1 4" xfId="189" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
+    <cellStyle name="Heading 1 5" xfId="179" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
+    <cellStyle name="Heading 1 6" xfId="300" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
+    <cellStyle name="Heading 1 7" xfId="341" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
+    <cellStyle name="Heading 1 8" xfId="334" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
+    <cellStyle name="Heading 1 9" xfId="425" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
+    <cellStyle name="Heading 2 10" xfId="435" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
+    <cellStyle name="Heading 2 11" xfId="622" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
+    <cellStyle name="Heading 2 12" xfId="668" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
+    <cellStyle name="Heading 2 13" xfId="678" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
+    <cellStyle name="Heading 2 2" xfId="50" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
+    <cellStyle name="Heading 2 3" xfId="176" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
+    <cellStyle name="Heading 2 4" xfId="188" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
+    <cellStyle name="Heading 2 5" xfId="180" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
+    <cellStyle name="Heading 2 6" xfId="301" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
+    <cellStyle name="Heading 2 7" xfId="338" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
+    <cellStyle name="Heading 2 8" xfId="295" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
+    <cellStyle name="Heading 2 9" xfId="426" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
+    <cellStyle name="Heading 3 10" xfId="434" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
+    <cellStyle name="Heading 3 11" xfId="623" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
+    <cellStyle name="Heading 3 12" xfId="669" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
+    <cellStyle name="Heading 3 13" xfId="706" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
+    <cellStyle name="Heading 3 2" xfId="51" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
+    <cellStyle name="Heading 3 3" xfId="177" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
+    <cellStyle name="Heading 3 4" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
+    <cellStyle name="Heading 3 5" xfId="247" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
+    <cellStyle name="Heading 3 6" xfId="302" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
+    <cellStyle name="Heading 3 7" xfId="337" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
+    <cellStyle name="Heading 3 8" xfId="376" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
+    <cellStyle name="Heading 3 9" xfId="427" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
+    <cellStyle name="Heading 4 10" xfId="462" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
+    <cellStyle name="Heading 4 11" xfId="624" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
+    <cellStyle name="Heading 4 12" xfId="670" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
+    <cellStyle name="Heading 4 13" xfId="696" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
+    <cellStyle name="Heading 4 2" xfId="52" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
+    <cellStyle name="Heading 4 3" xfId="178" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
+    <cellStyle name="Heading 4 4" xfId="187" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
+    <cellStyle name="Heading 4 5" xfId="215" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
+    <cellStyle name="Heading 4 6" xfId="303" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
+    <cellStyle name="Heading 4 7" xfId="342" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
+    <cellStyle name="Heading 4 8" xfId="335" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
+    <cellStyle name="Heading 4 9" xfId="428" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
+    <cellStyle name="HEADING1" xfId="526" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
+    <cellStyle name="HEADING2" xfId="527" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
+    <cellStyle name="Hyperlink 2" xfId="53" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
+    <cellStyle name="Hyperlink 2 2" xfId="54" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
+    <cellStyle name="Hyperlink 2 3" xfId="55" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
+    <cellStyle name="Hyperlink 2 4" xfId="113" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
+    <cellStyle name="Hyperlink 3" xfId="528" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
+    <cellStyle name="Input [yellow]" xfId="57" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
+    <cellStyle name="Input [yellow] 2" xfId="529" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
+    <cellStyle name="Input 10" xfId="433" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
+    <cellStyle name="Input 11" xfId="625" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
+    <cellStyle name="Input 12" xfId="671" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
+    <cellStyle name="Input 13" xfId="695" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
+    <cellStyle name="Input 2" xfId="56" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
+    <cellStyle name="Input 3" xfId="181" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
+    <cellStyle name="Input 4" xfId="217" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
+    <cellStyle name="Input 5" xfId="246" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
+    <cellStyle name="Input 6" xfId="305" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
+    <cellStyle name="Input 7" xfId="308" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
+    <cellStyle name="Input 8" xfId="375" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
+    <cellStyle name="Input 9" xfId="429" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
+    <cellStyle name="Item" xfId="530" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
+    <cellStyle name="Labels - Style3" xfId="531" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
+    <cellStyle name="Labels - Style3 2" xfId="532" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
+    <cellStyle name="Link Currency (0)" xfId="533" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
+    <cellStyle name="Link Currency (2)" xfId="534" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
+    <cellStyle name="Link Units (0)" xfId="535" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
+    <cellStyle name="Link Units (1)" xfId="536" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
+    <cellStyle name="Link Units (2)" xfId="537" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
+    <cellStyle name="Linked Cell 10" xfId="546" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
+    <cellStyle name="Linked Cell 11" xfId="626" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
+    <cellStyle name="Linked Cell 12" xfId="672" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
+    <cellStyle name="Linked Cell 13" xfId="705" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
+    <cellStyle name="Linked Cell 2" xfId="58" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
+    <cellStyle name="Linked Cell 3" xfId="182" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
+    <cellStyle name="Linked Cell 4" xfId="223" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
+    <cellStyle name="Linked Cell 5" xfId="252" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
+    <cellStyle name="Linked Cell 6" xfId="306" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
+    <cellStyle name="Linked Cell 7" xfId="336" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
+    <cellStyle name="Linked Cell 8" xfId="381" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
+    <cellStyle name="Linked Cell 9" xfId="430" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
+    <cellStyle name="Millares [0]_10 AVERIAS MASIVAS + ANT" xfId="538" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
+    <cellStyle name="Neutral 10" xfId="461" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
+    <cellStyle name="Neutral 11" xfId="627" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
+    <cellStyle name="Neutral 12" xfId="673" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
+    <cellStyle name="Neutral 13" xfId="694" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
+    <cellStyle name="Neutral 2" xfId="59" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
+    <cellStyle name="Neutral 3" xfId="183" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
+    <cellStyle name="Neutral 4" xfId="186" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
+    <cellStyle name="Neutral 5" xfId="184" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
+    <cellStyle name="Neutral 6" xfId="307" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
+    <cellStyle name="Neutral 7" xfId="304" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
+    <cellStyle name="Neutral 8" xfId="297" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
+    <cellStyle name="Neutral 9" xfId="431" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal - Style1" xfId="60"/>
-    <cellStyle name="Normal 10" xfId="61"/>
-    <cellStyle name="Normal 10 2" xfId="742"/>
-    <cellStyle name="Normal 11" xfId="62"/>
-    <cellStyle name="Normal 11 2" xfId="736"/>
-    <cellStyle name="Normal 12" xfId="63"/>
-    <cellStyle name="Normal 12 2" xfId="125"/>
-    <cellStyle name="Normal 12 2 2" xfId="539"/>
-    <cellStyle name="Normal 12 3" xfId="540"/>
-    <cellStyle name="Normal 13" xfId="114"/>
-    <cellStyle name="Normal 13 2" xfId="541"/>
-    <cellStyle name="Normal 14" xfId="115"/>
-    <cellStyle name="Normal 15" xfId="123"/>
-    <cellStyle name="Normal 15 4 4" xfId="740"/>
-    <cellStyle name="Normal 16" xfId="65"/>
-    <cellStyle name="Normal 16 2" xfId="542"/>
-    <cellStyle name="Normal 16 3" xfId="588"/>
-    <cellStyle name="Normal 16 4" xfId="634"/>
-    <cellStyle name="Normal 16 5" xfId="702"/>
-    <cellStyle name="Normal 16 6" xfId="726"/>
-    <cellStyle name="Normal 17" xfId="230"/>
-    <cellStyle name="Normal 17 2" xfId="543"/>
-    <cellStyle name="Normal 17 2 2" xfId="544"/>
-    <cellStyle name="Normal 17 3" xfId="589"/>
-    <cellStyle name="Normal 17 4" xfId="635"/>
-    <cellStyle name="Normal 17 5" xfId="703"/>
-    <cellStyle name="Normal 17 6" xfId="727"/>
-    <cellStyle name="Normal 18" xfId="259"/>
-    <cellStyle name="Normal 18 2" xfId="545"/>
-    <cellStyle name="Normal 18 3" xfId="590"/>
-    <cellStyle name="Normal 18 4" xfId="636"/>
-    <cellStyle name="Normal 18 5" xfId="704"/>
-    <cellStyle name="Normal 18 6" xfId="728"/>
-    <cellStyle name="Normal 19" xfId="346"/>
-    <cellStyle name="Normal 2" xfId="266"/>
-    <cellStyle name="Normal 2 10" xfId="116"/>
-    <cellStyle name="Normal 2 11" xfId="185"/>
-    <cellStyle name="Normal 2 11 2" xfId="547"/>
-    <cellStyle name="Normal 2 12" xfId="216"/>
-    <cellStyle name="Normal 2 13" xfId="245"/>
-    <cellStyle name="Normal 2 14" xfId="309"/>
-    <cellStyle name="Normal 2 15" xfId="298"/>
-    <cellStyle name="Normal 2 16" xfId="374"/>
-    <cellStyle name="Normal 2 17" xfId="432"/>
-    <cellStyle name="Normal 2 18" xfId="468"/>
-    <cellStyle name="Normal 2 19" xfId="628"/>
-    <cellStyle name="Normal 2 2" xfId="64"/>
-    <cellStyle name="Normal 2 2 2" xfId="66"/>
-    <cellStyle name="Normal 2 2 2 2" xfId="67"/>
-    <cellStyle name="Normal 2 2 2 2 2" xfId="126"/>
-    <cellStyle name="Normal 2 2 2 2 2 2" xfId="548"/>
-    <cellStyle name="Normal 2 2 2 2 3" xfId="549"/>
-    <cellStyle name="Normal 2 2 2 26" xfId="748"/>
-    <cellStyle name="Normal 2 2 2 3" xfId="68"/>
-    <cellStyle name="Normal 2 2 2 4" xfId="117"/>
-    <cellStyle name="Normal 2 2 2_0.JHOR JAHANIYA ESTIMATE" xfId="69"/>
-    <cellStyle name="Normal 2 2 3" xfId="70"/>
-    <cellStyle name="Normal 2 2 4" xfId="71"/>
-    <cellStyle name="Normal 2 2 5" xfId="72"/>
-    <cellStyle name="Normal 2 2 6" xfId="118"/>
-    <cellStyle name="Normal 2 2_Estimated BOQ, cost, summary" xfId="73"/>
-    <cellStyle name="Normal 2 20" xfId="676"/>
-    <cellStyle name="Normal 2 21" xfId="677"/>
-    <cellStyle name="Normal 2 3" xfId="74"/>
-    <cellStyle name="Normal 2 3 2" xfId="75"/>
-    <cellStyle name="Normal 2 3 3" xfId="131"/>
-    <cellStyle name="Normal 2 4" xfId="76"/>
-    <cellStyle name="Normal 2 4 2" xfId="743"/>
-    <cellStyle name="Normal 2 5" xfId="77"/>
-    <cellStyle name="Normal 2 6" xfId="78"/>
-    <cellStyle name="Normal 2 7" xfId="79"/>
-    <cellStyle name="Normal 2 7 2" xfId="550"/>
-    <cellStyle name="Normal 2 8" xfId="80"/>
-    <cellStyle name="Normal 2 8 2" xfId="551"/>
-    <cellStyle name="Normal 2 9" xfId="81"/>
-    <cellStyle name="Normal 2 9 2" xfId="127"/>
-    <cellStyle name="Normal 2 9 2 2" xfId="552"/>
-    <cellStyle name="Normal 2 9 3" xfId="553"/>
-    <cellStyle name="Normal 2_150m3" xfId="438"/>
-    <cellStyle name="Normal 20" xfId="388"/>
-    <cellStyle name="Normal 21" xfId="395"/>
-    <cellStyle name="Normal 22" xfId="475"/>
-    <cellStyle name="Normal 23" xfId="591"/>
-    <cellStyle name="Normal 24" xfId="637"/>
-    <cellStyle name="Normal 25" xfId="725"/>
-    <cellStyle name="Normal 25 4" xfId="738"/>
-    <cellStyle name="Normal 26" xfId="729"/>
-    <cellStyle name="Normal 27" xfId="735"/>
-    <cellStyle name="Normal 28" xfId="751"/>
-    <cellStyle name="Normal 29" xfId="756"/>
-    <cellStyle name="Normal 3" xfId="82"/>
-    <cellStyle name="Normal 3 2" xfId="83"/>
-    <cellStyle name="Normal 3 2 2" xfId="554"/>
-    <cellStyle name="Normal 3 22" xfId="741"/>
-    <cellStyle name="Normal 3 3" xfId="84"/>
-    <cellStyle name="Normal 3 3 2" xfId="128"/>
-    <cellStyle name="Normal 3 3 3" xfId="555"/>
-    <cellStyle name="Normal 3 3 4" xfId="556"/>
-    <cellStyle name="Normal 3 4" xfId="129"/>
-    <cellStyle name="Normal 3_Cost Estimate for ghat renovation" xfId="557"/>
-    <cellStyle name="Normal 30" xfId="757"/>
-    <cellStyle name="Normal 31" xfId="755"/>
-    <cellStyle name="Normal 32" xfId="750"/>
-    <cellStyle name="Normal 4" xfId="85"/>
-    <cellStyle name="Normal 4 2" xfId="86"/>
-    <cellStyle name="Normal 4 2 2" xfId="134"/>
-    <cellStyle name="Normal 4 2 3" xfId="558"/>
-    <cellStyle name="Normal 4 3" xfId="87"/>
-    <cellStyle name="Normal 4 3 2" xfId="135"/>
-    <cellStyle name="Normal 4 3 3" xfId="559"/>
-    <cellStyle name="Normal 4 4" xfId="88"/>
-    <cellStyle name="Normal 4 5" xfId="119"/>
-    <cellStyle name="Normal 4 6" xfId="733"/>
-    <cellStyle name="Normal 4_0.JHOR JAHANIYA ESTIMATE" xfId="89"/>
-    <cellStyle name="Normal 5" xfId="90"/>
-    <cellStyle name="Normal 5 2" xfId="91"/>
-    <cellStyle name="Normal 5 2 2" xfId="132"/>
-    <cellStyle name="Normal 5 2 2 2" xfId="136"/>
-    <cellStyle name="Normal 5 2 3" xfId="560"/>
-    <cellStyle name="Normal 5 2 3 2" xfId="561"/>
-    <cellStyle name="Normal 5 2 4" xfId="562"/>
-    <cellStyle name="Normal 5 2_Setidevi-1" xfId="133"/>
-    <cellStyle name="Normal 5 3" xfId="92"/>
-    <cellStyle name="Normal 5 6" xfId="563"/>
-    <cellStyle name="Normal 5_Setidevi-1" xfId="93"/>
-    <cellStyle name="Normal 6" xfId="94"/>
-    <cellStyle name="Normal 6 2" xfId="95"/>
-    <cellStyle name="Normal 6 3" xfId="120"/>
-    <cellStyle name="Normal 6 4" xfId="744"/>
-    <cellStyle name="Normal 7" xfId="96"/>
-    <cellStyle name="Normal 7 2" xfId="130"/>
-    <cellStyle name="Normal 7 3" xfId="564"/>
-    <cellStyle name="Normal 7 4" xfId="746"/>
-    <cellStyle name="Normal 8" xfId="97"/>
-    <cellStyle name="Normal 8 2" xfId="98"/>
-    <cellStyle name="Normal 8 3" xfId="121"/>
-    <cellStyle name="Normal 9" xfId="99"/>
-    <cellStyle name="Normal 9 2" xfId="565"/>
-    <cellStyle name="Normal_Rates" xfId="734"/>
-    <cellStyle name="Normalaprom-lat" xfId="100"/>
-    <cellStyle name="Note 10" xfId="583"/>
-    <cellStyle name="Note 11" xfId="629"/>
-    <cellStyle name="Note 12" xfId="684"/>
-    <cellStyle name="Note 13" xfId="701"/>
-    <cellStyle name="Note 2" xfId="101"/>
-    <cellStyle name="Note 3" xfId="205"/>
-    <cellStyle name="Note 4" xfId="237"/>
-    <cellStyle name="Note 5" xfId="261"/>
-    <cellStyle name="Note 6" xfId="329"/>
-    <cellStyle name="Note 7" xfId="366"/>
-    <cellStyle name="Note 8" xfId="390"/>
-    <cellStyle name="Note 9" xfId="453"/>
-    <cellStyle name="Output 10" xfId="584"/>
-    <cellStyle name="Output 11" xfId="630"/>
-    <cellStyle name="Output 12" xfId="685"/>
-    <cellStyle name="Output 13" xfId="700"/>
-    <cellStyle name="Output 2" xfId="102"/>
-    <cellStyle name="Output 3" xfId="206"/>
-    <cellStyle name="Output 4" xfId="238"/>
-    <cellStyle name="Output 5" xfId="262"/>
-    <cellStyle name="Output 6" xfId="330"/>
-    <cellStyle name="Output 7" xfId="367"/>
-    <cellStyle name="Output 8" xfId="391"/>
-    <cellStyle name="Output 9" xfId="454"/>
-    <cellStyle name="Percent [2]" xfId="103"/>
-    <cellStyle name="Percent [2] 2" xfId="104"/>
-    <cellStyle name="Percent [2] 3" xfId="122"/>
-    <cellStyle name="Percent 2" xfId="105"/>
-    <cellStyle name="Percent 2 2" xfId="137"/>
-    <cellStyle name="Percent 3" xfId="566"/>
-    <cellStyle name="Reset  - Style4" xfId="567"/>
-    <cellStyle name="special" xfId="568"/>
-    <cellStyle name="STYL1 - Style1" xfId="569"/>
-    <cellStyle name="STYL2 - Style2" xfId="570"/>
-    <cellStyle name="Table  - Style5" xfId="571"/>
-    <cellStyle name="Title  - Style6" xfId="572"/>
-    <cellStyle name="Title  - Style6 2" xfId="573"/>
-    <cellStyle name="Title 10" xfId="585"/>
-    <cellStyle name="Title 11" xfId="631"/>
-    <cellStyle name="Title 12" xfId="689"/>
-    <cellStyle name="Title 13" xfId="675"/>
-    <cellStyle name="Title 2" xfId="106"/>
-    <cellStyle name="Title 3" xfId="210"/>
-    <cellStyle name="Title 4" xfId="242"/>
-    <cellStyle name="Title 5" xfId="263"/>
-    <cellStyle name="Title 6" xfId="331"/>
-    <cellStyle name="Title 7" xfId="371"/>
-    <cellStyle name="Title 8" xfId="392"/>
-    <cellStyle name="Title 9" xfId="458"/>
-    <cellStyle name="Total 10" xfId="586"/>
-    <cellStyle name="Total 11" xfId="632"/>
-    <cellStyle name="Total 12" xfId="690"/>
-    <cellStyle name="Total 13" xfId="674"/>
-    <cellStyle name="Total 2" xfId="107"/>
-    <cellStyle name="Total 3" xfId="211"/>
-    <cellStyle name="Total 4" xfId="243"/>
-    <cellStyle name="Total 5" xfId="264"/>
-    <cellStyle name="Total 6" xfId="332"/>
-    <cellStyle name="Total 7" xfId="372"/>
-    <cellStyle name="Total 8" xfId="393"/>
-    <cellStyle name="Total 9" xfId="459"/>
-    <cellStyle name="TotCol - Style7" xfId="574"/>
-    <cellStyle name="TotRow - Style8" xfId="575"/>
-    <cellStyle name="Turn" xfId="576"/>
-    <cellStyle name="Warning Text 10" xfId="587"/>
-    <cellStyle name="Warning Text 11" xfId="633"/>
-    <cellStyle name="Warning Text 12" xfId="691"/>
-    <cellStyle name="Warning Text 13" xfId="699"/>
-    <cellStyle name="Warning Text 2" xfId="108"/>
-    <cellStyle name="Warning Text 3" xfId="212"/>
-    <cellStyle name="Warning Text 4" xfId="244"/>
-    <cellStyle name="Warning Text 5" xfId="265"/>
-    <cellStyle name="Warning Text 6" xfId="333"/>
-    <cellStyle name="Warning Text 7" xfId="373"/>
-    <cellStyle name="Warning Text 8" xfId="394"/>
-    <cellStyle name="Warning Text 9" xfId="460"/>
-    <cellStyle name="백분율_95" xfId="577"/>
-    <cellStyle name="콤마 [0]_95" xfId="578"/>
-    <cellStyle name="콤마_95" xfId="579"/>
-    <cellStyle name="통화 [0]_95" xfId="580"/>
-    <cellStyle name="통화_95" xfId="581"/>
-    <cellStyle name="표준_4월실적" xfId="582"/>
+    <cellStyle name="Normal - Style1" xfId="60" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
+    <cellStyle name="Normal 10" xfId="61" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
+    <cellStyle name="Normal 10 2" xfId="742" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
+    <cellStyle name="Normal 11" xfId="62" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
+    <cellStyle name="Normal 11 2" xfId="736" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
+    <cellStyle name="Normal 12" xfId="63" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
+    <cellStyle name="Normal 12 2" xfId="125" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
+    <cellStyle name="Normal 12 2 2" xfId="539" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
+    <cellStyle name="Normal 12 3" xfId="540" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
+    <cellStyle name="Normal 13" xfId="114" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
+    <cellStyle name="Normal 13 2" xfId="541" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
+    <cellStyle name="Normal 14" xfId="115" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
+    <cellStyle name="Normal 15" xfId="123" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
+    <cellStyle name="Normal 15 4 4" xfId="740" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
+    <cellStyle name="Normal 16" xfId="65" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
+    <cellStyle name="Normal 16 2" xfId="542" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
+    <cellStyle name="Normal 16 3" xfId="588" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
+    <cellStyle name="Normal 16 4" xfId="634" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
+    <cellStyle name="Normal 16 5" xfId="702" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
+    <cellStyle name="Normal 16 6" xfId="726" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
+    <cellStyle name="Normal 17" xfId="230" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
+    <cellStyle name="Normal 17 2" xfId="543" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
+    <cellStyle name="Normal 17 2 2" xfId="544" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
+    <cellStyle name="Normal 17 3" xfId="589" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
+    <cellStyle name="Normal 17 4" xfId="635" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
+    <cellStyle name="Normal 17 5" xfId="703" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
+    <cellStyle name="Normal 17 6" xfId="727" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
+    <cellStyle name="Normal 18" xfId="259" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
+    <cellStyle name="Normal 18 2" xfId="545" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
+    <cellStyle name="Normal 18 3" xfId="590" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
+    <cellStyle name="Normal 18 4" xfId="636" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
+    <cellStyle name="Normal 18 5" xfId="704" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
+    <cellStyle name="Normal 18 6" xfId="728" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
+    <cellStyle name="Normal 19" xfId="346" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
+    <cellStyle name="Normal 2" xfId="266" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
+    <cellStyle name="Normal 2 10" xfId="116" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
+    <cellStyle name="Normal 2 11" xfId="185" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
+    <cellStyle name="Normal 2 11 2" xfId="547" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
+    <cellStyle name="Normal 2 12" xfId="216" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
+    <cellStyle name="Normal 2 13" xfId="245" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
+    <cellStyle name="Normal 2 14" xfId="309" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
+    <cellStyle name="Normal 2 15" xfId="298" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
+    <cellStyle name="Normal 2 16" xfId="374" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
+    <cellStyle name="Normal 2 17" xfId="432" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
+    <cellStyle name="Normal 2 18" xfId="468" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
+    <cellStyle name="Normal 2 19" xfId="628" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
+    <cellStyle name="Normal 2 2" xfId="64" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="66" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="67" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
+    <cellStyle name="Normal 2 2 2 2 2" xfId="126" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
+    <cellStyle name="Normal 2 2 2 2 2 2" xfId="548" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
+    <cellStyle name="Normal 2 2 2 2 3" xfId="549" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
+    <cellStyle name="Normal 2 2 2 26" xfId="748" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
+    <cellStyle name="Normal 2 2 2 3" xfId="68" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
+    <cellStyle name="Normal 2 2 2 4" xfId="117" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
+    <cellStyle name="Normal 2 2 2_0.JHOR JAHANIYA ESTIMATE" xfId="69" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
+    <cellStyle name="Normal 2 2 3" xfId="70" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
+    <cellStyle name="Normal 2 2 4" xfId="71" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
+    <cellStyle name="Normal 2 2 5" xfId="72" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
+    <cellStyle name="Normal 2 2 6" xfId="118" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
+    <cellStyle name="Normal 2 2_Estimated BOQ, cost, summary" xfId="73" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
+    <cellStyle name="Normal 2 20" xfId="676" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
+    <cellStyle name="Normal 2 21" xfId="677" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
+    <cellStyle name="Normal 2 3" xfId="74" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="75" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
+    <cellStyle name="Normal 2 3 3" xfId="131" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
+    <cellStyle name="Normal 2 4" xfId="76" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
+    <cellStyle name="Normal 2 4 2" xfId="743" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
+    <cellStyle name="Normal 2 5" xfId="77" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
+    <cellStyle name="Normal 2 6" xfId="78" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
+    <cellStyle name="Normal 2 7" xfId="79" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
+    <cellStyle name="Normal 2 7 2" xfId="550" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
+    <cellStyle name="Normal 2 8" xfId="80" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
+    <cellStyle name="Normal 2 8 2" xfId="551" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
+    <cellStyle name="Normal 2 9" xfId="81" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
+    <cellStyle name="Normal 2 9 2" xfId="127" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
+    <cellStyle name="Normal 2 9 2 2" xfId="552" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
+    <cellStyle name="Normal 2 9 3" xfId="553" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
+    <cellStyle name="Normal 2_150m3" xfId="438" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
+    <cellStyle name="Normal 20" xfId="388" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
+    <cellStyle name="Normal 21" xfId="395" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
+    <cellStyle name="Normal 22" xfId="475" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
+    <cellStyle name="Normal 23" xfId="591" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
+    <cellStyle name="Normal 24" xfId="637" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
+    <cellStyle name="Normal 25" xfId="725" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
+    <cellStyle name="Normal 25 4" xfId="738" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
+    <cellStyle name="Normal 26" xfId="729" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
+    <cellStyle name="Normal 27" xfId="735" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
+    <cellStyle name="Normal 28" xfId="751" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
+    <cellStyle name="Normal 29" xfId="756" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
+    <cellStyle name="Normal 3" xfId="82" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
+    <cellStyle name="Normal 3 2" xfId="83" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
+    <cellStyle name="Normal 3 2 2" xfId="554" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
+    <cellStyle name="Normal 3 22" xfId="741" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
+    <cellStyle name="Normal 3 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
+    <cellStyle name="Normal 3 3 2" xfId="128" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
+    <cellStyle name="Normal 3 3 3" xfId="555" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
+    <cellStyle name="Normal 3 3 4" xfId="556" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
+    <cellStyle name="Normal 3 4" xfId="129" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
+    <cellStyle name="Normal 3_Cost Estimate for ghat renovation" xfId="557" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
+    <cellStyle name="Normal 30" xfId="757" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
+    <cellStyle name="Normal 31" xfId="755" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
+    <cellStyle name="Normal 32" xfId="750" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
+    <cellStyle name="Normal 4" xfId="85" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
+    <cellStyle name="Normal 4 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
+    <cellStyle name="Normal 4 2 2" xfId="134" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
+    <cellStyle name="Normal 4 2 3" xfId="558" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
+    <cellStyle name="Normal 4 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
+    <cellStyle name="Normal 4 3 2" xfId="135" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
+    <cellStyle name="Normal 4 3 3" xfId="559" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
+    <cellStyle name="Normal 4 4" xfId="88" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
+    <cellStyle name="Normal 4 5" xfId="119" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
+    <cellStyle name="Normal 4 6" xfId="733" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
+    <cellStyle name="Normal 4_0.JHOR JAHANIYA ESTIMATE" xfId="89" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
+    <cellStyle name="Normal 5" xfId="90" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
+    <cellStyle name="Normal 5 2" xfId="91" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
+    <cellStyle name="Normal 5 2 2" xfId="132" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
+    <cellStyle name="Normal 5 2 2 2" xfId="136" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
+    <cellStyle name="Normal 5 2 3" xfId="560" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
+    <cellStyle name="Normal 5 2 3 2" xfId="561" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
+    <cellStyle name="Normal 5 2 4" xfId="562" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
+    <cellStyle name="Normal 5 2_Setidevi-1" xfId="133" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
+    <cellStyle name="Normal 5 3" xfId="92" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
+    <cellStyle name="Normal 5 6" xfId="563" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
+    <cellStyle name="Normal 5_Setidevi-1" xfId="93" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
+    <cellStyle name="Normal 6" xfId="94" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
+    <cellStyle name="Normal 6 2" xfId="95" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
+    <cellStyle name="Normal 6 3" xfId="120" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
+    <cellStyle name="Normal 6 4" xfId="744" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
+    <cellStyle name="Normal 7" xfId="96" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
+    <cellStyle name="Normal 7 2" xfId="130" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
+    <cellStyle name="Normal 7 3" xfId="564" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
+    <cellStyle name="Normal 7 4" xfId="746" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
+    <cellStyle name="Normal 8" xfId="97" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
+    <cellStyle name="Normal 8 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
+    <cellStyle name="Normal 8 3" xfId="121" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
+    <cellStyle name="Normal 9" xfId="99" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
+    <cellStyle name="Normal 9 2" xfId="565" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
+    <cellStyle name="Normal_Rates" xfId="734" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
+    <cellStyle name="Normalaprom-lat" xfId="100" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
+    <cellStyle name="Note 10" xfId="583" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
+    <cellStyle name="Note 11" xfId="629" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
+    <cellStyle name="Note 12" xfId="684" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
+    <cellStyle name="Note 13" xfId="701" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
+    <cellStyle name="Note 2" xfId="101" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
+    <cellStyle name="Note 3" xfId="205" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
+    <cellStyle name="Note 4" xfId="237" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
+    <cellStyle name="Note 5" xfId="261" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
+    <cellStyle name="Note 6" xfId="329" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
+    <cellStyle name="Note 7" xfId="366" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
+    <cellStyle name="Note 8" xfId="390" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
+    <cellStyle name="Note 9" xfId="453" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
+    <cellStyle name="Output 10" xfId="584" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
+    <cellStyle name="Output 11" xfId="630" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
+    <cellStyle name="Output 12" xfId="685" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
+    <cellStyle name="Output 13" xfId="700" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
+    <cellStyle name="Output 2" xfId="102" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
+    <cellStyle name="Output 3" xfId="206" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
+    <cellStyle name="Output 4" xfId="238" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
+    <cellStyle name="Output 5" xfId="262" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
+    <cellStyle name="Output 6" xfId="330" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
+    <cellStyle name="Output 7" xfId="367" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
+    <cellStyle name="Output 8" xfId="391" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
+    <cellStyle name="Output 9" xfId="454" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
+    <cellStyle name="Percent [2]" xfId="103" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
+    <cellStyle name="Percent [2] 2" xfId="104" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
+    <cellStyle name="Percent [2] 3" xfId="122" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
+    <cellStyle name="Percent 2" xfId="105" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
+    <cellStyle name="Percent 2 2" xfId="137" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
+    <cellStyle name="Percent 3" xfId="566" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
+    <cellStyle name="Reset  - Style4" xfId="567" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
+    <cellStyle name="special" xfId="568" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
+    <cellStyle name="STYL1 - Style1" xfId="569" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
+    <cellStyle name="STYL2 - Style2" xfId="570" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
+    <cellStyle name="Table  - Style5" xfId="571" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
+    <cellStyle name="Title  - Style6" xfId="572" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
+    <cellStyle name="Title  - Style6 2" xfId="573" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
+    <cellStyle name="Title 10" xfId="585" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
+    <cellStyle name="Title 11" xfId="631" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
+    <cellStyle name="Title 12" xfId="689" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
+    <cellStyle name="Title 13" xfId="675" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
+    <cellStyle name="Title 2" xfId="106" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
+    <cellStyle name="Title 3" xfId="210" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
+    <cellStyle name="Title 4" xfId="242" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
+    <cellStyle name="Title 5" xfId="263" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
+    <cellStyle name="Title 6" xfId="331" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
+    <cellStyle name="Title 7" xfId="371" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
+    <cellStyle name="Title 8" xfId="392" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
+    <cellStyle name="Title 9" xfId="458" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
+    <cellStyle name="Total 10" xfId="586" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
+    <cellStyle name="Total 11" xfId="632" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
+    <cellStyle name="Total 12" xfId="690" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
+    <cellStyle name="Total 13" xfId="674" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
+    <cellStyle name="Total 2" xfId="107" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
+    <cellStyle name="Total 3" xfId="211" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
+    <cellStyle name="Total 4" xfId="243" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
+    <cellStyle name="Total 5" xfId="264" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
+    <cellStyle name="Total 6" xfId="332" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
+    <cellStyle name="Total 7" xfId="372" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
+    <cellStyle name="Total 8" xfId="393" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
+    <cellStyle name="Total 9" xfId="459" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
+    <cellStyle name="TotCol - Style7" xfId="574" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
+    <cellStyle name="TotRow - Style8" xfId="575" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
+    <cellStyle name="Turn" xfId="576" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
+    <cellStyle name="Warning Text 10" xfId="587" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
+    <cellStyle name="Warning Text 11" xfId="633" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
+    <cellStyle name="Warning Text 12" xfId="691" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
+    <cellStyle name="Warning Text 13" xfId="699" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
+    <cellStyle name="Warning Text 2" xfId="108" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
+    <cellStyle name="Warning Text 3" xfId="212" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
+    <cellStyle name="Warning Text 4" xfId="244" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
+    <cellStyle name="Warning Text 5" xfId="265" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
+    <cellStyle name="Warning Text 6" xfId="333" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
+    <cellStyle name="Warning Text 7" xfId="373" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
+    <cellStyle name="Warning Text 8" xfId="394" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
+    <cellStyle name="Warning Text 9" xfId="460" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
+    <cellStyle name="백분율_95" xfId="577" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
+    <cellStyle name="콤마 [0]_95" xfId="578" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
+    <cellStyle name="콤마_95" xfId="579" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
+    <cellStyle name="통화 [0]_95" xfId="580" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
+    <cellStyle name="통화_95" xfId="581" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
+    <cellStyle name="표준_4월실적" xfId="582" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3877,7 +3919,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Text Box 41"/>
+        <xdr:cNvPr id="4" name="Text Box 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3946,7 +3994,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Basic"/>
@@ -4095,7 +4143,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Basic"/>
@@ -4143,9 +4191,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4183,9 +4231,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4220,7 +4268,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4255,7 +4303,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4428,98 +4476,98 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R80"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" style="8" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.88671875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" style="1"/>
-    <col min="14" max="14" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
+    <col min="9" max="9" width="7.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="14" max="14" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
     <col min="16" max="16" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.109375" style="1"/>
+    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-    </row>
-    <row r="2" spans="1:18" ht="20.399999999999999">
-      <c r="A2" s="99" t="s">
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+    </row>
+    <row r="2" spans="1:18" ht="20.25">
+      <c r="A2" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-    </row>
-    <row r="5" spans="1:18" ht="19.8">
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+    </row>
+    <row r="5" spans="1:18" ht="19.5">
       <c r="A5" s="6"/>
       <c r="B5" s="4" t="s">
         <v>27</v>
@@ -4528,35 +4576,35 @@
         <v>93</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="101" t="s">
+      <c r="K5" s="126" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="101"/>
+      <c r="L5" s="126"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="96" t="s">
+      <c r="I6" s="121" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="O6" s="96" t="s">
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121"/>
+      <c r="O6" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="96"/>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="96"/>
-    </row>
-    <row r="7" spans="1:18" ht="17.399999999999999" thickBot="1">
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
+      <c r="R6" s="121"/>
+    </row>
+    <row r="7" spans="1:18" ht="17.25" thickBot="1">
       <c r="C7" s="5"/>
       <c r="D7" s="6"/>
       <c r="E7" s="3"/>
@@ -4567,7 +4615,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:18" ht="17.399999999999999" thickBot="1">
+    <row r="8" spans="1:18" ht="17.25" thickBot="1">
       <c r="A8" s="2"/>
       <c r="B8" s="12" t="s">
         <v>0</v>
@@ -4603,26 +4651,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="80" customFormat="1" ht="18">
+    <row r="9" spans="1:18" ht="18">
       <c r="A9" s="2"/>
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="89"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="90"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="92"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="88"/>
     </row>
     <row r="10" spans="1:18" ht="35.1" customHeight="1">
-      <c r="B10" s="84">
+      <c r="B10" s="80">
         <v>1</v>
       </c>
       <c r="C10" s="79" t="s">
@@ -4657,8 +4705,8 @@
       </c>
       <c r="L10" s="25"/>
     </row>
-    <row r="11" spans="1:18" ht="18.600000000000001">
-      <c r="B11" s="84"/>
+    <row r="11" spans="1:18" ht="18.75">
+      <c r="B11" s="80"/>
       <c r="C11" s="79"/>
       <c r="D11" s="24"/>
       <c r="E11" s="70"/>
@@ -4671,7 +4719,7 @@
       <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:18" ht="35.1" customHeight="1">
-      <c r="B12" s="84">
+      <c r="B12" s="80">
         <v>2</v>
       </c>
       <c r="C12" s="79" t="s">
@@ -4698,7 +4746,7 @@
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="B13" s="84"/>
+      <c r="B13" s="80"/>
       <c r="C13" s="21"/>
       <c r="D13" s="24">
         <v>2</v>
@@ -4721,7 +4769,7 @@
       <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:18">
-      <c r="B14" s="84"/>
+      <c r="B14" s="80"/>
       <c r="C14" s="20"/>
       <c r="D14" s="24"/>
       <c r="E14" s="70"/>
@@ -4745,7 +4793,7 @@
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="B15" s="84"/>
+      <c r="B15" s="80"/>
       <c r="C15" s="27"/>
       <c r="D15" s="24"/>
       <c r="E15" s="70"/>
@@ -4758,7 +4806,7 @@
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:18" ht="35.1" customHeight="1">
-      <c r="B16" s="84">
+      <c r="B16" s="80">
         <v>3</v>
       </c>
       <c r="C16" s="79" t="s">
@@ -4786,8 +4834,8 @@
       <c r="K16" s="72"/>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" spans="2:12" ht="18.600000000000001">
-      <c r="B17" s="84"/>
+    <row r="17" spans="2:12" ht="18.75">
+      <c r="B17" s="80"/>
       <c r="C17" s="79"/>
       <c r="D17" s="24">
         <v>2</v>
@@ -4811,8 +4859,8 @@
       <c r="K17" s="72"/>
       <c r="L17" s="25"/>
     </row>
-    <row r="18" spans="2:12" ht="18.600000000000001">
-      <c r="B18" s="84"/>
+    <row r="18" spans="2:12" ht="18.75">
+      <c r="B18" s="80"/>
       <c r="C18" s="79"/>
       <c r="D18" s="24">
         <v>1</v>
@@ -4837,7 +4885,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="84"/>
+      <c r="B19" s="80"/>
       <c r="C19" s="20"/>
       <c r="D19" s="24"/>
       <c r="E19" s="70"/>
@@ -4861,7 +4909,7 @@
       <c r="L19" s="25"/>
     </row>
     <row r="20" spans="2:12">
-      <c r="B20" s="84"/>
+      <c r="B20" s="80"/>
       <c r="C20" s="19" t="s">
         <v>29</v>
       </c>
@@ -4879,7 +4927,7 @@
       <c r="L20" s="25"/>
     </row>
     <row r="21" spans="2:12">
-      <c r="B21" s="84"/>
+      <c r="B21" s="80"/>
       <c r="C21" s="19" t="s">
         <v>30</v>
       </c>
@@ -4897,7 +4945,7 @@
       <c r="L21" s="25"/>
     </row>
     <row r="22" spans="2:12">
-      <c r="B22" s="84"/>
+      <c r="B22" s="80"/>
       <c r="C22" s="19" t="s">
         <v>38</v>
       </c>
@@ -4915,7 +4963,7 @@
       <c r="L22" s="25"/>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="84"/>
+      <c r="B23" s="80"/>
       <c r="C23" s="20"/>
       <c r="D23" s="24"/>
       <c r="E23" s="70"/>
@@ -4928,7 +4976,7 @@
       <c r="L23" s="25"/>
     </row>
     <row r="24" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B24" s="84">
+      <c r="B24" s="80">
         <v>4</v>
       </c>
       <c r="C24" s="79" t="s">
@@ -4957,7 +5005,7 @@
       <c r="L24" s="25"/>
     </row>
     <row r="25" spans="2:12">
-      <c r="B25" s="84"/>
+      <c r="B25" s="80"/>
       <c r="C25" s="19"/>
       <c r="D25" s="24">
         <f>E24/0.15</f>
@@ -4982,7 +5030,7 @@
       <c r="L25" s="25"/>
     </row>
     <row r="26" spans="2:12">
-      <c r="B26" s="84"/>
+      <c r="B26" s="80"/>
       <c r="C26" s="19" t="s">
         <v>81</v>
       </c>
@@ -5008,7 +5056,7 @@
       <c r="L26" s="25"/>
     </row>
     <row r="27" spans="2:12">
-      <c r="B27" s="84"/>
+      <c r="B27" s="80"/>
       <c r="C27" s="19"/>
       <c r="D27" s="24"/>
       <c r="E27" s="70"/>
@@ -5024,7 +5072,7 @@
       <c r="L27" s="25"/>
     </row>
     <row r="28" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B28" s="84">
+      <c r="B28" s="80">
         <v>5</v>
       </c>
       <c r="C28" s="79" t="s">
@@ -5054,7 +5102,7 @@
       <c r="L28" s="25"/>
     </row>
     <row r="29" spans="2:12">
-      <c r="B29" s="84"/>
+      <c r="B29" s="80"/>
       <c r="C29" s="18"/>
       <c r="D29" s="24">
         <v>2</v>
@@ -5080,7 +5128,7 @@
       <c r="L29" s="25"/>
     </row>
     <row r="30" spans="2:12">
-      <c r="B30" s="84"/>
+      <c r="B30" s="80"/>
       <c r="C30" s="18"/>
       <c r="D30" s="24">
         <v>2</v>
@@ -5106,7 +5154,7 @@
       <c r="L30" s="25"/>
     </row>
     <row r="31" spans="2:12">
-      <c r="B31" s="84"/>
+      <c r="B31" s="80"/>
       <c r="C31" s="18"/>
       <c r="D31" s="24"/>
       <c r="E31" s="70"/>
@@ -5132,7 +5180,7 @@
       <c r="L31" s="25"/>
     </row>
     <row r="32" spans="2:12">
-      <c r="B32" s="84"/>
+      <c r="B32" s="80"/>
       <c r="C32" s="19" t="s">
         <v>29</v>
       </c>
@@ -5150,7 +5198,7 @@
       <c r="L32" s="25"/>
     </row>
     <row r="33" spans="2:12">
-      <c r="B33" s="84"/>
+      <c r="B33" s="80"/>
       <c r="C33" s="19" t="s">
         <v>30</v>
       </c>
@@ -5168,7 +5216,7 @@
       <c r="L33" s="25"/>
     </row>
     <row r="34" spans="2:12">
-      <c r="B34" s="84"/>
+      <c r="B34" s="80"/>
       <c r="C34" s="19" t="s">
         <v>31</v>
       </c>
@@ -5186,7 +5234,7 @@
       <c r="L34" s="25"/>
     </row>
     <row r="35" spans="2:12">
-      <c r="B35" s="84"/>
+      <c r="B35" s="80"/>
       <c r="C35" s="20"/>
       <c r="D35" s="24"/>
       <c r="E35" s="70"/>
@@ -5199,7 +5247,7 @@
       <c r="L35" s="25"/>
     </row>
     <row r="36" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B36" s="85">
+      <c r="B36" s="81">
         <v>6</v>
       </c>
       <c r="C36" s="79" t="s">
@@ -5235,7 +5283,7 @@
       <c r="L36" s="25"/>
     </row>
     <row r="37" spans="2:12">
-      <c r="B37" s="85"/>
+      <c r="B37" s="81"/>
       <c r="C37" s="19" t="s">
         <v>29</v>
       </c>
@@ -5253,7 +5301,7 @@
       <c r="L37" s="25"/>
     </row>
     <row r="38" spans="2:12">
-      <c r="B38" s="85"/>
+      <c r="B38" s="81"/>
       <c r="C38" s="19" t="s">
         <v>30</v>
       </c>
@@ -5271,7 +5319,7 @@
       <c r="L38" s="25"/>
     </row>
     <row r="39" spans="2:12">
-      <c r="B39" s="85"/>
+      <c r="B39" s="81"/>
       <c r="C39" s="19" t="s">
         <v>31</v>
       </c>
@@ -5289,7 +5337,7 @@
       <c r="L39" s="25"/>
     </row>
     <row r="40" spans="2:12" ht="18" customHeight="1">
-      <c r="B40" s="84"/>
+      <c r="B40" s="80"/>
       <c r="C40" s="19"/>
       <c r="D40" s="24"/>
       <c r="E40" s="70"/>
@@ -5302,7 +5350,7 @@
       <c r="L40" s="25"/>
     </row>
     <row r="41" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B41" s="84">
+      <c r="B41" s="80">
         <v>7</v>
       </c>
       <c r="C41" s="79" t="s">
@@ -5331,7 +5379,7 @@
       <c r="L41" s="25"/>
     </row>
     <row r="42" spans="2:12">
-      <c r="B42" s="84"/>
+      <c r="B42" s="80"/>
       <c r="C42" s="21"/>
       <c r="D42" s="24">
         <f>D17</f>
@@ -5356,7 +5404,7 @@
       <c r="L42" s="25"/>
     </row>
     <row r="43" spans="2:12">
-      <c r="B43" s="84"/>
+      <c r="B43" s="80"/>
       <c r="C43" s="21"/>
       <c r="D43" s="24"/>
       <c r="E43" s="70"/>
@@ -5380,7 +5428,7 @@
       <c r="L43" s="25"/>
     </row>
     <row r="44" spans="2:12">
-      <c r="B44" s="84"/>
+      <c r="B44" s="80"/>
       <c r="C44" s="19" t="s">
         <v>29</v>
       </c>
@@ -5398,7 +5446,7 @@
       <c r="L44" s="25"/>
     </row>
     <row r="45" spans="2:12">
-      <c r="B45" s="84"/>
+      <c r="B45" s="80"/>
       <c r="C45" s="19" t="s">
         <v>30</v>
       </c>
@@ -5416,7 +5464,7 @@
       <c r="L45" s="25"/>
     </row>
     <row r="46" spans="2:12">
-      <c r="B46" s="85"/>
+      <c r="B46" s="81"/>
       <c r="C46" s="19"/>
       <c r="D46" s="72"/>
       <c r="E46" s="70"/>
@@ -5429,7 +5477,7 @@
       <c r="L46" s="25"/>
     </row>
     <row r="47" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B47" s="85">
+      <c r="B47" s="81">
         <v>8</v>
       </c>
       <c r="C47" s="79" t="s">
@@ -5458,7 +5506,7 @@
       <c r="L47" s="25"/>
     </row>
     <row r="48" spans="2:12">
-      <c r="B48" s="85"/>
+      <c r="B48" s="81"/>
       <c r="C48" s="19"/>
       <c r="D48" s="72">
         <f t="shared" si="0"/>
@@ -5483,7 +5531,7 @@
       <c r="L48" s="25"/>
     </row>
     <row r="49" spans="2:14">
-      <c r="B49" s="85"/>
+      <c r="B49" s="81"/>
       <c r="C49" s="19"/>
       <c r="D49" s="72">
         <f t="shared" si="0"/>
@@ -5508,7 +5556,7 @@
       <c r="L49" s="25"/>
     </row>
     <row r="50" spans="2:14">
-      <c r="B50" s="85"/>
+      <c r="B50" s="81"/>
       <c r="C50" s="19"/>
       <c r="D50" s="72"/>
       <c r="E50" s="72"/>
@@ -5532,7 +5580,7 @@
       <c r="L50" s="25"/>
     </row>
     <row r="51" spans="2:14">
-      <c r="B51" s="85"/>
+      <c r="B51" s="81"/>
       <c r="C51" s="19" t="s">
         <v>29</v>
       </c>
@@ -5550,7 +5598,7 @@
       <c r="L51" s="25"/>
     </row>
     <row r="52" spans="2:14">
-      <c r="B52" s="85"/>
+      <c r="B52" s="81"/>
       <c r="C52" s="19"/>
       <c r="D52" s="72"/>
       <c r="E52" s="72"/>
@@ -5563,7 +5611,7 @@
       <c r="L52" s="25"/>
     </row>
     <row r="53" spans="2:14">
-      <c r="B53" s="85"/>
+      <c r="B53" s="81"/>
       <c r="C53" s="19"/>
       <c r="D53" s="72"/>
       <c r="E53" s="72"/>
@@ -5576,7 +5624,7 @@
       <c r="L53" s="25"/>
     </row>
     <row r="54" spans="2:14" ht="33" customHeight="1">
-      <c r="B54" s="84">
+      <c r="B54" s="80">
         <v>9</v>
       </c>
       <c r="C54" s="21" t="s">
@@ -5608,7 +5656,7 @@
       </c>
     </row>
     <row r="55" spans="2:14">
-      <c r="B55" s="84"/>
+      <c r="B55" s="80"/>
       <c r="C55" s="30" t="s">
         <v>88</v>
       </c>
@@ -5626,7 +5674,7 @@
       <c r="L55" s="25"/>
     </row>
     <row r="56" spans="2:14">
-      <c r="B56" s="84"/>
+      <c r="B56" s="80"/>
       <c r="C56" s="21"/>
       <c r="D56" s="24"/>
       <c r="E56" s="70"/>
@@ -5639,7 +5687,7 @@
       <c r="L56" s="25"/>
     </row>
     <row r="57" spans="2:14" ht="33" customHeight="1">
-      <c r="B57" s="84">
+      <c r="B57" s="80">
         <v>10</v>
       </c>
       <c r="C57" s="21" t="s">
@@ -5668,7 +5716,7 @@
       </c>
     </row>
     <row r="58" spans="2:14">
-      <c r="B58" s="85"/>
+      <c r="B58" s="81"/>
       <c r="C58" s="29" t="s">
         <v>82</v>
       </c>
@@ -5688,7 +5736,7 @@
       <c r="L58" s="25"/>
     </row>
     <row r="59" spans="2:14">
-      <c r="B59" s="85"/>
+      <c r="B59" s="81"/>
       <c r="C59" s="29"/>
       <c r="D59" s="24"/>
       <c r="E59" s="24"/>
@@ -5701,7 +5749,7 @@
       <c r="L59" s="25"/>
     </row>
     <row r="60" spans="2:14">
-      <c r="B60" s="85"/>
+      <c r="B60" s="81"/>
       <c r="C60" s="20"/>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
@@ -5713,11 +5761,11 @@
       <c r="K60" s="20"/>
       <c r="L60" s="25"/>
     </row>
-    <row r="61" spans="2:14" s="80" customFormat="1" ht="18">
-      <c r="B61" s="85" t="s">
+    <row r="61" spans="2:14" ht="18">
+      <c r="B61" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="C61" s="86" t="s">
+      <c r="C61" s="82" t="s">
         <v>96</v>
       </c>
       <c r="D61" s="24"/>
@@ -5730,8 +5778,8 @@
       <c r="K61" s="73"/>
       <c r="L61" s="25"/>
     </row>
-    <row r="62" spans="2:14" s="80" customFormat="1">
-      <c r="B62" s="85"/>
+    <row r="62" spans="2:14">
+      <c r="B62" s="81"/>
       <c r="C62" s="29"/>
       <c r="D62" s="24"/>
       <c r="E62" s="24"/>
@@ -5743,11 +5791,11 @@
       <c r="K62" s="73"/>
       <c r="L62" s="25"/>
     </row>
-    <row r="63" spans="2:14" s="80" customFormat="1" ht="34.799999999999997">
-      <c r="B63" s="84">
+    <row r="63" spans="2:14" ht="36">
+      <c r="B63" s="80">
         <v>11</v>
       </c>
-      <c r="C63" s="93" t="s">
+      <c r="C63" s="89" t="s">
         <v>98</v>
       </c>
       <c r="D63" s="70">
@@ -5779,8 +5827,8 @@
       </c>
       <c r="L63" s="25"/>
     </row>
-    <row r="64" spans="2:14" s="80" customFormat="1">
-      <c r="B64" s="85"/>
+    <row r="64" spans="2:14">
+      <c r="B64" s="81"/>
       <c r="C64" s="29"/>
       <c r="D64" s="24"/>
       <c r="E64" s="24"/>
@@ -5792,11 +5840,11 @@
       <c r="K64" s="73"/>
       <c r="L64" s="25"/>
     </row>
-    <row r="65" spans="2:14" s="80" customFormat="1" ht="34.799999999999997">
-      <c r="B65" s="85">
+    <row r="65" spans="2:14" ht="36">
+      <c r="B65" s="81">
         <v>12</v>
       </c>
-      <c r="C65" s="93" t="s">
+      <c r="C65" s="89" t="s">
         <v>99</v>
       </c>
       <c r="D65" s="24">
@@ -5827,8 +5875,8 @@
       </c>
       <c r="L65" s="25"/>
     </row>
-    <row r="66" spans="2:14" s="80" customFormat="1">
-      <c r="B66" s="85"/>
+    <row r="66" spans="2:14">
+      <c r="B66" s="81"/>
       <c r="C66" s="29" t="s">
         <v>81</v>
       </c>
@@ -5845,11 +5893,11 @@
       </c>
       <c r="L66" s="25"/>
     </row>
-    <row r="67" spans="2:14" s="80" customFormat="1" ht="69.599999999999994">
-      <c r="B67" s="85">
+    <row r="67" spans="2:14" ht="72">
+      <c r="B67" s="81">
         <v>13</v>
       </c>
-      <c r="C67" s="93" t="s">
+      <c r="C67" s="89" t="s">
         <v>92</v>
       </c>
       <c r="D67" s="24">
@@ -5878,8 +5926,8 @@
       </c>
       <c r="L67" s="25"/>
     </row>
-    <row r="68" spans="2:14" s="80" customFormat="1">
-      <c r="B68" s="85"/>
+    <row r="68" spans="2:14">
+      <c r="B68" s="81"/>
       <c r="C68" s="29" t="s">
         <v>81</v>
       </c>
@@ -5895,13 +5943,13 @@
         <v>2468.2164634146343</v>
       </c>
       <c r="L68" s="25"/>
-      <c r="N68" s="80">
+      <c r="N68" s="1">
         <f>17/3.28</f>
         <v>5.1829268292682933</v>
       </c>
     </row>
-    <row r="69" spans="2:14" s="80" customFormat="1">
-      <c r="B69" s="85"/>
+    <row r="69" spans="2:14">
+      <c r="B69" s="81"/>
       <c r="C69" s="29"/>
       <c r="D69" s="24"/>
       <c r="E69" s="24"/>
@@ -5912,13 +5960,13 @@
       <c r="J69" s="73"/>
       <c r="K69" s="73"/>
       <c r="L69" s="25"/>
-      <c r="N69" s="80" t="e">
+      <c r="N69" s="1" t="e">
         <f>#REF!*N68*2*68.4</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="70" spans="2:14" ht="33" customHeight="1">
-      <c r="B70" s="85">
+      <c r="B70" s="81">
         <v>14</v>
       </c>
       <c r="C70" s="18" t="s">
@@ -5945,7 +5993,7 @@
       </c>
       <c r="L70" s="25"/>
     </row>
-    <row r="71" spans="2:14" ht="17.399999999999999" thickBot="1">
+    <row r="71" spans="2:14" ht="17.25" thickBot="1">
       <c r="B71" s="22"/>
       <c r="C71" s="26"/>
       <c r="D71" s="76"/>
@@ -6107,77 +6155,77 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M51"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-    </row>
-    <row r="2" spans="1:10" ht="24.6">
-      <c r="A2" s="103" t="s">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+    </row>
+    <row r="2" spans="1:10" ht="25.5">
+      <c r="A2" s="133" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-    </row>
-    <row r="3" spans="1:10" ht="18">
-      <c r="A3" s="104" t="s">
+      <c r="B2" s="133"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+    </row>
+    <row r="3" spans="1:10" ht="18.75">
+      <c r="A3" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="105" t="s">
+      <c r="A4" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="105"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="37"/>
@@ -6191,40 +6239,40 @@
       <c r="I5" s="37"/>
       <c r="J5" s="37"/>
     </row>
-    <row r="6" spans="1:10" ht="15.6">
+    <row r="6" spans="1:10" ht="15.75">
       <c r="A6" s="31" t="s">
         <v>55</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="106" t="e">
+      <c r="C6" s="136" t="e">
         <f>E51</f>
         <v>#REF!</v>
       </c>
-      <c r="D6" s="107"/>
+      <c r="D6" s="137"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
         <v>56</v>
       </c>
       <c r="H6" s="31"/>
-      <c r="I6" s="106" t="e">
+      <c r="I6" s="136" t="e">
         <f>H51</f>
         <v>#REF!</v>
       </c>
-      <c r="J6" s="107"/>
+      <c r="J6" s="137"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="32"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="109"/>
-    </row>
-    <row r="8" spans="1:10" ht="16.8">
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+    </row>
+    <row r="8" spans="1:10" ht="16.5">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -6249,32 +6297,32 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="110" t="s">
+      <c r="A10" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="129" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="112" t="s">
+      <c r="C10" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="112"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112" t="s">
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="131" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="110" t="s">
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="110" t="s">
+      <c r="J10" s="129" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="111"/>
-      <c r="B11" s="111"/>
+      <c r="A11" s="130"/>
+      <c r="B11" s="130"/>
       <c r="C11" s="39" t="s">
         <v>64</v>
       </c>
@@ -6293,10 +6341,10 @@
       <c r="H11" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="111"/>
-      <c r="J11" s="111"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.6">
+      <c r="I11" s="130"/>
+      <c r="J11" s="130"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75">
       <c r="A12" s="47">
         <v>1</v>
       </c>
@@ -6333,7 +6381,7 @@
       </c>
       <c r="J12" s="43"/>
     </row>
-    <row r="13" spans="1:10" ht="15.6">
+    <row r="13" spans="1:10" ht="15.75">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="43"/>
@@ -6345,7 +6393,7 @@
       <c r="I13" s="42"/>
       <c r="J13" s="43"/>
     </row>
-    <row r="14" spans="1:10" ht="31.2">
+    <row r="14" spans="1:10" ht="31.5">
       <c r="A14" s="49">
         <v>2</v>
       </c>
@@ -6382,7 +6430,7 @@
       </c>
       <c r="J14" s="43"/>
     </row>
-    <row r="15" spans="1:10" ht="15.6">
+    <row r="15" spans="1:10" ht="15.75">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="41"/>
@@ -6394,7 +6442,7 @@
       <c r="I15" s="42"/>
       <c r="J15" s="43"/>
     </row>
-    <row r="16" spans="1:10" ht="15.6">
+    <row r="16" spans="1:10" ht="15.75">
       <c r="A16" s="49">
         <v>3</v>
       </c>
@@ -6431,7 +6479,7 @@
       </c>
       <c r="J16" s="43"/>
     </row>
-    <row r="17" spans="1:13" ht="15.6">
+    <row r="17" spans="1:13" ht="15.75">
       <c r="A17" s="49"/>
       <c r="B17" s="52" t="s">
         <v>37</v>
@@ -6451,7 +6499,7 @@
       <c r="I17" s="42"/>
       <c r="J17" s="43"/>
     </row>
-    <row r="18" spans="1:13" ht="15.6">
+    <row r="18" spans="1:13" ht="15.75">
       <c r="A18" s="49"/>
       <c r="B18" s="52"/>
       <c r="C18" s="43"/>
@@ -6463,7 +6511,7 @@
       <c r="I18" s="42"/>
       <c r="J18" s="43"/>
     </row>
-    <row r="19" spans="1:13" ht="15.6">
+    <row r="19" spans="1:13" ht="15.75">
       <c r="A19" s="49">
         <v>4</v>
       </c>
@@ -6501,7 +6549,7 @@
       <c r="J19" s="43"/>
       <c r="M19" s="38"/>
     </row>
-    <row r="20" spans="1:13" ht="15.6">
+    <row r="20" spans="1:13" ht="15.75">
       <c r="A20" s="49"/>
       <c r="B20" s="53" t="s">
         <v>37</v>
@@ -6521,7 +6569,7 @@
       <c r="I20" s="42"/>
       <c r="J20" s="43"/>
     </row>
-    <row r="21" spans="1:13" ht="15.6">
+    <row r="21" spans="1:13" ht="15.75">
       <c r="A21" s="49"/>
       <c r="B21" s="52"/>
       <c r="C21" s="43"/>
@@ -6533,7 +6581,7 @@
       <c r="I21" s="42"/>
       <c r="J21" s="43"/>
     </row>
-    <row r="22" spans="1:13" ht="15.6">
+    <row r="22" spans="1:13" ht="15.75">
       <c r="A22" s="49">
         <v>5</v>
       </c>
@@ -6570,7 +6618,7 @@
       </c>
       <c r="J22" s="43"/>
     </row>
-    <row r="23" spans="1:13" ht="15.6">
+    <row r="23" spans="1:13" ht="15.75">
       <c r="A23" s="49"/>
       <c r="B23" s="53" t="s">
         <v>29</v>
@@ -6590,7 +6638,7 @@
       <c r="I23" s="42"/>
       <c r="J23" s="43"/>
     </row>
-    <row r="24" spans="1:13" ht="15.6">
+    <row r="24" spans="1:13" ht="15.75">
       <c r="A24" s="49"/>
       <c r="B24" s="53" t="s">
         <v>38</v>
@@ -6610,7 +6658,7 @@
       <c r="I24" s="42"/>
       <c r="J24" s="43"/>
     </row>
-    <row r="25" spans="1:13" ht="15.6">
+    <row r="25" spans="1:13" ht="15.75">
       <c r="A25" s="49"/>
       <c r="B25" s="53" t="s">
         <v>30</v>
@@ -6630,7 +6678,7 @@
       <c r="I25" s="42"/>
       <c r="J25" s="43"/>
     </row>
-    <row r="26" spans="1:13" ht="15.6">
+    <row r="26" spans="1:13" ht="15.75">
       <c r="A26" s="49"/>
       <c r="B26" s="53"/>
       <c r="C26" s="43"/>
@@ -6642,7 +6690,7 @@
       <c r="I26" s="42"/>
       <c r="J26" s="43"/>
     </row>
-    <row r="27" spans="1:13" ht="46.8">
+    <row r="27" spans="1:13" ht="31.5">
       <c r="A27" s="49">
         <v>6</v>
       </c>
@@ -6679,7 +6727,7 @@
       </c>
       <c r="J27" s="43"/>
     </row>
-    <row r="28" spans="1:13" ht="15.6">
+    <row r="28" spans="1:13" ht="15.75">
       <c r="A28" s="49"/>
       <c r="B28" s="53" t="s">
         <v>29</v>
@@ -6699,7 +6747,7 @@
       <c r="I28" s="42"/>
       <c r="J28" s="43"/>
     </row>
-    <row r="29" spans="1:13" ht="15.6">
+    <row r="29" spans="1:13" ht="15.75">
       <c r="A29" s="49"/>
       <c r="B29" s="53" t="s">
         <v>31</v>
@@ -6719,7 +6767,7 @@
       <c r="I29" s="42"/>
       <c r="J29" s="43"/>
     </row>
-    <row r="30" spans="1:13" ht="15.6">
+    <row r="30" spans="1:13" ht="15.75">
       <c r="A30" s="49"/>
       <c r="B30" s="53" t="s">
         <v>30</v>
@@ -6739,7 +6787,7 @@
       <c r="I30" s="42"/>
       <c r="J30" s="43"/>
     </row>
-    <row r="31" spans="1:13" ht="15.6">
+    <row r="31" spans="1:13" ht="15.75">
       <c r="A31" s="49"/>
       <c r="B31" s="53"/>
       <c r="C31" s="43"/>
@@ -6751,7 +6799,7 @@
       <c r="I31" s="42"/>
       <c r="J31" s="43"/>
     </row>
-    <row r="32" spans="1:13" ht="15.6">
+    <row r="32" spans="1:13" ht="15.75">
       <c r="A32" s="51">
         <v>7</v>
       </c>
@@ -6788,7 +6836,7 @@
       </c>
       <c r="J32" s="43"/>
     </row>
-    <row r="33" spans="1:10" ht="15.6">
+    <row r="33" spans="1:10" ht="15.75">
       <c r="A33" s="51"/>
       <c r="B33" s="53" t="s">
         <v>29</v>
@@ -6808,7 +6856,7 @@
       <c r="I33" s="42"/>
       <c r="J33" s="43"/>
     </row>
-    <row r="34" spans="1:10" ht="15.6">
+    <row r="34" spans="1:10" ht="15.75">
       <c r="A34" s="49"/>
       <c r="B34" s="53"/>
       <c r="C34" s="43"/>
@@ -6820,7 +6868,7 @@
       <c r="I34" s="42"/>
       <c r="J34" s="43"/>
     </row>
-    <row r="35" spans="1:10" ht="15.6">
+    <row r="35" spans="1:10" ht="15.75">
       <c r="A35" s="49">
         <v>8</v>
       </c>
@@ -6857,7 +6905,7 @@
       </c>
       <c r="J35" s="43"/>
     </row>
-    <row r="36" spans="1:10" ht="15.6">
+    <row r="36" spans="1:10" ht="15.75">
       <c r="A36" s="49"/>
       <c r="B36" s="53" t="s">
         <v>29</v>
@@ -6877,7 +6925,7 @@
       <c r="I36" s="42"/>
       <c r="J36" s="43"/>
     </row>
-    <row r="37" spans="1:10" ht="15.6">
+    <row r="37" spans="1:10" ht="15.75">
       <c r="A37" s="49"/>
       <c r="B37" s="53" t="s">
         <v>30</v>
@@ -6897,7 +6945,7 @@
       <c r="I37" s="42"/>
       <c r="J37" s="43"/>
     </row>
-    <row r="38" spans="1:10" ht="15.6">
+    <row r="38" spans="1:10" ht="15.75">
       <c r="A38" s="51"/>
       <c r="B38" s="53"/>
       <c r="C38" s="43"/>
@@ -6909,7 +6957,7 @@
       <c r="I38" s="42"/>
       <c r="J38" s="43"/>
     </row>
-    <row r="39" spans="1:10" ht="15.6">
+    <row r="39" spans="1:10" ht="15.75">
       <c r="A39" s="49">
         <v>9</v>
       </c>
@@ -6946,7 +6994,7 @@
       </c>
       <c r="J39" s="43"/>
     </row>
-    <row r="40" spans="1:10" ht="15.6">
+    <row r="40" spans="1:10" ht="15.75">
       <c r="A40" s="49"/>
       <c r="B40" s="50"/>
       <c r="C40" s="43"/>
@@ -6958,7 +7006,7 @@
       <c r="I40" s="42"/>
       <c r="J40" s="43"/>
     </row>
-    <row r="41" spans="1:10" ht="15.6">
+    <row r="41" spans="1:10" ht="15.75">
       <c r="A41" s="51">
         <v>10</v>
       </c>
@@ -6995,7 +7043,7 @@
       </c>
       <c r="J41" s="43"/>
     </row>
-    <row r="42" spans="1:10" ht="15.6">
+    <row r="42" spans="1:10" ht="15.75">
       <c r="A42" s="51"/>
       <c r="B42" s="56" t="s">
         <v>50</v>
@@ -7015,7 +7063,7 @@
       <c r="I42" s="42"/>
       <c r="J42" s="43"/>
     </row>
-    <row r="43" spans="1:10" ht="15.6">
+    <row r="43" spans="1:10" ht="15.75">
       <c r="A43" s="51"/>
       <c r="B43" s="55"/>
       <c r="C43" s="43"/>
@@ -7027,7 +7075,7 @@
       <c r="I43" s="42"/>
       <c r="J43" s="43"/>
     </row>
-    <row r="44" spans="1:10" ht="15.6">
+    <row r="44" spans="1:10" ht="15.75">
       <c r="A44" s="51">
         <v>11</v>
       </c>
@@ -7064,7 +7112,7 @@
       </c>
       <c r="J44" s="43"/>
     </row>
-    <row r="45" spans="1:10" ht="15.6">
+    <row r="45" spans="1:10" ht="15.75">
       <c r="A45" s="49"/>
       <c r="B45" s="57" t="s">
         <v>51</v>
@@ -7084,7 +7132,7 @@
       <c r="I45" s="42"/>
       <c r="J45" s="43"/>
     </row>
-    <row r="46" spans="1:10" ht="15.6">
+    <row r="46" spans="1:10" ht="15.75">
       <c r="A46" s="49"/>
       <c r="B46" s="50"/>
       <c r="C46" s="43"/>
@@ -7096,7 +7144,7 @@
       <c r="I46" s="42"/>
       <c r="J46" s="43"/>
     </row>
-    <row r="47" spans="1:10" ht="15.6">
+    <row r="47" spans="1:10" ht="15.75">
       <c r="A47" s="58">
         <v>12</v>
       </c>
@@ -7133,7 +7181,7 @@
       </c>
       <c r="J47" s="43"/>
     </row>
-    <row r="48" spans="1:10" ht="15.6">
+    <row r="48" spans="1:10" ht="15.75">
       <c r="A48" s="47"/>
       <c r="B48" s="60" t="s">
         <v>48</v>
@@ -7153,7 +7201,7 @@
       <c r="I48" s="42"/>
       <c r="J48" s="43"/>
     </row>
-    <row r="49" spans="1:10" ht="15.6">
+    <row r="49" spans="1:10" ht="15.75">
       <c r="A49" s="51"/>
       <c r="B49" s="55"/>
       <c r="C49" s="43"/>
@@ -7165,7 +7213,7 @@
       <c r="I49" s="42"/>
       <c r="J49" s="43"/>
     </row>
-    <row r="50" spans="1:10" ht="15.6">
+    <row r="50" spans="1:10" ht="15.75">
       <c r="A50" s="49">
         <v>12</v>
       </c>
@@ -7199,7 +7247,7 @@
       </c>
       <c r="J50" s="43"/>
     </row>
-    <row r="51" spans="1:10" ht="15.6">
+    <row r="51" spans="1:10" ht="15.75">
       <c r="A51" s="44"/>
       <c r="B51" s="45" t="s">
         <v>67</v>
@@ -7221,6 +7269,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:J7"/>
@@ -7230,12 +7284,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="J10:J11"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -7252,137 +7300,137 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R117"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8"/>
+  <dimension ref="A1:R121"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="81" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" style="81" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="81" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="81" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" style="81" customWidth="1"/>
-    <col min="8" max="8" width="11" style="81" customWidth="1"/>
-    <col min="9" max="9" width="7.5546875" style="81" customWidth="1"/>
-    <col min="10" max="10" width="10.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" style="81" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" style="81" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" style="81"/>
-    <col min="14" max="14" width="13.33203125" style="81" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="81"/>
-    <col min="16" max="16" width="14" style="81" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" style="81" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.109375" style="81"/>
+    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="14" max="14" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-    </row>
-    <row r="2" spans="1:18" ht="20.399999999999999">
-      <c r="A2" s="99" t="s">
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+    </row>
+    <row r="2" spans="1:18" ht="20.25">
+      <c r="A2" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-    </row>
-    <row r="5" spans="1:18" ht="19.8">
-      <c r="A5" s="82"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+    </row>
+    <row r="5" spans="1:18" ht="19.5">
+      <c r="A5" s="6"/>
       <c r="B5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="H5" s="82"/>
-      <c r="K5" s="101" t="s">
+      <c r="H5" s="6"/>
+      <c r="K5" s="126" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="101"/>
+      <c r="L5" s="126"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="96" t="s">
+      <c r="I6" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="O6" s="96" t="s">
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121"/>
+      <c r="O6" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="96"/>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="96"/>
-    </row>
-    <row r="7" spans="1:18" ht="17.399999999999999" thickBot="1">
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
+      <c r="R6" s="121"/>
+    </row>
+    <row r="7" spans="1:18" ht="17.25" thickBot="1">
       <c r="C7" s="5"/>
-      <c r="D7" s="82"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -7391,7 +7439,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:18" ht="17.399999999999999" thickBot="1">
+    <row r="8" spans="1:18" ht="17.25" thickBot="1">
       <c r="A8" s="2"/>
       <c r="B8" s="12" t="s">
         <v>0</v>
@@ -7429,60 +7477,60 @@
     </row>
     <row r="9" spans="1:18" ht="18">
       <c r="A9" s="2"/>
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="89"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="90"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="92"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="88"/>
     </row>
     <row r="10" spans="1:18" ht="35.1" customHeight="1">
-      <c r="B10" s="84">
+      <c r="B10" s="147">
         <v>1</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="148" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="119">
         <v>1</v>
       </c>
-      <c r="E10" s="70">
+      <c r="E10" s="116">
         <v>5</v>
       </c>
-      <c r="F10" s="70">
+      <c r="F10" s="116">
         <f>11/3.281</f>
         <v>3.3526363913441024</v>
       </c>
-      <c r="G10" s="70">
+      <c r="G10" s="116">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="H10" s="70">
+      <c r="H10" s="116">
         <f>D10*E10*F10*G10</f>
         <v>1.2572386467540384</v>
       </c>
-      <c r="I10" s="72" t="s">
+      <c r="I10" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="72">
+      <c r="J10" s="119">
         <v>3740</v>
       </c>
-      <c r="K10" s="72">
+      <c r="K10" s="119">
         <f>H10*J10</f>
         <v>4702.072538860104</v>
       </c>
       <c r="L10" s="25"/>
     </row>
-    <row r="11" spans="1:18" ht="18.600000000000001">
-      <c r="B11" s="84"/>
+    <row r="11" spans="1:18" ht="18.75">
+      <c r="B11" s="80"/>
       <c r="C11" s="79"/>
       <c r="D11" s="24"/>
       <c r="E11" s="70"/>
@@ -7494,1632 +7542,1623 @@
       <c r="K11" s="70"/>
       <c r="L11" s="25"/>
     </row>
-    <row r="12" spans="1:18" ht="55.8">
-      <c r="B12" s="84">
+    <row r="12" spans="1:18" ht="56.25">
+      <c r="B12" s="147">
         <v>2</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="148" t="s">
         <v>104</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="119">
         <v>2</v>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="116">
         <f>E10</f>
         <v>5</v>
       </c>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70">
+      <c r="F12" s="116"/>
+      <c r="G12" s="116">
         <v>1.4</v>
       </c>
-      <c r="H12" s="70">
+      <c r="H12" s="116">
         <f>D12*E12*G12</f>
         <v>14</v>
       </c>
-      <c r="I12" s="70"/>
-      <c r="J12" s="70"/>
-      <c r="K12" s="70"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="116"/>
       <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="B13" s="84"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="24">
+      <c r="B13" s="147"/>
+      <c r="C13" s="161"/>
+      <c r="D13" s="119">
         <v>2</v>
       </c>
-      <c r="E13" s="70">
+      <c r="E13" s="116">
         <f>F10-0.23*2</f>
         <v>2.8926363913441024</v>
       </c>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70">
+      <c r="F13" s="116"/>
+      <c r="G13" s="116">
         <v>1.4</v>
       </c>
-      <c r="H13" s="70">
+      <c r="H13" s="116">
         <f>D13*E13*G13</f>
         <v>8.0993818957634858</v>
       </c>
-      <c r="I13" s="70"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="70"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="116"/>
       <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:18">
-      <c r="B14" s="84"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24">
+      <c r="B14" s="147"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="119">
         <v>1</v>
       </c>
-      <c r="E14" s="70">
+      <c r="E14" s="116">
         <f>E10</f>
         <v>5</v>
       </c>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70">
+      <c r="F14" s="116"/>
+      <c r="G14" s="116">
         <v>0.45</v>
       </c>
-      <c r="H14" s="70">
+      <c r="H14" s="116">
         <f>D14*E14*G14</f>
         <v>2.25</v>
       </c>
-      <c r="I14" s="70"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="70"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="116"/>
+      <c r="K14" s="116"/>
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="B15" s="84"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="70">
-        <f>SUM(H12:H14)</f>
-        <v>24.349381895763486</v>
-      </c>
-      <c r="I15" s="24" t="s">
+      <c r="B15" s="147"/>
+      <c r="C15" s="162" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="119">
+        <v>1</v>
+      </c>
+      <c r="E15" s="116">
+        <f>(5.25/3.281)</f>
+        <v>1.6001219140505942</v>
+      </c>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116">
+        <f>((5.33+8)/2)/3.281</f>
+        <v>2.03139286802804</v>
+      </c>
+      <c r="H15" s="116">
+        <f t="shared" ref="H15:H17" si="0">D15*E15*G15</f>
+        <v>3.2504762441777535</v>
+      </c>
+      <c r="I15" s="116"/>
+      <c r="J15" s="116"/>
+      <c r="K15" s="116"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="B16" s="147"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="119">
+        <v>1</v>
+      </c>
+      <c r="E16" s="116">
+        <f>4.5/3.281</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="F16" s="116"/>
+      <c r="G16" s="116">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="H16" s="116">
+        <f t="shared" si="0"/>
+        <v>3.3441830397713468</v>
+      </c>
+      <c r="I16" s="116"/>
+      <c r="J16" s="116"/>
+      <c r="K16" s="116"/>
+      <c r="L16" s="25"/>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="147"/>
+      <c r="C17" s="162" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="119">
+        <v>-1</v>
+      </c>
+      <c r="E17" s="116">
+        <f>2.5/3.281</f>
+        <v>0.76196281621456874</v>
+      </c>
+      <c r="F17" s="116"/>
+      <c r="G17" s="116">
+        <f>6.5/3.281</f>
+        <v>1.9811033221578787</v>
+      </c>
+      <c r="H17" s="116">
+        <f t="shared" si="0"/>
+        <v>-1.5095270665634553</v>
+      </c>
+      <c r="I17" s="116"/>
+      <c r="J17" s="116"/>
+      <c r="K17" s="116"/>
+      <c r="L17" s="25"/>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="147"/>
+      <c r="C18" s="150"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="151"/>
+      <c r="H18" s="116">
+        <f>SUM(H12:H17)</f>
+        <v>29.434514113149135</v>
+      </c>
+      <c r="I18" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="70">
+      <c r="J18" s="116">
         <v>1982.2</v>
       </c>
-      <c r="K15" s="70">
-        <f>H15*J15</f>
-        <v>48265.34479378238</v>
-      </c>
-      <c r="L15" s="25"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="B16" s="84"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="70"/>
-      <c r="K16" s="70"/>
-      <c r="L16" s="25"/>
-    </row>
-    <row r="17" spans="2:14" ht="55.8">
-      <c r="B17" s="84">
-        <v>3</v>
-      </c>
-      <c r="C17" s="95" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" s="24"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="25"/>
-      <c r="N17" s="113" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
-      <c r="B18" s="84"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24">
-        <f>D10</f>
-        <v>1</v>
-      </c>
-      <c r="E18" s="70">
-        <f>E10</f>
-        <v>5</v>
-      </c>
-      <c r="F18" s="70">
-        <f>F10</f>
-        <v>3.3526363913441024</v>
-      </c>
-      <c r="G18" s="71">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="H18" s="70">
-        <f>D18*E18*F18*G18</f>
-        <v>1.2572386467540384</v>
-      </c>
-      <c r="I18" s="24"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="70"/>
+      <c r="K18" s="116">
+        <f>H18*J18</f>
+        <v>58345.093875084218</v>
+      </c>
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="2:14">
-      <c r="B19" s="84"/>
-      <c r="C19" s="20"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="27"/>
       <c r="D19" s="24"/>
       <c r="E19" s="70"/>
       <c r="F19" s="70"/>
       <c r="G19" s="71"/>
-      <c r="H19" s="70">
-        <f>SUM(H18)</f>
+      <c r="H19" s="70"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="25"/>
+    </row>
+    <row r="20" spans="2:14" ht="56.25">
+      <c r="B20" s="147">
+        <v>3</v>
+      </c>
+      <c r="C20" s="152" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="119"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="151"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="116"/>
+      <c r="K20" s="116"/>
+      <c r="L20" s="25"/>
+      <c r="N20" s="90" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" s="147"/>
+      <c r="C21" s="153"/>
+      <c r="D21" s="119">
+        <f>D10</f>
+        <v>1</v>
+      </c>
+      <c r="E21" s="116">
+        <f>E10</f>
+        <v>5</v>
+      </c>
+      <c r="F21" s="116">
+        <f>F10</f>
+        <v>3.3526363913441024</v>
+      </c>
+      <c r="G21" s="151">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="H21" s="116">
+        <f>D21*E21*F21*G21</f>
         <v>1.2572386467540384</v>
       </c>
-      <c r="I19" s="24" t="s">
+      <c r="I21" s="119"/>
+      <c r="J21" s="116"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="25"/>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="147"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="151"/>
+      <c r="H22" s="116">
+        <f>SUM(H21)</f>
+        <v>1.2572386467540384</v>
+      </c>
+      <c r="I22" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="70">
+      <c r="J22" s="116">
         <v>770.43</v>
       </c>
-      <c r="K19" s="70">
-        <f>H19*J19</f>
+      <c r="K22" s="116">
+        <f>H22*J22</f>
         <v>968.61437061871379</v>
       </c>
-      <c r="L19" s="25"/>
-    </row>
-    <row r="20" spans="2:14">
-      <c r="B20" s="84"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="70"/>
-      <c r="L20" s="25"/>
-    </row>
-    <row r="21" spans="2:14" ht="18.600000000000001">
-      <c r="B21" s="145">
+      <c r="L22" s="25"/>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="80"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="25"/>
+    </row>
+    <row r="24" spans="2:14" ht="18.75">
+      <c r="B24" s="154">
         <v>4</v>
       </c>
-      <c r="C21" s="113" t="s">
+      <c r="C24" s="155" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="74"/>
-      <c r="E21" s="146"/>
-      <c r="F21" s="146"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="146"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="146"/>
-      <c r="K21" s="146"/>
-      <c r="L21" s="25"/>
-    </row>
-    <row r="22" spans="2:14">
-      <c r="B22" s="145"/>
-      <c r="C22" s="148" t="s">
+      <c r="D24" s="151"/>
+      <c r="E24" s="156"/>
+      <c r="F24" s="156"/>
+      <c r="G24" s="151"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="151"/>
+      <c r="J24" s="156"/>
+      <c r="K24" s="156"/>
+      <c r="L24" s="25"/>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="154"/>
+      <c r="C25" s="157" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="74">
+      <c r="D25" s="151">
         <f>D14</f>
         <v>1</v>
       </c>
-      <c r="E22" s="146">
+      <c r="E25" s="156">
         <f>E14</f>
         <v>5</v>
       </c>
-      <c r="F22" s="146">
-        <f>F18</f>
+      <c r="F25" s="156">
+        <f>F21</f>
         <v>3.3526363913441024</v>
       </c>
-      <c r="G22" s="71"/>
-      <c r="H22" s="146">
-        <f>PRODUCT(D22:G22)</f>
+      <c r="G25" s="151"/>
+      <c r="H25" s="156">
+        <f>PRODUCT(D25:G25)</f>
         <v>16.763181956720512</v>
       </c>
-      <c r="I22" s="74"/>
-      <c r="J22" s="146"/>
-      <c r="K22" s="146"/>
-      <c r="L22" s="25"/>
-    </row>
-    <row r="23" spans="2:14">
-      <c r="B23" s="145"/>
-      <c r="C23" s="147"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="146">
-        <f>SUM(H22)</f>
+      <c r="I25" s="151"/>
+      <c r="J25" s="156"/>
+      <c r="K25" s="156"/>
+      <c r="L25" s="25"/>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="154"/>
+      <c r="C26" s="158"/>
+      <c r="D26" s="151"/>
+      <c r="E26" s="156"/>
+      <c r="F26" s="156"/>
+      <c r="G26" s="151"/>
+      <c r="H26" s="156">
+        <f>SUM(H25)</f>
         <v>16.763181956720512</v>
       </c>
-      <c r="I23" s="74" t="s">
+      <c r="I26" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="146">
+      <c r="J26" s="156">
         <f>Sheet1!H8/10</f>
         <v>155.75</v>
       </c>
-      <c r="K23" s="146">
-        <f>H23*J23</f>
+      <c r="K26" s="156">
+        <f>H26*J26</f>
         <v>2610.8655897592198</v>
       </c>
-      <c r="L23" s="25"/>
-    </row>
-    <row r="24" spans="2:14">
-      <c r="B24" s="84"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="70"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="70"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="25"/>
-    </row>
-    <row r="25" spans="2:14" s="94" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B25" s="84">
-        <v>5</v>
-      </c>
-      <c r="C25" s="79" t="s">
-        <v>134</v>
-      </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="73"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="25"/>
-    </row>
-    <row r="26" spans="2:14" s="94" customFormat="1">
-      <c r="B26" s="84"/>
-      <c r="C26" s="19" t="str">
-        <f>C22</f>
-        <v>-for flooring</v>
-      </c>
-      <c r="D26" s="24">
-        <f>D22</f>
-        <v>1</v>
-      </c>
-      <c r="E26" s="70">
-        <f>E22</f>
-        <v>5</v>
-      </c>
-      <c r="F26" s="70">
-        <f>F22</f>
-        <v>3.3526363913441024</v>
-      </c>
-      <c r="G26" s="70">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="H26" s="70">
-        <f>D26*E26*F26*G26</f>
-        <v>1.2572386467540384</v>
-      </c>
-      <c r="I26" s="24"/>
-      <c r="J26" s="73"/>
-      <c r="K26" s="70"/>
       <c r="L26" s="25"/>
     </row>
-    <row r="27" spans="2:14" s="94" customFormat="1">
-      <c r="B27" s="84"/>
-      <c r="C27" s="18"/>
+    <row r="27" spans="2:14">
+      <c r="B27" s="80"/>
+      <c r="C27" s="20"/>
       <c r="D27" s="24"/>
       <c r="E27" s="70"/>
-      <c r="F27" s="70" t="s">
+      <c r="F27" s="70"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="25"/>
+    </row>
+    <row r="28" spans="2:14" ht="35.1" customHeight="1">
+      <c r="B28" s="147">
+        <v>5</v>
+      </c>
+      <c r="C28" s="148" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="119"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="116"/>
+      <c r="G28" s="116"/>
+      <c r="H28" s="116"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="116"/>
+      <c r="K28" s="116"/>
+      <c r="L28" s="25"/>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="147"/>
+      <c r="C29" s="118" t="str">
+        <f>C25</f>
+        <v>-for flooring</v>
+      </c>
+      <c r="D29" s="119">
+        <f>D25</f>
+        <v>1</v>
+      </c>
+      <c r="E29" s="116">
+        <f>E25</f>
+        <v>5</v>
+      </c>
+      <c r="F29" s="116">
+        <f>F25</f>
+        <v>3.3526363913441024</v>
+      </c>
+      <c r="G29" s="116">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="H29" s="116">
+        <f>D29*E29*F29*G29</f>
+        <v>1.2572386467540384</v>
+      </c>
+      <c r="I29" s="119"/>
+      <c r="J29" s="116"/>
+      <c r="K29" s="116"/>
+      <c r="L29" s="25"/>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="147"/>
+      <c r="C30" s="159"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70">
-        <f>SUM(H26)</f>
+      <c r="G30" s="116"/>
+      <c r="H30" s="116">
+        <f>SUM(H29)</f>
         <v>1.2572386467540384</v>
       </c>
-      <c r="I27" s="24" t="s">
+      <c r="I30" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="73">
+      <c r="J30" s="116">
         <v>13351.1</v>
       </c>
-      <c r="K27" s="73">
-        <f>H27*J27</f>
+      <c r="K30" s="116">
+        <f>H30*J30</f>
         <v>16785.518896677844</v>
       </c>
-      <c r="L27" s="25"/>
-    </row>
-    <row r="28" spans="2:14" s="94" customFormat="1">
-      <c r="B28" s="84"/>
-      <c r="C28" s="19" t="s">
+      <c r="L30" s="25"/>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="147"/>
+      <c r="C31" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="73"/>
-      <c r="K28" s="73">
-        <f>0.13*H27*4169.92</f>
+      <c r="D31" s="119"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="116"/>
+      <c r="G31" s="116"/>
+      <c r="H31" s="116"/>
+      <c r="I31" s="119"/>
+      <c r="J31" s="116"/>
+      <c r="K31" s="116">
+        <f>0.13*H30*4169.92</f>
         <v>681.53599512343794</v>
       </c>
-      <c r="L28" s="25"/>
-    </row>
-    <row r="29" spans="2:14" s="94" customFormat="1">
-      <c r="B29" s="84"/>
-      <c r="C29" s="19" t="s">
+      <c r="L31" s="25"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" s="147"/>
+      <c r="C32" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="73">
-        <f>0.13*H27*1414.16</f>
+      <c r="D32" s="119"/>
+      <c r="E32" s="116"/>
+      <c r="F32" s="116"/>
+      <c r="G32" s="116"/>
+      <c r="H32" s="116"/>
+      <c r="I32" s="119"/>
+      <c r="J32" s="116"/>
+      <c r="K32" s="116">
+        <f>0.13*H30*1414.16</f>
         <v>231.13175861017984</v>
       </c>
-      <c r="L29" s="25"/>
-    </row>
-    <row r="30" spans="2:14" s="94" customFormat="1">
-      <c r="B30" s="84"/>
-      <c r="C30" s="19" t="s">
+      <c r="L32" s="25"/>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33" s="147"/>
+      <c r="C33" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="24"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73">
-        <f>0.13*H27*(1652.5+737.97+349.56)</f>
+      <c r="D33" s="119"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="116"/>
+      <c r="G33" s="116"/>
+      <c r="H33" s="116"/>
+      <c r="I33" s="119"/>
+      <c r="J33" s="116"/>
+      <c r="K33" s="116">
+        <f>0.13*H30*(1652.5+737.97+349.56)</f>
         <v>447.83330920451084</v>
       </c>
-      <c r="L30" s="25"/>
-    </row>
-    <row r="31" spans="2:14" s="94" customFormat="1" ht="18.600000000000001">
-      <c r="B31" s="84"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="73"/>
-      <c r="K31" s="73"/>
-      <c r="L31" s="25"/>
-    </row>
-    <row r="32" spans="2:14" ht="35.1" customHeight="1">
-      <c r="B32" s="153">
+      <c r="L33" s="25"/>
+    </row>
+    <row r="34" spans="2:12" ht="18.75">
+      <c r="B34" s="80"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="73"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="25"/>
+    </row>
+    <row r="35" spans="2:12" ht="35.1" customHeight="1">
+      <c r="B35" s="146">
         <v>4</v>
       </c>
-      <c r="C32" s="79" t="s">
+      <c r="C35" s="148" t="s">
         <v>80</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="154"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="25"/>
-    </row>
-    <row r="33" spans="2:12" s="94" customFormat="1">
-      <c r="B33" s="153"/>
-      <c r="C33" s="155" t="s">
+      <c r="D35" s="119"/>
+      <c r="E35" s="116"/>
+      <c r="F35" s="116"/>
+      <c r="G35" s="116"/>
+      <c r="H35" s="116"/>
+      <c r="I35" s="119"/>
+      <c r="J35" s="120"/>
+      <c r="K35" s="116"/>
+      <c r="L35" s="25"/>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" s="146"/>
+      <c r="C36" s="160" t="s">
         <v>136</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D36" s="119">
         <v>33</v>
       </c>
-      <c r="E33" s="70">
+      <c r="E36" s="116">
         <f>(2+4.833+16.17+4.833+2)/3.281</f>
         <v>9.0935690338311481</v>
       </c>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70">
+      <c r="F36" s="116"/>
+      <c r="G36" s="116">
         <f>10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
-      <c r="H33" s="70">
-        <f>D33*E33*G33</f>
+      <c r="H36" s="116">
+        <f>D36*E36*G36</f>
         <v>185.23936920767153</v>
       </c>
-      <c r="I33" s="24"/>
-      <c r="J33" s="154"/>
-      <c r="K33" s="73"/>
-      <c r="L33" s="25"/>
-    </row>
-    <row r="34" spans="2:12">
-      <c r="B34" s="153"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="24">
+      <c r="I36" s="119"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="116"/>
+      <c r="L36" s="25"/>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37" s="146"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="119">
         <v>32</v>
       </c>
-      <c r="E34" s="70">
+      <c r="E37" s="116">
         <f>(2+4.42+15.667+4.42+2)/3.281</f>
         <v>8.6885096007314839</v>
       </c>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70">
+      <c r="F37" s="116"/>
+      <c r="G37" s="116">
         <f>10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
-      <c r="H34" s="70">
-        <f t="shared" ref="H34" si="0">D34*E34*G34</f>
+      <c r="H37" s="116">
+        <f t="shared" ref="H37" si="1">D37*E37*G37</f>
         <v>171.62488100210336</v>
       </c>
-      <c r="I34" s="24"/>
-      <c r="J34" s="154"/>
-      <c r="K34" s="73"/>
-      <c r="L34" s="25"/>
-    </row>
-    <row r="35" spans="2:12" s="94" customFormat="1">
-      <c r="B35" s="153"/>
-      <c r="C35" s="155" t="s">
+      <c r="I37" s="119"/>
+      <c r="J37" s="120"/>
+      <c r="K37" s="116"/>
+      <c r="L37" s="25"/>
+    </row>
+    <row r="38" spans="2:12">
+      <c r="B38" s="146"/>
+      <c r="C38" s="160" t="s">
         <v>136</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D38" s="119">
         <v>23</v>
       </c>
-      <c r="E35" s="70">
+      <c r="E38" s="116">
         <f>(2+4.833+10.75+4.833+2)/3.281</f>
         <v>7.4416336482779624</v>
       </c>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70">
+      <c r="F38" s="116"/>
+      <c r="G38" s="116">
         <f>10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
-      <c r="H35" s="70">
-        <f>D35*E35*G35</f>
+      <c r="H38" s="116">
+        <f>D38*E38*G38</f>
         <v>105.65282340147724</v>
       </c>
-      <c r="I35" s="24"/>
-      <c r="J35" s="154"/>
-      <c r="K35" s="73"/>
-      <c r="L35" s="25"/>
-    </row>
-    <row r="36" spans="2:12" s="94" customFormat="1">
-      <c r="B36" s="153"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="24">
+      <c r="I38" s="119"/>
+      <c r="J38" s="120"/>
+      <c r="K38" s="116"/>
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="B39" s="146"/>
+      <c r="C39" s="118"/>
+      <c r="D39" s="119">
         <v>22</v>
       </c>
-      <c r="E36" s="70">
+      <c r="E39" s="116">
         <f>(2+4.42+10.25+4.42+2)/3.281</f>
         <v>7.0374885705577572</v>
       </c>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70">
+      <c r="F39" s="116"/>
+      <c r="G39" s="116">
         <f>10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
-      <c r="H36" s="70">
-        <f t="shared" ref="H36" si="1">D36*E36*G36</f>
+      <c r="H39" s="116">
+        <f t="shared" ref="H39" si="2">D39*E39*G39</f>
         <v>95.570832439673239</v>
       </c>
-      <c r="I36" s="24"/>
-      <c r="J36" s="154"/>
-      <c r="K36" s="73"/>
-      <c r="L36" s="25"/>
-    </row>
-    <row r="37" spans="2:12" s="94" customFormat="1">
-      <c r="B37" s="153"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="24">
+      <c r="I39" s="119"/>
+      <c r="J39" s="120"/>
+      <c r="K39" s="116"/>
+      <c r="L39" s="25"/>
+    </row>
+    <row r="40" spans="2:12">
+      <c r="B40" s="146"/>
+      <c r="C40" s="159"/>
+      <c r="D40" s="119">
         <v>10</v>
       </c>
-      <c r="E37" s="70">
+      <c r="E40" s="116">
         <f>(16.17+10.75+16.17+10.75)/3.281</f>
         <v>16.409631209996952</v>
       </c>
-      <c r="F37" s="70"/>
-      <c r="G37" s="70">
+      <c r="F40" s="116"/>
+      <c r="G40" s="116">
         <f>8*8/162</f>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H37" s="70">
-        <f>D37*E37*G37</f>
+      <c r="H40" s="116">
+        <f>D40*E40*G40</f>
         <v>64.828172681469425</v>
       </c>
-      <c r="I37" s="24"/>
-      <c r="J37" s="154"/>
-      <c r="K37" s="73"/>
-      <c r="L37" s="25"/>
-    </row>
-    <row r="38" spans="2:12" s="94" customFormat="1">
-      <c r="B38" s="153"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="24">
+      <c r="I40" s="119"/>
+      <c r="J40" s="120"/>
+      <c r="K40" s="116"/>
+      <c r="L40" s="25"/>
+    </row>
+    <row r="41" spans="2:12">
+      <c r="B41" s="146"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="119">
         <v>9</v>
       </c>
-      <c r="E38" s="70">
+      <c r="E41" s="116">
         <f>(15.667+10.25+15.667+10.25)/3.281</f>
         <v>15.798232246266382</v>
       </c>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70">
+      <c r="F41" s="116"/>
+      <c r="G41" s="116">
         <f>8*8/162</f>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H38" s="70">
-        <f>D38*E38*G38</f>
+      <c r="H41" s="116">
+        <f>D41*E41*G41</f>
         <v>56.171492431169355</v>
       </c>
-      <c r="I38" s="24"/>
-      <c r="J38" s="154"/>
-      <c r="K38" s="73"/>
-      <c r="L38" s="25"/>
-    </row>
-    <row r="39" spans="2:12" s="94" customFormat="1">
-      <c r="B39" s="153"/>
-      <c r="C39" s="155" t="s">
+      <c r="I41" s="119"/>
+      <c r="J41" s="120"/>
+      <c r="K41" s="116"/>
+      <c r="L41" s="25"/>
+    </row>
+    <row r="42" spans="2:12">
+      <c r="B42" s="146"/>
+      <c r="C42" s="160" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="24">
-        <f>2*TRUNC((E40/0.15),0)</f>
+      <c r="D42" s="119">
+        <f>2*TRUNC((E43/0.15),0)</f>
         <v>42</v>
       </c>
-      <c r="E39" s="70">
+      <c r="E42" s="116">
         <f>(16.17/3.281)</f>
         <v>4.928375495275831</v>
       </c>
-      <c r="F39" s="70"/>
-      <c r="G39" s="70">
-        <f t="shared" ref="G39:G41" si="2">8*8/162</f>
+      <c r="F42" s="116"/>
+      <c r="G42" s="116">
+        <f t="shared" ref="G42:G44" si="3">8*8/162</f>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H39" s="70">
-        <f t="shared" ref="H39:H40" si="3">D39*E39*G39</f>
+      <c r="H42" s="116">
+        <f t="shared" ref="H42:H43" si="4">D42*E42*G42</f>
         <v>81.774526736428598</v>
       </c>
-      <c r="I39" s="24"/>
-      <c r="J39" s="154"/>
-      <c r="K39" s="73"/>
-      <c r="L39" s="25"/>
-    </row>
-    <row r="40" spans="2:12" s="94" customFormat="1">
-      <c r="B40" s="153"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="24">
-        <f>2*TRUNC((E39/0.15),0)</f>
+      <c r="I42" s="119"/>
+      <c r="J42" s="120"/>
+      <c r="K42" s="116"/>
+      <c r="L42" s="25"/>
+    </row>
+    <row r="43" spans="2:12">
+      <c r="B43" s="146"/>
+      <c r="C43" s="118"/>
+      <c r="D43" s="119">
+        <f>2*TRUNC((E42/0.15),0)</f>
         <v>64</v>
       </c>
-      <c r="E40" s="70">
+      <c r="E43" s="116">
         <f>10.75/3.281</f>
         <v>3.2764401097226452</v>
       </c>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70">
-        <f t="shared" si="2"/>
+      <c r="F43" s="116"/>
+      <c r="G43" s="116">
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H40" s="70">
-        <f t="shared" si="3"/>
+      <c r="H43" s="116">
+        <f t="shared" si="4"/>
         <v>82.841349934715765</v>
       </c>
-      <c r="I40" s="24"/>
-      <c r="J40" s="154"/>
-      <c r="K40" s="73"/>
-      <c r="L40" s="25"/>
-    </row>
-    <row r="41" spans="2:12" s="94" customFormat="1">
-      <c r="B41" s="153"/>
-      <c r="C41" s="155" t="s">
+      <c r="I43" s="119"/>
+      <c r="J43" s="120"/>
+      <c r="K43" s="116"/>
+      <c r="L43" s="25"/>
+    </row>
+    <row r="44" spans="2:12">
+      <c r="B44" s="146"/>
+      <c r="C44" s="160" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="24">
-        <f>D34+D34+D36+D36-2-2</f>
+      <c r="D44" s="119">
+        <f>D37+D37+D39+D39-2-2</f>
         <v>104</v>
       </c>
-      <c r="E41" s="70">
+      <c r="E44" s="116">
         <f>(7+10+7)/12/3.281</f>
         <v>0.6095702529716549</v>
       </c>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70">
-        <f t="shared" si="2"/>
+      <c r="F44" s="116"/>
+      <c r="G44" s="116">
+        <f t="shared" si="3"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H41" s="70">
-        <f t="shared" ref="H41" si="4">D41*E41*G41</f>
+      <c r="H44" s="116">
+        <f t="shared" ref="H44" si="5">D44*E44*G44</f>
         <v>25.045059282588486</v>
       </c>
-      <c r="I41" s="24"/>
-      <c r="J41" s="154"/>
-      <c r="K41" s="73"/>
-      <c r="L41" s="25"/>
-    </row>
-    <row r="42" spans="2:12">
-      <c r="B42" s="153"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="156">
-        <f>SUM(H33:H41)</f>
+      <c r="I44" s="119"/>
+      <c r="J44" s="120"/>
+      <c r="K44" s="116"/>
+      <c r="L44" s="25"/>
+    </row>
+    <row r="45" spans="2:12">
+      <c r="B45" s="146"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="119"/>
+      <c r="E45" s="116"/>
+      <c r="F45" s="116"/>
+      <c r="G45" s="116"/>
+      <c r="H45" s="116">
+        <f>SUM(H36:H44)</f>
         <v>868.74850711729709</v>
       </c>
-      <c r="I42" s="24" t="s">
+      <c r="I45" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="154">
+      <c r="J45" s="120">
         <f>132360/1000</f>
         <v>132.36000000000001</v>
       </c>
-      <c r="K42" s="73">
-        <f>H42*J42</f>
+      <c r="K45" s="116">
+        <f>H45*J45</f>
         <v>114987.55240204546</v>
       </c>
-      <c r="L42" s="25"/>
-    </row>
-    <row r="43" spans="2:12">
-      <c r="B43" s="153"/>
-      <c r="C43" s="158" t="s">
+      <c r="L45" s="25"/>
+    </row>
+    <row r="46" spans="2:12">
+      <c r="B46" s="146"/>
+      <c r="C46" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="159"/>
-      <c r="E43" s="156"/>
-      <c r="F43" s="156"/>
-      <c r="G43" s="156"/>
-      <c r="H43" s="156"/>
-      <c r="I43" s="159"/>
-      <c r="J43" s="160"/>
-      <c r="K43" s="156">
-        <f>0.13*H42*106200/1000</f>
+      <c r="D46" s="119"/>
+      <c r="E46" s="116"/>
+      <c r="F46" s="116"/>
+      <c r="G46" s="116"/>
+      <c r="H46" s="116"/>
+      <c r="I46" s="119"/>
+      <c r="J46" s="120"/>
+      <c r="K46" s="116">
+        <f>0.13*H45*106200/1000</f>
         <v>11993.941889261405</v>
       </c>
-      <c r="L43" s="25"/>
-    </row>
-    <row r="44" spans="2:12" s="94" customFormat="1">
-      <c r="B44" s="153"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="70"/>
-      <c r="H44" s="70"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="154"/>
-      <c r="K44" s="157"/>
-      <c r="L44" s="25"/>
-    </row>
-    <row r="45" spans="2:12" s="94" customFormat="1" ht="37.200000000000003">
-      <c r="B45" s="153">
+      <c r="L46" s="25"/>
+    </row>
+    <row r="47" spans="2:12">
+      <c r="B47" s="114"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="115"/>
+      <c r="K47" s="117"/>
+      <c r="L47" s="25"/>
+    </row>
+    <row r="48" spans="2:12" ht="37.5">
+      <c r="B48" s="146">
         <v>5</v>
       </c>
-      <c r="C45" s="79" t="s">
+      <c r="C48" s="148" t="s">
         <v>138</v>
       </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="70"/>
-      <c r="H45" s="70"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="154"/>
-      <c r="K45" s="157"/>
-      <c r="L45" s="25"/>
-    </row>
-    <row r="46" spans="2:12" s="94" customFormat="1">
-      <c r="B46" s="153"/>
-      <c r="C46" s="155" t="s">
+      <c r="D48" s="119"/>
+      <c r="E48" s="116"/>
+      <c r="F48" s="116"/>
+      <c r="G48" s="116"/>
+      <c r="H48" s="116"/>
+      <c r="I48" s="119"/>
+      <c r="J48" s="120"/>
+      <c r="K48" s="116"/>
+      <c r="L48" s="25"/>
+    </row>
+    <row r="49" spans="2:12">
+      <c r="B49" s="146"/>
+      <c r="C49" s="160" t="s">
         <v>139</v>
       </c>
-      <c r="D46" s="24">
+      <c r="D49" s="119">
         <v>1</v>
       </c>
-      <c r="E46" s="70">
+      <c r="E49" s="116">
         <f>((16.42+11)*2)/3.281</f>
         <v>16.714416336482781</v>
       </c>
-      <c r="F46" s="70"/>
-      <c r="G46" s="70">
+      <c r="F49" s="116"/>
+      <c r="G49" s="116">
         <f>4.583/3.281</f>
         <v>1.3968302346845474</v>
       </c>
-      <c r="H46" s="70">
-        <f>PRODUCT(D46:G46)</f>
+      <c r="H49" s="116">
+        <f>PRODUCT(D49:G49)</f>
         <v>23.347202093904475</v>
       </c>
-      <c r="I46" s="24"/>
-      <c r="J46" s="154"/>
-      <c r="K46" s="157"/>
-      <c r="L46" s="25"/>
-    </row>
-    <row r="47" spans="2:12" s="94" customFormat="1">
-      <c r="B47" s="153"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="24">
+      <c r="I49" s="119"/>
+      <c r="J49" s="120"/>
+      <c r="K49" s="116"/>
+      <c r="L49" s="25"/>
+    </row>
+    <row r="50" spans="2:12">
+      <c r="B50" s="146"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="119">
         <v>1</v>
       </c>
-      <c r="E47" s="70">
+      <c r="E50" s="116">
         <f>((15.42+10)*2)/3.281</f>
         <v>15.49527583053947</v>
       </c>
-      <c r="F47" s="70"/>
-      <c r="G47" s="70">
+      <c r="F50" s="116"/>
+      <c r="G50" s="116">
         <f>4.17/3.281</f>
         <v>1.2709539774459007</v>
       </c>
-      <c r="H47" s="70">
-        <f>PRODUCT(D47:G47)</f>
+      <c r="H50" s="116">
+        <f>PRODUCT(D50:G50)</f>
         <v>19.693782448445472</v>
       </c>
-      <c r="I47" s="24"/>
-      <c r="J47" s="154"/>
-      <c r="K47" s="157"/>
-      <c r="L47" s="25"/>
-    </row>
-    <row r="48" spans="2:12" s="94" customFormat="1">
-      <c r="B48" s="153"/>
-      <c r="C48" s="155" t="s">
+      <c r="I50" s="119"/>
+      <c r="J50" s="120"/>
+      <c r="K50" s="116"/>
+      <c r="L50" s="25"/>
+    </row>
+    <row r="51" spans="2:12">
+      <c r="B51" s="146"/>
+      <c r="C51" s="160" t="s">
         <v>140</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D51" s="119">
         <v>1</v>
       </c>
-      <c r="E48" s="70">
+      <c r="E51" s="116">
         <f>(15.42/3.281)</f>
         <v>4.6997866504114594</v>
       </c>
-      <c r="F48" s="70">
+      <c r="F51" s="116">
         <f>10/3.281</f>
         <v>3.047851264858275</v>
       </c>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70">
-        <f>PRODUCT(D48:G48)</f>
+      <c r="G51" s="116"/>
+      <c r="H51" s="116">
+        <f>PRODUCT(D51:G51)</f>
         <v>14.324250687020601</v>
       </c>
-      <c r="I48" s="24"/>
-      <c r="J48" s="154"/>
-      <c r="K48" s="157"/>
-      <c r="L48" s="25"/>
-    </row>
-    <row r="49" spans="2:12" s="94" customFormat="1">
-      <c r="B49" s="153"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="70">
-        <f>SUM(H46:H48)</f>
+      <c r="I51" s="119"/>
+      <c r="J51" s="120"/>
+      <c r="K51" s="116"/>
+      <c r="L51" s="25"/>
+    </row>
+    <row r="52" spans="2:12">
+      <c r="B52" s="146"/>
+      <c r="C52" s="118"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="116"/>
+      <c r="F52" s="116"/>
+      <c r="G52" s="116"/>
+      <c r="H52" s="116">
+        <f>SUM(H49:H51)</f>
         <v>57.365235229370548</v>
       </c>
-      <c r="I49" s="24" t="s">
+      <c r="I52" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="J49" s="154">
+      <c r="J52" s="120">
         <v>922.71</v>
       </c>
-      <c r="K49" s="73">
-        <f>H49*J49</f>
+      <c r="K52" s="116">
+        <f>H52*J52</f>
         <v>52931.476198492499</v>
       </c>
-      <c r="L49" s="25"/>
-    </row>
-    <row r="50" spans="2:12" s="94" customFormat="1">
-      <c r="B50" s="153"/>
-      <c r="C50" s="158" t="s">
+      <c r="L52" s="25"/>
+    </row>
+    <row r="53" spans="2:12">
+      <c r="B53" s="146"/>
+      <c r="C53" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="D50" s="159"/>
-      <c r="E50" s="156"/>
-      <c r="F50" s="156"/>
-      <c r="G50" s="156"/>
-      <c r="H50" s="156"/>
-      <c r="I50" s="159"/>
-      <c r="J50" s="160"/>
-      <c r="K50" s="156">
-        <f>0.13*H49*46827.87/100</f>
+      <c r="D53" s="119"/>
+      <c r="E53" s="116"/>
+      <c r="F53" s="116"/>
+      <c r="G53" s="116"/>
+      <c r="H53" s="116"/>
+      <c r="I53" s="119"/>
+      <c r="J53" s="120"/>
+      <c r="K53" s="116">
+        <f>0.13*H52*46827.87/100</f>
         <v>3492.1793111924994</v>
       </c>
-      <c r="L50" s="25"/>
-    </row>
-    <row r="51" spans="2:12" s="94" customFormat="1">
-      <c r="B51" s="153"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="70"/>
-      <c r="F51" s="70"/>
-      <c r="G51" s="70"/>
-      <c r="H51" s="70"/>
-      <c r="I51" s="24"/>
-      <c r="J51" s="154"/>
-      <c r="K51" s="157"/>
-      <c r="L51" s="25"/>
-    </row>
-    <row r="52" spans="2:12" ht="55.8">
-      <c r="B52" s="84">
+      <c r="L53" s="25"/>
+    </row>
+    <row r="54" spans="2:12">
+      <c r="B54" s="114"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="115"/>
+      <c r="K54" s="117"/>
+      <c r="L54" s="25"/>
+    </row>
+    <row r="55" spans="2:12" ht="56.25">
+      <c r="B55" s="147">
         <v>6</v>
       </c>
-      <c r="C52" s="79" t="s">
+      <c r="C55" s="148" t="s">
         <v>145</v>
       </c>
-      <c r="D52" s="24"/>
-      <c r="E52" s="70"/>
-      <c r="F52" s="70"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="70"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="73"/>
-      <c r="K52" s="70"/>
-      <c r="L52" s="25"/>
-    </row>
-    <row r="53" spans="2:12" s="94" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B53" s="84"/>
-      <c r="C53" s="155" t="s">
+      <c r="D55" s="119"/>
+      <c r="E55" s="116"/>
+      <c r="F55" s="116"/>
+      <c r="G55" s="116"/>
+      <c r="H55" s="116"/>
+      <c r="I55" s="119"/>
+      <c r="J55" s="116"/>
+      <c r="K55" s="116"/>
+      <c r="L55" s="25"/>
+    </row>
+    <row r="56" spans="2:12" ht="35.1" customHeight="1">
+      <c r="B56" s="147"/>
+      <c r="C56" s="160" t="s">
         <v>143</v>
       </c>
-      <c r="D53" s="24">
+      <c r="D56" s="119">
         <v>2</v>
       </c>
-      <c r="E53" s="70">
-        <f>E22</f>
+      <c r="E56" s="116">
+        <f>E25</f>
         <v>5</v>
       </c>
-      <c r="F53" s="70">
-        <f>F22</f>
+      <c r="F56" s="116">
+        <f>F25</f>
         <v>3.3526363913441024</v>
       </c>
-      <c r="G53" s="70">
+      <c r="G56" s="116">
         <f>0.42/3.281</f>
         <v>0.12800975312404753</v>
       </c>
-      <c r="H53" s="70">
-        <f>D53*E53*F53*G53</f>
+      <c r="H56" s="116">
+        <f>D56*E56*F56*G56</f>
         <v>4.2917015677065615</v>
       </c>
-      <c r="I53" s="24"/>
-      <c r="J53" s="73"/>
-      <c r="K53" s="70"/>
-      <c r="L53" s="25"/>
-    </row>
-    <row r="54" spans="2:12">
-      <c r="B54" s="84"/>
-      <c r="C54" s="155" t="s">
+      <c r="I56" s="119"/>
+      <c r="J56" s="116"/>
+      <c r="K56" s="116"/>
+      <c r="L56" s="25"/>
+    </row>
+    <row r="57" spans="2:12">
+      <c r="B57" s="147"/>
+      <c r="C57" s="160" t="s">
         <v>142</v>
       </c>
-      <c r="D54" s="24">
+      <c r="D57" s="119">
         <v>2</v>
       </c>
-      <c r="E54" s="70">
-        <f>E65</f>
-        <v>5</v>
-      </c>
-      <c r="F54" s="70">
+      <c r="E57" s="116">
+        <f>E67</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="116">
         <v>0.15</v>
       </c>
-      <c r="G54" s="70">
+      <c r="G57" s="116">
         <f>4.17/3.281</f>
         <v>1.2709539774459007</v>
       </c>
-      <c r="H54" s="70">
-        <f>D54*E54*F54*G54</f>
-        <v>1.906430966168851</v>
-      </c>
-      <c r="I54" s="24"/>
-      <c r="J54" s="73"/>
-      <c r="K54" s="70"/>
-      <c r="L54" s="25"/>
-    </row>
-    <row r="55" spans="2:12">
-      <c r="B55" s="84"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="24">
+      <c r="H57" s="116">
+        <f>D57*E57*F57*G57</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="119"/>
+      <c r="J57" s="116"/>
+      <c r="K57" s="116"/>
+      <c r="L57" s="25"/>
+    </row>
+    <row r="58" spans="2:12">
+      <c r="B58" s="147"/>
+      <c r="C58" s="159"/>
+      <c r="D58" s="119">
         <v>2</v>
       </c>
-      <c r="E55" s="70">
+      <c r="E58" s="116">
         <f>10/3.281</f>
         <v>3.047851264858275</v>
       </c>
-      <c r="F55" s="70">
+      <c r="F58" s="116">
         <v>0.15</v>
       </c>
-      <c r="G55" s="70">
+      <c r="G58" s="116">
         <f>4.17/3.281</f>
         <v>1.2709539774459007</v>
       </c>
-      <c r="H55" s="70">
-        <f>D55*E55*F55*G55</f>
+      <c r="H58" s="116">
+        <f>D58*E58*F58*G58</f>
         <v>1.1621036063205432</v>
       </c>
-      <c r="I55" s="24"/>
-      <c r="J55" s="73"/>
-      <c r="K55" s="70"/>
-      <c r="L55" s="25"/>
-    </row>
-    <row r="56" spans="2:12" s="94" customFormat="1">
-      <c r="B56" s="84"/>
-      <c r="C56" s="155" t="s">
+      <c r="I58" s="119"/>
+      <c r="J58" s="116"/>
+      <c r="K58" s="116"/>
+      <c r="L58" s="25"/>
+    </row>
+    <row r="59" spans="2:12">
+      <c r="B59" s="147"/>
+      <c r="C59" s="160" t="s">
         <v>141</v>
       </c>
-      <c r="D56" s="24">
+      <c r="D59" s="119">
         <v>0.5</v>
       </c>
-      <c r="E56" s="70">
+      <c r="E59" s="116">
         <f>(14.25*2+8.833*2)/3.281</f>
         <v>14.070710149344711</v>
       </c>
-      <c r="F56" s="70">
+      <c r="F59" s="116">
         <f>0.583/3.281</f>
         <v>0.1776897287412374</v>
       </c>
-      <c r="G56" s="70">
+      <c r="G59" s="116">
         <f>0.583/3.281</f>
         <v>0.1776897287412374</v>
       </c>
-      <c r="H56" s="70">
-        <f>D56*E56*F56*G56</f>
+      <c r="H59" s="116">
+        <f>D59*E59*F59*G59</f>
         <v>0.222131766290218</v>
       </c>
-      <c r="I56" s="24"/>
-      <c r="J56" s="73"/>
-      <c r="K56" s="70"/>
-      <c r="L56" s="25"/>
-    </row>
-    <row r="57" spans="2:12">
-      <c r="B57" s="84"/>
-      <c r="C57" s="155"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="70"/>
-      <c r="F57" s="70" t="s">
+      <c r="I59" s="119"/>
+      <c r="J59" s="116"/>
+      <c r="K59" s="116"/>
+      <c r="L59" s="25"/>
+    </row>
+    <row r="60" spans="2:12">
+      <c r="B60" s="147"/>
+      <c r="C60" s="160"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="G57" s="70"/>
-      <c r="H57" s="70">
-        <f>SUM(H53:H56)</f>
-        <v>7.5823679064861738</v>
-      </c>
-      <c r="I57" s="24" t="s">
+      <c r="G60" s="116"/>
+      <c r="H60" s="116">
+        <f>SUM(H56:H59)</f>
+        <v>5.6759369403173228</v>
+      </c>
+      <c r="I60" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="J57" s="73">
-        <f>'[1]Table of Content 2'!$H$67</f>
-        <v>17107.900000000001</v>
-      </c>
-      <c r="K57" s="73">
-        <f>H57*J57</f>
-        <v>129718.39190737483</v>
-      </c>
-      <c r="L57" s="25"/>
-    </row>
-    <row r="58" spans="2:12">
-      <c r="B58" s="84"/>
-      <c r="C58" s="19" t="s">
+      <c r="J60" s="116">
+        <v>13957.29</v>
+      </c>
+      <c r="K60" s="116">
+        <f>H60*J60</f>
+        <v>79220.697897721577</v>
+      </c>
+      <c r="L60" s="25"/>
+    </row>
+    <row r="61" spans="2:12">
+      <c r="B61" s="147"/>
+      <c r="C61" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="D58" s="24"/>
-      <c r="E58" s="70"/>
-      <c r="F58" s="70"/>
-      <c r="G58" s="70"/>
-      <c r="H58" s="70"/>
-      <c r="I58" s="24"/>
-      <c r="J58" s="73"/>
-      <c r="K58" s="73">
-        <f>'[1]Update Descrip'!$G$676*H57*0.13</f>
-        <v>5689.899865442103</v>
-      </c>
-      <c r="L58" s="25"/>
-    </row>
-    <row r="59" spans="2:12">
-      <c r="B59" s="84"/>
-      <c r="C59" s="19" t="s">
+      <c r="D61" s="119"/>
+      <c r="E61" s="116"/>
+      <c r="F61" s="116"/>
+      <c r="G61" s="116"/>
+      <c r="H61" s="116"/>
+      <c r="I61" s="119"/>
+      <c r="J61" s="116"/>
+      <c r="K61" s="116">
+        <f>0.13*H60*5212.4</f>
+        <v>3846.0829820023018</v>
+      </c>
+      <c r="L61" s="25"/>
+    </row>
+    <row r="62" spans="2:12">
+      <c r="B62" s="147"/>
+      <c r="C62" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="D59" s="24"/>
-      <c r="E59" s="70"/>
-      <c r="F59" s="70"/>
-      <c r="G59" s="70"/>
-      <c r="H59" s="70"/>
-      <c r="I59" s="24"/>
-      <c r="J59" s="73"/>
-      <c r="K59" s="73">
-        <f>'[1]Update Descrip'!$G$679*H57*0.13</f>
-        <v>1050.2421193320972</v>
-      </c>
-      <c r="L59" s="25"/>
-    </row>
-    <row r="60" spans="2:12">
-      <c r="B60" s="84"/>
-      <c r="C60" s="19" t="s">
+      <c r="D62" s="119"/>
+      <c r="E62" s="116"/>
+      <c r="F62" s="116"/>
+      <c r="G62" s="116"/>
+      <c r="H62" s="116"/>
+      <c r="I62" s="119"/>
+      <c r="J62" s="116"/>
+      <c r="K62" s="116">
+        <f>0.13*H60*1350.6</f>
+        <v>996.56965610703492</v>
+      </c>
+      <c r="L62" s="25"/>
+    </row>
+    <row r="63" spans="2:12">
+      <c r="B63" s="147"/>
+      <c r="C63" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="D60" s="24"/>
-      <c r="E60" s="70"/>
-      <c r="F60" s="70"/>
-      <c r="G60" s="70"/>
-      <c r="H60" s="70"/>
-      <c r="I60" s="24"/>
-      <c r="J60" s="73"/>
-      <c r="K60" s="73">
-        <f>('[1]Update Descrip'!$G$677+'[1]Update Descrip'!$G$678)*H57*0.13</f>
-        <v>2911.8104946836561</v>
-      </c>
-      <c r="L60" s="25"/>
-    </row>
-    <row r="61" spans="2:12">
-      <c r="B61" s="84"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="71"/>
-      <c r="H61" s="70"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="73"/>
-      <c r="K61" s="73"/>
-      <c r="L61" s="25"/>
-    </row>
-    <row r="62" spans="2:12" s="94" customFormat="1">
-      <c r="B62" s="153"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="70"/>
-      <c r="F62" s="70"/>
-      <c r="G62" s="70"/>
-      <c r="H62" s="70"/>
-      <c r="I62" s="24"/>
-      <c r="J62" s="154"/>
-      <c r="K62" s="157"/>
-      <c r="L62" s="25"/>
-    </row>
-    <row r="63" spans="2:12" s="94" customFormat="1">
-      <c r="B63" s="153"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="70"/>
-      <c r="F63" s="70"/>
-      <c r="G63" s="70"/>
-      <c r="H63" s="70"/>
-      <c r="I63" s="24"/>
-      <c r="J63" s="154"/>
-      <c r="K63" s="157"/>
+      <c r="D63" s="119"/>
+      <c r="E63" s="116"/>
+      <c r="F63" s="116"/>
+      <c r="G63" s="116"/>
+      <c r="H63" s="116"/>
+      <c r="I63" s="119"/>
+      <c r="J63" s="116"/>
+      <c r="K63" s="116">
+        <f>0.13*H60*(1912.03+921.59)</f>
+        <v>2090.8482962668563</v>
+      </c>
       <c r="L63" s="25"/>
     </row>
-    <row r="64" spans="2:12" s="94" customFormat="1">
-      <c r="B64" s="153"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="70"/>
-      <c r="F64" s="70"/>
-      <c r="G64" s="70"/>
-      <c r="H64" s="70"/>
-      <c r="I64" s="24"/>
-      <c r="J64" s="154"/>
-      <c r="K64" s="157"/>
+    <row r="64" spans="2:12">
+      <c r="B64" s="147"/>
+      <c r="C64" s="118" t="s">
+        <v>146</v>
+      </c>
+      <c r="D64" s="119"/>
+      <c r="E64" s="116"/>
+      <c r="F64" s="116"/>
+      <c r="G64" s="116"/>
+      <c r="H64" s="116"/>
+      <c r="I64" s="119"/>
+      <c r="J64" s="116"/>
+      <c r="K64" s="116">
+        <f>0.13*H60*392.92</f>
+        <v>289.92458853663277</v>
+      </c>
       <c r="L64" s="25"/>
     </row>
-    <row r="65" spans="2:12" s="94" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B65" s="153">
+    <row r="65" spans="2:12">
+      <c r="B65" s="146"/>
+      <c r="C65" s="118" t="s">
+        <v>147</v>
+      </c>
+      <c r="D65" s="119"/>
+      <c r="E65" s="116"/>
+      <c r="F65" s="116"/>
+      <c r="G65" s="116"/>
+      <c r="H65" s="116"/>
+      <c r="I65" s="119"/>
+      <c r="J65" s="116"/>
+      <c r="K65" s="116">
+        <f>0.13*H60*14.15</f>
+        <v>10.440886001713716</v>
+      </c>
+      <c r="L65" s="25"/>
+    </row>
+    <row r="66" spans="2:12">
+      <c r="B66" s="114"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="70"/>
+      <c r="F66" s="70"/>
+      <c r="G66" s="70"/>
+      <c r="H66" s="70"/>
+      <c r="I66" s="24"/>
+      <c r="J66" s="115"/>
+      <c r="K66" s="117"/>
+      <c r="L66" s="25"/>
+    </row>
+    <row r="67" spans="2:12" ht="35.1" customHeight="1">
+      <c r="B67" s="146">
         <v>3</v>
       </c>
-      <c r="C65" s="79" t="s">
-        <v>75</v>
-      </c>
-      <c r="D65" s="24">
-        <v>2</v>
-      </c>
-      <c r="E65" s="70">
-        <f>E12</f>
-        <v>5</v>
-      </c>
-      <c r="F65" s="70">
-        <v>0.1</v>
-      </c>
-      <c r="G65" s="70">
-        <v>0.9</v>
-      </c>
-      <c r="H65" s="70">
-        <f>D65*E65*F65*G65</f>
-        <v>0.9</v>
-      </c>
-      <c r="I65" s="24"/>
-      <c r="J65" s="154"/>
-      <c r="K65" s="73"/>
-      <c r="L65" s="25"/>
-    </row>
-    <row r="66" spans="2:12" ht="18.600000000000001">
-      <c r="B66" s="84"/>
-      <c r="C66" s="149"/>
-      <c r="D66" s="150">
-        <v>2</v>
-      </c>
-      <c r="E66" s="151">
-        <f>E13</f>
-        <v>2.8926363913441024</v>
-      </c>
-      <c r="F66" s="151">
-        <v>0.1</v>
-      </c>
-      <c r="G66" s="151">
-        <v>0.9</v>
-      </c>
-      <c r="H66" s="151">
-        <f>D66*E66*F66*G66</f>
-        <v>0.52067455044193856</v>
-      </c>
-      <c r="I66" s="152"/>
-      <c r="J66" s="72"/>
-      <c r="K66" s="72"/>
-      <c r="L66" s="25"/>
-    </row>
-    <row r="67" spans="2:12" ht="18.600000000000001">
-      <c r="B67" s="84"/>
-      <c r="C67" s="79"/>
-      <c r="D67" s="24">
+      <c r="C67" s="148" t="s">
+        <v>150</v>
+      </c>
+      <c r="D67" s="119"/>
+      <c r="E67" s="116"/>
+      <c r="F67" s="116"/>
+      <c r="G67" s="116"/>
+      <c r="H67" s="116"/>
+      <c r="I67" s="119"/>
+      <c r="J67" s="120"/>
+      <c r="K67" s="116"/>
+      <c r="L67" s="25"/>
+    </row>
+    <row r="68" spans="2:12">
+      <c r="B68" s="147"/>
+      <c r="C68" s="118" t="str">
+        <f>C15</f>
+        <v>-at toilet of ward</v>
+      </c>
+      <c r="D68" s="163">
         <v>1</v>
       </c>
-      <c r="E67" s="70">
-        <f>2*(5+4)/3.28</f>
-        <v>5.4878048780487809</v>
-      </c>
-      <c r="F67" s="70">
+      <c r="E68" s="164">
+        <f>5.33/3.281</f>
+        <v>1.6245047241694606</v>
+      </c>
+      <c r="F68" s="164">
         <v>0.23</v>
       </c>
-      <c r="G67" s="70">
-        <v>0.45</v>
-      </c>
-      <c r="H67" s="70">
-        <f>D67*E67*F67*G67</f>
-        <v>0.5679878048780489</v>
-      </c>
-      <c r="I67" s="72"/>
-      <c r="J67" s="72"/>
-      <c r="K67" s="72"/>
-      <c r="L67" s="25"/>
-    </row>
-    <row r="68" spans="2:12">
-      <c r="B68" s="84"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="70"/>
-      <c r="F68" s="70"/>
-      <c r="G68" s="71"/>
-      <c r="H68" s="70">
-        <f>SUM(H65:H67)</f>
-        <v>1.9886623553199876</v>
-      </c>
-      <c r="I68" s="24" t="s">
+      <c r="G68" s="164">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="H68" s="164">
+        <f>D68*E68*F68*G68</f>
+        <v>0.91102977521237649</v>
+      </c>
+      <c r="I68" s="163"/>
+      <c r="J68" s="119"/>
+      <c r="K68" s="119"/>
+      <c r="L68" s="25"/>
+    </row>
+    <row r="69" spans="2:12">
+      <c r="B69" s="147"/>
+      <c r="C69" s="118" t="s">
+        <v>149</v>
+      </c>
+      <c r="D69" s="119">
+        <v>-1</v>
+      </c>
+      <c r="E69" s="116">
+        <f>2.5/3.281</f>
+        <v>0.76196281621456874</v>
+      </c>
+      <c r="F69" s="116">
+        <v>0.23</v>
+      </c>
+      <c r="G69" s="116">
+        <f>6.5/3.281</f>
+        <v>1.9811033221578787</v>
+      </c>
+      <c r="H69" s="164">
+        <f>D69*E69*F69*G69</f>
+        <v>-0.34719122530959468</v>
+      </c>
+      <c r="I69" s="119"/>
+      <c r="J69" s="119"/>
+      <c r="K69" s="119"/>
+      <c r="L69" s="25"/>
+    </row>
+    <row r="70" spans="2:12">
+      <c r="B70" s="147"/>
+      <c r="C70" s="118"/>
+      <c r="D70" s="119"/>
+      <c r="E70" s="116"/>
+      <c r="F70" s="116"/>
+      <c r="G70" s="151"/>
+      <c r="H70" s="116">
+        <f>SUM(H68:H69)</f>
+        <v>0.56383854990278182</v>
+      </c>
+      <c r="I70" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="J68" s="73">
-        <f>'[1]Table of Content 2'!$H$43</f>
-        <v>14911.97</v>
-      </c>
-      <c r="K68" s="73">
-        <f>H68*J68</f>
-        <v>29654.873382660993</v>
-      </c>
-      <c r="L68" s="25"/>
-    </row>
-    <row r="69" spans="2:12">
-      <c r="B69" s="84"/>
-      <c r="C69" s="19" t="s">
+      <c r="J70" s="116">
+        <v>14491.84</v>
+      </c>
+      <c r="K70" s="116">
+        <f>H70*J70</f>
+        <v>8171.0580510231293</v>
+      </c>
+      <c r="L70" s="25"/>
+    </row>
+    <row r="71" spans="2:12">
+      <c r="B71" s="147"/>
+      <c r="C71" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="D69" s="24"/>
-      <c r="E69" s="70"/>
-      <c r="F69" s="70"/>
-      <c r="G69" s="71"/>
-      <c r="H69" s="72"/>
-      <c r="I69" s="24"/>
-      <c r="J69" s="73"/>
-      <c r="K69" s="73">
-        <f>'[1]Update Descrip'!$G$397*H68*0.13</f>
-        <v>373.07902384509566</v>
-      </c>
-      <c r="L69" s="25"/>
-    </row>
-    <row r="70" spans="2:12">
-      <c r="B70" s="84"/>
-      <c r="C70" s="19" t="s">
+      <c r="D71" s="119"/>
+      <c r="E71" s="116"/>
+      <c r="F71" s="116"/>
+      <c r="G71" s="151"/>
+      <c r="H71" s="119"/>
+      <c r="I71" s="119"/>
+      <c r="J71" s="116"/>
+      <c r="K71" s="116">
+        <f>0.13*H70*912.17</f>
+        <v>66.861159308426664</v>
+      </c>
+      <c r="L71" s="25"/>
+    </row>
+    <row r="72" spans="2:12">
+      <c r="B72" s="147"/>
+      <c r="C72" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="D70" s="72"/>
-      <c r="E70" s="72"/>
-      <c r="F70" s="72"/>
-      <c r="G70" s="72"/>
-      <c r="H70" s="72"/>
-      <c r="I70" s="72"/>
-      <c r="J70" s="73"/>
-      <c r="K70" s="73">
-        <f>'[1]Update Descrip'!$G$398*H68*0.13</f>
-        <v>181.47498550225441</v>
-      </c>
-      <c r="L70" s="25"/>
-    </row>
-    <row r="71" spans="2:12">
-      <c r="B71" s="84"/>
-      <c r="C71" s="19" t="s">
+      <c r="D72" s="119"/>
+      <c r="E72" s="119"/>
+      <c r="F72" s="119"/>
+      <c r="G72" s="119"/>
+      <c r="H72" s="119"/>
+      <c r="I72" s="119"/>
+      <c r="J72" s="116"/>
+      <c r="K72" s="116">
+        <f>0.13*H70*953.37</f>
+        <v>69.881078581705964</v>
+      </c>
+      <c r="L72" s="25"/>
+    </row>
+    <row r="73" spans="2:12">
+      <c r="B73" s="147"/>
+      <c r="C73" s="118" t="s">
         <v>38</v>
       </c>
-      <c r="D71" s="24"/>
-      <c r="E71" s="70"/>
-      <c r="F71" s="70"/>
-      <c r="G71" s="71"/>
-      <c r="H71" s="70"/>
-      <c r="I71" s="24"/>
-      <c r="J71" s="73"/>
-      <c r="K71" s="73">
-        <f>'[1]Update Descrip'!$G$396*H68*0.13</f>
-        <v>2266.0123439021031</v>
-      </c>
-      <c r="L71" s="25"/>
-    </row>
-    <row r="72" spans="2:12">
-      <c r="B72" s="84"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="70"/>
-      <c r="F72" s="70"/>
-      <c r="G72" s="71"/>
-      <c r="H72" s="70"/>
-      <c r="I72" s="24"/>
-      <c r="J72" s="73"/>
-      <c r="K72" s="73"/>
-      <c r="L72" s="25"/>
-    </row>
-    <row r="73" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B73" s="85">
+      <c r="D73" s="119"/>
+      <c r="E73" s="116"/>
+      <c r="F73" s="116"/>
+      <c r="G73" s="151"/>
+      <c r="H73" s="116"/>
+      <c r="I73" s="119"/>
+      <c r="J73" s="116"/>
+      <c r="K73" s="116">
+        <f>0.13*H70*8481.2</f>
+        <v>621.66357622661155</v>
+      </c>
+      <c r="L73" s="25"/>
+    </row>
+    <row r="74" spans="2:12">
+      <c r="B74" s="80"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="70"/>
+      <c r="F74" s="70"/>
+      <c r="G74" s="71"/>
+      <c r="H74" s="70"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="73"/>
+      <c r="K74" s="73"/>
+      <c r="L74" s="25"/>
+    </row>
+    <row r="75" spans="2:12" ht="35.1" customHeight="1">
+      <c r="B75" s="147">
         <v>6</v>
       </c>
-      <c r="C73" s="79" t="s">
+      <c r="C75" s="148" t="s">
         <v>77</v>
       </c>
-      <c r="D73" s="24">
+      <c r="D75" s="119"/>
+      <c r="E75" s="119"/>
+      <c r="F75" s="119"/>
+      <c r="G75" s="116"/>
+      <c r="H75" s="119"/>
+      <c r="I75" s="151"/>
+      <c r="J75" s="116"/>
+      <c r="K75" s="119"/>
+      <c r="L75" s="25"/>
+    </row>
+    <row r="76" spans="2:12">
+      <c r="B76" s="147"/>
+      <c r="C76" s="118" t="s">
+        <v>151</v>
+      </c>
+      <c r="D76" s="119">
         <v>1</v>
       </c>
-      <c r="E73" s="24">
-        <f>E52</f>
-        <v>0</v>
-      </c>
-      <c r="F73" s="24">
-        <f>F52</f>
-        <v>0</v>
-      </c>
-      <c r="G73" s="70"/>
-      <c r="H73" s="72">
-        <f>F73*E73*D73</f>
-        <v>0</v>
-      </c>
-      <c r="I73" s="74" t="s">
+      <c r="E76" s="119">
+        <f>14.25/3.281</f>
+        <v>4.3431880524230415</v>
+      </c>
+      <c r="F76" s="119">
+        <f>8.833/3.281</f>
+        <v>2.6921670222493144</v>
+      </c>
+      <c r="G76" s="116"/>
+      <c r="H76" s="119">
+        <f>F76*E76*D76</f>
+        <v>11.692587646160538</v>
+      </c>
+      <c r="I76" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="J73" s="73">
-        <f>'[1]Table of Content 2'!$H$155</f>
-        <v>692.38</v>
-      </c>
-      <c r="K73" s="72">
-        <f>H73*J73</f>
-        <v>0</v>
-      </c>
-      <c r="L73" s="25"/>
-    </row>
-    <row r="74" spans="2:12">
-      <c r="B74" s="85"/>
-      <c r="C74" s="19" t="s">
+      <c r="J76" s="116">
+        <v>689.98</v>
+      </c>
+      <c r="K76" s="119">
+        <f>H76*J76</f>
+        <v>8067.6516240978481</v>
+      </c>
+      <c r="L76" s="25"/>
+    </row>
+    <row r="77" spans="2:12">
+      <c r="B77" s="147"/>
+      <c r="C77" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="71"/>
-      <c r="H74" s="24"/>
-      <c r="I74" s="74"/>
-      <c r="J74" s="73"/>
-      <c r="K74" s="69">
-        <f>'[1]Update Descrip'!$G$1804/10*H73*0.13</f>
-        <v>0</v>
-      </c>
-      <c r="L74" s="25"/>
-    </row>
-    <row r="75" spans="2:12">
-      <c r="B75" s="85"/>
-      <c r="C75" s="19" t="s">
+      <c r="D77" s="119"/>
+      <c r="E77" s="119"/>
+      <c r="F77" s="119"/>
+      <c r="G77" s="151"/>
+      <c r="H77" s="119"/>
+      <c r="I77" s="151"/>
+      <c r="J77" s="116"/>
+      <c r="K77" s="166">
+        <f>0.13*H76*1694.03/10</f>
+        <v>257.49872525292938</v>
+      </c>
+      <c r="L77" s="25"/>
+    </row>
+    <row r="78" spans="2:12">
+      <c r="B78" s="147"/>
+      <c r="C78" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
-      <c r="G75" s="71"/>
-      <c r="H75" s="24"/>
-      <c r="I75" s="74"/>
-      <c r="J75" s="73"/>
-      <c r="K75" s="69">
-        <f>'[1]Update Descrip'!$G$1805/10*H73*0.13</f>
-        <v>0</v>
-      </c>
-      <c r="L75" s="25"/>
-    </row>
-    <row r="76" spans="2:12">
-      <c r="B76" s="85"/>
-      <c r="C76" s="19" t="s">
+      <c r="D78" s="119"/>
+      <c r="E78" s="119"/>
+      <c r="F78" s="119"/>
+      <c r="G78" s="151"/>
+      <c r="H78" s="119"/>
+      <c r="I78" s="151"/>
+      <c r="J78" s="116"/>
+      <c r="K78" s="166">
+        <f>0.13*H76*572.02/10</f>
+        <v>86.949121809637774</v>
+      </c>
+      <c r="L78" s="25"/>
+    </row>
+    <row r="79" spans="2:12">
+      <c r="B79" s="147"/>
+      <c r="C79" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="D76" s="24"/>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="71"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="74"/>
-      <c r="J76" s="73"/>
-      <c r="K76" s="69">
-        <f>'[1]Update Descrip'!$G$1806/10*H73*0.13</f>
-        <v>0</v>
-      </c>
-      <c r="L76" s="25"/>
-    </row>
-    <row r="77" spans="2:12" ht="18" customHeight="1">
-      <c r="B77" s="84"/>
-      <c r="C77" s="19"/>
-      <c r="D77" s="24"/>
-      <c r="E77" s="70"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="71"/>
-      <c r="H77" s="70"/>
-      <c r="I77" s="24"/>
-      <c r="J77" s="73"/>
-      <c r="K77" s="73"/>
-      <c r="L77" s="25"/>
-    </row>
-    <row r="78" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B78" s="84">
-        <v>7</v>
-      </c>
-      <c r="C78" s="79" t="s">
-        <v>78</v>
-      </c>
-      <c r="D78" s="24">
-        <f>D65</f>
-        <v>2</v>
-      </c>
-      <c r="E78" s="24">
-        <f>E65</f>
-        <v>5</v>
-      </c>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24">
-        <f>G85</f>
-        <v>1.8709539774459008</v>
-      </c>
-      <c r="H78" s="70">
-        <f>D78*E78*G78</f>
-        <v>18.709539774459007</v>
-      </c>
-      <c r="I78" s="24"/>
-      <c r="J78" s="73"/>
-      <c r="K78" s="73"/>
-      <c r="L78" s="25"/>
-    </row>
-    <row r="79" spans="2:12">
-      <c r="B79" s="84"/>
-      <c r="C79" s="21"/>
-      <c r="D79" s="24">
-        <f>D66</f>
-        <v>2</v>
-      </c>
-      <c r="E79" s="24">
-        <f>E66</f>
-        <v>2.8926363913441024</v>
-      </c>
-      <c r="F79" s="24"/>
-      <c r="G79" s="24">
-        <f>G86</f>
-        <v>1.8709539774459008</v>
-      </c>
-      <c r="H79" s="70">
-        <f>D79*E79*G79</f>
-        <v>10.823979123380012</v>
-      </c>
-      <c r="I79" s="24"/>
-      <c r="J79" s="75"/>
-      <c r="K79" s="73"/>
+      <c r="D79" s="119"/>
+      <c r="E79" s="119"/>
+      <c r="F79" s="119"/>
+      <c r="G79" s="151"/>
+      <c r="H79" s="119"/>
+      <c r="I79" s="151"/>
+      <c r="J79" s="116"/>
+      <c r="K79" s="166">
+        <f>0.13*H76*1207.6/10</f>
+        <v>183.55959493954506</v>
+      </c>
       <c r="L79" s="25"/>
     </row>
-    <row r="80" spans="2:12">
-      <c r="B80" s="84"/>
-      <c r="C80" s="21"/>
+    <row r="80" spans="2:12" ht="18" customHeight="1">
+      <c r="B80" s="80"/>
+      <c r="C80" s="19"/>
       <c r="D80" s="24"/>
       <c r="E80" s="70"/>
       <c r="F80" s="70"/>
       <c r="G80" s="71"/>
-      <c r="H80" s="70">
-        <f>SUM(H78:H79)</f>
-        <v>29.533518897839016</v>
-      </c>
-      <c r="I80" s="24" t="s">
+      <c r="H80" s="70"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="73"/>
+      <c r="K80" s="73"/>
+      <c r="L80" s="25"/>
+    </row>
+    <row r="81" spans="2:14" ht="35.1" customHeight="1">
+      <c r="B81" s="147">
+        <v>7</v>
+      </c>
+      <c r="C81" s="148" t="s">
+        <v>78</v>
+      </c>
+      <c r="D81" s="119"/>
+      <c r="E81" s="119"/>
+      <c r="F81" s="119"/>
+      <c r="G81" s="119"/>
+      <c r="H81" s="116"/>
+      <c r="I81" s="119"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="116"/>
+      <c r="L81" s="25"/>
+    </row>
+    <row r="82" spans="2:14">
+      <c r="B82" s="147"/>
+      <c r="C82" s="118" t="s">
+        <v>152</v>
+      </c>
+      <c r="D82" s="119">
+        <v>2</v>
+      </c>
+      <c r="E82" s="119">
+        <f>15.42/3.281</f>
+        <v>4.6997866504114594</v>
+      </c>
+      <c r="F82" s="119"/>
+      <c r="G82" s="119">
+        <f>4.583/3.281</f>
+        <v>1.3968302346845474</v>
+      </c>
+      <c r="H82" s="116">
+        <f>D82*E82*G82</f>
+        <v>13.129608179723084</v>
+      </c>
+      <c r="I82" s="119"/>
+      <c r="J82" s="116"/>
+      <c r="K82" s="116"/>
+      <c r="L82" s="25"/>
+    </row>
+    <row r="83" spans="2:14">
+      <c r="B83" s="147"/>
+      <c r="C83" s="149"/>
+      <c r="D83" s="119">
+        <v>2</v>
+      </c>
+      <c r="E83" s="119">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="F83" s="119"/>
+      <c r="G83" s="119">
+        <f>4.583/3.281</f>
+        <v>1.3968302346845474</v>
+      </c>
+      <c r="H83" s="116">
+        <f>D83*E83*G83</f>
+        <v>8.5146615951511571</v>
+      </c>
+      <c r="I83" s="119"/>
+      <c r="J83" s="165"/>
+      <c r="K83" s="116"/>
+      <c r="L83" s="25"/>
+    </row>
+    <row r="84" spans="2:14">
+      <c r="B84" s="147"/>
+      <c r="C84" s="149"/>
+      <c r="D84" s="119"/>
+      <c r="E84" s="116"/>
+      <c r="F84" s="116"/>
+      <c r="G84" s="151"/>
+      <c r="H84" s="116">
+        <f>SUM(H82:H83)</f>
+        <v>21.644269774874239</v>
+      </c>
+      <c r="I84" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="J80" s="73">
-        <f>'[1]Table of Content 2'!$H$215</f>
-        <v>402.23</v>
-      </c>
-      <c r="K80" s="73">
-        <f>H80*J80</f>
-        <v>11879.267306277789</v>
-      </c>
-      <c r="L80" s="25"/>
-    </row>
-    <row r="81" spans="2:14">
-      <c r="B81" s="84"/>
-      <c r="C81" s="19" t="s">
+      <c r="J84" s="116">
+        <v>415.5</v>
+      </c>
+      <c r="K84" s="116">
+        <f>H84*J84</f>
+        <v>8993.1940914602455</v>
+      </c>
+      <c r="L84" s="25"/>
+    </row>
+    <row r="85" spans="2:14">
+      <c r="B85" s="147"/>
+      <c r="C85" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="D81" s="24"/>
-      <c r="E81" s="70"/>
-      <c r="F81" s="70"/>
-      <c r="G81" s="71"/>
-      <c r="H81" s="70"/>
-      <c r="I81" s="24"/>
-      <c r="J81" s="75"/>
-      <c r="K81" s="73">
-        <f>'[1]Update Descrip'!$G$2611/100*H80*0.13</f>
-        <v>298.08272177497503</v>
-      </c>
-      <c r="L81" s="25"/>
-    </row>
-    <row r="82" spans="2:14">
-      <c r="B82" s="84"/>
-      <c r="C82" s="19" t="s">
+      <c r="D85" s="119"/>
+      <c r="E85" s="116"/>
+      <c r="F85" s="116"/>
+      <c r="G85" s="151"/>
+      <c r="H85" s="116"/>
+      <c r="I85" s="119"/>
+      <c r="J85" s="165"/>
+      <c r="K85" s="116">
+        <f>0.13*H84*7010.67/100</f>
+        <v>197.26308261740283</v>
+      </c>
+      <c r="L85" s="25"/>
+    </row>
+    <row r="86" spans="2:14">
+      <c r="B86" s="147"/>
+      <c r="C86" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="D82" s="24"/>
-      <c r="E82" s="70"/>
-      <c r="F82" s="70"/>
-      <c r="G82" s="71"/>
-      <c r="H82" s="70"/>
-      <c r="I82" s="24"/>
-      <c r="J82" s="75"/>
-      <c r="K82" s="73">
-        <f>'[1]Update Descrip'!$G$2612/100*H80*0.13</f>
-        <v>140.5293134380685</v>
-      </c>
-      <c r="L82" s="25"/>
-    </row>
-    <row r="83" spans="2:14">
-      <c r="B83" s="85"/>
-      <c r="C83" s="19"/>
-      <c r="D83" s="72"/>
-      <c r="E83" s="70"/>
-      <c r="F83" s="70"/>
-      <c r="G83" s="71"/>
-      <c r="H83" s="72"/>
-      <c r="I83" s="72"/>
-      <c r="J83" s="72"/>
-      <c r="K83" s="72"/>
-      <c r="L83" s="25"/>
-    </row>
-    <row r="84" spans="2:14" ht="35.1" customHeight="1">
-      <c r="B84" s="85">
-        <v>8</v>
-      </c>
-      <c r="C84" s="79" t="s">
-        <v>79</v>
-      </c>
-      <c r="D84" s="72">
-        <f>D52</f>
-        <v>0</v>
-      </c>
-      <c r="E84" s="72">
-        <f>E52</f>
-        <v>0</v>
-      </c>
-      <c r="F84" s="72"/>
-      <c r="G84" s="72">
-        <f>F52</f>
-        <v>0</v>
-      </c>
-      <c r="H84" s="72">
-        <f>D84*E84*G84</f>
-        <v>0</v>
-      </c>
-      <c r="I84" s="72"/>
-      <c r="J84" s="72"/>
-      <c r="K84" s="72"/>
-      <c r="L84" s="25"/>
-    </row>
-    <row r="85" spans="2:14">
-      <c r="B85" s="85"/>
-      <c r="C85" s="19"/>
-      <c r="D85" s="72">
-        <f>D54</f>
-        <v>2</v>
-      </c>
-      <c r="E85" s="72">
-        <f>E54</f>
-        <v>5</v>
-      </c>
-      <c r="F85" s="72"/>
-      <c r="G85" s="72">
-        <f>G54+0.3+0.3</f>
-        <v>1.8709539774459008</v>
-      </c>
-      <c r="H85" s="72">
-        <f t="shared" ref="H85:H86" si="5">D85*E85*G85</f>
-        <v>18.709539774459007</v>
-      </c>
-      <c r="I85" s="72"/>
-      <c r="J85" s="72"/>
-      <c r="K85" s="72"/>
-      <c r="L85" s="25"/>
-    </row>
-    <row r="86" spans="2:14">
-      <c r="B86" s="85"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="72">
-        <f>D55</f>
-        <v>2</v>
-      </c>
-      <c r="E86" s="72">
-        <f>E55</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="F86" s="72"/>
-      <c r="G86" s="72">
-        <f>G55+0.3+0.3</f>
-        <v>1.8709539774459008</v>
-      </c>
-      <c r="H86" s="72">
-        <f t="shared" si="5"/>
-        <v>11.404778893300218</v>
-      </c>
-      <c r="I86" s="72"/>
-      <c r="J86" s="72"/>
-      <c r="K86" s="72"/>
+      <c r="D86" s="119"/>
+      <c r="E86" s="116"/>
+      <c r="F86" s="116"/>
+      <c r="G86" s="151"/>
+      <c r="H86" s="116"/>
+      <c r="I86" s="119"/>
+      <c r="J86" s="165"/>
+      <c r="K86" s="116">
+        <f>0.13*H84*4639.73/100</f>
+        <v>130.5506381433504</v>
+      </c>
       <c r="L86" s="25"/>
     </row>
     <row r="87" spans="2:14">
-      <c r="B87" s="85"/>
+      <c r="B87" s="81"/>
       <c r="C87" s="19"/>
       <c r="D87" s="72"/>
-      <c r="E87" s="72"/>
-      <c r="F87" s="72"/>
-      <c r="G87" s="72"/>
-      <c r="H87" s="72">
-        <f>SUM(H84:H86)</f>
-        <v>30.114318667759225</v>
-      </c>
-      <c r="I87" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="J87" s="72">
-        <f>'[1]Table of Content 2'!$H$187</f>
-        <v>286.77</v>
-      </c>
-      <c r="K87" s="72">
-        <f>H87*J87</f>
-        <v>8635.8831643533122</v>
-      </c>
+      <c r="E87" s="70"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="71"/>
+      <c r="H87" s="72"/>
+      <c r="I87" s="72"/>
+      <c r="J87" s="72"/>
+      <c r="K87" s="72"/>
       <c r="L87" s="25"/>
     </row>
-    <row r="88" spans="2:14">
-      <c r="B88" s="85"/>
-      <c r="C88" s="19" t="s">
-        <v>29</v>
+    <row r="88" spans="2:14" ht="35.1" customHeight="1">
+      <c r="B88" s="81">
+        <v>8</v>
+      </c>
+      <c r="C88" s="79" t="s">
+        <v>79</v>
       </c>
       <c r="D88" s="72"/>
       <c r="E88" s="72"/>
@@ -9128,346 +9167,337 @@
       <c r="H88" s="72"/>
       <c r="I88" s="72"/>
       <c r="J88" s="72"/>
-      <c r="K88" s="72">
-        <f>'[1]Update Descrip'!$H$2269/10*H87*0.13</f>
-        <v>300.55174145895751</v>
-      </c>
+      <c r="K88" s="72"/>
       <c r="L88" s="25"/>
     </row>
     <row r="89" spans="2:14">
-      <c r="B89" s="85"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="72"/>
-      <c r="E89" s="72"/>
+      <c r="B89" s="81"/>
+      <c r="C89" s="19" t="str">
+        <f>C82</f>
+        <v>-At shear wall</v>
+      </c>
+      <c r="D89" s="72">
+        <f>D57</f>
+        <v>2</v>
+      </c>
+      <c r="E89" s="72">
+        <f>E57</f>
+        <v>0</v>
+      </c>
       <c r="F89" s="72"/>
-      <c r="G89" s="72"/>
-      <c r="H89" s="72"/>
+      <c r="G89" s="72">
+        <f>G57+0.3+0.3</f>
+        <v>1.8709539774459008</v>
+      </c>
+      <c r="H89" s="72">
+        <f t="shared" ref="H89:H90" si="6">D89*E89*G89</f>
+        <v>0</v>
+      </c>
       <c r="I89" s="72"/>
       <c r="J89" s="72"/>
       <c r="K89" s="72"/>
       <c r="L89" s="25"/>
     </row>
     <row r="90" spans="2:14">
-      <c r="B90" s="85"/>
+      <c r="B90" s="81"/>
       <c r="C90" s="19"/>
-      <c r="D90" s="72"/>
-      <c r="E90" s="72"/>
+      <c r="D90" s="72">
+        <f>D58</f>
+        <v>2</v>
+      </c>
+      <c r="E90" s="72">
+        <f>E58</f>
+        <v>3.047851264858275</v>
+      </c>
       <c r="F90" s="72"/>
-      <c r="G90" s="72"/>
-      <c r="H90" s="72"/>
+      <c r="G90" s="72">
+        <f>G58+0.3+0.3</f>
+        <v>1.8709539774459008</v>
+      </c>
+      <c r="H90" s="72">
+        <f t="shared" si="6"/>
+        <v>11.404778893300218</v>
+      </c>
       <c r="I90" s="72"/>
       <c r="J90" s="72"/>
       <c r="K90" s="72"/>
       <c r="L90" s="25"/>
     </row>
-    <row r="91" spans="2:14" ht="33" customHeight="1">
-      <c r="B91" s="84">
+    <row r="91" spans="2:14">
+      <c r="B91" s="81"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
+      <c r="G91" s="72"/>
+      <c r="H91" s="72">
+        <f>SUM(H88:H90)</f>
+        <v>11.404778893300218</v>
+      </c>
+      <c r="I91" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="J91" s="72">
+        <f>'[1]Table of Content 2'!$H$187</f>
+        <v>286.77</v>
+      </c>
+      <c r="K91" s="72">
+        <f>H91*J91</f>
+        <v>3270.5484432317035</v>
+      </c>
+      <c r="L91" s="25"/>
+    </row>
+    <row r="92" spans="2:14">
+      <c r="B92" s="81"/>
+      <c r="C92" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D92" s="72"/>
+      <c r="E92" s="72"/>
+      <c r="F92" s="72"/>
+      <c r="G92" s="72"/>
+      <c r="H92" s="72"/>
+      <c r="I92" s="72"/>
+      <c r="J92" s="72"/>
+      <c r="K92" s="72">
+        <f>'[1]Update Descrip'!$H$2269/10*H91*0.13</f>
+        <v>113.82379907553776</v>
+      </c>
+      <c r="L92" s="25"/>
+    </row>
+    <row r="93" spans="2:14">
+      <c r="B93" s="81"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="72"/>
+      <c r="E93" s="72"/>
+      <c r="F93" s="72"/>
+      <c r="G93" s="72"/>
+      <c r="H93" s="72"/>
+      <c r="I93" s="72"/>
+      <c r="J93" s="72"/>
+      <c r="K93" s="72"/>
+      <c r="L93" s="25"/>
+    </row>
+    <row r="94" spans="2:14">
+      <c r="B94" s="81"/>
+      <c r="C94" s="19"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+      <c r="F94" s="72"/>
+      <c r="G94" s="72"/>
+      <c r="H94" s="72"/>
+      <c r="I94" s="72"/>
+      <c r="J94" s="72"/>
+      <c r="K94" s="72"/>
+      <c r="L94" s="25"/>
+    </row>
+    <row r="95" spans="2:14" ht="33" customHeight="1">
+      <c r="B95" s="80">
         <v>9</v>
       </c>
-      <c r="C91" s="21" t="s">
+      <c r="C95" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D91" s="24">
+      <c r="D95" s="24">
         <v>1</v>
       </c>
-      <c r="E91" s="70"/>
-      <c r="F91" s="70"/>
-      <c r="G91" s="71"/>
-      <c r="H91" s="70">
-        <f>+D91</f>
+      <c r="E95" s="70"/>
+      <c r="F95" s="70"/>
+      <c r="G95" s="71"/>
+      <c r="H95" s="70">
+        <f>+D95</f>
         <v>1</v>
       </c>
-      <c r="I91" s="24" t="s">
+      <c r="I95" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="J91" s="73">
+      <c r="J95" s="73">
         <v>4659</v>
       </c>
-      <c r="K91" s="73">
-        <f>H91*J91</f>
+      <c r="K95" s="73">
+        <f>H95*J95</f>
         <v>4659</v>
       </c>
-      <c r="L91" s="25"/>
-      <c r="N91" s="81" t="s">
+      <c r="L95" s="25"/>
+      <c r="N95" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="92" spans="2:14">
-      <c r="B92" s="84"/>
-      <c r="C92" s="30" t="s">
+    <row r="96" spans="2:14">
+      <c r="B96" s="80"/>
+      <c r="C96" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D92" s="24"/>
-      <c r="E92" s="70"/>
-      <c r="F92" s="70"/>
-      <c r="G92" s="71"/>
-      <c r="H92" s="70"/>
-      <c r="I92" s="24"/>
-      <c r="J92" s="73"/>
-      <c r="K92" s="73">
-        <f>0.13*K91</f>
-        <v>605.67000000000007</v>
-      </c>
-      <c r="L92" s="25"/>
-    </row>
-    <row r="93" spans="2:14">
-      <c r="B93" s="84"/>
-      <c r="C93" s="21"/>
-      <c r="D93" s="24"/>
-      <c r="E93" s="70"/>
-      <c r="F93" s="70"/>
-      <c r="G93" s="71"/>
-      <c r="H93" s="70"/>
-      <c r="I93" s="24"/>
-      <c r="J93" s="73"/>
-      <c r="K93" s="73"/>
-      <c r="L93" s="25"/>
-    </row>
-    <row r="94" spans="2:14" ht="33" customHeight="1">
-      <c r="B94" s="84">
-        <v>10</v>
-      </c>
-      <c r="C94" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D94" s="24"/>
-      <c r="E94" s="70"/>
-      <c r="F94" s="70"/>
-      <c r="G94" s="71"/>
-      <c r="H94" s="70">
-        <v>1</v>
-      </c>
-      <c r="I94" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="J94" s="73">
-        <v>9938</v>
-      </c>
-      <c r="K94" s="73">
-        <f>H94*J94</f>
-        <v>9938</v>
-      </c>
-      <c r="L94" s="25"/>
-      <c r="N94" s="81" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="95" spans="2:14">
-      <c r="B95" s="85"/>
-      <c r="C95" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="D95" s="24"/>
-      <c r="E95" s="24"/>
-      <c r="F95" s="24"/>
-      <c r="G95" s="70"/>
-      <c r="H95" s="24"/>
-      <c r="I95" s="24"/>
-      <c r="J95" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="K95" s="73">
-        <f>0.13*K94</f>
-        <v>1291.94</v>
-      </c>
-      <c r="L95" s="25"/>
-    </row>
-    <row r="96" spans="2:14">
-      <c r="B96" s="85"/>
-      <c r="C96" s="29"/>
       <c r="D96" s="24"/>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="70"/>
-      <c r="H96" s="24"/>
+      <c r="E96" s="70"/>
+      <c r="F96" s="70"/>
+      <c r="G96" s="71"/>
+      <c r="H96" s="70"/>
       <c r="I96" s="24"/>
       <c r="J96" s="73"/>
-      <c r="K96" s="73"/>
+      <c r="K96" s="73">
+        <f>0.13*K95</f>
+        <v>605.67000000000007</v>
+      </c>
       <c r="L96" s="25"/>
     </row>
     <row r="97" spans="2:14">
-      <c r="B97" s="85"/>
-      <c r="C97" s="20"/>
-      <c r="D97" s="20"/>
-      <c r="E97" s="20"/>
-      <c r="F97" s="20"/>
-      <c r="G97" s="20"/>
-      <c r="H97" s="20"/>
-      <c r="I97" s="20"/>
-      <c r="J97" s="20"/>
-      <c r="K97" s="20"/>
+      <c r="B97" s="80"/>
+      <c r="C97" s="21"/>
+      <c r="D97" s="24"/>
+      <c r="E97" s="70"/>
+      <c r="F97" s="70"/>
+      <c r="G97" s="71"/>
+      <c r="H97" s="70"/>
+      <c r="I97" s="24"/>
+      <c r="J97" s="73"/>
+      <c r="K97" s="73"/>
       <c r="L97" s="25"/>
     </row>
-    <row r="98" spans="2:14" ht="18">
-      <c r="B98" s="85" t="s">
-        <v>97</v>
-      </c>
-      <c r="C98" s="86" t="s">
-        <v>96</v>
+    <row r="98" spans="2:14" ht="33" customHeight="1">
+      <c r="B98" s="80">
+        <v>10</v>
+      </c>
+      <c r="C98" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="70"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="73"/>
-      <c r="K98" s="73"/>
+      <c r="E98" s="70"/>
+      <c r="F98" s="70"/>
+      <c r="G98" s="71"/>
+      <c r="H98" s="70">
+        <v>1</v>
+      </c>
+      <c r="I98" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="J98" s="73">
+        <v>9938</v>
+      </c>
+      <c r="K98" s="73">
+        <f>H98*J98</f>
+        <v>9938</v>
+      </c>
       <c r="L98" s="25"/>
+      <c r="N98" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="99" spans="2:14">
-      <c r="B99" s="85"/>
-      <c r="C99" s="29"/>
+      <c r="B99" s="81"/>
+      <c r="C99" s="29" t="s">
+        <v>82</v>
+      </c>
       <c r="D99" s="24"/>
       <c r="E99" s="24"/>
       <c r="F99" s="24"/>
       <c r="G99" s="70"/>
       <c r="H99" s="24"/>
       <c r="I99" s="24"/>
-      <c r="J99" s="73"/>
-      <c r="K99" s="73"/>
+      <c r="J99" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="K99" s="73">
+        <f>0.13*K98</f>
+        <v>1291.94</v>
+      </c>
       <c r="L99" s="25"/>
     </row>
-    <row r="100" spans="2:14" ht="34.799999999999997">
-      <c r="B100" s="84">
-        <v>11</v>
-      </c>
-      <c r="C100" s="93" t="s">
-        <v>98</v>
-      </c>
-      <c r="D100" s="70">
-        <v>2</v>
-      </c>
-      <c r="E100" s="70">
-        <f>25/3.28</f>
-        <v>7.6219512195121952</v>
-      </c>
-      <c r="F100" s="70">
-        <f>17/3.28</f>
-        <v>5.1829268292682933</v>
-      </c>
+    <row r="100" spans="2:14">
+      <c r="B100" s="81"/>
+      <c r="C100" s="29"/>
+      <c r="D100" s="24"/>
+      <c r="E100" s="24"/>
+      <c r="F100" s="24"/>
       <c r="G100" s="70"/>
-      <c r="H100" s="70">
-        <f>F100*E100*D100</f>
-        <v>79.008030933967888</v>
-      </c>
-      <c r="I100" s="70" t="s">
-        <v>90</v>
-      </c>
-      <c r="J100" s="70">
-        <f>'[2]Table of Content 2'!$H$329</f>
-        <v>68.400000000000006</v>
-      </c>
-      <c r="K100" s="70">
-        <f>H100*J100</f>
-        <v>5404.1493158834037</v>
-      </c>
+      <c r="H100" s="24"/>
+      <c r="I100" s="24"/>
+      <c r="J100" s="73"/>
+      <c r="K100" s="73"/>
       <c r="L100" s="25"/>
     </row>
     <row r="101" spans="2:14">
-      <c r="B101" s="85"/>
-      <c r="C101" s="29"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="70"/>
-      <c r="H101" s="24"/>
-      <c r="I101" s="24"/>
-      <c r="J101" s="73"/>
-      <c r="K101" s="73"/>
+      <c r="B101" s="81"/>
+      <c r="C101" s="20"/>
+      <c r="D101" s="20"/>
+      <c r="E101" s="20"/>
+      <c r="F101" s="20"/>
+      <c r="G101" s="20"/>
+      <c r="H101" s="20"/>
+      <c r="I101" s="20"/>
+      <c r="J101" s="20"/>
+      <c r="K101" s="20"/>
       <c r="L101" s="25"/>
     </row>
-    <row r="102" spans="2:14" ht="34.799999999999997">
-      <c r="B102" s="85">
-        <v>12</v>
-      </c>
-      <c r="C102" s="93" t="s">
-        <v>99</v>
-      </c>
-      <c r="D102" s="24">
-        <v>2</v>
-      </c>
-      <c r="E102" s="24">
-        <f>E100</f>
-        <v>7.6219512195121952</v>
-      </c>
-      <c r="F102" s="24">
-        <f>F100</f>
-        <v>5.1829268292682933</v>
-      </c>
+    <row r="102" spans="2:14" ht="18">
+      <c r="B102" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="C102" s="82" t="s">
+        <v>96</v>
+      </c>
+      <c r="D102" s="24"/>
+      <c r="E102" s="24"/>
+      <c r="F102" s="24"/>
       <c r="G102" s="70"/>
-      <c r="H102" s="70">
-        <f>F102*E102*D102</f>
-        <v>79.008030933967888</v>
-      </c>
-      <c r="I102" s="70" t="s">
-        <v>90</v>
-      </c>
-      <c r="J102" s="73">
-        <v>369.1</v>
-      </c>
-      <c r="K102" s="73">
-        <f>H102*J102</f>
-        <v>29161.864217727551</v>
-      </c>
+      <c r="H102" s="24"/>
+      <c r="I102" s="24"/>
+      <c r="J102" s="73"/>
+      <c r="K102" s="73"/>
       <c r="L102" s="25"/>
     </row>
     <row r="103" spans="2:14">
-      <c r="B103" s="85"/>
-      <c r="C103" s="29" t="s">
-        <v>81</v>
-      </c>
+      <c r="B103" s="81"/>
+      <c r="C103" s="29"/>
       <c r="D103" s="24"/>
       <c r="E103" s="24"/>
       <c r="F103" s="24"/>
       <c r="G103" s="70"/>
-      <c r="H103" s="70"/>
-      <c r="I103" s="70"/>
+      <c r="H103" s="24"/>
+      <c r="I103" s="24"/>
       <c r="J103" s="73"/>
-      <c r="K103" s="73">
-        <f>124.6*H102*0.13</f>
-        <v>1279.772085068412</v>
-      </c>
+      <c r="K103" s="73"/>
       <c r="L103" s="25"/>
     </row>
-    <row r="104" spans="2:14" ht="69.599999999999994">
-      <c r="B104" s="85">
-        <v>13</v>
-      </c>
-      <c r="C104" s="93" t="s">
-        <v>92</v>
-      </c>
-      <c r="D104" s="24">
-        <v>1</v>
-      </c>
-      <c r="E104" s="24">
-        <f>E102</f>
+    <row r="104" spans="2:14" ht="36">
+      <c r="B104" s="80">
+        <v>11</v>
+      </c>
+      <c r="C104" s="89" t="s">
+        <v>98</v>
+      </c>
+      <c r="D104" s="70">
+        <v>2</v>
+      </c>
+      <c r="E104" s="70">
+        <f>25/3.28</f>
         <v>7.6219512195121952</v>
       </c>
-      <c r="F104" s="24"/>
+      <c r="F104" s="70">
+        <f>17/3.28</f>
+        <v>5.1829268292682933</v>
+      </c>
       <c r="G104" s="70"/>
-      <c r="H104" s="24">
-        <f>E104</f>
-        <v>7.6219512195121952</v>
-      </c>
-      <c r="I104" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="J104" s="73">
-        <f>'[1]Table of Content 2'!$H$412</f>
-        <v>2761</v>
-      </c>
-      <c r="K104" s="73">
+      <c r="H104" s="70">
+        <f>F104*E104*D104</f>
+        <v>79.008030933967888</v>
+      </c>
+      <c r="I104" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="J104" s="70">
+        <f>'[2]Table of Content 2'!$H$329</f>
+        <v>68.400000000000006</v>
+      </c>
+      <c r="K104" s="70">
         <f>H104*J104</f>
-        <v>21044.207317073171</v>
+        <v>5404.1493158834037</v>
       </c>
       <c r="L104" s="25"/>
     </row>
     <row r="105" spans="2:14">
-      <c r="B105" s="85"/>
-      <c r="C105" s="29" t="s">
-        <v>81</v>
-      </c>
+      <c r="B105" s="81"/>
+      <c r="C105" s="29"/>
       <c r="D105" s="24"/>
       <c r="E105" s="24"/>
       <c r="F105" s="24"/>
@@ -9475,196 +9505,297 @@
       <c r="H105" s="24"/>
       <c r="I105" s="24"/>
       <c r="J105" s="73"/>
-      <c r="K105" s="73">
-        <f>2491*H104*0.13</f>
+      <c r="K105" s="73"/>
+      <c r="L105" s="25"/>
+    </row>
+    <row r="106" spans="2:14" ht="36">
+      <c r="B106" s="81">
+        <v>12</v>
+      </c>
+      <c r="C106" s="89" t="s">
+        <v>99</v>
+      </c>
+      <c r="D106" s="24">
+        <v>2</v>
+      </c>
+      <c r="E106" s="24">
+        <f>E104</f>
+        <v>7.6219512195121952</v>
+      </c>
+      <c r="F106" s="24">
+        <f>F104</f>
+        <v>5.1829268292682933</v>
+      </c>
+      <c r="G106" s="70"/>
+      <c r="H106" s="70">
+        <f>F106*E106*D106</f>
+        <v>79.008030933967888</v>
+      </c>
+      <c r="I106" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="J106" s="73">
+        <v>369.1</v>
+      </c>
+      <c r="K106" s="73">
+        <f>H106*J106</f>
+        <v>29161.864217727551</v>
+      </c>
+      <c r="L106" s="25"/>
+    </row>
+    <row r="107" spans="2:14">
+      <c r="B107" s="81"/>
+      <c r="C107" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="70"/>
+      <c r="H107" s="70"/>
+      <c r="I107" s="70"/>
+      <c r="J107" s="73"/>
+      <c r="K107" s="73">
+        <f>124.6*H106*0.13</f>
+        <v>1279.772085068412</v>
+      </c>
+      <c r="L107" s="25"/>
+    </row>
+    <row r="108" spans="2:14" ht="72">
+      <c r="B108" s="81">
+        <v>13</v>
+      </c>
+      <c r="C108" s="89" t="s">
+        <v>92</v>
+      </c>
+      <c r="D108" s="24">
+        <v>1</v>
+      </c>
+      <c r="E108" s="24">
+        <f>E106</f>
+        <v>7.6219512195121952</v>
+      </c>
+      <c r="F108" s="24"/>
+      <c r="G108" s="70"/>
+      <c r="H108" s="24">
+        <f>E108</f>
+        <v>7.6219512195121952</v>
+      </c>
+      <c r="I108" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J108" s="73">
+        <f>'[1]Table of Content 2'!$H$412</f>
+        <v>2761</v>
+      </c>
+      <c r="K108" s="73">
+        <f>H108*J108</f>
+        <v>21044.207317073171</v>
+      </c>
+      <c r="L108" s="25"/>
+    </row>
+    <row r="109" spans="2:14">
+      <c r="B109" s="81"/>
+      <c r="C109" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D109" s="24"/>
+      <c r="E109" s="24"/>
+      <c r="F109" s="24"/>
+      <c r="G109" s="70"/>
+      <c r="H109" s="24"/>
+      <c r="I109" s="24"/>
+      <c r="J109" s="73"/>
+      <c r="K109" s="73">
+        <f>2491*H108*0.13</f>
         <v>2468.2164634146343</v>
       </c>
-      <c r="L105" s="25"/>
-      <c r="N105" s="81">
+      <c r="L109" s="25"/>
+      <c r="N109" s="1">
         <f>17/3.28</f>
         <v>5.1829268292682933</v>
       </c>
     </row>
-    <row r="106" spans="2:14">
-      <c r="B106" s="85"/>
-      <c r="C106" s="29"/>
-      <c r="D106" s="24"/>
-      <c r="E106" s="24"/>
-      <c r="F106" s="24"/>
-      <c r="G106" s="70"/>
-      <c r="H106" s="24"/>
-      <c r="I106" s="24"/>
-      <c r="J106" s="73"/>
-      <c r="K106" s="73"/>
-      <c r="L106" s="25"/>
-      <c r="N106" s="81" t="e">
-        <f>#REF!*N105*2*68.4</f>
+    <row r="110" spans="2:14">
+      <c r="B110" s="81"/>
+      <c r="C110" s="29"/>
+      <c r="D110" s="24"/>
+      <c r="E110" s="24"/>
+      <c r="F110" s="24"/>
+      <c r="G110" s="70"/>
+      <c r="H110" s="24"/>
+      <c r="I110" s="24"/>
+      <c r="J110" s="73"/>
+      <c r="K110" s="73"/>
+      <c r="L110" s="25"/>
+      <c r="N110" s="1" t="e">
+        <f>#REF!*N109*2*68.4</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="107" spans="2:14" ht="33" customHeight="1">
-      <c r="B107" s="85">
+    <row r="111" spans="2:14" ht="33" customHeight="1">
+      <c r="B111" s="81">
         <v>14</v>
       </c>
-      <c r="C107" s="18" t="s">
+      <c r="C111" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D107" s="24">
+      <c r="D111" s="24">
         <v>1</v>
       </c>
-      <c r="E107" s="24"/>
-      <c r="F107" s="24"/>
-      <c r="G107" s="24"/>
-      <c r="H107" s="24">
+      <c r="E111" s="24"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="24"/>
+      <c r="H111" s="24">
         <v>1</v>
       </c>
-      <c r="I107" s="24" t="s">
+      <c r="I111" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="J107" s="73">
+      <c r="J111" s="73">
         <v>1000</v>
       </c>
-      <c r="K107" s="73">
-        <f>H107*J107</f>
+      <c r="K111" s="73">
+        <f>H111*J111</f>
         <v>1000</v>
       </c>
-      <c r="L107" s="25"/>
-    </row>
-    <row r="108" spans="2:14" ht="17.399999999999999" thickBot="1">
-      <c r="B108" s="22"/>
-      <c r="C108" s="26"/>
-      <c r="D108" s="76"/>
-      <c r="E108" s="77"/>
-      <c r="F108" s="77"/>
-      <c r="G108" s="77"/>
-      <c r="H108" s="77"/>
-      <c r="I108" s="76"/>
-      <c r="J108" s="77"/>
-      <c r="K108" s="78">
-        <f>SUM(K8:K107)</f>
-        <v>528050.98482284159</v>
-      </c>
-      <c r="L108" s="23"/>
-    </row>
-    <row r="109" spans="2:14">
-      <c r="C109" s="9"/>
-      <c r="D109" s="83"/>
-      <c r="E109" s="83"/>
-      <c r="F109" s="83"/>
-      <c r="G109" s="83"/>
-      <c r="H109" s="83"/>
-      <c r="I109" s="83"/>
-      <c r="J109" s="83"/>
-      <c r="K109" s="11"/>
-      <c r="L109" s="8"/>
-    </row>
-    <row r="110" spans="2:14">
-      <c r="C110" s="5"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="J110" s="65"/>
-      <c r="K110" s="65" t="s">
-        <v>71</v>
-      </c>
-      <c r="L110" s="65" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="111" spans="2:14">
-      <c r="C111" s="5"/>
-      <c r="H111" s="64"/>
-      <c r="I111" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="J111" s="67"/>
-      <c r="K111" s="67">
-        <f>+K108</f>
-        <v>528050.98482284159</v>
-      </c>
-      <c r="L111" s="67"/>
-    </row>
-    <row r="112" spans="2:14">
-      <c r="C112" s="5"/>
-      <c r="H112" s="64"/>
-      <c r="I112" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="J112" s="68"/>
-      <c r="K112" s="67">
-        <v>200000</v>
-      </c>
-      <c r="L112" s="68">
-        <v>100</v>
-      </c>
+      <c r="L111" s="25"/>
+    </row>
+    <row r="112" spans="2:14" ht="17.25" thickBot="1">
+      <c r="B112" s="22"/>
+      <c r="C112" s="26"/>
+      <c r="D112" s="76"/>
+      <c r="E112" s="77"/>
+      <c r="F112" s="77"/>
+      <c r="G112" s="77"/>
+      <c r="H112" s="77"/>
+      <c r="I112" s="76"/>
+      <c r="J112" s="77"/>
+      <c r="K112" s="78">
+        <f>SUM(K8:K111)</f>
+        <v>461715.70282650145</v>
+      </c>
+      <c r="L112" s="23"/>
     </row>
     <row r="113" spans="3:12">
-      <c r="C113" s="5"/>
-      <c r="H113" s="64"/>
-      <c r="I113" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="J113" s="68"/>
-      <c r="K113" s="67">
-        <f>0.95*K112</f>
-        <v>190000</v>
-      </c>
-      <c r="L113" s="68">
-        <f>K113/K111*100</f>
-        <v>35.98137404548995</v>
-      </c>
+      <c r="C113" s="9"/>
+      <c r="D113" s="10"/>
+      <c r="E113" s="10"/>
+      <c r="F113" s="10"/>
+      <c r="G113" s="10"/>
+      <c r="H113" s="10"/>
+      <c r="I113" s="10"/>
+      <c r="J113" s="10"/>
+      <c r="K113" s="11"/>
+      <c r="L113" s="8"/>
     </row>
     <row r="114" spans="3:12">
       <c r="C114" s="5"/>
-      <c r="H114" s="64"/>
-      <c r="I114" s="66" t="s">
-        <v>15</v>
-      </c>
-      <c r="J114" s="68"/>
-      <c r="K114" s="67">
-        <f>K111-K113</f>
-        <v>338050.98482284159</v>
-      </c>
-      <c r="L114" s="68">
-        <f>K114/K112*100</f>
-        <v>169.0254924114208</v>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="J114" s="65"/>
+      <c r="K114" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="L114" s="65" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="115" spans="3:12">
       <c r="C115" s="5"/>
       <c r="H115" s="64"/>
       <c r="I115" s="66" t="s">
-        <v>20</v>
-      </c>
-      <c r="J115" s="68"/>
+        <v>13</v>
+      </c>
+      <c r="J115" s="67"/>
       <c r="K115" s="67">
-        <f>L115*K112/100</f>
-        <v>4000</v>
-      </c>
-      <c r="L115" s="68">
-        <v>2</v>
-      </c>
+        <f>+K112</f>
+        <v>461715.70282650145</v>
+      </c>
+      <c r="L115" s="67"/>
     </row>
     <row r="116" spans="3:12">
       <c r="C116" s="5"/>
-      <c r="H116" s="63"/>
+      <c r="H116" s="64"/>
       <c r="I116" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="J116" s="68"/>
+      <c r="K116" s="67">
+        <v>200000</v>
+      </c>
+      <c r="L116" s="68">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" spans="3:12">
+      <c r="C117" s="5"/>
+      <c r="H117" s="64"/>
+      <c r="I117" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="J117" s="68"/>
+      <c r="K117" s="67">
+        <f>0.95*K116</f>
+        <v>190000</v>
+      </c>
+      <c r="L117" s="68">
+        <f>K117/K115*100</f>
+        <v>41.150863797109402</v>
+      </c>
+    </row>
+    <row r="118" spans="3:12">
+      <c r="C118" s="5"/>
+      <c r="H118" s="64"/>
+      <c r="I118" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="J118" s="68"/>
+      <c r="K118" s="67">
+        <f>K115-K117</f>
+        <v>271715.70282650145</v>
+      </c>
+      <c r="L118" s="68">
+        <f>K118/K116*100</f>
+        <v>135.85785141325073</v>
+      </c>
+    </row>
+    <row r="119" spans="3:12">
+      <c r="C119" s="5"/>
+      <c r="H119" s="64"/>
+      <c r="I119" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="J119" s="68"/>
+      <c r="K119" s="67">
+        <f>L119*K116/100</f>
+        <v>4000</v>
+      </c>
+      <c r="L119" s="68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="3:12">
+      <c r="C120" s="5"/>
+      <c r="H120" s="63"/>
+      <c r="I120" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="J116" s="68"/>
-      <c r="K116" s="68">
-        <f>L116*K112/100</f>
+      <c r="J120" s="68"/>
+      <c r="K120" s="68">
+        <f>L120*K116/100</f>
         <v>6000</v>
       </c>
-      <c r="L116" s="68">
+      <c r="L120" s="68">
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="3:12">
-      <c r="G117" s="62"/>
+    <row r="121" spans="3:12">
+      <c r="G121" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -9684,242 +9815,242 @@
     <oddHeader>&amp;RPage &amp;P of &amp;N</oddHeader>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="72" max="11" man="1"/>
-    <brk id="108" max="11" man="1"/>
+    <brk id="74" max="11" man="1"/>
+    <brk id="112" max="11" man="1"/>
   </rowBreaks>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <col min="2" max="3" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="3" width="13.85546875" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21">
-      <c r="A1" s="114">
+    <row r="1" spans="1:8" ht="19.5">
+      <c r="A1" s="91">
         <v>152</v>
       </c>
-      <c r="B1" s="115" t="s">
+      <c r="B1" s="138" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.6">
-      <c r="A2" s="117" t="s">
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75">
+      <c r="A2" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="140" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-    </row>
-    <row r="3" spans="1:8" ht="64.8">
-      <c r="A3" s="118"/>
-      <c r="B3" s="119" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+    </row>
+    <row r="3" spans="1:8" ht="31.5">
+      <c r="A3" s="93"/>
+      <c r="B3" s="94" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="119" t="s">
+      <c r="C3" s="94" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="119" t="s">
+      <c r="D3" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="119" t="s">
+      <c r="E3" s="94" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="119" t="s">
+      <c r="F3" s="94" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="119" t="s">
+      <c r="G3" s="94" t="s">
         <v>117</v>
       </c>
-      <c r="H3" s="119" t="s">
+      <c r="H3" s="94" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16.8">
-      <c r="A4" s="118"/>
-      <c r="B4" s="120" t="s">
+    <row r="4" spans="1:8" ht="16.5">
+      <c r="A4" s="93"/>
+      <c r="B4" s="142" t="s">
         <v>119</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="122">
+      <c r="D4" s="96">
         <v>0.5</v>
       </c>
-      <c r="E4" s="123" t="s">
+      <c r="E4" s="97" t="s">
         <v>121</v>
       </c>
-      <c r="F4" s="124">
+      <c r="F4" s="98">
         <v>1245</v>
       </c>
-      <c r="G4" s="124">
+      <c r="G4" s="98">
         <f>FLOOR(D4*F4,0.01)</f>
         <v>622.5</v>
       </c>
-      <c r="H4" s="125"/>
-    </row>
-    <row r="5" spans="1:8" ht="18">
-      <c r="A5" s="118"/>
-      <c r="B5" s="142"/>
-      <c r="C5" s="126" t="s">
+      <c r="H4" s="99"/>
+    </row>
+    <row r="5" spans="1:8" ht="16.5">
+      <c r="A5" s="93"/>
+      <c r="B5" s="143"/>
+      <c r="C5" s="100" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="127">
+      <c r="D5" s="101">
         <v>1</v>
       </c>
-      <c r="E5" s="126" t="s">
+      <c r="E5" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="128">
+      <c r="F5" s="102">
         <v>935</v>
       </c>
-      <c r="G5" s="128">
+      <c r="G5" s="102">
         <f>FLOOR(D5*F5,0.01)</f>
         <v>935</v>
       </c>
-      <c r="H5" s="129">
+      <c r="H5" s="103">
         <f>SUM(G4+G5)</f>
         <v>1557.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18">
-      <c r="A6" s="118"/>
-      <c r="B6" s="130" t="s">
+    <row r="6" spans="1:8" ht="16.5">
+      <c r="A6" s="93"/>
+      <c r="B6" s="144" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="123" t="s">
+      <c r="C6" s="97" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="122">
+      <c r="D6" s="96">
         <f>420*0</f>
         <v>0</v>
       </c>
-      <c r="E6" s="123" t="s">
+      <c r="E6" s="97" t="s">
         <v>125</v>
       </c>
-      <c r="F6" s="131">
+      <c r="F6" s="104">
         <v>15.145</v>
       </c>
-      <c r="G6" s="132">
+      <c r="G6" s="105">
         <f>FLOOR(D6*F6,0.01)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="125"/>
-    </row>
-    <row r="7" spans="1:8" ht="18">
-      <c r="A7" s="118"/>
-      <c r="B7" s="141"/>
-      <c r="C7" s="126" t="s">
+      <c r="H6" s="99"/>
+    </row>
+    <row r="7" spans="1:8" ht="16.5">
+      <c r="A7" s="93"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="100" t="s">
         <v>126</v>
       </c>
-      <c r="D7" s="127">
+      <c r="D7" s="101">
         <f>0.71*0</f>
         <v>0</v>
       </c>
-      <c r="E7" s="126" t="s">
+      <c r="E7" s="100" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="128">
+      <c r="F7" s="102">
         <v>3177.9</v>
       </c>
-      <c r="G7" s="128">
+      <c r="G7" s="102">
         <f>FLOOR(D7*F7,0.01)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="133">
+      <c r="H7" s="106">
         <f>SUM(G6:G7)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="20.399999999999999">
-      <c r="A8" s="118"/>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="134" t="s">
+    <row r="8" spans="1:8" ht="16.5">
+      <c r="A8" s="93"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="107" t="s">
         <v>128</v>
       </c>
-      <c r="G8" s="135"/>
-      <c r="H8" s="128">
+      <c r="G8" s="108"/>
+      <c r="H8" s="102">
         <f>SUM(H7,H5)</f>
         <v>1557.5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="20.399999999999999">
-      <c r="A9" s="118"/>
-      <c r="B9" s="118" t="s">
+    <row r="9" spans="1:8" ht="16.5">
+      <c r="A9" s="93"/>
+      <c r="B9" s="93" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="134" t="s">
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="107" t="s">
         <v>130</v>
       </c>
-      <c r="G9" s="135"/>
-      <c r="H9" s="136">
+      <c r="G9" s="108"/>
+      <c r="H9" s="109">
         <f>FLOOR(H8*0.15,0.01)</f>
         <v>233.62</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="20.399999999999999">
-      <c r="A10" s="137"/>
-      <c r="B10" s="138">
+    <row r="10" spans="1:8" ht="16.5">
+      <c r="A10" s="110"/>
+      <c r="B10" s="111">
         <f>+H10</f>
         <v>1791.12</v>
       </c>
-      <c r="C10" s="139" t="s">
+      <c r="C10" s="112" t="s">
         <v>131</v>
       </c>
-      <c r="D10" s="136">
+      <c r="D10" s="109">
         <f>INT(B10/B11*100)/100</f>
         <v>179.11</v>
       </c>
-      <c r="E10" s="118" t="s">
+      <c r="E10" s="93" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="134" t="s">
+      <c r="F10" s="107" t="s">
         <v>133</v>
       </c>
-      <c r="G10" s="135"/>
-      <c r="H10" s="136">
+      <c r="G10" s="108"/>
+      <c r="H10" s="109">
         <f>SUM(H8:H9)</f>
         <v>1791.12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="16.8">
-      <c r="A11" s="118"/>
-      <c r="B11" s="140">
+    <row r="11" spans="1:8" ht="15.75">
+      <c r="A11" s="93"/>
+      <c r="B11" s="113">
         <v>10</v>
       </c>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="118"/>
-      <c r="F11" s="118"/>
-      <c r="G11" s="118"/>
-      <c r="H11" s="118"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/बजेट माग estimate/Swasthya chauki/water tank 2082_2083.xlsx
+++ b/बजेट माग estimate/Swasthya chauki/water tank 2082_2083.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\बजेट माग estimate\Swasthya chauki\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\082_083\ward1\बजेट माग estimate\Swasthya chauki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CB71DE-6F9E-4F38-8020-C2AA8868A1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="0" windowWidth="15120" windowHeight="10905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-132" yWindow="0" windowWidth="15120" windowHeight="10908" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ESTIMATE" sheetId="25" r:id="rId1"/>
@@ -24,12 +23,12 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">ESTIMATE!$A$1:$L$71</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">me!$A$1:$L$112</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">me!$A$1:$L$154</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">ESTIMATE!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">me!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">WCR!$1:$11</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -45,12 +44,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>DELL</author>
   </authors>
   <commentList>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="F10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -74,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="G10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -103,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="171">
   <si>
     <t>S.N.</t>
   </si>
@@ -622,43 +621,132 @@
     <t>-deduction for opening</t>
   </si>
   <si>
-    <t>e'O{+tNnfdf lrDgL e§fsf] O{+6fsf] uf/f] l;d]G6 d;nf -!M^_ df</t>
-  </si>
-  <si>
     <t>-at water tank</t>
   </si>
   <si>
     <t>-At shear wall</t>
+  </si>
+  <si>
+    <t>-at floor</t>
+  </si>
+  <si>
+    <r>
+      <t>kf]/l;lng Un]H8 6fO{n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Ordinary floor and Wall Tile-as per approved standard of manufactured country</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t xml:space="preserve"> !M$ l;d]G6 afn'jfdf 5fKg] sfd .</t>
+    </r>
+  </si>
+  <si>
+    <t>vat on porcelain glazed tile</t>
+  </si>
+  <si>
+    <t>vat on white cement</t>
+  </si>
+  <si>
+    <t>#*X&amp;% dL=dL=lr/fg ;fn sf7sf] k|m]d $ dL=dL= P]gf vfkf agfO</t>
+  </si>
+  <si>
+    <t>-at swasthya prasasan</t>
+  </si>
+  <si>
+    <t>vat on materials</t>
+  </si>
+  <si>
+    <t>$ dL=dL= df]6fO{sf] P]gf sf7sf] lni6L nufO{ hf]8\g] sfd</t>
+  </si>
+  <si>
+    <t>-at ward rooms</t>
+  </si>
+  <si>
+    <t>-near ladder of swasthya</t>
+  </si>
+  <si>
+    <t>-ladder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kmnfd] 3'Dg] e¥ofË M $Æ–^Æ Ø ;Ddsf] dWod &gt;]0fLsf] sfnf] kfO{k kf]i6 k|of]u u/ #÷$Æx#÷$Æ sf] :Sjfo/ kfO{k df !!÷$ÆØ sf] dWod &gt;]0fLsf] sfnf] kfO{ksf] x\of08/]n  k|of]u u/L @Ú–)Æ  b]lv @Ú–^Æ rf}8fO{;Ddsf] kmnfd] 3'Dg] e¥ofË cfjZos ;fdu|Lx? ;lxt </t>
+  </si>
+  <si>
+    <t>rm</t>
+  </si>
+  <si>
+    <t>-!M@ efudf jf6/ k|'km sDkfp08 ld;fO{ 8]Dk k|'lkm+Ë ug</t>
+  </si>
+  <si>
+    <t>Provisional sum for unforseen works</t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">e'O{+tNnfdf lrDgL e§fsf] O{+6fsf] uf/f] l;d]G6 d;nf -!M^_ df </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>as per site engineer</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ps sf]6 jf6/ k|'km l;d]G6 sf]6 nufpg] sfd </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b'O{ sf]6 Knfli6s O{dNzg k]G6 nufpg] sfd -k|fOd/ ;lxt_ </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="21">
-    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="#."/>
-    <numFmt numFmtId="168" formatCode="0.00_)"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_ * #,##0_)&quot;$&quot;_ ;_ * \(#,##0\)&quot;$&quot;_ ;_ * &quot;-&quot;_)&quot;$&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="172" formatCode="General_)"/>
-    <numFmt numFmtId="173" formatCode="_ * #,##0_)_$_ ;_ * \(#,##0\)_$_ ;_ * &quot;-&quot;_)_$_ ;_ @_ "/>
-    <numFmt numFmtId="174" formatCode="_ * #,##0.00_)&quot;$&quot;_ ;_ * \(#,##0.00\)&quot;$&quot;_ ;_ * &quot;-&quot;??_)&quot;$&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="175" formatCode="_ * #,##0.00_)_$_ ;_ * \(#,##0.00\)_$_ ;_ * &quot;-&quot;??_)_$_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="mmmm\ d\,\ yyyy"/>
-    <numFmt numFmtId="177" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#.##0\)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="_ &quot;\&quot;* #,##0_ ;_ &quot;\&quot;* \-#,##0_ ;_ &quot;\&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="181" formatCode="_ &quot;\&quot;* #,##0.00_ ;_ &quot;\&quot;* \-#,##0.00_ ;_ &quot;\&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="182" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="#."/>
+    <numFmt numFmtId="169" formatCode="0.00_)"/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_ * #,##0_)&quot;$&quot;_ ;_ * \(#,##0\)&quot;$&quot;_ ;_ * &quot;-&quot;_)&quot;$&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="173" formatCode="General_)"/>
+    <numFmt numFmtId="174" formatCode="_ * #,##0_)_$_ ;_ * \(#,##0\)_$_ ;_ * &quot;-&quot;_)_$_ ;_ @_ "/>
+    <numFmt numFmtId="175" formatCode="_ * #,##0.00_)&quot;$&quot;_ ;_ * \(#,##0.00\)&quot;$&quot;_ ;_ * &quot;-&quot;??_)&quot;$&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_)_$_ ;_ * \(#,##0.00\)_$_ ;_ * &quot;-&quot;??_)_$_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="mmmm\ d\,\ yyyy"/>
+    <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#.##0\)"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="181" formatCode="_ &quot;\&quot;* #,##0_ ;_ &quot;\&quot;* \-#,##0_ ;_ &quot;\&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="182" formatCode="_ &quot;\&quot;* #,##0.00_ ;_ &quot;\&quot;* \-#,##0.00_ ;_ &quot;\&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="183" formatCode="0.0"/>
   </numFmts>
-  <fonts count="86">
+  <fonts count="87">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1157,6 +1245,11 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1889,7 +1982,7 @@
   </borders>
   <cellStyleXfs count="759">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1917,35 +2010,35 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -1971,7 +2064,7 @@
     <xf numFmtId="10" fontId="5" fillId="24" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -2020,10 +2113,10 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -2392,41 +2485,41 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyNumberFormat="0" applyFont="0">
       <alignment horizontal="center" vertical="justify"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="166" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="167" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="174" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="175" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
-    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="5" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="15"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="14" fontId="34" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="38" fontId="29" fillId="0" borderId="16">
       <alignment vertical="center"/>
@@ -2440,11 +2533,11 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="175" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
@@ -2474,12 +2567,12 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="29" borderId="15"/>
     <xf numFmtId="0" fontId="45" fillId="27" borderId="15"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="175" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="172" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -2523,10 +2616,10 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="179" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="180" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="181" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="47" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -2675,41 +2768,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="57" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="57" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="58" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2719,7 +2812,7 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="49" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="49" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2729,14 +2822,14 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="49" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="49" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="49" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="49" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2785,24 +2878,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="65" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="65" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="65" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="48" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2846,15 +2939,15 @@
     <xf numFmtId="0" fontId="66" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="43" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="51" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="51" fillId="2" borderId="23" xfId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2888,10 +2981,10 @@
     <xf numFmtId="0" fontId="67" fillId="2" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="51" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="51" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="51" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="51" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2906,7 +2999,7 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="49" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="49" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2976,7 +3069,7 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="51" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="51" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="51" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2995,6 +3088,64 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="51" fillId="33" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="183" fontId="51" fillId="33" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="51" fillId="33" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="52" fillId="33" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="183" fontId="52" fillId="33" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="52" fillId="33" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="justify"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="33" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="33" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="33" borderId="23" xfId="734" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="33" borderId="23" xfId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3013,6 +3164,24 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3028,24 +3197,6 @@
     <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3070,824 +3221,773 @@
     <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="51" fillId="33" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="51" fillId="33" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="52" fillId="33" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="51" fillId="33" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="182" fontId="52" fillId="33" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="52" fillId="33" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="justify"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="33" borderId="23" xfId="734" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="23" xfId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="70" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="759">
-    <cellStyle name="??" xfId="476" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="?? [0.00]_PERSONAL" xfId="477" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="???? [0.00]_PERSONAL" xfId="478" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="????_PERSONAL" xfId="479" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="??_PERSONAL" xfId="480" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="20% - Accent1 10" xfId="457" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="20% - Accent1 11" xfId="592" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="20% - Accent1 12" xfId="638" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="20% - Accent1 13" xfId="724" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="20% - Accent1 3" xfId="138" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="20% - Accent1 4" xfId="209" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="20% - Accent1 5" xfId="241" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="20% - Accent1 6" xfId="267" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="20% - Accent1 7" xfId="328" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="20% - Accent1 8" xfId="370" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="20% - Accent1 9" xfId="396" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="20% - Accent2 10" xfId="467" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="20% - Accent2 11" xfId="593" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="20% - Accent2 12" xfId="639" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="20% - Accent2 13" xfId="723" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="20% - Accent2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="20% - Accent2 3" xfId="139" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="20% - Accent2 4" xfId="222" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="20% - Accent2 5" xfId="251" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="20% - Accent2 6" xfId="268" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="20% - Accent2 7" xfId="340" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="20% - Accent2 8" xfId="380" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="20% - Accent2 9" xfId="397" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="20% - Accent3 10" xfId="456" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="20% - Accent3 11" xfId="594" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="20% - Accent3 12" xfId="640" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="20% - Accent3 13" xfId="722" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="20% - Accent3 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="20% - Accent3 3" xfId="140" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="20% - Accent3 4" xfId="208" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="20% - Accent3 5" xfId="240" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="20% - Accent3 6" xfId="269" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="20% - Accent3 7" xfId="327" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="20% - Accent3 8" xfId="369" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="20% - Accent3 9" xfId="398" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="20% - Accent4 10" xfId="455" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="20% - Accent4 11" xfId="595" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="20% - Accent4 12" xfId="641" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="20% - Accent4 13" xfId="721" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="20% - Accent4 2" xfId="5" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="20% - Accent4 3" xfId="141" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="20% - Accent4 4" xfId="207" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="20% - Accent4 5" xfId="239" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="20% - Accent4 6" xfId="270" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="20% - Accent4 7" xfId="326" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="20% - Accent4 8" xfId="368" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="20% - Accent4 9" xfId="399" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="20% - Accent5 10" xfId="452" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="20% - Accent5 11" xfId="596" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="20% - Accent5 12" xfId="642" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="20% - Accent5 13" xfId="720" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="20% - Accent5 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="20% - Accent5 3" xfId="142" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="20% - Accent5 4" xfId="204" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="20% - Accent5 5" xfId="236" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="20% - Accent5 6" xfId="271" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="20% - Accent5 7" xfId="325" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="20% - Accent5 8" xfId="365" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="20% - Accent5 9" xfId="400" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="20% - Accent6 10" xfId="451" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="20% - Accent6 11" xfId="597" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="20% - Accent6 12" xfId="643" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="20% - Accent6 13" xfId="719" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="20% - Accent6 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="20% - Accent6 3" xfId="143" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="20% - Accent6 4" xfId="231" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="20% - Accent6 5" xfId="260" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="20% - Accent6 6" xfId="272" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="20% - Accent6 7" xfId="324" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="20% - Accent6 8" xfId="389" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="20% - Accent6 9" xfId="401" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="40% - Accent1 10" xfId="466" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="40% - Accent1 11" xfId="598" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="40% - Accent1 12" xfId="644" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="40% - Accent1 13" xfId="718" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="40% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="40% - Accent1 3" xfId="144" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="40% - Accent1 4" xfId="203" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="40% - Accent1 5" xfId="235" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="40% - Accent1 6" xfId="273" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="40% - Accent1 7" xfId="348" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="40% - Accent1 8" xfId="364" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="40% - Accent1 9" xfId="402" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="40% - Accent2 10" xfId="450" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="40% - Accent2 11" xfId="599" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="40% - Accent2 12" xfId="645" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="40% - Accent2 13" xfId="717" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="40% - Accent2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="40% - Accent2 3" xfId="145" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="40% - Accent2 4" xfId="221" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="40% - Accent2 5" xfId="250" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="40% - Accent2 6" xfId="274" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="40% - Accent2 7" xfId="351" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="40% - Accent2 8" xfId="379" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="40% - Accent2 9" xfId="403" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="40% - Accent3 10" xfId="449" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="40% - Accent3 11" xfId="600" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="40% - Accent3 12" xfId="646" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="40% - Accent3 13" xfId="716" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="40% - Accent3 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="40% - Accent3 3" xfId="146" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="40% - Accent3 4" xfId="202" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="40% - Accent3 5" xfId="234" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="40% - Accent3 6" xfId="275" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="40% - Accent3 7" xfId="347" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="40% - Accent3 8" xfId="363" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="40% - Accent3 9" xfId="404" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="40% - Accent4 10" xfId="469" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="40% - Accent4 11" xfId="601" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="40% - Accent4 12" xfId="647" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="40% - Accent4 13" xfId="715" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="40% - Accent4 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="40% - Accent4 3" xfId="147" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="40% - Accent4 4" xfId="201" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
-    <cellStyle name="40% - Accent4 5" xfId="233" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
-    <cellStyle name="40% - Accent4 6" xfId="276" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
-    <cellStyle name="40% - Accent4 7" xfId="323" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
-    <cellStyle name="40% - Accent4 8" xfId="362" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
-    <cellStyle name="40% - Accent4 9" xfId="405" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
-    <cellStyle name="40% - Accent5 10" xfId="448" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
-    <cellStyle name="40% - Accent5 11" xfId="602" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="40% - Accent5 12" xfId="648" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
-    <cellStyle name="40% - Accent5 13" xfId="714" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
-    <cellStyle name="40% - Accent5 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
-    <cellStyle name="40% - Accent5 3" xfId="148" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
-    <cellStyle name="40% - Accent5 4" xfId="224" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
-    <cellStyle name="40% - Accent5 5" xfId="253" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
-    <cellStyle name="40% - Accent5 6" xfId="277" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="40% - Accent5 7" xfId="322" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
-    <cellStyle name="40% - Accent5 8" xfId="382" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
-    <cellStyle name="40% - Accent5 9" xfId="406" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
-    <cellStyle name="40% - Accent6 10" xfId="465" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
-    <cellStyle name="40% - Accent6 11" xfId="603" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
-    <cellStyle name="40% - Accent6 12" xfId="649" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
-    <cellStyle name="40% - Accent6 13" xfId="713" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
-    <cellStyle name="40% - Accent6 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
-    <cellStyle name="40% - Accent6 3" xfId="149" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
-    <cellStyle name="40% - Accent6 4" xfId="200" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
-    <cellStyle name="40% - Accent6 5" xfId="232" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
-    <cellStyle name="40% - Accent6 6" xfId="278" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
-    <cellStyle name="40% - Accent6 7" xfId="321" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
-    <cellStyle name="40% - Accent6 8" xfId="361" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
-    <cellStyle name="40% - Accent6 9" xfId="407" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
-    <cellStyle name="60% - Accent1 10" xfId="447" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
-    <cellStyle name="60% - Accent1 11" xfId="604" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
-    <cellStyle name="60% - Accent1 12" xfId="650" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
-    <cellStyle name="60% - Accent1 13" xfId="712" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
-    <cellStyle name="60% - Accent1 2" xfId="14" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
-    <cellStyle name="60% - Accent1 3" xfId="150" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
-    <cellStyle name="60% - Accent1 4" xfId="220" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
-    <cellStyle name="60% - Accent1 5" xfId="249" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
-    <cellStyle name="60% - Accent1 6" xfId="279" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
-    <cellStyle name="60% - Accent1 7" xfId="339" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
-    <cellStyle name="60% - Accent1 8" xfId="378" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
-    <cellStyle name="60% - Accent1 9" xfId="408" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
-    <cellStyle name="60% - Accent2 10" xfId="446" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
-    <cellStyle name="60% - Accent2 11" xfId="605" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
-    <cellStyle name="60% - Accent2 12" xfId="651" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
-    <cellStyle name="60% - Accent2 13" xfId="711" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
-    <cellStyle name="60% - Accent2 2" xfId="15" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
-    <cellStyle name="60% - Accent2 3" xfId="151" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
-    <cellStyle name="60% - Accent2 4" xfId="199" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
-    <cellStyle name="60% - Accent2 5" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
-    <cellStyle name="60% - Accent2 6" xfId="280" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
-    <cellStyle name="60% - Accent2 7" xfId="320" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
-    <cellStyle name="60% - Accent2 8" xfId="360" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
-    <cellStyle name="60% - Accent2 9" xfId="409" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
-    <cellStyle name="60% - Accent3 10" xfId="445" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
-    <cellStyle name="60% - Accent3 11" xfId="606" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
-    <cellStyle name="60% - Accent3 12" xfId="652" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
-    <cellStyle name="60% - Accent3 13" xfId="710" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
-    <cellStyle name="60% - Accent3 2" xfId="16" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
-    <cellStyle name="60% - Accent3 3" xfId="152" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
-    <cellStyle name="60% - Accent3 4" xfId="198" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
-    <cellStyle name="60% - Accent3 5" xfId="166" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
-    <cellStyle name="60% - Accent3 6" xfId="281" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
-    <cellStyle name="60% - Accent3 7" xfId="350" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
-    <cellStyle name="60% - Accent3 8" xfId="359" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
-    <cellStyle name="60% - Accent3 9" xfId="410" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
-    <cellStyle name="60% - Accent4 10" xfId="444" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
-    <cellStyle name="60% - Accent4 11" xfId="607" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
-    <cellStyle name="60% - Accent4 12" xfId="653" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
-    <cellStyle name="60% - Accent4 13" xfId="698" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
-    <cellStyle name="60% - Accent4 2" xfId="17" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
-    <cellStyle name="60% - Accent4 3" xfId="153" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
-    <cellStyle name="60% - Accent4 4" xfId="197" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
-    <cellStyle name="60% - Accent4 5" xfId="167" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
-    <cellStyle name="60% - Accent4 6" xfId="282" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
-    <cellStyle name="60% - Accent4 7" xfId="319" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
-    <cellStyle name="60% - Accent4 8" xfId="358" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
-    <cellStyle name="60% - Accent4 9" xfId="411" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
-    <cellStyle name="60% - Accent5 10" xfId="471" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
-    <cellStyle name="60% - Accent5 11" xfId="608" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
-    <cellStyle name="60% - Accent5 12" xfId="654" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
-    <cellStyle name="60% - Accent5 13" xfId="688" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
-    <cellStyle name="60% - Accent5 2" xfId="18" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
-    <cellStyle name="60% - Accent5 3" xfId="154" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
-    <cellStyle name="60% - Accent5 4" xfId="196" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
-    <cellStyle name="60% - Accent5 5" xfId="213" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
-    <cellStyle name="60% - Accent5 6" xfId="283" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
-    <cellStyle name="60% - Accent5 7" xfId="349" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
-    <cellStyle name="60% - Accent5 8" xfId="357" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
-    <cellStyle name="60% - Accent5 9" xfId="412" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
-    <cellStyle name="60% - Accent6 10" xfId="474" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
-    <cellStyle name="60% - Accent6 11" xfId="609" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
-    <cellStyle name="60% - Accent6 12" xfId="655" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
-    <cellStyle name="60% - Accent6 13" xfId="693" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
-    <cellStyle name="60% - Accent6 2" xfId="19" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
-    <cellStyle name="60% - Accent6 3" xfId="155" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
-    <cellStyle name="60% - Accent6 4" xfId="227" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
-    <cellStyle name="60% - Accent6 5" xfId="256" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
-    <cellStyle name="60% - Accent6 6" xfId="284" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
-    <cellStyle name="60% - Accent6 7" xfId="318" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
-    <cellStyle name="60% - Accent6 8" xfId="385" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
-    <cellStyle name="60% - Accent6 9" xfId="413" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
-    <cellStyle name="Accent1 10" xfId="470" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
-    <cellStyle name="Accent1 11" xfId="610" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
-    <cellStyle name="Accent1 12" xfId="656" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
-    <cellStyle name="Accent1 13" xfId="687" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
-    <cellStyle name="Accent1 2" xfId="20" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
-    <cellStyle name="Accent1 3" xfId="156" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
-    <cellStyle name="Accent1 4" xfId="229" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
-    <cellStyle name="Accent1 5" xfId="258" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
-    <cellStyle name="Accent1 6" xfId="285" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
-    <cellStyle name="Accent1 7" xfId="317" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
-    <cellStyle name="Accent1 8" xfId="387" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
-    <cellStyle name="Accent1 9" xfId="414" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
-    <cellStyle name="Accent2 10" xfId="443" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
-    <cellStyle name="Accent2 11" xfId="611" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
-    <cellStyle name="Accent2 12" xfId="657" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
-    <cellStyle name="Accent2 13" xfId="686" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
-    <cellStyle name="Accent2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
-    <cellStyle name="Accent2 3" xfId="157" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
-    <cellStyle name="Accent2 4" xfId="226" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
-    <cellStyle name="Accent2 5" xfId="255" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
-    <cellStyle name="Accent2 6" xfId="286" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
-    <cellStyle name="Accent2 7" xfId="345" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
-    <cellStyle name="Accent2 8" xfId="384" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
-    <cellStyle name="Accent2 9" xfId="415" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
-    <cellStyle name="Accent3 10" xfId="442" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
-    <cellStyle name="Accent3 11" xfId="612" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
-    <cellStyle name="Accent3 12" xfId="658" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
-    <cellStyle name="Accent3 13" xfId="683" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
-    <cellStyle name="Accent3 2" xfId="22" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
-    <cellStyle name="Accent3 3" xfId="158" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
-    <cellStyle name="Accent3 4" xfId="195" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
-    <cellStyle name="Accent3 5" xfId="168" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
-    <cellStyle name="Accent3 6" xfId="287" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
-    <cellStyle name="Accent3 7" xfId="344" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
-    <cellStyle name="Accent3 8" xfId="356" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
-    <cellStyle name="Accent3 9" xfId="416" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
-    <cellStyle name="Accent4 10" xfId="441" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
-    <cellStyle name="Accent4 11" xfId="613" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
-    <cellStyle name="Accent4 12" xfId="659" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
-    <cellStyle name="Accent4 13" xfId="709" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
-    <cellStyle name="Accent4 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
-    <cellStyle name="Accent4 3" xfId="159" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
-    <cellStyle name="Accent4 4" xfId="194" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
-    <cellStyle name="Accent4 5" xfId="169" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
-    <cellStyle name="Accent4 6" xfId="288" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
-    <cellStyle name="Accent4 7" xfId="316" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
-    <cellStyle name="Accent4 8" xfId="355" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
-    <cellStyle name="Accent4 9" xfId="417" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
-    <cellStyle name="Accent5 10" xfId="464" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
-    <cellStyle name="Accent5 11" xfId="614" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
-    <cellStyle name="Accent5 12" xfId="660" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
-    <cellStyle name="Accent5 13" xfId="682" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
-    <cellStyle name="Accent5 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
-    <cellStyle name="Accent5 3" xfId="160" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
-    <cellStyle name="Accent5 4" xfId="193" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
-    <cellStyle name="Accent5 5" xfId="170" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
-    <cellStyle name="Accent5 6" xfId="289" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
-    <cellStyle name="Accent5 7" xfId="315" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
-    <cellStyle name="Accent5 8" xfId="354" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
-    <cellStyle name="Accent5 9" xfId="418" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
-    <cellStyle name="Accent6 10" xfId="440" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
-    <cellStyle name="Accent6 11" xfId="615" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
-    <cellStyle name="Accent6 12" xfId="661" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
-    <cellStyle name="Accent6 13" xfId="692" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
-    <cellStyle name="Accent6 2" xfId="25" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
-    <cellStyle name="Accent6 3" xfId="161" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
-    <cellStyle name="Accent6 4" xfId="219" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
-    <cellStyle name="Accent6 5" xfId="248" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
-    <cellStyle name="Accent6 6" xfId="290" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
-    <cellStyle name="Accent6 7" xfId="314" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
-    <cellStyle name="Accent6 8" xfId="377" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
-    <cellStyle name="Accent6 9" xfId="419" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
-    <cellStyle name="as" xfId="481" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
-    <cellStyle name="Bad 10" xfId="473" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
-    <cellStyle name="Bad 11" xfId="616" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
-    <cellStyle name="Bad 12" xfId="662" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
-    <cellStyle name="Bad 13" xfId="681" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
-    <cellStyle name="Bad 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
-    <cellStyle name="Bad 3" xfId="162" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
-    <cellStyle name="Bad 4" xfId="192" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
-    <cellStyle name="Bad 5" xfId="214" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
-    <cellStyle name="Bad 6" xfId="291" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
-    <cellStyle name="Bad 7" xfId="343" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
-    <cellStyle name="Bad 8" xfId="353" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
-    <cellStyle name="Bad 9" xfId="420" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
-    <cellStyle name="Calc Currency (0)" xfId="482" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
-    <cellStyle name="Calc Currency (2)" xfId="483" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
-    <cellStyle name="Calc Percent (0)" xfId="484" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
-    <cellStyle name="Calc Percent (1)" xfId="485" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
-    <cellStyle name="Calc Percent (2)" xfId="486" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
-    <cellStyle name="Calc Units (0)" xfId="487" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
-    <cellStyle name="Calc Units (1)" xfId="488" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
-    <cellStyle name="Calc Units (2)" xfId="489" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="Calculation 10" xfId="439" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
-    <cellStyle name="Calculation 11" xfId="617" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
-    <cellStyle name="Calculation 12" xfId="663" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
-    <cellStyle name="Calculation 13" xfId="680" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
-    <cellStyle name="Calculation 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
-    <cellStyle name="Calculation 3" xfId="163" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
-    <cellStyle name="Calculation 4" xfId="228" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
-    <cellStyle name="Calculation 5" xfId="257" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
-    <cellStyle name="Calculation 6" xfId="292" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
-    <cellStyle name="Calculation 7" xfId="313" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
-    <cellStyle name="Calculation 8" xfId="386" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
-    <cellStyle name="Calculation 9" xfId="421" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
-    <cellStyle name="Check Cell 10" xfId="472" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
-    <cellStyle name="Check Cell 11" xfId="618" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="Check Cell 12" xfId="664" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
-    <cellStyle name="Check Cell 13" xfId="708" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
-    <cellStyle name="Check Cell 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
-    <cellStyle name="Check Cell 3" xfId="164" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
-    <cellStyle name="Check Cell 4" xfId="191" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
-    <cellStyle name="Check Cell 5" xfId="171" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="Check Cell 6" xfId="293" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
-    <cellStyle name="Check Cell 7" xfId="312" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
-    <cellStyle name="Check Cell 8" xfId="352" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
-    <cellStyle name="Check Cell 9" xfId="422" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
+    <cellStyle name="??" xfId="476"/>
+    <cellStyle name="?? [0.00]_PERSONAL" xfId="477"/>
+    <cellStyle name="???? [0.00]_PERSONAL" xfId="478"/>
+    <cellStyle name="????_PERSONAL" xfId="479"/>
+    <cellStyle name="??_PERSONAL" xfId="480"/>
+    <cellStyle name="20% - Accent1 10" xfId="457"/>
+    <cellStyle name="20% - Accent1 11" xfId="592"/>
+    <cellStyle name="20% - Accent1 12" xfId="638"/>
+    <cellStyle name="20% - Accent1 13" xfId="724"/>
+    <cellStyle name="20% - Accent1 2" xfId="2"/>
+    <cellStyle name="20% - Accent1 3" xfId="138"/>
+    <cellStyle name="20% - Accent1 4" xfId="209"/>
+    <cellStyle name="20% - Accent1 5" xfId="241"/>
+    <cellStyle name="20% - Accent1 6" xfId="267"/>
+    <cellStyle name="20% - Accent1 7" xfId="328"/>
+    <cellStyle name="20% - Accent1 8" xfId="370"/>
+    <cellStyle name="20% - Accent1 9" xfId="396"/>
+    <cellStyle name="20% - Accent2 10" xfId="467"/>
+    <cellStyle name="20% - Accent2 11" xfId="593"/>
+    <cellStyle name="20% - Accent2 12" xfId="639"/>
+    <cellStyle name="20% - Accent2 13" xfId="723"/>
+    <cellStyle name="20% - Accent2 2" xfId="3"/>
+    <cellStyle name="20% - Accent2 3" xfId="139"/>
+    <cellStyle name="20% - Accent2 4" xfId="222"/>
+    <cellStyle name="20% - Accent2 5" xfId="251"/>
+    <cellStyle name="20% - Accent2 6" xfId="268"/>
+    <cellStyle name="20% - Accent2 7" xfId="340"/>
+    <cellStyle name="20% - Accent2 8" xfId="380"/>
+    <cellStyle name="20% - Accent2 9" xfId="397"/>
+    <cellStyle name="20% - Accent3 10" xfId="456"/>
+    <cellStyle name="20% - Accent3 11" xfId="594"/>
+    <cellStyle name="20% - Accent3 12" xfId="640"/>
+    <cellStyle name="20% - Accent3 13" xfId="722"/>
+    <cellStyle name="20% - Accent3 2" xfId="4"/>
+    <cellStyle name="20% - Accent3 3" xfId="140"/>
+    <cellStyle name="20% - Accent3 4" xfId="208"/>
+    <cellStyle name="20% - Accent3 5" xfId="240"/>
+    <cellStyle name="20% - Accent3 6" xfId="269"/>
+    <cellStyle name="20% - Accent3 7" xfId="327"/>
+    <cellStyle name="20% - Accent3 8" xfId="369"/>
+    <cellStyle name="20% - Accent3 9" xfId="398"/>
+    <cellStyle name="20% - Accent4 10" xfId="455"/>
+    <cellStyle name="20% - Accent4 11" xfId="595"/>
+    <cellStyle name="20% - Accent4 12" xfId="641"/>
+    <cellStyle name="20% - Accent4 13" xfId="721"/>
+    <cellStyle name="20% - Accent4 2" xfId="5"/>
+    <cellStyle name="20% - Accent4 3" xfId="141"/>
+    <cellStyle name="20% - Accent4 4" xfId="207"/>
+    <cellStyle name="20% - Accent4 5" xfId="239"/>
+    <cellStyle name="20% - Accent4 6" xfId="270"/>
+    <cellStyle name="20% - Accent4 7" xfId="326"/>
+    <cellStyle name="20% - Accent4 8" xfId="368"/>
+    <cellStyle name="20% - Accent4 9" xfId="399"/>
+    <cellStyle name="20% - Accent5 10" xfId="452"/>
+    <cellStyle name="20% - Accent5 11" xfId="596"/>
+    <cellStyle name="20% - Accent5 12" xfId="642"/>
+    <cellStyle name="20% - Accent5 13" xfId="720"/>
+    <cellStyle name="20% - Accent5 2" xfId="6"/>
+    <cellStyle name="20% - Accent5 3" xfId="142"/>
+    <cellStyle name="20% - Accent5 4" xfId="204"/>
+    <cellStyle name="20% - Accent5 5" xfId="236"/>
+    <cellStyle name="20% - Accent5 6" xfId="271"/>
+    <cellStyle name="20% - Accent5 7" xfId="325"/>
+    <cellStyle name="20% - Accent5 8" xfId="365"/>
+    <cellStyle name="20% - Accent5 9" xfId="400"/>
+    <cellStyle name="20% - Accent6 10" xfId="451"/>
+    <cellStyle name="20% - Accent6 11" xfId="597"/>
+    <cellStyle name="20% - Accent6 12" xfId="643"/>
+    <cellStyle name="20% - Accent6 13" xfId="719"/>
+    <cellStyle name="20% - Accent6 2" xfId="7"/>
+    <cellStyle name="20% - Accent6 3" xfId="143"/>
+    <cellStyle name="20% - Accent6 4" xfId="231"/>
+    <cellStyle name="20% - Accent6 5" xfId="260"/>
+    <cellStyle name="20% - Accent6 6" xfId="272"/>
+    <cellStyle name="20% - Accent6 7" xfId="324"/>
+    <cellStyle name="20% - Accent6 8" xfId="389"/>
+    <cellStyle name="20% - Accent6 9" xfId="401"/>
+    <cellStyle name="40% - Accent1 10" xfId="466"/>
+    <cellStyle name="40% - Accent1 11" xfId="598"/>
+    <cellStyle name="40% - Accent1 12" xfId="644"/>
+    <cellStyle name="40% - Accent1 13" xfId="718"/>
+    <cellStyle name="40% - Accent1 2" xfId="8"/>
+    <cellStyle name="40% - Accent1 3" xfId="144"/>
+    <cellStyle name="40% - Accent1 4" xfId="203"/>
+    <cellStyle name="40% - Accent1 5" xfId="235"/>
+    <cellStyle name="40% - Accent1 6" xfId="273"/>
+    <cellStyle name="40% - Accent1 7" xfId="348"/>
+    <cellStyle name="40% - Accent1 8" xfId="364"/>
+    <cellStyle name="40% - Accent1 9" xfId="402"/>
+    <cellStyle name="40% - Accent2 10" xfId="450"/>
+    <cellStyle name="40% - Accent2 11" xfId="599"/>
+    <cellStyle name="40% - Accent2 12" xfId="645"/>
+    <cellStyle name="40% - Accent2 13" xfId="717"/>
+    <cellStyle name="40% - Accent2 2" xfId="9"/>
+    <cellStyle name="40% - Accent2 3" xfId="145"/>
+    <cellStyle name="40% - Accent2 4" xfId="221"/>
+    <cellStyle name="40% - Accent2 5" xfId="250"/>
+    <cellStyle name="40% - Accent2 6" xfId="274"/>
+    <cellStyle name="40% - Accent2 7" xfId="351"/>
+    <cellStyle name="40% - Accent2 8" xfId="379"/>
+    <cellStyle name="40% - Accent2 9" xfId="403"/>
+    <cellStyle name="40% - Accent3 10" xfId="449"/>
+    <cellStyle name="40% - Accent3 11" xfId="600"/>
+    <cellStyle name="40% - Accent3 12" xfId="646"/>
+    <cellStyle name="40% - Accent3 13" xfId="716"/>
+    <cellStyle name="40% - Accent3 2" xfId="10"/>
+    <cellStyle name="40% - Accent3 3" xfId="146"/>
+    <cellStyle name="40% - Accent3 4" xfId="202"/>
+    <cellStyle name="40% - Accent3 5" xfId="234"/>
+    <cellStyle name="40% - Accent3 6" xfId="275"/>
+    <cellStyle name="40% - Accent3 7" xfId="347"/>
+    <cellStyle name="40% - Accent3 8" xfId="363"/>
+    <cellStyle name="40% - Accent3 9" xfId="404"/>
+    <cellStyle name="40% - Accent4 10" xfId="469"/>
+    <cellStyle name="40% - Accent4 11" xfId="601"/>
+    <cellStyle name="40% - Accent4 12" xfId="647"/>
+    <cellStyle name="40% - Accent4 13" xfId="715"/>
+    <cellStyle name="40% - Accent4 2" xfId="11"/>
+    <cellStyle name="40% - Accent4 3" xfId="147"/>
+    <cellStyle name="40% - Accent4 4" xfId="201"/>
+    <cellStyle name="40% - Accent4 5" xfId="233"/>
+    <cellStyle name="40% - Accent4 6" xfId="276"/>
+    <cellStyle name="40% - Accent4 7" xfId="323"/>
+    <cellStyle name="40% - Accent4 8" xfId="362"/>
+    <cellStyle name="40% - Accent4 9" xfId="405"/>
+    <cellStyle name="40% - Accent5 10" xfId="448"/>
+    <cellStyle name="40% - Accent5 11" xfId="602"/>
+    <cellStyle name="40% - Accent5 12" xfId="648"/>
+    <cellStyle name="40% - Accent5 13" xfId="714"/>
+    <cellStyle name="40% - Accent5 2" xfId="12"/>
+    <cellStyle name="40% - Accent5 3" xfId="148"/>
+    <cellStyle name="40% - Accent5 4" xfId="224"/>
+    <cellStyle name="40% - Accent5 5" xfId="253"/>
+    <cellStyle name="40% - Accent5 6" xfId="277"/>
+    <cellStyle name="40% - Accent5 7" xfId="322"/>
+    <cellStyle name="40% - Accent5 8" xfId="382"/>
+    <cellStyle name="40% - Accent5 9" xfId="406"/>
+    <cellStyle name="40% - Accent6 10" xfId="465"/>
+    <cellStyle name="40% - Accent6 11" xfId="603"/>
+    <cellStyle name="40% - Accent6 12" xfId="649"/>
+    <cellStyle name="40% - Accent6 13" xfId="713"/>
+    <cellStyle name="40% - Accent6 2" xfId="13"/>
+    <cellStyle name="40% - Accent6 3" xfId="149"/>
+    <cellStyle name="40% - Accent6 4" xfId="200"/>
+    <cellStyle name="40% - Accent6 5" xfId="232"/>
+    <cellStyle name="40% - Accent6 6" xfId="278"/>
+    <cellStyle name="40% - Accent6 7" xfId="321"/>
+    <cellStyle name="40% - Accent6 8" xfId="361"/>
+    <cellStyle name="40% - Accent6 9" xfId="407"/>
+    <cellStyle name="60% - Accent1 10" xfId="447"/>
+    <cellStyle name="60% - Accent1 11" xfId="604"/>
+    <cellStyle name="60% - Accent1 12" xfId="650"/>
+    <cellStyle name="60% - Accent1 13" xfId="712"/>
+    <cellStyle name="60% - Accent1 2" xfId="14"/>
+    <cellStyle name="60% - Accent1 3" xfId="150"/>
+    <cellStyle name="60% - Accent1 4" xfId="220"/>
+    <cellStyle name="60% - Accent1 5" xfId="249"/>
+    <cellStyle name="60% - Accent1 6" xfId="279"/>
+    <cellStyle name="60% - Accent1 7" xfId="339"/>
+    <cellStyle name="60% - Accent1 8" xfId="378"/>
+    <cellStyle name="60% - Accent1 9" xfId="408"/>
+    <cellStyle name="60% - Accent2 10" xfId="446"/>
+    <cellStyle name="60% - Accent2 11" xfId="605"/>
+    <cellStyle name="60% - Accent2 12" xfId="651"/>
+    <cellStyle name="60% - Accent2 13" xfId="711"/>
+    <cellStyle name="60% - Accent2 2" xfId="15"/>
+    <cellStyle name="60% - Accent2 3" xfId="151"/>
+    <cellStyle name="60% - Accent2 4" xfId="199"/>
+    <cellStyle name="60% - Accent2 5" xfId="165"/>
+    <cellStyle name="60% - Accent2 6" xfId="280"/>
+    <cellStyle name="60% - Accent2 7" xfId="320"/>
+    <cellStyle name="60% - Accent2 8" xfId="360"/>
+    <cellStyle name="60% - Accent2 9" xfId="409"/>
+    <cellStyle name="60% - Accent3 10" xfId="445"/>
+    <cellStyle name="60% - Accent3 11" xfId="606"/>
+    <cellStyle name="60% - Accent3 12" xfId="652"/>
+    <cellStyle name="60% - Accent3 13" xfId="710"/>
+    <cellStyle name="60% - Accent3 2" xfId="16"/>
+    <cellStyle name="60% - Accent3 3" xfId="152"/>
+    <cellStyle name="60% - Accent3 4" xfId="198"/>
+    <cellStyle name="60% - Accent3 5" xfId="166"/>
+    <cellStyle name="60% - Accent3 6" xfId="281"/>
+    <cellStyle name="60% - Accent3 7" xfId="350"/>
+    <cellStyle name="60% - Accent3 8" xfId="359"/>
+    <cellStyle name="60% - Accent3 9" xfId="410"/>
+    <cellStyle name="60% - Accent4 10" xfId="444"/>
+    <cellStyle name="60% - Accent4 11" xfId="607"/>
+    <cellStyle name="60% - Accent4 12" xfId="653"/>
+    <cellStyle name="60% - Accent4 13" xfId="698"/>
+    <cellStyle name="60% - Accent4 2" xfId="17"/>
+    <cellStyle name="60% - Accent4 3" xfId="153"/>
+    <cellStyle name="60% - Accent4 4" xfId="197"/>
+    <cellStyle name="60% - Accent4 5" xfId="167"/>
+    <cellStyle name="60% - Accent4 6" xfId="282"/>
+    <cellStyle name="60% - Accent4 7" xfId="319"/>
+    <cellStyle name="60% - Accent4 8" xfId="358"/>
+    <cellStyle name="60% - Accent4 9" xfId="411"/>
+    <cellStyle name="60% - Accent5 10" xfId="471"/>
+    <cellStyle name="60% - Accent5 11" xfId="608"/>
+    <cellStyle name="60% - Accent5 12" xfId="654"/>
+    <cellStyle name="60% - Accent5 13" xfId="688"/>
+    <cellStyle name="60% - Accent5 2" xfId="18"/>
+    <cellStyle name="60% - Accent5 3" xfId="154"/>
+    <cellStyle name="60% - Accent5 4" xfId="196"/>
+    <cellStyle name="60% - Accent5 5" xfId="213"/>
+    <cellStyle name="60% - Accent5 6" xfId="283"/>
+    <cellStyle name="60% - Accent5 7" xfId="349"/>
+    <cellStyle name="60% - Accent5 8" xfId="357"/>
+    <cellStyle name="60% - Accent5 9" xfId="412"/>
+    <cellStyle name="60% - Accent6 10" xfId="474"/>
+    <cellStyle name="60% - Accent6 11" xfId="609"/>
+    <cellStyle name="60% - Accent6 12" xfId="655"/>
+    <cellStyle name="60% - Accent6 13" xfId="693"/>
+    <cellStyle name="60% - Accent6 2" xfId="19"/>
+    <cellStyle name="60% - Accent6 3" xfId="155"/>
+    <cellStyle name="60% - Accent6 4" xfId="227"/>
+    <cellStyle name="60% - Accent6 5" xfId="256"/>
+    <cellStyle name="60% - Accent6 6" xfId="284"/>
+    <cellStyle name="60% - Accent6 7" xfId="318"/>
+    <cellStyle name="60% - Accent6 8" xfId="385"/>
+    <cellStyle name="60% - Accent6 9" xfId="413"/>
+    <cellStyle name="Accent1 10" xfId="470"/>
+    <cellStyle name="Accent1 11" xfId="610"/>
+    <cellStyle name="Accent1 12" xfId="656"/>
+    <cellStyle name="Accent1 13" xfId="687"/>
+    <cellStyle name="Accent1 2" xfId="20"/>
+    <cellStyle name="Accent1 3" xfId="156"/>
+    <cellStyle name="Accent1 4" xfId="229"/>
+    <cellStyle name="Accent1 5" xfId="258"/>
+    <cellStyle name="Accent1 6" xfId="285"/>
+    <cellStyle name="Accent1 7" xfId="317"/>
+    <cellStyle name="Accent1 8" xfId="387"/>
+    <cellStyle name="Accent1 9" xfId="414"/>
+    <cellStyle name="Accent2 10" xfId="443"/>
+    <cellStyle name="Accent2 11" xfId="611"/>
+    <cellStyle name="Accent2 12" xfId="657"/>
+    <cellStyle name="Accent2 13" xfId="686"/>
+    <cellStyle name="Accent2 2" xfId="21"/>
+    <cellStyle name="Accent2 3" xfId="157"/>
+    <cellStyle name="Accent2 4" xfId="226"/>
+    <cellStyle name="Accent2 5" xfId="255"/>
+    <cellStyle name="Accent2 6" xfId="286"/>
+    <cellStyle name="Accent2 7" xfId="345"/>
+    <cellStyle name="Accent2 8" xfId="384"/>
+    <cellStyle name="Accent2 9" xfId="415"/>
+    <cellStyle name="Accent3 10" xfId="442"/>
+    <cellStyle name="Accent3 11" xfId="612"/>
+    <cellStyle name="Accent3 12" xfId="658"/>
+    <cellStyle name="Accent3 13" xfId="683"/>
+    <cellStyle name="Accent3 2" xfId="22"/>
+    <cellStyle name="Accent3 3" xfId="158"/>
+    <cellStyle name="Accent3 4" xfId="195"/>
+    <cellStyle name="Accent3 5" xfId="168"/>
+    <cellStyle name="Accent3 6" xfId="287"/>
+    <cellStyle name="Accent3 7" xfId="344"/>
+    <cellStyle name="Accent3 8" xfId="356"/>
+    <cellStyle name="Accent3 9" xfId="416"/>
+    <cellStyle name="Accent4 10" xfId="441"/>
+    <cellStyle name="Accent4 11" xfId="613"/>
+    <cellStyle name="Accent4 12" xfId="659"/>
+    <cellStyle name="Accent4 13" xfId="709"/>
+    <cellStyle name="Accent4 2" xfId="23"/>
+    <cellStyle name="Accent4 3" xfId="159"/>
+    <cellStyle name="Accent4 4" xfId="194"/>
+    <cellStyle name="Accent4 5" xfId="169"/>
+    <cellStyle name="Accent4 6" xfId="288"/>
+    <cellStyle name="Accent4 7" xfId="316"/>
+    <cellStyle name="Accent4 8" xfId="355"/>
+    <cellStyle name="Accent4 9" xfId="417"/>
+    <cellStyle name="Accent5 10" xfId="464"/>
+    <cellStyle name="Accent5 11" xfId="614"/>
+    <cellStyle name="Accent5 12" xfId="660"/>
+    <cellStyle name="Accent5 13" xfId="682"/>
+    <cellStyle name="Accent5 2" xfId="24"/>
+    <cellStyle name="Accent5 3" xfId="160"/>
+    <cellStyle name="Accent5 4" xfId="193"/>
+    <cellStyle name="Accent5 5" xfId="170"/>
+    <cellStyle name="Accent5 6" xfId="289"/>
+    <cellStyle name="Accent5 7" xfId="315"/>
+    <cellStyle name="Accent5 8" xfId="354"/>
+    <cellStyle name="Accent5 9" xfId="418"/>
+    <cellStyle name="Accent6 10" xfId="440"/>
+    <cellStyle name="Accent6 11" xfId="615"/>
+    <cellStyle name="Accent6 12" xfId="661"/>
+    <cellStyle name="Accent6 13" xfId="692"/>
+    <cellStyle name="Accent6 2" xfId="25"/>
+    <cellStyle name="Accent6 3" xfId="161"/>
+    <cellStyle name="Accent6 4" xfId="219"/>
+    <cellStyle name="Accent6 5" xfId="248"/>
+    <cellStyle name="Accent6 6" xfId="290"/>
+    <cellStyle name="Accent6 7" xfId="314"/>
+    <cellStyle name="Accent6 8" xfId="377"/>
+    <cellStyle name="Accent6 9" xfId="419"/>
+    <cellStyle name="as" xfId="481"/>
+    <cellStyle name="Bad 10" xfId="473"/>
+    <cellStyle name="Bad 11" xfId="616"/>
+    <cellStyle name="Bad 12" xfId="662"/>
+    <cellStyle name="Bad 13" xfId="681"/>
+    <cellStyle name="Bad 2" xfId="26"/>
+    <cellStyle name="Bad 3" xfId="162"/>
+    <cellStyle name="Bad 4" xfId="192"/>
+    <cellStyle name="Bad 5" xfId="214"/>
+    <cellStyle name="Bad 6" xfId="291"/>
+    <cellStyle name="Bad 7" xfId="343"/>
+    <cellStyle name="Bad 8" xfId="353"/>
+    <cellStyle name="Bad 9" xfId="420"/>
+    <cellStyle name="Calc Currency (0)" xfId="482"/>
+    <cellStyle name="Calc Currency (2)" xfId="483"/>
+    <cellStyle name="Calc Percent (0)" xfId="484"/>
+    <cellStyle name="Calc Percent (1)" xfId="485"/>
+    <cellStyle name="Calc Percent (2)" xfId="486"/>
+    <cellStyle name="Calc Units (0)" xfId="487"/>
+    <cellStyle name="Calc Units (1)" xfId="488"/>
+    <cellStyle name="Calc Units (2)" xfId="489"/>
+    <cellStyle name="Calculation 10" xfId="439"/>
+    <cellStyle name="Calculation 11" xfId="617"/>
+    <cellStyle name="Calculation 12" xfId="663"/>
+    <cellStyle name="Calculation 13" xfId="680"/>
+    <cellStyle name="Calculation 2" xfId="27"/>
+    <cellStyle name="Calculation 3" xfId="163"/>
+    <cellStyle name="Calculation 4" xfId="228"/>
+    <cellStyle name="Calculation 5" xfId="257"/>
+    <cellStyle name="Calculation 6" xfId="292"/>
+    <cellStyle name="Calculation 7" xfId="313"/>
+    <cellStyle name="Calculation 8" xfId="386"/>
+    <cellStyle name="Calculation 9" xfId="421"/>
+    <cellStyle name="Check Cell 10" xfId="472"/>
+    <cellStyle name="Check Cell 11" xfId="618"/>
+    <cellStyle name="Check Cell 12" xfId="664"/>
+    <cellStyle name="Check Cell 13" xfId="708"/>
+    <cellStyle name="Check Cell 2" xfId="28"/>
+    <cellStyle name="Check Cell 3" xfId="164"/>
+    <cellStyle name="Check Cell 4" xfId="191"/>
+    <cellStyle name="Check Cell 5" xfId="171"/>
+    <cellStyle name="Check Cell 6" xfId="293"/>
+    <cellStyle name="Check Cell 7" xfId="312"/>
+    <cellStyle name="Check Cell 8" xfId="352"/>
+    <cellStyle name="Check Cell 9" xfId="422"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [00]" xfId="490" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
-    <cellStyle name="Comma 10" xfId="732" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
-    <cellStyle name="Comma 11" xfId="731" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
-    <cellStyle name="Comma 12" xfId="752" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
-    <cellStyle name="Comma 13" xfId="753" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
-    <cellStyle name="Comma 14" xfId="754" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
-    <cellStyle name="Comma 15" xfId="758" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
-    <cellStyle name="Comma 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
-    <cellStyle name="Comma 2 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
-    <cellStyle name="Comma 2 2 2" xfId="491" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
-    <cellStyle name="Comma 2 2 2 2" xfId="739" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
-    <cellStyle name="Comma 2 2 2 2 2" xfId="749" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
-    <cellStyle name="Comma 2 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
-    <cellStyle name="Comma 2 3 2" xfId="109" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
-    <cellStyle name="Comma 2 4" xfId="492" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
-    <cellStyle name="Comma 2 5" xfId="737" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
-    <cellStyle name="Comma 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
-    <cellStyle name="Comma 3 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
-    <cellStyle name="Comma 3 2 2" xfId="493" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
-    <cellStyle name="Comma 3 3" xfId="34" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
-    <cellStyle name="Comma 3 4" xfId="110" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
-    <cellStyle name="Comma 3 5" xfId="745" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
-    <cellStyle name="Comma 4" xfId="35" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
-    <cellStyle name="Comma 4 2" xfId="36" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
-    <cellStyle name="Comma 4 3" xfId="111" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
-    <cellStyle name="Comma 4 4" xfId="747" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
-    <cellStyle name="Comma 5" xfId="37" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
-    <cellStyle name="Comma 5 2" xfId="494" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
-    <cellStyle name="Comma 6" xfId="112" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
-    <cellStyle name="Comma 6 2" xfId="495" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
-    <cellStyle name="Comma 7" xfId="496" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
-    <cellStyle name="Comma 7 2" xfId="497" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
-    <cellStyle name="Comma 8" xfId="498" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
-    <cellStyle name="Comma 9" xfId="730" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
-    <cellStyle name="Comma0" xfId="499" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
-    <cellStyle name="Comma0 - Modelo1" xfId="500" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
-    <cellStyle name="Comma0 - Style1" xfId="501" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
-    <cellStyle name="Comma1 - Modelo2" xfId="502" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
-    <cellStyle name="Comma1 - Style2" xfId="503" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
-    <cellStyle name="ContentsHyperlink" xfId="124" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
-    <cellStyle name="Currency [00]" xfId="504" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
-    <cellStyle name="Currency0" xfId="505" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
-    <cellStyle name="Custom - Style1" xfId="506" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
-    <cellStyle name="Data   - Style2" xfId="507" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
-    <cellStyle name="Date" xfId="508" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
-    <cellStyle name="Date Short" xfId="509" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
-    <cellStyle name="DELTA" xfId="510" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
-    <cellStyle name="Dia" xfId="511" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
-    <cellStyle name="Encabez1" xfId="512" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
-    <cellStyle name="Encabez2" xfId="513" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
-    <cellStyle name="Enter Currency (0)" xfId="514" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
-    <cellStyle name="Enter Currency (2)" xfId="515" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
-    <cellStyle name="Enter Units (0)" xfId="516" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
-    <cellStyle name="Enter Units (1)" xfId="517" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
-    <cellStyle name="Enter Units (2)" xfId="518" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
-    <cellStyle name="Explanatory Text 10" xfId="437" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
-    <cellStyle name="Explanatory Text 11" xfId="619" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
-    <cellStyle name="Explanatory Text 12" xfId="665" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
-    <cellStyle name="Explanatory Text 13" xfId="707" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
-    <cellStyle name="Explanatory Text 2" xfId="38" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
-    <cellStyle name="Explanatory Text 3" xfId="172" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
-    <cellStyle name="Explanatory Text 4" xfId="190" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
-    <cellStyle name="Explanatory Text 5" xfId="173" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
-    <cellStyle name="Explanatory Text 6" xfId="296" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
-    <cellStyle name="Explanatory Text 7" xfId="311" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
-    <cellStyle name="Explanatory Text 8" xfId="294" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
-    <cellStyle name="Explanatory Text 9" xfId="423" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
-    <cellStyle name="F2" xfId="39" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
-    <cellStyle name="F3" xfId="40" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
-    <cellStyle name="F4" xfId="41" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
-    <cellStyle name="F5" xfId="42" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
-    <cellStyle name="F6" xfId="43" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
-    <cellStyle name="F7" xfId="44" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
-    <cellStyle name="F8" xfId="45" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
-    <cellStyle name="Fijo" xfId="519" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
-    <cellStyle name="Financiero" xfId="520" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
-    <cellStyle name="Fixed" xfId="521" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
-    <cellStyle name="Formulas" xfId="522" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
-    <cellStyle name="General" xfId="46" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
-    <cellStyle name="Good 10" xfId="463" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
-    <cellStyle name="Good 11" xfId="620" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
-    <cellStyle name="Good 12" xfId="666" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
-    <cellStyle name="Good 13" xfId="679" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
-    <cellStyle name="Good 2" xfId="47" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
-    <cellStyle name="Good 3" xfId="174" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
-    <cellStyle name="Good 4" xfId="225" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
-    <cellStyle name="Good 5" xfId="254" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
-    <cellStyle name="Good 6" xfId="299" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
-    <cellStyle name="Good 7" xfId="310" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
-    <cellStyle name="Good 8" xfId="383" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
-    <cellStyle name="Good 9" xfId="424" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
-    <cellStyle name="Grey" xfId="48" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
-    <cellStyle name="Grey 2" xfId="523" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
-    <cellStyle name="Header1" xfId="524" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
-    <cellStyle name="Header2" xfId="525" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
-    <cellStyle name="Heading 1 10" xfId="436" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
-    <cellStyle name="Heading 1 11" xfId="621" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
-    <cellStyle name="Heading 1 12" xfId="667" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
-    <cellStyle name="Heading 1 13" xfId="697" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
-    <cellStyle name="Heading 1 2" xfId="49" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
-    <cellStyle name="Heading 1 3" xfId="175" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
-    <cellStyle name="Heading 1 4" xfId="189" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
-    <cellStyle name="Heading 1 5" xfId="179" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
-    <cellStyle name="Heading 1 6" xfId="300" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
-    <cellStyle name="Heading 1 7" xfId="341" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
-    <cellStyle name="Heading 1 8" xfId="334" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
-    <cellStyle name="Heading 1 9" xfId="425" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
-    <cellStyle name="Heading 2 10" xfId="435" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
-    <cellStyle name="Heading 2 11" xfId="622" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
-    <cellStyle name="Heading 2 12" xfId="668" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
-    <cellStyle name="Heading 2 13" xfId="678" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
-    <cellStyle name="Heading 2 2" xfId="50" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
-    <cellStyle name="Heading 2 3" xfId="176" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
-    <cellStyle name="Heading 2 4" xfId="188" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
-    <cellStyle name="Heading 2 5" xfId="180" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
-    <cellStyle name="Heading 2 6" xfId="301" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
-    <cellStyle name="Heading 2 7" xfId="338" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
-    <cellStyle name="Heading 2 8" xfId="295" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
-    <cellStyle name="Heading 2 9" xfId="426" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
-    <cellStyle name="Heading 3 10" xfId="434" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
-    <cellStyle name="Heading 3 11" xfId="623" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
-    <cellStyle name="Heading 3 12" xfId="669" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
-    <cellStyle name="Heading 3 13" xfId="706" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
-    <cellStyle name="Heading 3 2" xfId="51" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
-    <cellStyle name="Heading 3 3" xfId="177" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
-    <cellStyle name="Heading 3 4" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
-    <cellStyle name="Heading 3 5" xfId="247" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
-    <cellStyle name="Heading 3 6" xfId="302" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
-    <cellStyle name="Heading 3 7" xfId="337" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
-    <cellStyle name="Heading 3 8" xfId="376" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
-    <cellStyle name="Heading 3 9" xfId="427" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
-    <cellStyle name="Heading 4 10" xfId="462" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
-    <cellStyle name="Heading 4 11" xfId="624" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
-    <cellStyle name="Heading 4 12" xfId="670" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
-    <cellStyle name="Heading 4 13" xfId="696" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
-    <cellStyle name="Heading 4 2" xfId="52" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
-    <cellStyle name="Heading 4 3" xfId="178" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
-    <cellStyle name="Heading 4 4" xfId="187" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
-    <cellStyle name="Heading 4 5" xfId="215" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
-    <cellStyle name="Heading 4 6" xfId="303" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
-    <cellStyle name="Heading 4 7" xfId="342" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
-    <cellStyle name="Heading 4 8" xfId="335" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
-    <cellStyle name="Heading 4 9" xfId="428" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
-    <cellStyle name="HEADING1" xfId="526" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
-    <cellStyle name="HEADING2" xfId="527" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
-    <cellStyle name="Hyperlink 2" xfId="53" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
-    <cellStyle name="Hyperlink 2 2" xfId="54" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
-    <cellStyle name="Hyperlink 2 3" xfId="55" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
-    <cellStyle name="Hyperlink 2 4" xfId="113" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
-    <cellStyle name="Hyperlink 3" xfId="528" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
-    <cellStyle name="Input [yellow]" xfId="57" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
-    <cellStyle name="Input [yellow] 2" xfId="529" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
-    <cellStyle name="Input 10" xfId="433" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
-    <cellStyle name="Input 11" xfId="625" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
-    <cellStyle name="Input 12" xfId="671" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
-    <cellStyle name="Input 13" xfId="695" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
-    <cellStyle name="Input 2" xfId="56" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
-    <cellStyle name="Input 3" xfId="181" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
-    <cellStyle name="Input 4" xfId="217" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
-    <cellStyle name="Input 5" xfId="246" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
-    <cellStyle name="Input 6" xfId="305" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
-    <cellStyle name="Input 7" xfId="308" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
-    <cellStyle name="Input 8" xfId="375" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
-    <cellStyle name="Input 9" xfId="429" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
-    <cellStyle name="Item" xfId="530" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
-    <cellStyle name="Labels - Style3" xfId="531" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
-    <cellStyle name="Labels - Style3 2" xfId="532" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
-    <cellStyle name="Link Currency (0)" xfId="533" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
-    <cellStyle name="Link Currency (2)" xfId="534" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
-    <cellStyle name="Link Units (0)" xfId="535" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
-    <cellStyle name="Link Units (1)" xfId="536" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
-    <cellStyle name="Link Units (2)" xfId="537" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
-    <cellStyle name="Linked Cell 10" xfId="546" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
-    <cellStyle name="Linked Cell 11" xfId="626" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
-    <cellStyle name="Linked Cell 12" xfId="672" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
-    <cellStyle name="Linked Cell 13" xfId="705" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
-    <cellStyle name="Linked Cell 2" xfId="58" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
-    <cellStyle name="Linked Cell 3" xfId="182" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
-    <cellStyle name="Linked Cell 4" xfId="223" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
-    <cellStyle name="Linked Cell 5" xfId="252" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
-    <cellStyle name="Linked Cell 6" xfId="306" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
-    <cellStyle name="Linked Cell 7" xfId="336" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
-    <cellStyle name="Linked Cell 8" xfId="381" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
-    <cellStyle name="Linked Cell 9" xfId="430" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
-    <cellStyle name="Millares [0]_10 AVERIAS MASIVAS + ANT" xfId="538" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
-    <cellStyle name="Neutral 10" xfId="461" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
-    <cellStyle name="Neutral 11" xfId="627" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
-    <cellStyle name="Neutral 12" xfId="673" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
-    <cellStyle name="Neutral 13" xfId="694" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
-    <cellStyle name="Neutral 2" xfId="59" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
-    <cellStyle name="Neutral 3" xfId="183" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
-    <cellStyle name="Neutral 4" xfId="186" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
-    <cellStyle name="Neutral 5" xfId="184" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
-    <cellStyle name="Neutral 6" xfId="307" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
-    <cellStyle name="Neutral 7" xfId="304" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
-    <cellStyle name="Neutral 8" xfId="297" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
-    <cellStyle name="Neutral 9" xfId="431" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
+    <cellStyle name="Comma [00]" xfId="490"/>
+    <cellStyle name="Comma 10" xfId="732"/>
+    <cellStyle name="Comma 11" xfId="731"/>
+    <cellStyle name="Comma 12" xfId="752"/>
+    <cellStyle name="Comma 13" xfId="753"/>
+    <cellStyle name="Comma 14" xfId="754"/>
+    <cellStyle name="Comma 15" xfId="758"/>
+    <cellStyle name="Comma 2" xfId="29"/>
+    <cellStyle name="Comma 2 2" xfId="30"/>
+    <cellStyle name="Comma 2 2 2" xfId="491"/>
+    <cellStyle name="Comma 2 2 2 2" xfId="739"/>
+    <cellStyle name="Comma 2 2 2 2 2" xfId="749"/>
+    <cellStyle name="Comma 2 3" xfId="31"/>
+    <cellStyle name="Comma 2 3 2" xfId="109"/>
+    <cellStyle name="Comma 2 4" xfId="492"/>
+    <cellStyle name="Comma 2 5" xfId="737"/>
+    <cellStyle name="Comma 3" xfId="32"/>
+    <cellStyle name="Comma 3 2" xfId="33"/>
+    <cellStyle name="Comma 3 2 2" xfId="493"/>
+    <cellStyle name="Comma 3 3" xfId="34"/>
+    <cellStyle name="Comma 3 4" xfId="110"/>
+    <cellStyle name="Comma 3 5" xfId="745"/>
+    <cellStyle name="Comma 4" xfId="35"/>
+    <cellStyle name="Comma 4 2" xfId="36"/>
+    <cellStyle name="Comma 4 3" xfId="111"/>
+    <cellStyle name="Comma 4 4" xfId="747"/>
+    <cellStyle name="Comma 5" xfId="37"/>
+    <cellStyle name="Comma 5 2" xfId="494"/>
+    <cellStyle name="Comma 6" xfId="112"/>
+    <cellStyle name="Comma 6 2" xfId="495"/>
+    <cellStyle name="Comma 7" xfId="496"/>
+    <cellStyle name="Comma 7 2" xfId="497"/>
+    <cellStyle name="Comma 8" xfId="498"/>
+    <cellStyle name="Comma 9" xfId="730"/>
+    <cellStyle name="Comma0" xfId="499"/>
+    <cellStyle name="Comma0 - Modelo1" xfId="500"/>
+    <cellStyle name="Comma0 - Style1" xfId="501"/>
+    <cellStyle name="Comma1 - Modelo2" xfId="502"/>
+    <cellStyle name="Comma1 - Style2" xfId="503"/>
+    <cellStyle name="ContentsHyperlink" xfId="124"/>
+    <cellStyle name="Currency [00]" xfId="504"/>
+    <cellStyle name="Currency0" xfId="505"/>
+    <cellStyle name="Custom - Style1" xfId="506"/>
+    <cellStyle name="Data   - Style2" xfId="507"/>
+    <cellStyle name="Date" xfId="508"/>
+    <cellStyle name="Date Short" xfId="509"/>
+    <cellStyle name="DELTA" xfId="510"/>
+    <cellStyle name="Dia" xfId="511"/>
+    <cellStyle name="Encabez1" xfId="512"/>
+    <cellStyle name="Encabez2" xfId="513"/>
+    <cellStyle name="Enter Currency (0)" xfId="514"/>
+    <cellStyle name="Enter Currency (2)" xfId="515"/>
+    <cellStyle name="Enter Units (0)" xfId="516"/>
+    <cellStyle name="Enter Units (1)" xfId="517"/>
+    <cellStyle name="Enter Units (2)" xfId="518"/>
+    <cellStyle name="Explanatory Text 10" xfId="437"/>
+    <cellStyle name="Explanatory Text 11" xfId="619"/>
+    <cellStyle name="Explanatory Text 12" xfId="665"/>
+    <cellStyle name="Explanatory Text 13" xfId="707"/>
+    <cellStyle name="Explanatory Text 2" xfId="38"/>
+    <cellStyle name="Explanatory Text 3" xfId="172"/>
+    <cellStyle name="Explanatory Text 4" xfId="190"/>
+    <cellStyle name="Explanatory Text 5" xfId="173"/>
+    <cellStyle name="Explanatory Text 6" xfId="296"/>
+    <cellStyle name="Explanatory Text 7" xfId="311"/>
+    <cellStyle name="Explanatory Text 8" xfId="294"/>
+    <cellStyle name="Explanatory Text 9" xfId="423"/>
+    <cellStyle name="F2" xfId="39"/>
+    <cellStyle name="F3" xfId="40"/>
+    <cellStyle name="F4" xfId="41"/>
+    <cellStyle name="F5" xfId="42"/>
+    <cellStyle name="F6" xfId="43"/>
+    <cellStyle name="F7" xfId="44"/>
+    <cellStyle name="F8" xfId="45"/>
+    <cellStyle name="Fijo" xfId="519"/>
+    <cellStyle name="Financiero" xfId="520"/>
+    <cellStyle name="Fixed" xfId="521"/>
+    <cellStyle name="Formulas" xfId="522"/>
+    <cellStyle name="General" xfId="46"/>
+    <cellStyle name="Good 10" xfId="463"/>
+    <cellStyle name="Good 11" xfId="620"/>
+    <cellStyle name="Good 12" xfId="666"/>
+    <cellStyle name="Good 13" xfId="679"/>
+    <cellStyle name="Good 2" xfId="47"/>
+    <cellStyle name="Good 3" xfId="174"/>
+    <cellStyle name="Good 4" xfId="225"/>
+    <cellStyle name="Good 5" xfId="254"/>
+    <cellStyle name="Good 6" xfId="299"/>
+    <cellStyle name="Good 7" xfId="310"/>
+    <cellStyle name="Good 8" xfId="383"/>
+    <cellStyle name="Good 9" xfId="424"/>
+    <cellStyle name="Grey" xfId="48"/>
+    <cellStyle name="Grey 2" xfId="523"/>
+    <cellStyle name="Header1" xfId="524"/>
+    <cellStyle name="Header2" xfId="525"/>
+    <cellStyle name="Heading 1 10" xfId="436"/>
+    <cellStyle name="Heading 1 11" xfId="621"/>
+    <cellStyle name="Heading 1 12" xfId="667"/>
+    <cellStyle name="Heading 1 13" xfId="697"/>
+    <cellStyle name="Heading 1 2" xfId="49"/>
+    <cellStyle name="Heading 1 3" xfId="175"/>
+    <cellStyle name="Heading 1 4" xfId="189"/>
+    <cellStyle name="Heading 1 5" xfId="179"/>
+    <cellStyle name="Heading 1 6" xfId="300"/>
+    <cellStyle name="Heading 1 7" xfId="341"/>
+    <cellStyle name="Heading 1 8" xfId="334"/>
+    <cellStyle name="Heading 1 9" xfId="425"/>
+    <cellStyle name="Heading 2 10" xfId="435"/>
+    <cellStyle name="Heading 2 11" xfId="622"/>
+    <cellStyle name="Heading 2 12" xfId="668"/>
+    <cellStyle name="Heading 2 13" xfId="678"/>
+    <cellStyle name="Heading 2 2" xfId="50"/>
+    <cellStyle name="Heading 2 3" xfId="176"/>
+    <cellStyle name="Heading 2 4" xfId="188"/>
+    <cellStyle name="Heading 2 5" xfId="180"/>
+    <cellStyle name="Heading 2 6" xfId="301"/>
+    <cellStyle name="Heading 2 7" xfId="338"/>
+    <cellStyle name="Heading 2 8" xfId="295"/>
+    <cellStyle name="Heading 2 9" xfId="426"/>
+    <cellStyle name="Heading 3 10" xfId="434"/>
+    <cellStyle name="Heading 3 11" xfId="623"/>
+    <cellStyle name="Heading 3 12" xfId="669"/>
+    <cellStyle name="Heading 3 13" xfId="706"/>
+    <cellStyle name="Heading 3 2" xfId="51"/>
+    <cellStyle name="Heading 3 3" xfId="177"/>
+    <cellStyle name="Heading 3 4" xfId="218"/>
+    <cellStyle name="Heading 3 5" xfId="247"/>
+    <cellStyle name="Heading 3 6" xfId="302"/>
+    <cellStyle name="Heading 3 7" xfId="337"/>
+    <cellStyle name="Heading 3 8" xfId="376"/>
+    <cellStyle name="Heading 3 9" xfId="427"/>
+    <cellStyle name="Heading 4 10" xfId="462"/>
+    <cellStyle name="Heading 4 11" xfId="624"/>
+    <cellStyle name="Heading 4 12" xfId="670"/>
+    <cellStyle name="Heading 4 13" xfId="696"/>
+    <cellStyle name="Heading 4 2" xfId="52"/>
+    <cellStyle name="Heading 4 3" xfId="178"/>
+    <cellStyle name="Heading 4 4" xfId="187"/>
+    <cellStyle name="Heading 4 5" xfId="215"/>
+    <cellStyle name="Heading 4 6" xfId="303"/>
+    <cellStyle name="Heading 4 7" xfId="342"/>
+    <cellStyle name="Heading 4 8" xfId="335"/>
+    <cellStyle name="Heading 4 9" xfId="428"/>
+    <cellStyle name="HEADING1" xfId="526"/>
+    <cellStyle name="HEADING2" xfId="527"/>
+    <cellStyle name="Hyperlink 2" xfId="53"/>
+    <cellStyle name="Hyperlink 2 2" xfId="54"/>
+    <cellStyle name="Hyperlink 2 3" xfId="55"/>
+    <cellStyle name="Hyperlink 2 4" xfId="113"/>
+    <cellStyle name="Hyperlink 3" xfId="528"/>
+    <cellStyle name="Input [yellow]" xfId="57"/>
+    <cellStyle name="Input [yellow] 2" xfId="529"/>
+    <cellStyle name="Input 10" xfId="433"/>
+    <cellStyle name="Input 11" xfId="625"/>
+    <cellStyle name="Input 12" xfId="671"/>
+    <cellStyle name="Input 13" xfId="695"/>
+    <cellStyle name="Input 2" xfId="56"/>
+    <cellStyle name="Input 3" xfId="181"/>
+    <cellStyle name="Input 4" xfId="217"/>
+    <cellStyle name="Input 5" xfId="246"/>
+    <cellStyle name="Input 6" xfId="305"/>
+    <cellStyle name="Input 7" xfId="308"/>
+    <cellStyle name="Input 8" xfId="375"/>
+    <cellStyle name="Input 9" xfId="429"/>
+    <cellStyle name="Item" xfId="530"/>
+    <cellStyle name="Labels - Style3" xfId="531"/>
+    <cellStyle name="Labels - Style3 2" xfId="532"/>
+    <cellStyle name="Link Currency (0)" xfId="533"/>
+    <cellStyle name="Link Currency (2)" xfId="534"/>
+    <cellStyle name="Link Units (0)" xfId="535"/>
+    <cellStyle name="Link Units (1)" xfId="536"/>
+    <cellStyle name="Link Units (2)" xfId="537"/>
+    <cellStyle name="Linked Cell 10" xfId="546"/>
+    <cellStyle name="Linked Cell 11" xfId="626"/>
+    <cellStyle name="Linked Cell 12" xfId="672"/>
+    <cellStyle name="Linked Cell 13" xfId="705"/>
+    <cellStyle name="Linked Cell 2" xfId="58"/>
+    <cellStyle name="Linked Cell 3" xfId="182"/>
+    <cellStyle name="Linked Cell 4" xfId="223"/>
+    <cellStyle name="Linked Cell 5" xfId="252"/>
+    <cellStyle name="Linked Cell 6" xfId="306"/>
+    <cellStyle name="Linked Cell 7" xfId="336"/>
+    <cellStyle name="Linked Cell 8" xfId="381"/>
+    <cellStyle name="Linked Cell 9" xfId="430"/>
+    <cellStyle name="Millares [0]_10 AVERIAS MASIVAS + ANT" xfId="538"/>
+    <cellStyle name="Neutral 10" xfId="461"/>
+    <cellStyle name="Neutral 11" xfId="627"/>
+    <cellStyle name="Neutral 12" xfId="673"/>
+    <cellStyle name="Neutral 13" xfId="694"/>
+    <cellStyle name="Neutral 2" xfId="59"/>
+    <cellStyle name="Neutral 3" xfId="183"/>
+    <cellStyle name="Neutral 4" xfId="186"/>
+    <cellStyle name="Neutral 5" xfId="184"/>
+    <cellStyle name="Neutral 6" xfId="307"/>
+    <cellStyle name="Neutral 7" xfId="304"/>
+    <cellStyle name="Neutral 8" xfId="297"/>
+    <cellStyle name="Neutral 9" xfId="431"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal - Style1" xfId="60" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
-    <cellStyle name="Normal 10" xfId="61" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
-    <cellStyle name="Normal 10 2" xfId="742" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
-    <cellStyle name="Normal 11" xfId="62" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
-    <cellStyle name="Normal 11 2" xfId="736" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
-    <cellStyle name="Normal 12" xfId="63" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
-    <cellStyle name="Normal 12 2" xfId="125" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
-    <cellStyle name="Normal 12 2 2" xfId="539" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
-    <cellStyle name="Normal 12 3" xfId="540" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
-    <cellStyle name="Normal 13" xfId="114" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
-    <cellStyle name="Normal 13 2" xfId="541" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
-    <cellStyle name="Normal 14" xfId="115" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
-    <cellStyle name="Normal 15" xfId="123" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
-    <cellStyle name="Normal 15 4 4" xfId="740" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
-    <cellStyle name="Normal 16" xfId="65" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
-    <cellStyle name="Normal 16 2" xfId="542" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
-    <cellStyle name="Normal 16 3" xfId="588" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
-    <cellStyle name="Normal 16 4" xfId="634" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
-    <cellStyle name="Normal 16 5" xfId="702" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
-    <cellStyle name="Normal 16 6" xfId="726" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
-    <cellStyle name="Normal 17" xfId="230" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
-    <cellStyle name="Normal 17 2" xfId="543" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
-    <cellStyle name="Normal 17 2 2" xfId="544" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
-    <cellStyle name="Normal 17 3" xfId="589" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
-    <cellStyle name="Normal 17 4" xfId="635" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
-    <cellStyle name="Normal 17 5" xfId="703" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
-    <cellStyle name="Normal 17 6" xfId="727" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
-    <cellStyle name="Normal 18" xfId="259" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
-    <cellStyle name="Normal 18 2" xfId="545" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
-    <cellStyle name="Normal 18 3" xfId="590" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
-    <cellStyle name="Normal 18 4" xfId="636" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
-    <cellStyle name="Normal 18 5" xfId="704" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
-    <cellStyle name="Normal 18 6" xfId="728" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
-    <cellStyle name="Normal 19" xfId="346" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
-    <cellStyle name="Normal 2" xfId="266" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
-    <cellStyle name="Normal 2 10" xfId="116" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
-    <cellStyle name="Normal 2 11" xfId="185" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
-    <cellStyle name="Normal 2 11 2" xfId="547" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
-    <cellStyle name="Normal 2 12" xfId="216" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
-    <cellStyle name="Normal 2 13" xfId="245" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
-    <cellStyle name="Normal 2 14" xfId="309" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
-    <cellStyle name="Normal 2 15" xfId="298" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
-    <cellStyle name="Normal 2 16" xfId="374" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
-    <cellStyle name="Normal 2 17" xfId="432" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
-    <cellStyle name="Normal 2 18" xfId="468" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
-    <cellStyle name="Normal 2 19" xfId="628" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
-    <cellStyle name="Normal 2 2" xfId="64" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
-    <cellStyle name="Normal 2 2 2" xfId="66" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
-    <cellStyle name="Normal 2 2 2 2" xfId="67" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
-    <cellStyle name="Normal 2 2 2 2 2" xfId="126" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
-    <cellStyle name="Normal 2 2 2 2 2 2" xfId="548" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
-    <cellStyle name="Normal 2 2 2 2 3" xfId="549" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
-    <cellStyle name="Normal 2 2 2 26" xfId="748" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
-    <cellStyle name="Normal 2 2 2 3" xfId="68" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
-    <cellStyle name="Normal 2 2 2 4" xfId="117" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
-    <cellStyle name="Normal 2 2 2_0.JHOR JAHANIYA ESTIMATE" xfId="69" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
-    <cellStyle name="Normal 2 2 3" xfId="70" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
-    <cellStyle name="Normal 2 2 4" xfId="71" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
-    <cellStyle name="Normal 2 2 5" xfId="72" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
-    <cellStyle name="Normal 2 2 6" xfId="118" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
-    <cellStyle name="Normal 2 2_Estimated BOQ, cost, summary" xfId="73" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
-    <cellStyle name="Normal 2 20" xfId="676" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
-    <cellStyle name="Normal 2 21" xfId="677" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
-    <cellStyle name="Normal 2 3" xfId="74" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
-    <cellStyle name="Normal 2 3 2" xfId="75" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
-    <cellStyle name="Normal 2 3 3" xfId="131" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
-    <cellStyle name="Normal 2 4" xfId="76" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
-    <cellStyle name="Normal 2 4 2" xfId="743" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
-    <cellStyle name="Normal 2 5" xfId="77" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
-    <cellStyle name="Normal 2 6" xfId="78" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
-    <cellStyle name="Normal 2 7" xfId="79" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
-    <cellStyle name="Normal 2 7 2" xfId="550" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
-    <cellStyle name="Normal 2 8" xfId="80" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
-    <cellStyle name="Normal 2 8 2" xfId="551" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
-    <cellStyle name="Normal 2 9" xfId="81" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
-    <cellStyle name="Normal 2 9 2" xfId="127" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
-    <cellStyle name="Normal 2 9 2 2" xfId="552" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
-    <cellStyle name="Normal 2 9 3" xfId="553" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
-    <cellStyle name="Normal 2_150m3" xfId="438" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
-    <cellStyle name="Normal 20" xfId="388" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
-    <cellStyle name="Normal 21" xfId="395" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
-    <cellStyle name="Normal 22" xfId="475" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
-    <cellStyle name="Normal 23" xfId="591" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
-    <cellStyle name="Normal 24" xfId="637" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
-    <cellStyle name="Normal 25" xfId="725" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
-    <cellStyle name="Normal 25 4" xfId="738" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
-    <cellStyle name="Normal 26" xfId="729" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
-    <cellStyle name="Normal 27" xfId="735" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
-    <cellStyle name="Normal 28" xfId="751" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
-    <cellStyle name="Normal 29" xfId="756" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
-    <cellStyle name="Normal 3" xfId="82" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
-    <cellStyle name="Normal 3 2" xfId="83" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
-    <cellStyle name="Normal 3 2 2" xfId="554" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
-    <cellStyle name="Normal 3 22" xfId="741" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
-    <cellStyle name="Normal 3 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
-    <cellStyle name="Normal 3 3 2" xfId="128" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
-    <cellStyle name="Normal 3 3 3" xfId="555" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
-    <cellStyle name="Normal 3 3 4" xfId="556" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
-    <cellStyle name="Normal 3 4" xfId="129" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
-    <cellStyle name="Normal 3_Cost Estimate for ghat renovation" xfId="557" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
-    <cellStyle name="Normal 30" xfId="757" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
-    <cellStyle name="Normal 31" xfId="755" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
-    <cellStyle name="Normal 32" xfId="750" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
-    <cellStyle name="Normal 4" xfId="85" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
-    <cellStyle name="Normal 4 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
-    <cellStyle name="Normal 4 2 2" xfId="134" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
-    <cellStyle name="Normal 4 2 3" xfId="558" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
-    <cellStyle name="Normal 4 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
-    <cellStyle name="Normal 4 3 2" xfId="135" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
-    <cellStyle name="Normal 4 3 3" xfId="559" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
-    <cellStyle name="Normal 4 4" xfId="88" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
-    <cellStyle name="Normal 4 5" xfId="119" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
-    <cellStyle name="Normal 4 6" xfId="733" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
-    <cellStyle name="Normal 4_0.JHOR JAHANIYA ESTIMATE" xfId="89" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
-    <cellStyle name="Normal 5" xfId="90" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
-    <cellStyle name="Normal 5 2" xfId="91" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
-    <cellStyle name="Normal 5 2 2" xfId="132" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
-    <cellStyle name="Normal 5 2 2 2" xfId="136" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
-    <cellStyle name="Normal 5 2 3" xfId="560" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
-    <cellStyle name="Normal 5 2 3 2" xfId="561" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
-    <cellStyle name="Normal 5 2 4" xfId="562" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
-    <cellStyle name="Normal 5 2_Setidevi-1" xfId="133" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
-    <cellStyle name="Normal 5 3" xfId="92" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
-    <cellStyle name="Normal 5 6" xfId="563" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
-    <cellStyle name="Normal 5_Setidevi-1" xfId="93" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
-    <cellStyle name="Normal 6" xfId="94" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
-    <cellStyle name="Normal 6 2" xfId="95" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
-    <cellStyle name="Normal 6 3" xfId="120" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
-    <cellStyle name="Normal 6 4" xfId="744" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
-    <cellStyle name="Normal 7" xfId="96" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
-    <cellStyle name="Normal 7 2" xfId="130" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
-    <cellStyle name="Normal 7 3" xfId="564" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
-    <cellStyle name="Normal 7 4" xfId="746" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
-    <cellStyle name="Normal 8" xfId="97" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
-    <cellStyle name="Normal 8 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
-    <cellStyle name="Normal 8 3" xfId="121" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
-    <cellStyle name="Normal 9" xfId="99" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
-    <cellStyle name="Normal 9 2" xfId="565" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
-    <cellStyle name="Normal_Rates" xfId="734" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
-    <cellStyle name="Normalaprom-lat" xfId="100" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
-    <cellStyle name="Note 10" xfId="583" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
-    <cellStyle name="Note 11" xfId="629" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
-    <cellStyle name="Note 12" xfId="684" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
-    <cellStyle name="Note 13" xfId="701" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
-    <cellStyle name="Note 2" xfId="101" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
-    <cellStyle name="Note 3" xfId="205" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
-    <cellStyle name="Note 4" xfId="237" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
-    <cellStyle name="Note 5" xfId="261" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
-    <cellStyle name="Note 6" xfId="329" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
-    <cellStyle name="Note 7" xfId="366" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
-    <cellStyle name="Note 8" xfId="390" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
-    <cellStyle name="Note 9" xfId="453" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
-    <cellStyle name="Output 10" xfId="584" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
-    <cellStyle name="Output 11" xfId="630" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
-    <cellStyle name="Output 12" xfId="685" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
-    <cellStyle name="Output 13" xfId="700" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
-    <cellStyle name="Output 2" xfId="102" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
-    <cellStyle name="Output 3" xfId="206" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
-    <cellStyle name="Output 4" xfId="238" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
-    <cellStyle name="Output 5" xfId="262" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
-    <cellStyle name="Output 6" xfId="330" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
-    <cellStyle name="Output 7" xfId="367" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
-    <cellStyle name="Output 8" xfId="391" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
-    <cellStyle name="Output 9" xfId="454" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
-    <cellStyle name="Percent [2]" xfId="103" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
-    <cellStyle name="Percent [2] 2" xfId="104" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
-    <cellStyle name="Percent [2] 3" xfId="122" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
-    <cellStyle name="Percent 2" xfId="105" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
-    <cellStyle name="Percent 2 2" xfId="137" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
-    <cellStyle name="Percent 3" xfId="566" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
-    <cellStyle name="Reset  - Style4" xfId="567" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
-    <cellStyle name="special" xfId="568" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
-    <cellStyle name="STYL1 - Style1" xfId="569" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
-    <cellStyle name="STYL2 - Style2" xfId="570" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
-    <cellStyle name="Table  - Style5" xfId="571" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
-    <cellStyle name="Title  - Style6" xfId="572" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
-    <cellStyle name="Title  - Style6 2" xfId="573" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
-    <cellStyle name="Title 10" xfId="585" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
-    <cellStyle name="Title 11" xfId="631" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
-    <cellStyle name="Title 12" xfId="689" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
-    <cellStyle name="Title 13" xfId="675" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
-    <cellStyle name="Title 2" xfId="106" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
-    <cellStyle name="Title 3" xfId="210" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
-    <cellStyle name="Title 4" xfId="242" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
-    <cellStyle name="Title 5" xfId="263" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
-    <cellStyle name="Title 6" xfId="331" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
-    <cellStyle name="Title 7" xfId="371" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
-    <cellStyle name="Title 8" xfId="392" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
-    <cellStyle name="Title 9" xfId="458" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
-    <cellStyle name="Total 10" xfId="586" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
-    <cellStyle name="Total 11" xfId="632" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
-    <cellStyle name="Total 12" xfId="690" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
-    <cellStyle name="Total 13" xfId="674" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
-    <cellStyle name="Total 2" xfId="107" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
-    <cellStyle name="Total 3" xfId="211" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
-    <cellStyle name="Total 4" xfId="243" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
-    <cellStyle name="Total 5" xfId="264" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
-    <cellStyle name="Total 6" xfId="332" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
-    <cellStyle name="Total 7" xfId="372" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
-    <cellStyle name="Total 8" xfId="393" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
-    <cellStyle name="Total 9" xfId="459" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
-    <cellStyle name="TotCol - Style7" xfId="574" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
-    <cellStyle name="TotRow - Style8" xfId="575" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
-    <cellStyle name="Turn" xfId="576" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
-    <cellStyle name="Warning Text 10" xfId="587" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
-    <cellStyle name="Warning Text 11" xfId="633" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
-    <cellStyle name="Warning Text 12" xfId="691" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
-    <cellStyle name="Warning Text 13" xfId="699" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
-    <cellStyle name="Warning Text 2" xfId="108" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
-    <cellStyle name="Warning Text 3" xfId="212" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
-    <cellStyle name="Warning Text 4" xfId="244" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
-    <cellStyle name="Warning Text 5" xfId="265" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
-    <cellStyle name="Warning Text 6" xfId="333" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
-    <cellStyle name="Warning Text 7" xfId="373" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
-    <cellStyle name="Warning Text 8" xfId="394" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
-    <cellStyle name="Warning Text 9" xfId="460" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
-    <cellStyle name="백분율_95" xfId="577" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
-    <cellStyle name="콤마 [0]_95" xfId="578" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
-    <cellStyle name="콤마_95" xfId="579" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
-    <cellStyle name="통화 [0]_95" xfId="580" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
-    <cellStyle name="통화_95" xfId="581" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
-    <cellStyle name="표준_4월실적" xfId="582" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
+    <cellStyle name="Normal - Style1" xfId="60"/>
+    <cellStyle name="Normal 10" xfId="61"/>
+    <cellStyle name="Normal 10 2" xfId="742"/>
+    <cellStyle name="Normal 11" xfId="62"/>
+    <cellStyle name="Normal 11 2" xfId="736"/>
+    <cellStyle name="Normal 12" xfId="63"/>
+    <cellStyle name="Normal 12 2" xfId="125"/>
+    <cellStyle name="Normal 12 2 2" xfId="539"/>
+    <cellStyle name="Normal 12 3" xfId="540"/>
+    <cellStyle name="Normal 13" xfId="114"/>
+    <cellStyle name="Normal 13 2" xfId="541"/>
+    <cellStyle name="Normal 14" xfId="115"/>
+    <cellStyle name="Normal 15" xfId="123"/>
+    <cellStyle name="Normal 15 4 4" xfId="740"/>
+    <cellStyle name="Normal 16" xfId="65"/>
+    <cellStyle name="Normal 16 2" xfId="542"/>
+    <cellStyle name="Normal 16 3" xfId="588"/>
+    <cellStyle name="Normal 16 4" xfId="634"/>
+    <cellStyle name="Normal 16 5" xfId="702"/>
+    <cellStyle name="Normal 16 6" xfId="726"/>
+    <cellStyle name="Normal 17" xfId="230"/>
+    <cellStyle name="Normal 17 2" xfId="543"/>
+    <cellStyle name="Normal 17 2 2" xfId="544"/>
+    <cellStyle name="Normal 17 3" xfId="589"/>
+    <cellStyle name="Normal 17 4" xfId="635"/>
+    <cellStyle name="Normal 17 5" xfId="703"/>
+    <cellStyle name="Normal 17 6" xfId="727"/>
+    <cellStyle name="Normal 18" xfId="259"/>
+    <cellStyle name="Normal 18 2" xfId="545"/>
+    <cellStyle name="Normal 18 3" xfId="590"/>
+    <cellStyle name="Normal 18 4" xfId="636"/>
+    <cellStyle name="Normal 18 5" xfId="704"/>
+    <cellStyle name="Normal 18 6" xfId="728"/>
+    <cellStyle name="Normal 19" xfId="346"/>
+    <cellStyle name="Normal 2" xfId="266"/>
+    <cellStyle name="Normal 2 10" xfId="116"/>
+    <cellStyle name="Normal 2 11" xfId="185"/>
+    <cellStyle name="Normal 2 11 2" xfId="547"/>
+    <cellStyle name="Normal 2 12" xfId="216"/>
+    <cellStyle name="Normal 2 13" xfId="245"/>
+    <cellStyle name="Normal 2 14" xfId="309"/>
+    <cellStyle name="Normal 2 15" xfId="298"/>
+    <cellStyle name="Normal 2 16" xfId="374"/>
+    <cellStyle name="Normal 2 17" xfId="432"/>
+    <cellStyle name="Normal 2 18" xfId="468"/>
+    <cellStyle name="Normal 2 19" xfId="628"/>
+    <cellStyle name="Normal 2 2" xfId="64"/>
+    <cellStyle name="Normal 2 2 2" xfId="66"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="67"/>
+    <cellStyle name="Normal 2 2 2 2 2" xfId="126"/>
+    <cellStyle name="Normal 2 2 2 2 2 2" xfId="548"/>
+    <cellStyle name="Normal 2 2 2 2 3" xfId="549"/>
+    <cellStyle name="Normal 2 2 2 26" xfId="748"/>
+    <cellStyle name="Normal 2 2 2 3" xfId="68"/>
+    <cellStyle name="Normal 2 2 2 4" xfId="117"/>
+    <cellStyle name="Normal 2 2 2_0.JHOR JAHANIYA ESTIMATE" xfId="69"/>
+    <cellStyle name="Normal 2 2 3" xfId="70"/>
+    <cellStyle name="Normal 2 2 4" xfId="71"/>
+    <cellStyle name="Normal 2 2 5" xfId="72"/>
+    <cellStyle name="Normal 2 2 6" xfId="118"/>
+    <cellStyle name="Normal 2 2_Estimated BOQ, cost, summary" xfId="73"/>
+    <cellStyle name="Normal 2 20" xfId="676"/>
+    <cellStyle name="Normal 2 21" xfId="677"/>
+    <cellStyle name="Normal 2 3" xfId="74"/>
+    <cellStyle name="Normal 2 3 2" xfId="75"/>
+    <cellStyle name="Normal 2 3 3" xfId="131"/>
+    <cellStyle name="Normal 2 4" xfId="76"/>
+    <cellStyle name="Normal 2 4 2" xfId="743"/>
+    <cellStyle name="Normal 2 5" xfId="77"/>
+    <cellStyle name="Normal 2 6" xfId="78"/>
+    <cellStyle name="Normal 2 7" xfId="79"/>
+    <cellStyle name="Normal 2 7 2" xfId="550"/>
+    <cellStyle name="Normal 2 8" xfId="80"/>
+    <cellStyle name="Normal 2 8 2" xfId="551"/>
+    <cellStyle name="Normal 2 9" xfId="81"/>
+    <cellStyle name="Normal 2 9 2" xfId="127"/>
+    <cellStyle name="Normal 2 9 2 2" xfId="552"/>
+    <cellStyle name="Normal 2 9 3" xfId="553"/>
+    <cellStyle name="Normal 2_150m3" xfId="438"/>
+    <cellStyle name="Normal 20" xfId="388"/>
+    <cellStyle name="Normal 21" xfId="395"/>
+    <cellStyle name="Normal 22" xfId="475"/>
+    <cellStyle name="Normal 23" xfId="591"/>
+    <cellStyle name="Normal 24" xfId="637"/>
+    <cellStyle name="Normal 25" xfId="725"/>
+    <cellStyle name="Normal 25 4" xfId="738"/>
+    <cellStyle name="Normal 26" xfId="729"/>
+    <cellStyle name="Normal 27" xfId="735"/>
+    <cellStyle name="Normal 28" xfId="751"/>
+    <cellStyle name="Normal 29" xfId="756"/>
+    <cellStyle name="Normal 3" xfId="82"/>
+    <cellStyle name="Normal 3 2" xfId="83"/>
+    <cellStyle name="Normal 3 2 2" xfId="554"/>
+    <cellStyle name="Normal 3 22" xfId="741"/>
+    <cellStyle name="Normal 3 3" xfId="84"/>
+    <cellStyle name="Normal 3 3 2" xfId="128"/>
+    <cellStyle name="Normal 3 3 3" xfId="555"/>
+    <cellStyle name="Normal 3 3 4" xfId="556"/>
+    <cellStyle name="Normal 3 4" xfId="129"/>
+    <cellStyle name="Normal 3_Cost Estimate for ghat renovation" xfId="557"/>
+    <cellStyle name="Normal 30" xfId="757"/>
+    <cellStyle name="Normal 31" xfId="755"/>
+    <cellStyle name="Normal 32" xfId="750"/>
+    <cellStyle name="Normal 4" xfId="85"/>
+    <cellStyle name="Normal 4 2" xfId="86"/>
+    <cellStyle name="Normal 4 2 2" xfId="134"/>
+    <cellStyle name="Normal 4 2 3" xfId="558"/>
+    <cellStyle name="Normal 4 3" xfId="87"/>
+    <cellStyle name="Normal 4 3 2" xfId="135"/>
+    <cellStyle name="Normal 4 3 3" xfId="559"/>
+    <cellStyle name="Normal 4 4" xfId="88"/>
+    <cellStyle name="Normal 4 5" xfId="119"/>
+    <cellStyle name="Normal 4 6" xfId="733"/>
+    <cellStyle name="Normal 4_0.JHOR JAHANIYA ESTIMATE" xfId="89"/>
+    <cellStyle name="Normal 5" xfId="90"/>
+    <cellStyle name="Normal 5 2" xfId="91"/>
+    <cellStyle name="Normal 5 2 2" xfId="132"/>
+    <cellStyle name="Normal 5 2 2 2" xfId="136"/>
+    <cellStyle name="Normal 5 2 3" xfId="560"/>
+    <cellStyle name="Normal 5 2 3 2" xfId="561"/>
+    <cellStyle name="Normal 5 2 4" xfId="562"/>
+    <cellStyle name="Normal 5 2_Setidevi-1" xfId="133"/>
+    <cellStyle name="Normal 5 3" xfId="92"/>
+    <cellStyle name="Normal 5 6" xfId="563"/>
+    <cellStyle name="Normal 5_Setidevi-1" xfId="93"/>
+    <cellStyle name="Normal 6" xfId="94"/>
+    <cellStyle name="Normal 6 2" xfId="95"/>
+    <cellStyle name="Normal 6 3" xfId="120"/>
+    <cellStyle name="Normal 6 4" xfId="744"/>
+    <cellStyle name="Normal 7" xfId="96"/>
+    <cellStyle name="Normal 7 2" xfId="130"/>
+    <cellStyle name="Normal 7 3" xfId="564"/>
+    <cellStyle name="Normal 7 4" xfId="746"/>
+    <cellStyle name="Normal 8" xfId="97"/>
+    <cellStyle name="Normal 8 2" xfId="98"/>
+    <cellStyle name="Normal 8 3" xfId="121"/>
+    <cellStyle name="Normal 9" xfId="99"/>
+    <cellStyle name="Normal 9 2" xfId="565"/>
+    <cellStyle name="Normal_Rates" xfId="734"/>
+    <cellStyle name="Normalaprom-lat" xfId="100"/>
+    <cellStyle name="Note 10" xfId="583"/>
+    <cellStyle name="Note 11" xfId="629"/>
+    <cellStyle name="Note 12" xfId="684"/>
+    <cellStyle name="Note 13" xfId="701"/>
+    <cellStyle name="Note 2" xfId="101"/>
+    <cellStyle name="Note 3" xfId="205"/>
+    <cellStyle name="Note 4" xfId="237"/>
+    <cellStyle name="Note 5" xfId="261"/>
+    <cellStyle name="Note 6" xfId="329"/>
+    <cellStyle name="Note 7" xfId="366"/>
+    <cellStyle name="Note 8" xfId="390"/>
+    <cellStyle name="Note 9" xfId="453"/>
+    <cellStyle name="Output 10" xfId="584"/>
+    <cellStyle name="Output 11" xfId="630"/>
+    <cellStyle name="Output 12" xfId="685"/>
+    <cellStyle name="Output 13" xfId="700"/>
+    <cellStyle name="Output 2" xfId="102"/>
+    <cellStyle name="Output 3" xfId="206"/>
+    <cellStyle name="Output 4" xfId="238"/>
+    <cellStyle name="Output 5" xfId="262"/>
+    <cellStyle name="Output 6" xfId="330"/>
+    <cellStyle name="Output 7" xfId="367"/>
+    <cellStyle name="Output 8" xfId="391"/>
+    <cellStyle name="Output 9" xfId="454"/>
+    <cellStyle name="Percent [2]" xfId="103"/>
+    <cellStyle name="Percent [2] 2" xfId="104"/>
+    <cellStyle name="Percent [2] 3" xfId="122"/>
+    <cellStyle name="Percent 2" xfId="105"/>
+    <cellStyle name="Percent 2 2" xfId="137"/>
+    <cellStyle name="Percent 3" xfId="566"/>
+    <cellStyle name="Reset  - Style4" xfId="567"/>
+    <cellStyle name="special" xfId="568"/>
+    <cellStyle name="STYL1 - Style1" xfId="569"/>
+    <cellStyle name="STYL2 - Style2" xfId="570"/>
+    <cellStyle name="Table  - Style5" xfId="571"/>
+    <cellStyle name="Title  - Style6" xfId="572"/>
+    <cellStyle name="Title  - Style6 2" xfId="573"/>
+    <cellStyle name="Title 10" xfId="585"/>
+    <cellStyle name="Title 11" xfId="631"/>
+    <cellStyle name="Title 12" xfId="689"/>
+    <cellStyle name="Title 13" xfId="675"/>
+    <cellStyle name="Title 2" xfId="106"/>
+    <cellStyle name="Title 3" xfId="210"/>
+    <cellStyle name="Title 4" xfId="242"/>
+    <cellStyle name="Title 5" xfId="263"/>
+    <cellStyle name="Title 6" xfId="331"/>
+    <cellStyle name="Title 7" xfId="371"/>
+    <cellStyle name="Title 8" xfId="392"/>
+    <cellStyle name="Title 9" xfId="458"/>
+    <cellStyle name="Total 10" xfId="586"/>
+    <cellStyle name="Total 11" xfId="632"/>
+    <cellStyle name="Total 12" xfId="690"/>
+    <cellStyle name="Total 13" xfId="674"/>
+    <cellStyle name="Total 2" xfId="107"/>
+    <cellStyle name="Total 3" xfId="211"/>
+    <cellStyle name="Total 4" xfId="243"/>
+    <cellStyle name="Total 5" xfId="264"/>
+    <cellStyle name="Total 6" xfId="332"/>
+    <cellStyle name="Total 7" xfId="372"/>
+    <cellStyle name="Total 8" xfId="393"/>
+    <cellStyle name="Total 9" xfId="459"/>
+    <cellStyle name="TotCol - Style7" xfId="574"/>
+    <cellStyle name="TotRow - Style8" xfId="575"/>
+    <cellStyle name="Turn" xfId="576"/>
+    <cellStyle name="Warning Text 10" xfId="587"/>
+    <cellStyle name="Warning Text 11" xfId="633"/>
+    <cellStyle name="Warning Text 12" xfId="691"/>
+    <cellStyle name="Warning Text 13" xfId="699"/>
+    <cellStyle name="Warning Text 2" xfId="108"/>
+    <cellStyle name="Warning Text 3" xfId="212"/>
+    <cellStyle name="Warning Text 4" xfId="244"/>
+    <cellStyle name="Warning Text 5" xfId="265"/>
+    <cellStyle name="Warning Text 6" xfId="333"/>
+    <cellStyle name="Warning Text 7" xfId="373"/>
+    <cellStyle name="Warning Text 8" xfId="394"/>
+    <cellStyle name="Warning Text 9" xfId="460"/>
+    <cellStyle name="백분율_95" xfId="577"/>
+    <cellStyle name="콤마 [0]_95" xfId="578"/>
+    <cellStyle name="콤마_95" xfId="579"/>
+    <cellStyle name="통화 [0]_95" xfId="580"/>
+    <cellStyle name="통화_95" xfId="581"/>
+    <cellStyle name="표준_4월실적" xfId="582"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3994,7 +4094,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Basic"/>
@@ -4143,7 +4243,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Basic"/>
@@ -4191,9 +4291,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4231,9 +4331,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4268,7 +4368,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4303,7 +4403,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4476,98 +4576,98 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R80"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" style="8" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="1"/>
-    <col min="14" max="14" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="9" max="9" width="7.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" style="1"/>
+    <col min="14" max="14" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
     <col min="16" max="16" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
-    </row>
-    <row r="2" spans="1:18" ht="20.25">
-      <c r="A2" s="124" t="s">
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+    </row>
+    <row r="2" spans="1:18" ht="20.399999999999999">
+      <c r="A2" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="145" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="123"/>
-      <c r="L3" s="123"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="145"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="125" t="s">
+      <c r="A4" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="125"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="125"/>
-      <c r="L4" s="125"/>
-    </row>
-    <row r="5" spans="1:18" ht="19.5">
+      <c r="B4" s="147"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="147"/>
+      <c r="K4" s="147"/>
+      <c r="L4" s="147"/>
+    </row>
+    <row r="5" spans="1:18" ht="19.8">
       <c r="A5" s="6"/>
       <c r="B5" s="4" t="s">
         <v>27</v>
@@ -4576,35 +4676,35 @@
         <v>93</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="126" t="s">
+      <c r="K5" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="126"/>
+      <c r="L5" s="148"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="B6" s="122" t="s">
+      <c r="B6" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
+      <c r="C6" s="144"/>
+      <c r="D6" s="144"/>
+      <c r="E6" s="144"/>
+      <c r="F6" s="144"/>
+      <c r="G6" s="144"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="121" t="s">
+      <c r="I6" s="143" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="121"/>
-      <c r="O6" s="121" t="s">
+      <c r="J6" s="143"/>
+      <c r="K6" s="143"/>
+      <c r="L6" s="143"/>
+      <c r="O6" s="143" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="121"/>
-      <c r="Q6" s="121"/>
-      <c r="R6" s="121"/>
-    </row>
-    <row r="7" spans="1:18" ht="17.25" thickBot="1">
+      <c r="P6" s="143"/>
+      <c r="Q6" s="143"/>
+      <c r="R6" s="143"/>
+    </row>
+    <row r="7" spans="1:18" ht="17.399999999999999" thickBot="1">
       <c r="C7" s="5"/>
       <c r="D7" s="6"/>
       <c r="E7" s="3"/>
@@ -4615,7 +4715,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:18" ht="17.25" thickBot="1">
+    <row r="8" spans="1:18" ht="17.399999999999999" thickBot="1">
       <c r="A8" s="2"/>
       <c r="B8" s="12" t="s">
         <v>0</v>
@@ -4705,7 +4805,7 @@
       </c>
       <c r="L10" s="25"/>
     </row>
-    <row r="11" spans="1:18" ht="18.75">
+    <row r="11" spans="1:18" ht="18.600000000000001">
       <c r="B11" s="80"/>
       <c r="C11" s="79"/>
       <c r="D11" s="24"/>
@@ -4834,7 +4934,7 @@
       <c r="K16" s="72"/>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" spans="2:12" ht="18.75">
+    <row r="17" spans="2:12" ht="18.600000000000001">
       <c r="B17" s="80"/>
       <c r="C17" s="79"/>
       <c r="D17" s="24">
@@ -4859,7 +4959,7 @@
       <c r="K17" s="72"/>
       <c r="L17" s="25"/>
     </row>
-    <row r="18" spans="2:12" ht="18.75">
+    <row r="18" spans="2:12" ht="18.600000000000001">
       <c r="B18" s="80"/>
       <c r="C18" s="79"/>
       <c r="D18" s="24">
@@ -5791,7 +5891,7 @@
       <c r="K62" s="73"/>
       <c r="L62" s="25"/>
     </row>
-    <row r="63" spans="2:14" ht="36">
+    <row r="63" spans="2:14" ht="34.799999999999997">
       <c r="B63" s="80">
         <v>11</v>
       </c>
@@ -5840,7 +5940,7 @@
       <c r="K64" s="73"/>
       <c r="L64" s="25"/>
     </row>
-    <row r="65" spans="2:14" ht="36">
+    <row r="65" spans="2:14" ht="34.799999999999997">
       <c r="B65" s="81">
         <v>12</v>
       </c>
@@ -5893,7 +5993,7 @@
       </c>
       <c r="L66" s="25"/>
     </row>
-    <row r="67" spans="2:14" ht="72">
+    <row r="67" spans="2:14" ht="69.599999999999994">
       <c r="B67" s="81">
         <v>13</v>
       </c>
@@ -5993,7 +6093,7 @@
       </c>
       <c r="L70" s="25"/>
     </row>
-    <row r="71" spans="2:14" ht="17.25" thickBot="1">
+    <row r="71" spans="2:14" ht="17.399999999999999" thickBot="1">
       <c r="B71" s="22"/>
       <c r="C71" s="26"/>
       <c r="D71" s="76"/>
@@ -6155,77 +6255,77 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-    </row>
-    <row r="2" spans="1:10" ht="25.5">
-      <c r="A2" s="133" t="s">
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+    </row>
+    <row r="2" spans="1:10" ht="24.6">
+      <c r="A2" s="150" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="133"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-    </row>
-    <row r="3" spans="1:10" ht="18.75">
-      <c r="A3" s="134" t="s">
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+    </row>
+    <row r="3" spans="1:10" ht="18">
+      <c r="A3" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="134"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
+      <c r="B3" s="151"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="151"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="151"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="135" t="s">
+      <c r="A4" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="152"/>
+      <c r="H4" s="152"/>
+      <c r="I4" s="152"/>
+      <c r="J4" s="152"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="37"/>
@@ -6239,40 +6339,40 @@
       <c r="I5" s="37"/>
       <c r="J5" s="37"/>
     </row>
-    <row r="6" spans="1:10" ht="15.75">
+    <row r="6" spans="1:10" ht="15.6">
       <c r="A6" s="31" t="s">
         <v>55</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="136" t="e">
+      <c r="C6" s="153" t="e">
         <f>E51</f>
         <v>#REF!</v>
       </c>
-      <c r="D6" s="137"/>
+      <c r="D6" s="154"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
         <v>56</v>
       </c>
       <c r="H6" s="31"/>
-      <c r="I6" s="136" t="e">
+      <c r="I6" s="153" t="e">
         <f>H51</f>
         <v>#REF!</v>
       </c>
-      <c r="J6" s="137"/>
+      <c r="J6" s="154"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="32"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="128"/>
-    </row>
-    <row r="8" spans="1:10" ht="16.5">
+      <c r="C7" s="155"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="155"/>
+      <c r="H7" s="156"/>
+      <c r="I7" s="156"/>
+      <c r="J7" s="156"/>
+    </row>
+    <row r="8" spans="1:10" ht="16.8">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -6297,32 +6397,32 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="129" t="s">
+      <c r="A10" s="157" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="129" t="s">
+      <c r="B10" s="157" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="131" t="s">
+      <c r="C10" s="159" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131" t="s">
+      <c r="D10" s="159"/>
+      <c r="E10" s="159"/>
+      <c r="F10" s="159" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="129" t="s">
+      <c r="G10" s="159"/>
+      <c r="H10" s="159"/>
+      <c r="I10" s="157" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="129" t="s">
+      <c r="J10" s="157" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="130"/>
-      <c r="B11" s="130"/>
+      <c r="A11" s="158"/>
+      <c r="B11" s="158"/>
       <c r="C11" s="39" t="s">
         <v>64</v>
       </c>
@@ -6341,10 +6441,10 @@
       <c r="H11" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.75">
+      <c r="I11" s="158"/>
+      <c r="J11" s="158"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.6">
       <c r="A12" s="47">
         <v>1</v>
       </c>
@@ -6381,7 +6481,7 @@
       </c>
       <c r="J12" s="43"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75">
+    <row r="13" spans="1:10" ht="15.6">
       <c r="A13" s="49"/>
       <c r="B13" s="50"/>
       <c r="C13" s="43"/>
@@ -6393,7 +6493,7 @@
       <c r="I13" s="42"/>
       <c r="J13" s="43"/>
     </row>
-    <row r="14" spans="1:10" ht="31.5">
+    <row r="14" spans="1:10" ht="31.2">
       <c r="A14" s="49">
         <v>2</v>
       </c>
@@ -6430,7 +6530,7 @@
       </c>
       <c r="J14" s="43"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75">
+    <row r="15" spans="1:10" ht="15.6">
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="41"/>
@@ -6442,7 +6542,7 @@
       <c r="I15" s="42"/>
       <c r="J15" s="43"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75">
+    <row r="16" spans="1:10" ht="15.6">
       <c r="A16" s="49">
         <v>3</v>
       </c>
@@ -6479,7 +6579,7 @@
       </c>
       <c r="J16" s="43"/>
     </row>
-    <row r="17" spans="1:13" ht="15.75">
+    <row r="17" spans="1:13" ht="15.6">
       <c r="A17" s="49"/>
       <c r="B17" s="52" t="s">
         <v>37</v>
@@ -6499,7 +6599,7 @@
       <c r="I17" s="42"/>
       <c r="J17" s="43"/>
     </row>
-    <row r="18" spans="1:13" ht="15.75">
+    <row r="18" spans="1:13" ht="15.6">
       <c r="A18" s="49"/>
       <c r="B18" s="52"/>
       <c r="C18" s="43"/>
@@ -6511,7 +6611,7 @@
       <c r="I18" s="42"/>
       <c r="J18" s="43"/>
     </row>
-    <row r="19" spans="1:13" ht="15.75">
+    <row r="19" spans="1:13" ht="15.6">
       <c r="A19" s="49">
         <v>4</v>
       </c>
@@ -6549,7 +6649,7 @@
       <c r="J19" s="43"/>
       <c r="M19" s="38"/>
     </row>
-    <row r="20" spans="1:13" ht="15.75">
+    <row r="20" spans="1:13" ht="15.6">
       <c r="A20" s="49"/>
       <c r="B20" s="53" t="s">
         <v>37</v>
@@ -6569,7 +6669,7 @@
       <c r="I20" s="42"/>
       <c r="J20" s="43"/>
     </row>
-    <row r="21" spans="1:13" ht="15.75">
+    <row r="21" spans="1:13" ht="15.6">
       <c r="A21" s="49"/>
       <c r="B21" s="52"/>
       <c r="C21" s="43"/>
@@ -6581,7 +6681,7 @@
       <c r="I21" s="42"/>
       <c r="J21" s="43"/>
     </row>
-    <row r="22" spans="1:13" ht="15.75">
+    <row r="22" spans="1:13" ht="15.6">
       <c r="A22" s="49">
         <v>5</v>
       </c>
@@ -6618,7 +6718,7 @@
       </c>
       <c r="J22" s="43"/>
     </row>
-    <row r="23" spans="1:13" ht="15.75">
+    <row r="23" spans="1:13" ht="15.6">
       <c r="A23" s="49"/>
       <c r="B23" s="53" t="s">
         <v>29</v>
@@ -6638,7 +6738,7 @@
       <c r="I23" s="42"/>
       <c r="J23" s="43"/>
     </row>
-    <row r="24" spans="1:13" ht="15.75">
+    <row r="24" spans="1:13" ht="15.6">
       <c r="A24" s="49"/>
       <c r="B24" s="53" t="s">
         <v>38</v>
@@ -6658,7 +6758,7 @@
       <c r="I24" s="42"/>
       <c r="J24" s="43"/>
     </row>
-    <row r="25" spans="1:13" ht="15.75">
+    <row r="25" spans="1:13" ht="15.6">
       <c r="A25" s="49"/>
       <c r="B25" s="53" t="s">
         <v>30</v>
@@ -6678,7 +6778,7 @@
       <c r="I25" s="42"/>
       <c r="J25" s="43"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75">
+    <row r="26" spans="1:13" ht="15.6">
       <c r="A26" s="49"/>
       <c r="B26" s="53"/>
       <c r="C26" s="43"/>
@@ -6690,7 +6790,7 @@
       <c r="I26" s="42"/>
       <c r="J26" s="43"/>
     </row>
-    <row r="27" spans="1:13" ht="31.5">
+    <row r="27" spans="1:13" ht="46.8">
       <c r="A27" s="49">
         <v>6</v>
       </c>
@@ -6727,7 +6827,7 @@
       </c>
       <c r="J27" s="43"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75">
+    <row r="28" spans="1:13" ht="15.6">
       <c r="A28" s="49"/>
       <c r="B28" s="53" t="s">
         <v>29</v>
@@ -6747,7 +6847,7 @@
       <c r="I28" s="42"/>
       <c r="J28" s="43"/>
     </row>
-    <row r="29" spans="1:13" ht="15.75">
+    <row r="29" spans="1:13" ht="15.6">
       <c r="A29" s="49"/>
       <c r="B29" s="53" t="s">
         <v>31</v>
@@ -6767,7 +6867,7 @@
       <c r="I29" s="42"/>
       <c r="J29" s="43"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75">
+    <row r="30" spans="1:13" ht="15.6">
       <c r="A30" s="49"/>
       <c r="B30" s="53" t="s">
         <v>30</v>
@@ -6787,7 +6887,7 @@
       <c r="I30" s="42"/>
       <c r="J30" s="43"/>
     </row>
-    <row r="31" spans="1:13" ht="15.75">
+    <row r="31" spans="1:13" ht="15.6">
       <c r="A31" s="49"/>
       <c r="B31" s="53"/>
       <c r="C31" s="43"/>
@@ -6799,7 +6899,7 @@
       <c r="I31" s="42"/>
       <c r="J31" s="43"/>
     </row>
-    <row r="32" spans="1:13" ht="15.75">
+    <row r="32" spans="1:13" ht="15.6">
       <c r="A32" s="51">
         <v>7</v>
       </c>
@@ -6836,7 +6936,7 @@
       </c>
       <c r="J32" s="43"/>
     </row>
-    <row r="33" spans="1:10" ht="15.75">
+    <row r="33" spans="1:10" ht="15.6">
       <c r="A33" s="51"/>
       <c r="B33" s="53" t="s">
         <v>29</v>
@@ -6856,7 +6956,7 @@
       <c r="I33" s="42"/>
       <c r="J33" s="43"/>
     </row>
-    <row r="34" spans="1:10" ht="15.75">
+    <row r="34" spans="1:10" ht="15.6">
       <c r="A34" s="49"/>
       <c r="B34" s="53"/>
       <c r="C34" s="43"/>
@@ -6868,7 +6968,7 @@
       <c r="I34" s="42"/>
       <c r="J34" s="43"/>
     </row>
-    <row r="35" spans="1:10" ht="15.75">
+    <row r="35" spans="1:10" ht="15.6">
       <c r="A35" s="49">
         <v>8</v>
       </c>
@@ -6905,7 +7005,7 @@
       </c>
       <c r="J35" s="43"/>
     </row>
-    <row r="36" spans="1:10" ht="15.75">
+    <row r="36" spans="1:10" ht="15.6">
       <c r="A36" s="49"/>
       <c r="B36" s="53" t="s">
         <v>29</v>
@@ -6925,7 +7025,7 @@
       <c r="I36" s="42"/>
       <c r="J36" s="43"/>
     </row>
-    <row r="37" spans="1:10" ht="15.75">
+    <row r="37" spans="1:10" ht="15.6">
       <c r="A37" s="49"/>
       <c r="B37" s="53" t="s">
         <v>30</v>
@@ -6945,7 +7045,7 @@
       <c r="I37" s="42"/>
       <c r="J37" s="43"/>
     </row>
-    <row r="38" spans="1:10" ht="15.75">
+    <row r="38" spans="1:10" ht="15.6">
       <c r="A38" s="51"/>
       <c r="B38" s="53"/>
       <c r="C38" s="43"/>
@@ -6957,7 +7057,7 @@
       <c r="I38" s="42"/>
       <c r="J38" s="43"/>
     </row>
-    <row r="39" spans="1:10" ht="15.75">
+    <row r="39" spans="1:10" ht="15.6">
       <c r="A39" s="49">
         <v>9</v>
       </c>
@@ -6994,7 +7094,7 @@
       </c>
       <c r="J39" s="43"/>
     </row>
-    <row r="40" spans="1:10" ht="15.75">
+    <row r="40" spans="1:10" ht="15.6">
       <c r="A40" s="49"/>
       <c r="B40" s="50"/>
       <c r="C40" s="43"/>
@@ -7006,7 +7106,7 @@
       <c r="I40" s="42"/>
       <c r="J40" s="43"/>
     </row>
-    <row r="41" spans="1:10" ht="15.75">
+    <row r="41" spans="1:10" ht="15.6">
       <c r="A41" s="51">
         <v>10</v>
       </c>
@@ -7043,7 +7143,7 @@
       </c>
       <c r="J41" s="43"/>
     </row>
-    <row r="42" spans="1:10" ht="15.75">
+    <row r="42" spans="1:10" ht="15.6">
       <c r="A42" s="51"/>
       <c r="B42" s="56" t="s">
         <v>50</v>
@@ -7063,7 +7163,7 @@
       <c r="I42" s="42"/>
       <c r="J42" s="43"/>
     </row>
-    <row r="43" spans="1:10" ht="15.75">
+    <row r="43" spans="1:10" ht="15.6">
       <c r="A43" s="51"/>
       <c r="B43" s="55"/>
       <c r="C43" s="43"/>
@@ -7075,7 +7175,7 @@
       <c r="I43" s="42"/>
       <c r="J43" s="43"/>
     </row>
-    <row r="44" spans="1:10" ht="15.75">
+    <row r="44" spans="1:10" ht="15.6">
       <c r="A44" s="51">
         <v>11</v>
       </c>
@@ -7112,7 +7212,7 @@
       </c>
       <c r="J44" s="43"/>
     </row>
-    <row r="45" spans="1:10" ht="15.75">
+    <row r="45" spans="1:10" ht="15.6">
       <c r="A45" s="49"/>
       <c r="B45" s="57" t="s">
         <v>51</v>
@@ -7132,7 +7232,7 @@
       <c r="I45" s="42"/>
       <c r="J45" s="43"/>
     </row>
-    <row r="46" spans="1:10" ht="15.75">
+    <row r="46" spans="1:10" ht="15.6">
       <c r="A46" s="49"/>
       <c r="B46" s="50"/>
       <c r="C46" s="43"/>
@@ -7144,7 +7244,7 @@
       <c r="I46" s="42"/>
       <c r="J46" s="43"/>
     </row>
-    <row r="47" spans="1:10" ht="15.75">
+    <row r="47" spans="1:10" ht="15.6">
       <c r="A47" s="58">
         <v>12</v>
       </c>
@@ -7181,7 +7281,7 @@
       </c>
       <c r="J47" s="43"/>
     </row>
-    <row r="48" spans="1:10" ht="15.75">
+    <row r="48" spans="1:10" ht="15.6">
       <c r="A48" s="47"/>
       <c r="B48" s="60" t="s">
         <v>48</v>
@@ -7201,7 +7301,7 @@
       <c r="I48" s="42"/>
       <c r="J48" s="43"/>
     </row>
-    <row r="49" spans="1:10" ht="15.75">
+    <row r="49" spans="1:10" ht="15.6">
       <c r="A49" s="51"/>
       <c r="B49" s="55"/>
       <c r="C49" s="43"/>
@@ -7213,7 +7313,7 @@
       <c r="I49" s="42"/>
       <c r="J49" s="43"/>
     </row>
-    <row r="50" spans="1:10" ht="15.75">
+    <row r="50" spans="1:10" ht="15.6">
       <c r="A50" s="49">
         <v>12</v>
       </c>
@@ -7247,7 +7347,7 @@
       </c>
       <c r="J50" s="43"/>
     </row>
-    <row r="51" spans="1:10" ht="15.75">
+    <row r="51" spans="1:10" ht="15.6">
       <c r="A51" s="44"/>
       <c r="B51" s="45" t="s">
         <v>67</v>
@@ -7269,12 +7369,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="I6:J6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:J7"/>
@@ -7284,6 +7378,12 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="J10:J11"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -7300,98 +7400,98 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R121"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <dimension ref="A1:T163"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="1"/>
-    <col min="14" max="14" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="9" max="9" width="7.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" style="1"/>
+    <col min="14" max="14" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" style="1"/>
     <col min="16" max="16" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
-    </row>
-    <row r="2" spans="1:18" ht="20.25">
-      <c r="A2" s="124" t="s">
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+    </row>
+    <row r="2" spans="1:18" ht="20.399999999999999">
+      <c r="A2" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="145" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="123"/>
-      <c r="L3" s="123"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="145"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="125" t="s">
+      <c r="A4" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="125"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="125"/>
-      <c r="L4" s="125"/>
-    </row>
-    <row r="5" spans="1:18" ht="19.5">
+      <c r="B4" s="147"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="147"/>
+      <c r="K4" s="147"/>
+      <c r="L4" s="147"/>
+    </row>
+    <row r="5" spans="1:18" ht="19.8">
       <c r="A5" s="6"/>
       <c r="B5" s="4" t="s">
         <v>27</v>
@@ -7400,35 +7500,35 @@
         <v>101</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="126" t="s">
+      <c r="K5" s="148" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="126"/>
+      <c r="L5" s="148"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="B6" s="122" t="s">
+      <c r="B6" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
+      <c r="C6" s="144"/>
+      <c r="D6" s="144"/>
+      <c r="E6" s="144"/>
+      <c r="F6" s="144"/>
+      <c r="G6" s="144"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="121" t="s">
+      <c r="I6" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="121"/>
-      <c r="O6" s="121" t="s">
+      <c r="J6" s="143"/>
+      <c r="K6" s="143"/>
+      <c r="L6" s="143"/>
+      <c r="O6" s="143" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="121"/>
-      <c r="Q6" s="121"/>
-      <c r="R6" s="121"/>
-    </row>
-    <row r="7" spans="1:18" ht="17.25" thickBot="1">
+      <c r="P6" s="143"/>
+      <c r="Q6" s="143"/>
+      <c r="R6" s="143"/>
+    </row>
+    <row r="7" spans="1:18" ht="17.399999999999999" thickBot="1">
       <c r="C7" s="5"/>
       <c r="D7" s="6"/>
       <c r="E7" s="3"/>
@@ -7439,7 +7539,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:18" ht="17.25" thickBot="1">
+    <row r="8" spans="1:18" ht="17.399999999999999" thickBot="1">
       <c r="A8" s="2"/>
       <c r="B8" s="12" t="s">
         <v>0</v>
@@ -7494,10 +7594,10 @@
       <c r="L9" s="88"/>
     </row>
     <row r="10" spans="1:18" ht="35.1" customHeight="1">
-      <c r="B10" s="147">
+      <c r="B10" s="123">
         <v>1</v>
       </c>
-      <c r="C10" s="148" t="s">
+      <c r="C10" s="124" t="s">
         <v>105</v>
       </c>
       <c r="D10" s="119">
@@ -7517,98 +7617,98 @@
         <f>D10*E10*F10*G10</f>
         <v>1.2572386467540384</v>
       </c>
-      <c r="I10" s="119" t="s">
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="25"/>
+    </row>
+    <row r="11" spans="1:18" s="121" customFormat="1">
+      <c r="B11" s="123"/>
+      <c r="C11" s="138" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" s="119">
+        <v>1</v>
+      </c>
+      <c r="E11" s="116">
+        <f>5.17/3.281</f>
+        <v>1.5757391039317281</v>
+      </c>
+      <c r="F11" s="116">
+        <f>2/3.281</f>
+        <v>0.6095702529716549</v>
+      </c>
+      <c r="G11" s="116">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="H11" s="116">
+        <f t="shared" ref="H11" si="0">D11*E11*F11*G11</f>
+        <v>7.2039276315074424E-2</v>
+      </c>
+      <c r="I11" s="119"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="119"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="12" spans="1:18" s="121" customFormat="1">
+      <c r="B12" s="123"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="116"/>
+      <c r="H12" s="116">
+        <f>SUM(H10:H11)</f>
+        <v>1.3292779230691127</v>
+      </c>
+      <c r="I12" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="119">
+      <c r="J12" s="119">
         <v>3740</v>
       </c>
-      <c r="K10" s="119">
-        <f>H10*J10</f>
-        <v>4702.072538860104</v>
-      </c>
-      <c r="L10" s="25"/>
-    </row>
-    <row r="11" spans="1:18" ht="18.75">
-      <c r="B11" s="80"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="70"/>
-      <c r="L11" s="25"/>
-    </row>
-    <row r="12" spans="1:18" ht="56.25">
-      <c r="B12" s="147">
+      <c r="K12" s="119">
+        <f>H12*J12</f>
+        <v>4971.4994322784814</v>
+      </c>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="1:18" ht="18.600000000000001">
+      <c r="B13" s="80"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="25"/>
+    </row>
+    <row r="14" spans="1:18" ht="55.8">
+      <c r="B14" s="123">
         <v>2</v>
       </c>
-      <c r="C12" s="148" t="s">
+      <c r="C14" s="124" t="s">
         <v>104</v>
       </c>
-      <c r="D12" s="119">
+      <c r="D14" s="119">
         <v>2</v>
-      </c>
-      <c r="E12" s="116">
-        <f>E10</f>
-        <v>5</v>
-      </c>
-      <c r="F12" s="116"/>
-      <c r="G12" s="116">
-        <v>1.4</v>
-      </c>
-      <c r="H12" s="116">
-        <f>D12*E12*G12</f>
-        <v>14</v>
-      </c>
-      <c r="I12" s="116"/>
-      <c r="J12" s="116"/>
-      <c r="K12" s="116"/>
-      <c r="L12" s="25"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="B13" s="147"/>
-      <c r="C13" s="161"/>
-      <c r="D13" s="119">
-        <v>2</v>
-      </c>
-      <c r="E13" s="116">
-        <f>F10-0.23*2</f>
-        <v>2.8926363913441024</v>
-      </c>
-      <c r="F13" s="116"/>
-      <c r="G13" s="116">
-        <v>1.4</v>
-      </c>
-      <c r="H13" s="116">
-        <f>D13*E13*G13</f>
-        <v>8.0993818957634858</v>
-      </c>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="116"/>
-      <c r="L13" s="25"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="B14" s="147"/>
-      <c r="C14" s="161"/>
-      <c r="D14" s="119">
-        <v>1</v>
       </c>
       <c r="E14" s="116">
         <f>E10</f>
         <v>5</v>
       </c>
-      <c r="F14" s="116"/>
+      <c r="F14" s="116">
+        <v>0.23</v>
+      </c>
       <c r="G14" s="116">
-        <v>0.45</v>
+        <v>1.4</v>
       </c>
       <c r="H14" s="116">
         <f>D14*E14*G14</f>
-        <v>2.25</v>
+        <v>14</v>
       </c>
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
@@ -7616,25 +7716,24 @@
       <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="B15" s="147"/>
-      <c r="C15" s="162" t="s">
-        <v>148</v>
-      </c>
+      <c r="B15" s="123"/>
+      <c r="C15" s="137"/>
       <c r="D15" s="119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="116">
-        <f>(5.25/3.281)</f>
-        <v>1.6001219140505942</v>
-      </c>
-      <c r="F15" s="116"/>
+        <f>F10-0.23*2</f>
+        <v>2.8926363913441024</v>
+      </c>
+      <c r="F15" s="116">
+        <v>0.23</v>
+      </c>
       <c r="G15" s="116">
-        <f>((5.33+8)/2)/3.281</f>
-        <v>2.03139286802804</v>
+        <v>1.4</v>
       </c>
       <c r="H15" s="116">
-        <f t="shared" ref="H15:H17" si="0">D15*E15*G15</f>
-        <v>3.2504762441777535</v>
+        <f>D15*E15*G15</f>
+        <v>8.0993818957634858</v>
       </c>
       <c r="I15" s="116"/>
       <c r="J15" s="116"/>
@@ -7642,164 +7741,194 @@
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="B16" s="147"/>
-      <c r="C16" s="161"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="137"/>
       <c r="D16" s="119">
         <v>1</v>
       </c>
       <c r="E16" s="116">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="F16" s="116"/>
+        <f>E10</f>
+        <v>5</v>
+      </c>
+      <c r="F16" s="116">
+        <v>0.23</v>
+      </c>
       <c r="G16" s="116">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
+        <v>0.45</v>
       </c>
       <c r="H16" s="116">
-        <f t="shared" si="0"/>
-        <v>3.3441830397713468</v>
+        <f>D16*E16*G16</f>
+        <v>2.25</v>
       </c>
       <c r="I16" s="116"/>
       <c r="J16" s="116"/>
       <c r="K16" s="116"/>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" spans="2:14">
-      <c r="B17" s="147"/>
-      <c r="C17" s="162" t="s">
-        <v>149</v>
+    <row r="17" spans="2:14" s="121" customFormat="1">
+      <c r="B17" s="123"/>
+      <c r="C17" s="138" t="s">
+        <v>161</v>
       </c>
       <c r="D17" s="119">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E17" s="116">
-        <f>2.5/3.281</f>
-        <v>0.76196281621456874</v>
-      </c>
-      <c r="F17" s="116"/>
+        <f>3.75/3.281</f>
+        <v>1.1429442243218531</v>
+      </c>
+      <c r="F17" s="116">
+        <v>0.23</v>
+      </c>
       <c r="G17" s="116">
-        <f>6.5/3.281</f>
-        <v>1.9811033221578787</v>
+        <f>2/3.281</f>
+        <v>0.6095702529716549</v>
       </c>
       <c r="H17" s="116">
-        <f t="shared" si="0"/>
-        <v>-1.5095270665634553</v>
+        <f>D17*E17*G17</f>
+        <v>0.6967047999523639</v>
       </c>
       <c r="I17" s="116"/>
       <c r="J17" s="116"/>
       <c r="K17" s="116"/>
       <c r="L17" s="25"/>
     </row>
-    <row r="18" spans="2:14">
-      <c r="B18" s="147"/>
-      <c r="C18" s="150"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="151"/>
+    <row r="18" spans="2:14" s="121" customFormat="1">
+      <c r="B18" s="123"/>
+      <c r="C18" s="138" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="119">
+        <v>1</v>
+      </c>
+      <c r="E18" s="116">
+        <f>2/3.281</f>
+        <v>0.6095702529716549</v>
+      </c>
+      <c r="F18" s="116">
+        <v>0.1</v>
+      </c>
+      <c r="G18" s="116">
+        <f>25/12/3.281</f>
+        <v>0.63496901351214063</v>
+      </c>
       <c r="H18" s="116">
-        <f>SUM(H12:H17)</f>
-        <v>29.434514113149135</v>
-      </c>
-      <c r="I18" s="119" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="116">
-        <v>1982.2</v>
-      </c>
-      <c r="K18" s="116">
-        <f>H18*J18</f>
-        <v>58345.093875084218</v>
-      </c>
+        <f t="shared" ref="H18" si="1">D18*E18*F18*G18</f>
+        <v>3.8705822219575775E-2</v>
+      </c>
+      <c r="I18" s="119"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="119"/>
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="2:14">
-      <c r="B19" s="80"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="70"/>
-      <c r="K19" s="70"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="138" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="119">
+        <v>1</v>
+      </c>
+      <c r="E19" s="116">
+        <f>(5.25/3.281)</f>
+        <v>1.6001219140505942</v>
+      </c>
+      <c r="F19" s="116">
+        <v>0.23</v>
+      </c>
+      <c r="G19" s="116">
+        <f>((5.33+8)/2)/3.281</f>
+        <v>2.03139286802804</v>
+      </c>
+      <c r="H19" s="116">
+        <f t="shared" ref="H19:H21" si="2">D19*E19*G19</f>
+        <v>3.2504762441777535</v>
+      </c>
+      <c r="I19" s="116"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="116"/>
       <c r="L19" s="25"/>
     </row>
-    <row r="20" spans="2:14" ht="56.25">
-      <c r="B20" s="147">
-        <v>3</v>
-      </c>
-      <c r="C20" s="152" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="119"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="151"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="119"/>
+    <row r="20" spans="2:14">
+      <c r="B20" s="123"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="119">
+        <v>1</v>
+      </c>
+      <c r="E20" s="116">
+        <f>4.5/3.281</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="F20" s="116">
+        <v>0.23</v>
+      </c>
+      <c r="G20" s="116">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="H20" s="116">
+        <f t="shared" si="2"/>
+        <v>3.3441830397713468</v>
+      </c>
+      <c r="I20" s="116"/>
       <c r="J20" s="116"/>
       <c r="K20" s="116"/>
       <c r="L20" s="25"/>
-      <c r="N20" s="90" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="21" spans="2:14">
-      <c r="B21" s="147"/>
-      <c r="C21" s="153"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="138" t="s">
+        <v>149</v>
+      </c>
       <c r="D21" s="119">
-        <f>D10</f>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E21" s="116">
-        <f>E10</f>
-        <v>5</v>
+        <f>2.5/3.281</f>
+        <v>0.76196281621456874</v>
       </c>
       <c r="F21" s="116">
-        <f>F10</f>
-        <v>3.3526363913441024</v>
-      </c>
-      <c r="G21" s="151">
-        <v>7.4999999999999997E-2</v>
+        <v>0.23</v>
+      </c>
+      <c r="G21" s="116">
+        <f>6.5/3.281</f>
+        <v>1.9811033221578787</v>
       </c>
       <c r="H21" s="116">
-        <f>D21*E21*F21*G21</f>
-        <v>1.2572386467540384</v>
-      </c>
-      <c r="I21" s="119"/>
+        <f t="shared" si="2"/>
+        <v>-1.5095270665634553</v>
+      </c>
+      <c r="I21" s="116"/>
       <c r="J21" s="116"/>
       <c r="K21" s="116"/>
       <c r="L21" s="25"/>
     </row>
     <row r="22" spans="2:14">
-      <c r="B22" s="147"/>
-      <c r="C22" s="150"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="126"/>
       <c r="D22" s="119"/>
       <c r="E22" s="116"/>
       <c r="F22" s="116"/>
-      <c r="G22" s="151"/>
+      <c r="G22" s="127"/>
       <c r="H22" s="116">
-        <f>SUM(H21)</f>
-        <v>1.2572386467540384</v>
+        <f>SUM(H14:H21)</f>
+        <v>30.169924735321075</v>
       </c>
       <c r="I22" s="119" t="s">
         <v>24</v>
       </c>
       <c r="J22" s="116">
-        <v>770.43</v>
+        <v>1982.2</v>
       </c>
       <c r="K22" s="116">
         <f>H22*J22</f>
-        <v>968.61437061871379</v>
+        <v>59802.824810353435</v>
       </c>
       <c r="L22" s="25"/>
     </row>
     <row r="23" spans="2:14">
       <c r="B23" s="80"/>
-      <c r="C23" s="20"/>
+      <c r="C23" s="27"/>
       <c r="D23" s="24"/>
       <c r="E23" s="70"/>
       <c r="F23" s="70"/>
@@ -7810,71 +7939,73 @@
       <c r="K23" s="70"/>
       <c r="L23" s="25"/>
     </row>
-    <row r="24" spans="2:14" ht="18.75">
-      <c r="B24" s="154">
-        <v>4</v>
-      </c>
-      <c r="C24" s="155" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" s="151"/>
-      <c r="E24" s="156"/>
-      <c r="F24" s="156"/>
-      <c r="G24" s="151"/>
-      <c r="H24" s="156"/>
-      <c r="I24" s="151"/>
-      <c r="J24" s="156"/>
-      <c r="K24" s="156"/>
+    <row r="24" spans="2:14" ht="55.8">
+      <c r="B24" s="123">
+        <v>3</v>
+      </c>
+      <c r="C24" s="128" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="119"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="116"/>
+      <c r="G24" s="127"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="116"/>
       <c r="L24" s="25"/>
+      <c r="N24" s="90" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="25" spans="2:14">
-      <c r="B25" s="154"/>
-      <c r="C25" s="157" t="s">
-        <v>135</v>
-      </c>
-      <c r="D25" s="151">
-        <f>D14</f>
+      <c r="B25" s="123"/>
+      <c r="C25" s="129"/>
+      <c r="D25" s="119">
+        <f>D10</f>
         <v>1</v>
       </c>
-      <c r="E25" s="156">
-        <f>E14</f>
+      <c r="E25" s="116">
+        <f>E10</f>
         <v>5</v>
       </c>
-      <c r="F25" s="156">
-        <f>F21</f>
+      <c r="F25" s="116">
+        <f>F10</f>
         <v>3.3526363913441024</v>
       </c>
-      <c r="G25" s="151"/>
-      <c r="H25" s="156">
-        <f>PRODUCT(D25:G25)</f>
-        <v>16.763181956720512</v>
-      </c>
-      <c r="I25" s="151"/>
-      <c r="J25" s="156"/>
-      <c r="K25" s="156"/>
+      <c r="G25" s="127">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="H25" s="116">
+        <f>D25*E25*F25*G25</f>
+        <v>1.2572386467540384</v>
+      </c>
+      <c r="I25" s="119"/>
+      <c r="J25" s="116"/>
+      <c r="K25" s="116"/>
       <c r="L25" s="25"/>
     </row>
     <row r="26" spans="2:14">
-      <c r="B26" s="154"/>
-      <c r="C26" s="158"/>
-      <c r="D26" s="151"/>
-      <c r="E26" s="156"/>
-      <c r="F26" s="156"/>
-      <c r="G26" s="151"/>
-      <c r="H26" s="156">
+      <c r="B26" s="123"/>
+      <c r="C26" s="126"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="127"/>
+      <c r="H26" s="116">
         <f>SUM(H25)</f>
-        <v>16.763181956720512</v>
-      </c>
-      <c r="I26" s="151" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" s="156">
-        <f>Sheet1!H8/10</f>
-        <v>155.75</v>
-      </c>
-      <c r="K26" s="156">
+        <v>1.2572386467540384</v>
+      </c>
+      <c r="I26" s="119" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="116">
+        <v>770.43</v>
+      </c>
+      <c r="K26" s="116">
         <f>H26*J26</f>
-        <v>2610.8655897592198</v>
+        <v>968.61437061871379</v>
       </c>
       <c r="L26" s="25"/>
     </row>
@@ -7891,100 +8022,93 @@
       <c r="K27" s="70"/>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="2:14" ht="35.1" customHeight="1">
-      <c r="B28" s="147">
+    <row r="28" spans="2:14" ht="18.600000000000001">
+      <c r="B28" s="130">
+        <v>4</v>
+      </c>
+      <c r="C28" s="131" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="127"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="127"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="127"/>
+      <c r="J28" s="132"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="25"/>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="130"/>
+      <c r="C29" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" s="127">
+        <f>D16</f>
+        <v>1</v>
+      </c>
+      <c r="E29" s="132">
+        <f>E16</f>
         <v>5</v>
       </c>
-      <c r="C28" s="148" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28" s="119"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="116"/>
-      <c r="I28" s="119"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="25"/>
-    </row>
-    <row r="29" spans="2:14">
-      <c r="B29" s="147"/>
-      <c r="C29" s="118" t="str">
-        <f>C25</f>
-        <v>-for flooring</v>
-      </c>
-      <c r="D29" s="119">
-        <f>D25</f>
-        <v>1</v>
-      </c>
-      <c r="E29" s="116">
-        <f>E25</f>
-        <v>5</v>
-      </c>
-      <c r="F29" s="116">
+      <c r="F29" s="132">
         <f>F25</f>
         <v>3.3526363913441024</v>
       </c>
-      <c r="G29" s="116">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="H29" s="116">
-        <f>D29*E29*F29*G29</f>
-        <v>1.2572386467540384</v>
-      </c>
-      <c r="I29" s="119"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="116"/>
+      <c r="G29" s="127"/>
+      <c r="H29" s="132">
+        <f>PRODUCT(D29:G29)</f>
+        <v>16.763181956720512</v>
+      </c>
+      <c r="I29" s="127"/>
+      <c r="J29" s="132"/>
+      <c r="K29" s="132"/>
       <c r="L29" s="25"/>
     </row>
     <row r="30" spans="2:14">
-      <c r="B30" s="147"/>
-      <c r="C30" s="159"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="116" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="116"/>
-      <c r="H30" s="116">
+      <c r="B30" s="130"/>
+      <c r="C30" s="134"/>
+      <c r="D30" s="127"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="132"/>
+      <c r="G30" s="127"/>
+      <c r="H30" s="132">
         <f>SUM(H29)</f>
-        <v>1.2572386467540384</v>
-      </c>
-      <c r="I30" s="119" t="s">
-        <v>24</v>
-      </c>
-      <c r="J30" s="116">
-        <v>13351.1</v>
-      </c>
-      <c r="K30" s="116">
+        <v>16.763181956720512</v>
+      </c>
+      <c r="I30" s="127" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="132">
+        <f>Sheet1!H8/10</f>
+        <v>155.75</v>
+      </c>
+      <c r="K30" s="132">
         <f>H30*J30</f>
-        <v>16785.518896677844</v>
+        <v>2610.8655897592198</v>
       </c>
       <c r="L30" s="25"/>
     </row>
     <row r="31" spans="2:14">
-      <c r="B31" s="147"/>
-      <c r="C31" s="118" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="119"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="119"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="116">
-        <f>0.13*H30*4169.92</f>
-        <v>681.53599512343794</v>
-      </c>
+      <c r="B31" s="80"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
       <c r="L31" s="25"/>
     </row>
-    <row r="32" spans="2:14">
-      <c r="B32" s="147"/>
-      <c r="C32" s="118" t="s">
-        <v>30</v>
+    <row r="32" spans="2:14" ht="35.1" customHeight="1">
+      <c r="B32" s="123">
+        <v>5</v>
+      </c>
+      <c r="C32" s="124" t="s">
+        <v>134</v>
       </c>
       <c r="D32" s="119"/>
       <c r="E32" s="116"/>
@@ -7993,49 +8117,68 @@
       <c r="H32" s="116"/>
       <c r="I32" s="119"/>
       <c r="J32" s="116"/>
-      <c r="K32" s="116">
-        <f>0.13*H30*1414.16</f>
-        <v>231.13175861017984</v>
-      </c>
+      <c r="K32" s="116"/>
       <c r="L32" s="25"/>
     </row>
     <row r="33" spans="2:12">
-      <c r="B33" s="147"/>
-      <c r="C33" s="118" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" s="119"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="116"/>
-      <c r="G33" s="116"/>
-      <c r="H33" s="116"/>
+      <c r="B33" s="123"/>
+      <c r="C33" s="118" t="str">
+        <f>C29</f>
+        <v>-for flooring</v>
+      </c>
+      <c r="D33" s="119">
+        <f>D29</f>
+        <v>1</v>
+      </c>
+      <c r="E33" s="116">
+        <f>E29</f>
+        <v>5</v>
+      </c>
+      <c r="F33" s="116">
+        <f>F29</f>
+        <v>3.3526363913441024</v>
+      </c>
+      <c r="G33" s="116">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="H33" s="116">
+        <f>D33*E33*F33*G33</f>
+        <v>1.2572386467540384</v>
+      </c>
       <c r="I33" s="119"/>
       <c r="J33" s="116"/>
-      <c r="K33" s="116">
-        <f>0.13*H30*(1652.5+737.97+349.56)</f>
-        <v>447.83330920451084</v>
-      </c>
+      <c r="K33" s="116"/>
       <c r="L33" s="25"/>
     </row>
-    <row r="34" spans="2:12" ht="18.75">
-      <c r="B34" s="80"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="73"/>
-      <c r="K34" s="73"/>
+    <row r="34" spans="2:12">
+      <c r="B34" s="123"/>
+      <c r="C34" s="135"/>
+      <c r="D34" s="119"/>
+      <c r="E34" s="116"/>
+      <c r="F34" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="116"/>
+      <c r="H34" s="116">
+        <f>SUM(H33)</f>
+        <v>1.2572386467540384</v>
+      </c>
+      <c r="I34" s="119" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="116">
+        <v>13351.1</v>
+      </c>
+      <c r="K34" s="116">
+        <f>H34*J34</f>
+        <v>16785.518896677844</v>
+      </c>
       <c r="L34" s="25"/>
     </row>
-    <row r="35" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B35" s="146">
-        <v>4</v>
-      </c>
-      <c r="C35" s="148" t="s">
-        <v>80</v>
+    <row r="35" spans="2:12">
+      <c r="B35" s="123"/>
+      <c r="C35" s="118" t="s">
+        <v>29</v>
       </c>
       <c r="D35" s="119"/>
       <c r="E35" s="116"/>
@@ -8043,128 +8186,99 @@
       <c r="G35" s="116"/>
       <c r="H35" s="116"/>
       <c r="I35" s="119"/>
-      <c r="J35" s="120"/>
-      <c r="K35" s="116"/>
+      <c r="J35" s="116"/>
+      <c r="K35" s="116">
+        <f>0.13*H34*4169.92</f>
+        <v>681.53599512343794</v>
+      </c>
       <c r="L35" s="25"/>
     </row>
     <row r="36" spans="2:12">
-      <c r="B36" s="146"/>
-      <c r="C36" s="160" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" s="119">
-        <v>33</v>
-      </c>
-      <c r="E36" s="116">
-        <f>(2+4.833+16.17+4.833+2)/3.281</f>
-        <v>9.0935690338311481</v>
-      </c>
+      <c r="B36" s="123"/>
+      <c r="C36" s="118" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="119"/>
+      <c r="E36" s="116"/>
       <c r="F36" s="116"/>
-      <c r="G36" s="116">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
-      </c>
-      <c r="H36" s="116">
-        <f>D36*E36*G36</f>
-        <v>185.23936920767153</v>
-      </c>
+      <c r="G36" s="116"/>
+      <c r="H36" s="116"/>
       <c r="I36" s="119"/>
-      <c r="J36" s="120"/>
-      <c r="K36" s="116"/>
+      <c r="J36" s="116"/>
+      <c r="K36" s="116">
+        <f>0.13*H34*1414.16</f>
+        <v>231.13175861017984</v>
+      </c>
       <c r="L36" s="25"/>
     </row>
     <row r="37" spans="2:12">
-      <c r="B37" s="146"/>
-      <c r="C37" s="118"/>
-      <c r="D37" s="119">
-        <v>32</v>
-      </c>
-      <c r="E37" s="116">
-        <f>(2+4.42+15.667+4.42+2)/3.281</f>
-        <v>8.6885096007314839</v>
-      </c>
+      <c r="B37" s="123"/>
+      <c r="C37" s="118" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="119"/>
+      <c r="E37" s="116"/>
       <c r="F37" s="116"/>
-      <c r="G37" s="116">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
-      </c>
-      <c r="H37" s="116">
-        <f t="shared" ref="H37" si="1">D37*E37*G37</f>
-        <v>171.62488100210336</v>
-      </c>
+      <c r="G37" s="116"/>
+      <c r="H37" s="116"/>
       <c r="I37" s="119"/>
-      <c r="J37" s="120"/>
-      <c r="K37" s="116"/>
+      <c r="J37" s="116"/>
+      <c r="K37" s="116">
+        <f>0.13*H34*(1652.5+737.97+349.56)</f>
+        <v>447.83330920451084</v>
+      </c>
       <c r="L37" s="25"/>
     </row>
-    <row r="38" spans="2:12">
-      <c r="B38" s="146"/>
-      <c r="C38" s="160" t="s">
-        <v>136</v>
-      </c>
-      <c r="D38" s="119">
-        <v>23</v>
-      </c>
-      <c r="E38" s="116">
-        <f>(2+4.833+10.75+4.833+2)/3.281</f>
-        <v>7.4416336482779624</v>
-      </c>
-      <c r="F38" s="116"/>
-      <c r="G38" s="116">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
-      </c>
-      <c r="H38" s="116">
-        <f>D38*E38*G38</f>
-        <v>105.65282340147724</v>
-      </c>
-      <c r="I38" s="119"/>
-      <c r="J38" s="120"/>
-      <c r="K38" s="116"/>
+    <row r="38" spans="2:12" ht="18.600000000000001">
+      <c r="B38" s="80"/>
+      <c r="C38" s="79"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="73"/>
+      <c r="K38" s="73"/>
       <c r="L38" s="25"/>
     </row>
-    <row r="39" spans="2:12">
-      <c r="B39" s="146"/>
-      <c r="C39" s="118"/>
-      <c r="D39" s="119">
-        <v>22</v>
-      </c>
-      <c r="E39" s="116">
-        <f>(2+4.42+10.25+4.42+2)/3.281</f>
-        <v>7.0374885705577572</v>
-      </c>
+    <row r="39" spans="2:12" ht="35.1" customHeight="1">
+      <c r="B39" s="122">
+        <v>6</v>
+      </c>
+      <c r="C39" s="124" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="119"/>
+      <c r="E39" s="116"/>
       <c r="F39" s="116"/>
-      <c r="G39" s="116">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
-      </c>
-      <c r="H39" s="116">
-        <f t="shared" ref="H39" si="2">D39*E39*G39</f>
-        <v>95.570832439673239</v>
-      </c>
+      <c r="G39" s="116"/>
+      <c r="H39" s="116"/>
       <c r="I39" s="119"/>
       <c r="J39" s="120"/>
       <c r="K39" s="116"/>
       <c r="L39" s="25"/>
     </row>
     <row r="40" spans="2:12">
-      <c r="B40" s="146"/>
-      <c r="C40" s="159"/>
+      <c r="B40" s="122"/>
+      <c r="C40" s="136" t="s">
+        <v>136</v>
+      </c>
       <c r="D40" s="119">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E40" s="116">
-        <f>(16.17+10.75+16.17+10.75)/3.281</f>
-        <v>16.409631209996952</v>
+        <f>(2+5.917+16.17+5.917+2)/3.281</f>
+        <v>9.7543431880524238</v>
       </c>
       <c r="F40" s="116"/>
       <c r="G40" s="116">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
       </c>
       <c r="H40" s="116">
         <f>D40*E40*G40</f>
-        <v>64.828172681469425</v>
+        <v>198.69958346032715</v>
       </c>
       <c r="I40" s="119"/>
       <c r="J40" s="120"/>
@@ -8172,23 +8286,23 @@
       <c r="L40" s="25"/>
     </row>
     <row r="41" spans="2:12">
-      <c r="B41" s="146"/>
+      <c r="B41" s="122"/>
       <c r="C41" s="118"/>
       <c r="D41" s="119">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E41" s="116">
-        <f>(15.667+10.25+15.667+10.25)/3.281</f>
-        <v>15.798232246266382</v>
+        <f>(2+5.5+15.667+5.5+2)/3.281</f>
+        <v>9.3468454739408724</v>
       </c>
       <c r="F41" s="116"/>
       <c r="G41" s="116">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
       </c>
       <c r="H41" s="116">
-        <f>D41*E41*G41</f>
-        <v>56.171492431169355</v>
+        <f t="shared" ref="H41" si="3">D41*E41*G41</f>
+        <v>184.62904639883203</v>
       </c>
       <c r="I41" s="119"/>
       <c r="J41" s="120"/>
@@ -8196,26 +8310,25 @@
       <c r="L41" s="25"/>
     </row>
     <row r="42" spans="2:12">
-      <c r="B42" s="146"/>
-      <c r="C42" s="160" t="s">
-        <v>137</v>
+      <c r="B42" s="122"/>
+      <c r="C42" s="136" t="s">
+        <v>136</v>
       </c>
       <c r="D42" s="119">
-        <f>2*TRUNC((E43/0.15),0)</f>
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="E42" s="116">
-        <f>(16.17/3.281)</f>
-        <v>4.928375495275831</v>
+        <f>(2+5.917+10.75+5.917+2)/3.281</f>
+        <v>8.1024078024992381</v>
       </c>
       <c r="F42" s="116"/>
       <c r="G42" s="116">
-        <f t="shared" ref="G42:G44" si="3">8*8/162</f>
-        <v>0.39506172839506171</v>
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
       </c>
       <c r="H42" s="116">
-        <f t="shared" ref="H42:H43" si="4">D42*E42*G42</f>
-        <v>81.774526736428598</v>
+        <f>D42*E42*G42</f>
+        <v>115.03418485029782</v>
       </c>
       <c r="I42" s="119"/>
       <c r="J42" s="120"/>
@@ -8223,24 +8336,23 @@
       <c r="L42" s="25"/>
     </row>
     <row r="43" spans="2:12">
-      <c r="B43" s="146"/>
+      <c r="B43" s="122"/>
       <c r="C43" s="118"/>
       <c r="D43" s="119">
-        <f>2*TRUNC((E42/0.15),0)</f>
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E43" s="116">
-        <f>10.75/3.281</f>
-        <v>3.2764401097226452</v>
+        <f>(2+5.5+10.25+5.5+2)/3.281</f>
+        <v>7.6958244437671439</v>
       </c>
       <c r="F43" s="116"/>
       <c r="G43" s="116">
-        <f t="shared" si="3"/>
-        <v>0.39506172839506171</v>
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
       </c>
       <c r="H43" s="116">
-        <f t="shared" si="4"/>
-        <v>82.841349934715765</v>
+        <f t="shared" ref="H43" si="4">D43*E43*G43</f>
+        <v>104.51119614992416</v>
       </c>
       <c r="I43" s="119"/>
       <c r="J43" s="120"/>
@@ -8248,26 +8360,23 @@
       <c r="L43" s="25"/>
     </row>
     <row r="44" spans="2:12">
-      <c r="B44" s="146"/>
-      <c r="C44" s="160" t="s">
-        <v>144</v>
-      </c>
+      <c r="B44" s="122"/>
+      <c r="C44" s="135"/>
       <c r="D44" s="119">
-        <f>D37+D37+D39+D39-2-2</f>
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="E44" s="116">
-        <f>(7+10+7)/12/3.281</f>
-        <v>0.6095702529716549</v>
+        <f>(16.17+10.75+16.17+10.75)/3.281</f>
+        <v>16.409631209996952</v>
       </c>
       <c r="F44" s="116"/>
       <c r="G44" s="116">
-        <f t="shared" si="3"/>
+        <f>8*8/162</f>
         <v>0.39506172839506171</v>
       </c>
       <c r="H44" s="116">
-        <f t="shared" ref="H44" si="5">D44*E44*G44</f>
-        <v>25.045059282588486</v>
+        <f>D44*E44*G44</f>
+        <v>77.79380721776333</v>
       </c>
       <c r="I44" s="119"/>
       <c r="J44" s="120"/>
@@ -8275,97 +8384,125 @@
       <c r="L44" s="25"/>
     </row>
     <row r="45" spans="2:12">
-      <c r="B45" s="146"/>
+      <c r="B45" s="122"/>
       <c r="C45" s="118"/>
-      <c r="D45" s="119"/>
-      <c r="E45" s="116"/>
+      <c r="D45" s="119">
+        <v>11</v>
+      </c>
+      <c r="E45" s="116">
+        <f>(15.667+10.25+15.667+10.25)/3.281</f>
+        <v>15.798232246266382</v>
+      </c>
       <c r="F45" s="116"/>
-      <c r="G45" s="116"/>
+      <c r="G45" s="116">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
       <c r="H45" s="116">
-        <f>SUM(H36:H44)</f>
-        <v>868.74850711729709</v>
-      </c>
-      <c r="I45" s="119" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="120">
-        <f>132360/1000</f>
-        <v>132.36000000000001</v>
-      </c>
-      <c r="K45" s="116">
-        <f>H45*J45</f>
-        <v>114987.55240204546</v>
-      </c>
+        <f>D45*E45*G45</f>
+        <v>68.654046304762545</v>
+      </c>
+      <c r="I45" s="119"/>
+      <c r="J45" s="120"/>
+      <c r="K45" s="116"/>
       <c r="L45" s="25"/>
     </row>
     <row r="46" spans="2:12">
-      <c r="B46" s="146"/>
-      <c r="C46" s="118" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" s="119"/>
-      <c r="E46" s="116"/>
+      <c r="B46" s="122"/>
+      <c r="C46" s="136" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" s="119">
+        <f>2*TRUNC((E47/0.15),0)</f>
+        <v>42</v>
+      </c>
+      <c r="E46" s="116">
+        <f>(16.17/3.281)</f>
+        <v>4.928375495275831</v>
+      </c>
       <c r="F46" s="116"/>
-      <c r="G46" s="116"/>
-      <c r="H46" s="116"/>
+      <c r="G46" s="116">
+        <f t="shared" ref="G46:G50" si="5">8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="H46" s="116">
+        <f t="shared" ref="H46:H47" si="6">D46*E46*G46</f>
+        <v>81.774526736428598</v>
+      </c>
       <c r="I46" s="119"/>
       <c r="J46" s="120"/>
-      <c r="K46" s="116">
-        <f>0.13*H45*106200/1000</f>
-        <v>11993.941889261405</v>
-      </c>
+      <c r="K46" s="116"/>
       <c r="L46" s="25"/>
     </row>
     <row r="47" spans="2:12">
-      <c r="B47" s="114"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="115"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="122"/>
+      <c r="C47" s="118"/>
+      <c r="D47" s="119">
+        <f>2*TRUNC((E46/0.15),0)</f>
+        <v>64</v>
+      </c>
+      <c r="E47" s="116">
+        <f>10.75/3.281</f>
+        <v>3.2764401097226452</v>
+      </c>
+      <c r="F47" s="116"/>
+      <c r="G47" s="116">
+        <f t="shared" si="5"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="H47" s="116">
+        <f t="shared" si="6"/>
+        <v>82.841349934715765</v>
+      </c>
+      <c r="I47" s="119"/>
+      <c r="J47" s="120"/>
+      <c r="K47" s="116"/>
       <c r="L47" s="25"/>
     </row>
-    <row r="48" spans="2:12" ht="37.5">
-      <c r="B48" s="146">
-        <v>5</v>
-      </c>
-      <c r="C48" s="148" t="s">
-        <v>138</v>
-      </c>
-      <c r="D48" s="119"/>
-      <c r="E48" s="116"/>
+    <row r="48" spans="2:12" s="121" customFormat="1">
+      <c r="B48" s="123"/>
+      <c r="C48" s="136" t="s">
+        <v>149</v>
+      </c>
+      <c r="D48" s="119">
+        <f>-2*5</f>
+        <v>-10</v>
+      </c>
+      <c r="E48" s="116">
+        <v>0.6</v>
+      </c>
       <c r="F48" s="116"/>
-      <c r="G48" s="116"/>
-      <c r="H48" s="116"/>
+      <c r="G48" s="116">
+        <f t="shared" si="5"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="H48" s="116">
+        <f t="shared" ref="H48:H49" si="7">PRODUCT(D48:G48)</f>
+        <v>-2.3703703703703702</v>
+      </c>
       <c r="I48" s="119"/>
-      <c r="J48" s="120"/>
+      <c r="J48" s="116"/>
       <c r="K48" s="116"/>
       <c r="L48" s="25"/>
     </row>
-    <row r="49" spans="2:12">
-      <c r="B49" s="146"/>
-      <c r="C49" s="160" t="s">
-        <v>139</v>
-      </c>
+    <row r="49" spans="2:12" s="121" customFormat="1">
+      <c r="B49" s="122"/>
+      <c r="C49" s="136"/>
       <c r="D49" s="119">
-        <v>1</v>
+        <f>-2*5</f>
+        <v>-10</v>
       </c>
       <c r="E49" s="116">
-        <f>((16.42+11)*2)/3.281</f>
-        <v>16.714416336482781</v>
+        <v>0.6</v>
       </c>
       <c r="F49" s="116"/>
       <c r="G49" s="116">
-        <f>4.583/3.281</f>
-        <v>1.3968302346845474</v>
+        <f t="shared" si="5"/>
+        <v>0.39506172839506171</v>
       </c>
       <c r="H49" s="116">
-        <f>PRODUCT(D49:G49)</f>
-        <v>23.347202093904475</v>
+        <f t="shared" si="7"/>
+        <v>-2.3703703703703702</v>
       </c>
       <c r="I49" s="119"/>
       <c r="J49" s="120"/>
@@ -8373,23 +8510,26 @@
       <c r="L49" s="25"/>
     </row>
     <row r="50" spans="2:12">
-      <c r="B50" s="146"/>
-      <c r="C50" s="118"/>
-      <c r="D50" s="119">
-        <v>1</v>
+      <c r="B50" s="122"/>
+      <c r="C50" s="136" t="s">
+        <v>144</v>
+      </c>
+      <c r="D50" s="168">
+        <f>28*2+17*2</f>
+        <v>90</v>
       </c>
       <c r="E50" s="116">
-        <f>((15.42+10)*2)/3.281</f>
-        <v>15.49527583053947</v>
+        <f>(1+1.42+1)/3.281</f>
+        <v>1.04236513258153</v>
       </c>
       <c r="F50" s="116"/>
       <c r="G50" s="116">
-        <f>4.17/3.281</f>
-        <v>1.2709539774459007</v>
+        <f t="shared" si="5"/>
+        <v>0.39506172839506171</v>
       </c>
       <c r="H50" s="116">
-        <f>PRODUCT(D50:G50)</f>
-        <v>19.693782448445472</v>
+        <f t="shared" ref="H50" si="8">D50*E50*G50</f>
+        <v>37.061871380676621</v>
       </c>
       <c r="I50" s="119"/>
       <c r="J50" s="120"/>
@@ -8397,179 +8537,171 @@
       <c r="L50" s="25"/>
     </row>
     <row r="51" spans="2:12">
-      <c r="B51" s="146"/>
-      <c r="C51" s="160" t="s">
-        <v>140</v>
-      </c>
-      <c r="D51" s="119">
-        <v>1</v>
-      </c>
-      <c r="E51" s="116">
-        <f>(15.42/3.281)</f>
-        <v>4.6997866504114594</v>
-      </c>
-      <c r="F51" s="116">
-        <f>10/3.281</f>
-        <v>3.047851264858275</v>
-      </c>
+      <c r="B51" s="122"/>
+      <c r="C51" s="118"/>
+      <c r="D51" s="119"/>
+      <c r="E51" s="116"/>
+      <c r="F51" s="116"/>
       <c r="G51" s="116"/>
       <c r="H51" s="116">
-        <f>PRODUCT(D51:G51)</f>
-        <v>14.324250687020601</v>
-      </c>
-      <c r="I51" s="119"/>
-      <c r="J51" s="120"/>
-      <c r="K51" s="116"/>
+        <f>SUM(H40:H50)</f>
+        <v>946.25887169298721</v>
+      </c>
+      <c r="I51" s="119" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="120">
+        <f>132360/1000</f>
+        <v>132.36000000000001</v>
+      </c>
+      <c r="K51" s="116">
+        <f>H51*J51</f>
+        <v>125246.82425728381</v>
+      </c>
       <c r="L51" s="25"/>
     </row>
     <row r="52" spans="2:12">
-      <c r="B52" s="146"/>
-      <c r="C52" s="118"/>
+      <c r="B52" s="122"/>
+      <c r="C52" s="118" t="s">
+        <v>81</v>
+      </c>
       <c r="D52" s="119"/>
       <c r="E52" s="116"/>
       <c r="F52" s="116"/>
       <c r="G52" s="116"/>
-      <c r="H52" s="116">
-        <f>SUM(H49:H51)</f>
-        <v>57.365235229370548</v>
-      </c>
-      <c r="I52" s="119" t="s">
-        <v>23</v>
-      </c>
-      <c r="J52" s="120">
-        <v>922.71</v>
-      </c>
+      <c r="H52" s="116"/>
+      <c r="I52" s="119"/>
+      <c r="J52" s="120"/>
       <c r="K52" s="116">
-        <f>H52*J52</f>
-        <v>52931.476198492499</v>
+        <f>0.13*H51*106200/1000</f>
+        <v>13064.049982593382</v>
       </c>
       <c r="L52" s="25"/>
     </row>
     <row r="53" spans="2:12">
-      <c r="B53" s="146"/>
-      <c r="C53" s="118" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" s="119"/>
-      <c r="E53" s="116"/>
-      <c r="F53" s="116"/>
-      <c r="G53" s="116"/>
-      <c r="H53" s="116"/>
-      <c r="I53" s="119"/>
-      <c r="J53" s="120"/>
-      <c r="K53" s="116">
-        <f>0.13*H52*46827.87/100</f>
-        <v>3492.1793111924994</v>
-      </c>
+      <c r="B53" s="114"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="115"/>
+      <c r="K53" s="117"/>
       <c r="L53" s="25"/>
     </row>
-    <row r="54" spans="2:12">
-      <c r="B54" s="114"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="70"/>
-      <c r="I54" s="24"/>
-      <c r="J54" s="115"/>
-      <c r="K54" s="117"/>
+    <row r="54" spans="2:12" ht="37.200000000000003">
+      <c r="B54" s="122">
+        <v>7</v>
+      </c>
+      <c r="C54" s="124" t="s">
+        <v>138</v>
+      </c>
+      <c r="D54" s="119"/>
+      <c r="E54" s="116"/>
+      <c r="F54" s="116"/>
+      <c r="G54" s="116"/>
+      <c r="H54" s="116"/>
+      <c r="I54" s="119"/>
+      <c r="J54" s="120"/>
+      <c r="K54" s="116"/>
       <c r="L54" s="25"/>
     </row>
-    <row r="55" spans="2:12" ht="56.25">
-      <c r="B55" s="147">
-        <v>6</v>
-      </c>
-      <c r="C55" s="148" t="s">
-        <v>145</v>
-      </c>
-      <c r="D55" s="119"/>
-      <c r="E55" s="116"/>
+    <row r="55" spans="2:12">
+      <c r="B55" s="122"/>
+      <c r="C55" s="136" t="s">
+        <v>139</v>
+      </c>
+      <c r="D55" s="119">
+        <v>1</v>
+      </c>
+      <c r="E55" s="116">
+        <f>((16.42+11)*2)/3.281</f>
+        <v>16.714416336482781</v>
+      </c>
       <c r="F55" s="116"/>
-      <c r="G55" s="116"/>
-      <c r="H55" s="116"/>
+      <c r="G55" s="116">
+        <f>4.583/3.281</f>
+        <v>1.3968302346845474</v>
+      </c>
+      <c r="H55" s="116">
+        <f>PRODUCT(D55:G55)</f>
+        <v>23.347202093904475</v>
+      </c>
       <c r="I55" s="119"/>
-      <c r="J55" s="116"/>
+      <c r="J55" s="120"/>
       <c r="K55" s="116"/>
       <c r="L55" s="25"/>
     </row>
-    <row r="56" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B56" s="147"/>
-      <c r="C56" s="160" t="s">
-        <v>143</v>
-      </c>
+    <row r="56" spans="2:12">
+      <c r="B56" s="122"/>
+      <c r="C56" s="118"/>
       <c r="D56" s="119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="116">
-        <f>E25</f>
-        <v>5</v>
-      </c>
-      <c r="F56" s="116">
-        <f>F25</f>
-        <v>3.3526363913441024</v>
-      </c>
+        <f>((15.42+10)*2)/3.281</f>
+        <v>15.49527583053947</v>
+      </c>
+      <c r="F56" s="116"/>
       <c r="G56" s="116">
-        <f>0.42/3.281</f>
-        <v>0.12800975312404753</v>
+        <f>4.17/3.281</f>
+        <v>1.2709539774459007</v>
       </c>
       <c r="H56" s="116">
-        <f>D56*E56*F56*G56</f>
-        <v>4.2917015677065615</v>
+        <f t="shared" ref="H56:H58" si="9">PRODUCT(D56:G56)</f>
+        <v>19.693782448445472</v>
       </c>
       <c r="I56" s="119"/>
-      <c r="J56" s="116"/>
+      <c r="J56" s="120"/>
       <c r="K56" s="116"/>
       <c r="L56" s="25"/>
     </row>
     <row r="57" spans="2:12">
-      <c r="B57" s="147"/>
-      <c r="C57" s="160" t="s">
-        <v>142</v>
+      <c r="B57" s="122"/>
+      <c r="C57" s="136" t="s">
+        <v>140</v>
       </c>
       <c r="D57" s="119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="116">
-        <f>E67</f>
-        <v>0</v>
+        <f>(15.42/3.281)</f>
+        <v>4.6997866504114594</v>
       </c>
       <c r="F57" s="116">
-        <v>0.15</v>
-      </c>
-      <c r="G57" s="116">
-        <f>4.17/3.281</f>
-        <v>1.2709539774459007</v>
-      </c>
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="G57" s="116"/>
       <c r="H57" s="116">
-        <f>D57*E57*F57*G57</f>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>14.324250687020601</v>
       </c>
       <c r="I57" s="119"/>
-      <c r="J57" s="116"/>
+      <c r="J57" s="120"/>
       <c r="K57" s="116"/>
       <c r="L57" s="25"/>
     </row>
-    <row r="58" spans="2:12">
-      <c r="B58" s="147"/>
-      <c r="C58" s="159"/>
+    <row r="58" spans="2:12" s="121" customFormat="1">
+      <c r="B58" s="123"/>
+      <c r="C58" s="136" t="s">
+        <v>149</v>
+      </c>
       <c r="D58" s="119">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E58" s="116">
-        <f>10/3.281</f>
-        <v>3.047851264858275</v>
+        <v>0.6</v>
       </c>
       <c r="F58" s="116">
-        <v>0.15</v>
-      </c>
-      <c r="G58" s="116">
-        <f>4.17/3.281</f>
-        <v>1.2709539774459007</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="G58" s="116"/>
       <c r="H58" s="116">
-        <f>D58*E58*F58*G58</f>
-        <v>1.1621036063205432</v>
+        <f t="shared" si="9"/>
+        <v>-0.36</v>
       </c>
       <c r="I58" s="119"/>
       <c r="J58" s="116"/>
@@ -8577,81 +8709,65 @@
       <c r="L58" s="25"/>
     </row>
     <row r="59" spans="2:12">
-      <c r="B59" s="147"/>
-      <c r="C59" s="160" t="s">
-        <v>141</v>
-      </c>
-      <c r="D59" s="119">
-        <v>0.5</v>
-      </c>
-      <c r="E59" s="116">
-        <f>(14.25*2+8.833*2)/3.281</f>
-        <v>14.070710149344711</v>
-      </c>
-      <c r="F59" s="116">
-        <f>0.583/3.281</f>
-        <v>0.1776897287412374</v>
-      </c>
-      <c r="G59" s="116">
-        <f>0.583/3.281</f>
-        <v>0.1776897287412374</v>
-      </c>
+      <c r="B59" s="122"/>
+      <c r="C59" s="118"/>
+      <c r="D59" s="119"/>
+      <c r="E59" s="116"/>
+      <c r="F59" s="116"/>
+      <c r="G59" s="116"/>
       <c r="H59" s="116">
-        <f>D59*E59*F59*G59</f>
-        <v>0.222131766290218</v>
-      </c>
-      <c r="I59" s="119"/>
-      <c r="J59" s="116"/>
-      <c r="K59" s="116"/>
+        <f>SUM(H55:H58)</f>
+        <v>57.005235229370548</v>
+      </c>
+      <c r="I59" s="119" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" s="120">
+        <v>922.71</v>
+      </c>
+      <c r="K59" s="116">
+        <f>H59*J59</f>
+        <v>52599.300598492504</v>
+      </c>
       <c r="L59" s="25"/>
     </row>
     <row r="60" spans="2:12">
-      <c r="B60" s="147"/>
-      <c r="C60" s="160"/>
+      <c r="B60" s="122"/>
+      <c r="C60" s="118" t="s">
+        <v>81</v>
+      </c>
       <c r="D60" s="119"/>
       <c r="E60" s="116"/>
-      <c r="F60" s="116" t="s">
-        <v>32</v>
-      </c>
+      <c r="F60" s="116"/>
       <c r="G60" s="116"/>
-      <c r="H60" s="116">
-        <f>SUM(H56:H59)</f>
-        <v>5.6759369403173228</v>
-      </c>
-      <c r="I60" s="119" t="s">
-        <v>24</v>
-      </c>
-      <c r="J60" s="116">
-        <v>13957.29</v>
-      </c>
+      <c r="H60" s="116"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="120"/>
       <c r="K60" s="116">
-        <f>H60*J60</f>
-        <v>79220.697897721577</v>
+        <f>0.13*H59*46827.87/100</f>
+        <v>3470.2638680324994</v>
       </c>
       <c r="L60" s="25"/>
     </row>
     <row r="61" spans="2:12">
-      <c r="B61" s="147"/>
-      <c r="C61" s="118" t="s">
-        <v>29</v>
-      </c>
-      <c r="D61" s="119"/>
-      <c r="E61" s="116"/>
-      <c r="F61" s="116"/>
-      <c r="G61" s="116"/>
-      <c r="H61" s="116"/>
-      <c r="I61" s="119"/>
-      <c r="J61" s="116"/>
-      <c r="K61" s="116">
-        <f>0.13*H60*5212.4</f>
-        <v>3846.0829820023018</v>
-      </c>
+      <c r="B61" s="114"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="115"/>
+      <c r="K61" s="117"/>
       <c r="L61" s="25"/>
     </row>
-    <row r="62" spans="2:12">
-      <c r="B62" s="147"/>
-      <c r="C62" s="118" t="s">
-        <v>30</v>
+    <row r="62" spans="2:12" ht="55.8">
+      <c r="B62" s="123">
+        <v>8</v>
+      </c>
+      <c r="C62" s="124" t="s">
+        <v>145</v>
       </c>
       <c r="D62" s="119"/>
       <c r="E62" s="116"/>
@@ -8660,1142 +8776,2030 @@
       <c r="H62" s="116"/>
       <c r="I62" s="119"/>
       <c r="J62" s="116"/>
-      <c r="K62" s="116">
-        <f>0.13*H60*1350.6</f>
-        <v>996.56965610703492</v>
-      </c>
+      <c r="K62" s="116"/>
       <c r="L62" s="25"/>
     </row>
     <row r="63" spans="2:12">
-      <c r="B63" s="147"/>
-      <c r="C63" s="118" t="s">
-        <v>31</v>
-      </c>
-      <c r="D63" s="119"/>
-      <c r="E63" s="116"/>
-      <c r="F63" s="116"/>
-      <c r="G63" s="116"/>
-      <c r="H63" s="116"/>
+      <c r="B63" s="123"/>
+      <c r="C63" s="136" t="s">
+        <v>143</v>
+      </c>
+      <c r="D63" s="119">
+        <v>2</v>
+      </c>
+      <c r="E63" s="116">
+        <f>E29</f>
+        <v>5</v>
+      </c>
+      <c r="F63" s="116">
+        <f>F29</f>
+        <v>3.3526363913441024</v>
+      </c>
+      <c r="G63" s="116">
+        <f>0.42/3.281</f>
+        <v>0.12800975312404753</v>
+      </c>
+      <c r="H63" s="116">
+        <f>D63*E63*F63*G63</f>
+        <v>4.2917015677065615</v>
+      </c>
       <c r="I63" s="119"/>
       <c r="J63" s="116"/>
-      <c r="K63" s="116">
-        <f>0.13*H60*(1912.03+921.59)</f>
-        <v>2090.8482962668563</v>
-      </c>
+      <c r="K63" s="116"/>
       <c r="L63" s="25"/>
     </row>
     <row r="64" spans="2:12">
-      <c r="B64" s="147"/>
-      <c r="C64" s="118" t="s">
-        <v>146</v>
-      </c>
-      <c r="D64" s="119"/>
-      <c r="E64" s="116"/>
-      <c r="F64" s="116"/>
-      <c r="G64" s="116"/>
-      <c r="H64" s="116"/>
+      <c r="B64" s="123"/>
+      <c r="C64" s="136" t="s">
+        <v>142</v>
+      </c>
+      <c r="D64" s="119">
+        <v>2</v>
+      </c>
+      <c r="E64" s="116">
+        <f>E63</f>
+        <v>5</v>
+      </c>
+      <c r="F64" s="116">
+        <v>0.15</v>
+      </c>
+      <c r="G64" s="116">
+        <f>5.25/3.281</f>
+        <v>1.6001219140505942</v>
+      </c>
+      <c r="H64" s="116">
+        <f>D64*E64*F64*G64</f>
+        <v>2.4001828710758915</v>
+      </c>
       <c r="I64" s="119"/>
       <c r="J64" s="116"/>
-      <c r="K64" s="116">
-        <f>0.13*H60*392.92</f>
-        <v>289.92458853663277</v>
-      </c>
+      <c r="K64" s="116"/>
       <c r="L64" s="25"/>
     </row>
     <row r="65" spans="2:12">
-      <c r="B65" s="146"/>
-      <c r="C65" s="118" t="s">
-        <v>147</v>
-      </c>
-      <c r="D65" s="119"/>
-      <c r="E65" s="116"/>
-      <c r="F65" s="116"/>
-      <c r="G65" s="116"/>
-      <c r="H65" s="116"/>
+      <c r="B65" s="123"/>
+      <c r="C65" s="135"/>
+      <c r="D65" s="119">
+        <v>2</v>
+      </c>
+      <c r="E65" s="116">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="F65" s="116">
+        <v>0.15</v>
+      </c>
+      <c r="G65" s="116">
+        <f>5.25/3.281</f>
+        <v>1.6001219140505942</v>
+      </c>
+      <c r="H65" s="116">
+        <f>D65*E65*F65*G65</f>
+        <v>1.4630800798999641</v>
+      </c>
       <c r="I65" s="119"/>
       <c r="J65" s="116"/>
-      <c r="K65" s="116">
-        <f>0.13*H60*14.15</f>
-        <v>10.440886001713716</v>
-      </c>
+      <c r="K65" s="116"/>
       <c r="L65" s="25"/>
     </row>
     <row r="66" spans="2:12">
-      <c r="B66" s="114"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="24"/>
-      <c r="E66" s="70"/>
-      <c r="F66" s="70"/>
-      <c r="G66" s="70"/>
-      <c r="H66" s="70"/>
-      <c r="I66" s="24"/>
-      <c r="J66" s="115"/>
-      <c r="K66" s="117"/>
+      <c r="B66" s="123"/>
+      <c r="C66" s="136" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="119">
+        <v>0.5</v>
+      </c>
+      <c r="E66" s="116">
+        <f>(13.42*2+8*2)/3.281</f>
+        <v>13.05699481865285</v>
+      </c>
+      <c r="F66" s="116">
+        <f>1/3.281</f>
+        <v>0.30478512648582745</v>
+      </c>
+      <c r="G66" s="116">
+        <f>1/3.281</f>
+        <v>0.30478512648582745</v>
+      </c>
+      <c r="H66" s="116">
+        <f>D66*E66*F66*G66</f>
+        <v>0.60645806420723891</v>
+      </c>
+      <c r="I66" s="119"/>
+      <c r="J66" s="116"/>
+      <c r="K66" s="116"/>
       <c r="L66" s="25"/>
     </row>
-    <row r="67" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B67" s="146">
-        <v>3</v>
-      </c>
-      <c r="C67" s="148" t="s">
-        <v>150</v>
-      </c>
-      <c r="D67" s="119"/>
-      <c r="E67" s="116"/>
-      <c r="F67" s="116"/>
-      <c r="G67" s="116"/>
-      <c r="H67" s="116"/>
+    <row r="67" spans="2:12" s="121" customFormat="1">
+      <c r="B67" s="123"/>
+      <c r="C67" s="136" t="s">
+        <v>149</v>
+      </c>
+      <c r="D67" s="119">
+        <v>-1</v>
+      </c>
+      <c r="E67" s="116">
+        <v>0.6</v>
+      </c>
+      <c r="F67" s="116">
+        <v>0.6</v>
+      </c>
+      <c r="G67" s="116">
+        <f>0.42/3.281</f>
+        <v>0.12800975312404753</v>
+      </c>
+      <c r="H67" s="116">
+        <f>D67*E67*F67*G67</f>
+        <v>-4.6083511124657105E-2</v>
+      </c>
       <c r="I67" s="119"/>
-      <c r="J67" s="120"/>
+      <c r="J67" s="116"/>
       <c r="K67" s="116"/>
       <c r="L67" s="25"/>
     </row>
     <row r="68" spans="2:12">
-      <c r="B68" s="147"/>
-      <c r="C68" s="118" t="str">
-        <f>C15</f>
-        <v>-at toilet of ward</v>
-      </c>
-      <c r="D68" s="163">
-        <v>1</v>
-      </c>
-      <c r="E68" s="164">
-        <f>5.33/3.281</f>
-        <v>1.6245047241694606</v>
-      </c>
-      <c r="F68" s="164">
-        <v>0.23</v>
-      </c>
-      <c r="G68" s="164">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="H68" s="164">
-        <f>D68*E68*F68*G68</f>
-        <v>0.91102977521237649</v>
-      </c>
-      <c r="I68" s="163"/>
-      <c r="J68" s="119"/>
-      <c r="K68" s="119"/>
+      <c r="B68" s="123"/>
+      <c r="C68" s="136"/>
+      <c r="D68" s="119"/>
+      <c r="E68" s="116"/>
+      <c r="F68" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="G68" s="116"/>
+      <c r="H68" s="116">
+        <f>SUM(H63:H67)</f>
+        <v>8.7153390717649994</v>
+      </c>
+      <c r="I68" s="119" t="s">
+        <v>24</v>
+      </c>
+      <c r="J68" s="116">
+        <v>13957.29</v>
+      </c>
+      <c r="K68" s="116">
+        <f>H68*J68</f>
+        <v>121642.51487295491</v>
+      </c>
       <c r="L68" s="25"/>
     </row>
     <row r="69" spans="2:12">
-      <c r="B69" s="147"/>
+      <c r="B69" s="123"/>
       <c r="C69" s="118" t="s">
-        <v>149</v>
-      </c>
-      <c r="D69" s="119">
-        <v>-1</v>
-      </c>
-      <c r="E69" s="116">
-        <f>2.5/3.281</f>
-        <v>0.76196281621456874</v>
-      </c>
-      <c r="F69" s="116">
-        <v>0.23</v>
-      </c>
-      <c r="G69" s="116">
-        <f>6.5/3.281</f>
-        <v>1.9811033221578787</v>
-      </c>
-      <c r="H69" s="164">
-        <f>D69*E69*F69*G69</f>
-        <v>-0.34719122530959468</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D69" s="119"/>
+      <c r="E69" s="116"/>
+      <c r="F69" s="116"/>
+      <c r="G69" s="116"/>
+      <c r="H69" s="116"/>
       <c r="I69" s="119"/>
-      <c r="J69" s="119"/>
-      <c r="K69" s="119"/>
+      <c r="J69" s="116"/>
+      <c r="K69" s="116">
+        <f>0.13*H68*5212.4</f>
+        <v>5905.6183390968245</v>
+      </c>
       <c r="L69" s="25"/>
     </row>
     <row r="70" spans="2:12">
-      <c r="B70" s="147"/>
-      <c r="C70" s="118"/>
+      <c r="B70" s="123"/>
+      <c r="C70" s="118" t="s">
+        <v>30</v>
+      </c>
       <c r="D70" s="119"/>
       <c r="E70" s="116"/>
       <c r="F70" s="116"/>
-      <c r="G70" s="151"/>
-      <c r="H70" s="116">
-        <f>SUM(H68:H69)</f>
-        <v>0.56383854990278182</v>
-      </c>
-      <c r="I70" s="119" t="s">
-        <v>35</v>
-      </c>
-      <c r="J70" s="116">
-        <v>14491.84</v>
-      </c>
+      <c r="G70" s="116"/>
+      <c r="H70" s="116"/>
+      <c r="I70" s="119"/>
+      <c r="J70" s="116"/>
       <c r="K70" s="116">
-        <f>H70*J70</f>
-        <v>8171.0580510231293</v>
+        <f>0.13*H68*1350.6</f>
+        <v>1530.221803542355</v>
       </c>
       <c r="L70" s="25"/>
     </row>
     <row r="71" spans="2:12">
-      <c r="B71" s="147"/>
+      <c r="B71" s="123"/>
       <c r="C71" s="118" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D71" s="119"/>
       <c r="E71" s="116"/>
       <c r="F71" s="116"/>
-      <c r="G71" s="151"/>
-      <c r="H71" s="119"/>
+      <c r="G71" s="116"/>
+      <c r="H71" s="116"/>
       <c r="I71" s="119"/>
       <c r="J71" s="116"/>
       <c r="K71" s="116">
-        <f>0.13*H70*912.17</f>
-        <v>66.861159308426664</v>
+        <f>0.13*H68*(1912.03+921.59)</f>
+        <v>3210.4746830695158</v>
       </c>
       <c r="L71" s="25"/>
     </row>
     <row r="72" spans="2:12">
-      <c r="B72" s="147"/>
+      <c r="B72" s="123"/>
       <c r="C72" s="118" t="s">
-        <v>30</v>
+        <v>146</v>
       </c>
       <c r="D72" s="119"/>
-      <c r="E72" s="119"/>
-      <c r="F72" s="119"/>
-      <c r="G72" s="119"/>
-      <c r="H72" s="119"/>
+      <c r="E72" s="116"/>
+      <c r="F72" s="116"/>
+      <c r="G72" s="116"/>
+      <c r="H72" s="116"/>
       <c r="I72" s="119"/>
       <c r="J72" s="116"/>
       <c r="K72" s="116">
-        <f>0.13*H70*953.37</f>
-        <v>69.881078581705964</v>
+        <f>0.13*H68*392.92</f>
+        <v>445.17603365012752</v>
       </c>
       <c r="L72" s="25"/>
     </row>
     <row r="73" spans="2:12">
-      <c r="B73" s="147"/>
+      <c r="B73" s="122"/>
       <c r="C73" s="118" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="D73" s="119"/>
       <c r="E73" s="116"/>
       <c r="F73" s="116"/>
-      <c r="G73" s="151"/>
+      <c r="G73" s="116"/>
       <c r="H73" s="116"/>
       <c r="I73" s="119"/>
       <c r="J73" s="116"/>
       <c r="K73" s="116">
-        <f>0.13*H70*8481.2</f>
-        <v>621.66357622661155</v>
+        <f>0.13*H68*14.15</f>
+        <v>16.031866222511717</v>
       </c>
       <c r="L73" s="25"/>
     </row>
     <row r="74" spans="2:12">
-      <c r="B74" s="80"/>
-      <c r="C74" s="20"/>
+      <c r="B74" s="114"/>
+      <c r="C74" s="19"/>
       <c r="D74" s="24"/>
       <c r="E74" s="70"/>
       <c r="F74" s="70"/>
-      <c r="G74" s="71"/>
+      <c r="G74" s="70"/>
       <c r="H74" s="70"/>
       <c r="I74" s="24"/>
-      <c r="J74" s="73"/>
-      <c r="K74" s="73"/>
+      <c r="J74" s="115"/>
+      <c r="K74" s="117"/>
       <c r="L74" s="25"/>
     </row>
-    <row r="75" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B75" s="147">
-        <v>6</v>
-      </c>
-      <c r="C75" s="148" t="s">
-        <v>77</v>
+    <row r="75" spans="2:12" ht="52.8">
+      <c r="B75" s="122">
+        <v>9</v>
+      </c>
+      <c r="C75" s="124" t="s">
+        <v>168</v>
       </c>
       <c r="D75" s="119"/>
-      <c r="E75" s="119"/>
-      <c r="F75" s="119"/>
+      <c r="E75" s="116"/>
+      <c r="F75" s="116"/>
       <c r="G75" s="116"/>
-      <c r="H75" s="119"/>
-      <c r="I75" s="151"/>
-      <c r="J75" s="116"/>
-      <c r="K75" s="119"/>
+      <c r="H75" s="116"/>
+      <c r="I75" s="119"/>
+      <c r="J75" s="120"/>
+      <c r="K75" s="116"/>
       <c r="L75" s="25"/>
     </row>
     <row r="76" spans="2:12">
-      <c r="B76" s="147"/>
-      <c r="C76" s="118" t="s">
-        <v>151</v>
-      </c>
-      <c r="D76" s="119">
+      <c r="B76" s="123"/>
+      <c r="C76" s="118" t="str">
+        <f>C19</f>
+        <v>-at toilet of ward</v>
+      </c>
+      <c r="D76" s="139">
         <v>1</v>
       </c>
-      <c r="E76" s="119">
-        <f>14.25/3.281</f>
-        <v>4.3431880524230415</v>
-      </c>
-      <c r="F76" s="119">
-        <f>8.833/3.281</f>
-        <v>2.6921670222493144</v>
-      </c>
-      <c r="G76" s="116"/>
-      <c r="H76" s="119">
-        <f>F76*E76*D76</f>
-        <v>11.692587646160538</v>
-      </c>
-      <c r="I76" s="151" t="s">
-        <v>23</v>
-      </c>
-      <c r="J76" s="116">
-        <v>689.98</v>
-      </c>
-      <c r="K76" s="119">
-        <f>H76*J76</f>
-        <v>8067.6516240978481</v>
-      </c>
+      <c r="E76" s="140">
+        <f>5.33/3.281</f>
+        <v>1.6245047241694606</v>
+      </c>
+      <c r="F76" s="140">
+        <v>0.23</v>
+      </c>
+      <c r="G76" s="140">
+        <f>8.75/3.281</f>
+        <v>2.6668698567509903</v>
+      </c>
+      <c r="H76" s="140">
+        <f>D76*E76*F76*G76</f>
+        <v>0.99643881663853684</v>
+      </c>
+      <c r="I76" s="139"/>
+      <c r="J76" s="119"/>
+      <c r="K76" s="119"/>
       <c r="L76" s="25"/>
     </row>
     <row r="77" spans="2:12">
-      <c r="B77" s="147"/>
+      <c r="B77" s="123"/>
       <c r="C77" s="118" t="s">
+        <v>149</v>
+      </c>
+      <c r="D77" s="119">
+        <v>-1</v>
+      </c>
+      <c r="E77" s="116">
+        <f>2.5/3.281</f>
+        <v>0.76196281621456874</v>
+      </c>
+      <c r="F77" s="116">
+        <v>0.23</v>
+      </c>
+      <c r="G77" s="116">
+        <f>6.5/3.281</f>
+        <v>1.9811033221578787</v>
+      </c>
+      <c r="H77" s="140">
+        <f>D77*E77*F77*G77</f>
+        <v>-0.34719122530959468</v>
+      </c>
+      <c r="I77" s="119"/>
+      <c r="J77" s="119"/>
+      <c r="K77" s="119"/>
+      <c r="L77" s="25"/>
+    </row>
+    <row r="78" spans="2:12">
+      <c r="B78" s="123"/>
+      <c r="C78" s="118"/>
+      <c r="D78" s="119"/>
+      <c r="E78" s="116"/>
+      <c r="F78" s="116"/>
+      <c r="G78" s="127"/>
+      <c r="H78" s="116">
+        <f>SUM(H76:H77)</f>
+        <v>0.64924759132894216</v>
+      </c>
+      <c r="I78" s="119" t="s">
+        <v>35</v>
+      </c>
+      <c r="J78" s="116">
+        <v>14491.84</v>
+      </c>
+      <c r="K78" s="116">
+        <f>H78*J78</f>
+        <v>9408.7922139244165</v>
+      </c>
+      <c r="L78" s="25"/>
+    </row>
+    <row r="79" spans="2:12">
+      <c r="B79" s="123"/>
+      <c r="C79" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="D77" s="119"/>
-      <c r="E77" s="119"/>
-      <c r="F77" s="119"/>
-      <c r="G77" s="151"/>
-      <c r="H77" s="119"/>
-      <c r="I77" s="151"/>
-      <c r="J77" s="116"/>
-      <c r="K77" s="166">
-        <f>0.13*H76*1694.03/10</f>
-        <v>257.49872525292938</v>
-      </c>
-      <c r="L77" s="25"/>
-    </row>
-    <row r="78" spans="2:12">
-      <c r="B78" s="147"/>
-      <c r="C78" s="118" t="s">
+      <c r="D79" s="119"/>
+      <c r="E79" s="116"/>
+      <c r="F79" s="116"/>
+      <c r="G79" s="127"/>
+      <c r="H79" s="119"/>
+      <c r="I79" s="119"/>
+      <c r="J79" s="116"/>
+      <c r="K79" s="116">
+        <f>0.13*H78*912.17</f>
+        <v>76.989142799727745</v>
+      </c>
+      <c r="L79" s="25"/>
+    </row>
+    <row r="80" spans="2:12">
+      <c r="B80" s="123"/>
+      <c r="C80" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="D78" s="119"/>
-      <c r="E78" s="119"/>
-      <c r="F78" s="119"/>
-      <c r="G78" s="151"/>
-      <c r="H78" s="119"/>
-      <c r="I78" s="151"/>
-      <c r="J78" s="116"/>
-      <c r="K78" s="166">
-        <f>0.13*H76*572.02/10</f>
-        <v>86.949121809637774</v>
-      </c>
-      <c r="L78" s="25"/>
-    </row>
-    <row r="79" spans="2:12">
-      <c r="B79" s="147"/>
-      <c r="C79" s="118" t="s">
-        <v>31</v>
-      </c>
-      <c r="D79" s="119"/>
-      <c r="E79" s="119"/>
-      <c r="F79" s="119"/>
-      <c r="G79" s="151"/>
-      <c r="H79" s="119"/>
-      <c r="I79" s="151"/>
-      <c r="J79" s="116"/>
-      <c r="K79" s="166">
-        <f>0.13*H76*1207.6/10</f>
-        <v>183.55959493954506</v>
-      </c>
-      <c r="L79" s="25"/>
-    </row>
-    <row r="80" spans="2:12" ht="18" customHeight="1">
-      <c r="B80" s="80"/>
-      <c r="C80" s="19"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="70"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="71"/>
-      <c r="H80" s="70"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="73"/>
-      <c r="K80" s="73"/>
+      <c r="D80" s="119"/>
+      <c r="E80" s="119"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="119"/>
+      <c r="H80" s="119"/>
+      <c r="I80" s="119"/>
+      <c r="J80" s="116"/>
+      <c r="K80" s="116">
+        <f>0.13*H78*953.37</f>
+        <v>80.466512898885568</v>
+      </c>
       <c r="L80" s="25"/>
     </row>
-    <row r="81" spans="2:14" ht="35.1" customHeight="1">
-      <c r="B81" s="147">
-        <v>7</v>
-      </c>
-      <c r="C81" s="148" t="s">
-        <v>78</v>
+    <row r="81" spans="2:12">
+      <c r="B81" s="123"/>
+      <c r="C81" s="118" t="s">
+        <v>38</v>
       </c>
       <c r="D81" s="119"/>
-      <c r="E81" s="119"/>
-      <c r="F81" s="119"/>
-      <c r="G81" s="119"/>
+      <c r="E81" s="116"/>
+      <c r="F81" s="116"/>
+      <c r="G81" s="127"/>
       <c r="H81" s="116"/>
       <c r="I81" s="119"/>
       <c r="J81" s="116"/>
-      <c r="K81" s="116"/>
+      <c r="K81" s="116">
+        <f>0.13*H78*8481.2</f>
+        <v>715.83182730527324</v>
+      </c>
       <c r="L81" s="25"/>
     </row>
-    <row r="82" spans="2:14">
-      <c r="B82" s="147"/>
-      <c r="C82" s="118" t="s">
-        <v>152</v>
-      </c>
-      <c r="D82" s="119">
+    <row r="82" spans="2:12">
+      <c r="B82" s="80"/>
+      <c r="C82" s="20"/>
+      <c r="D82" s="24"/>
+      <c r="E82" s="70"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="71"/>
+      <c r="H82" s="70"/>
+      <c r="I82" s="24"/>
+      <c r="J82" s="73"/>
+      <c r="K82" s="73"/>
+      <c r="L82" s="25"/>
+    </row>
+    <row r="83" spans="2:12" ht="35.1" customHeight="1">
+      <c r="B83" s="123">
+        <v>10</v>
+      </c>
+      <c r="C83" s="124" t="s">
+        <v>78</v>
+      </c>
+      <c r="D83" s="119"/>
+      <c r="E83" s="119"/>
+      <c r="F83" s="119"/>
+      <c r="G83" s="119"/>
+      <c r="H83" s="116"/>
+      <c r="I83" s="119"/>
+      <c r="J83" s="116"/>
+      <c r="K83" s="116"/>
+      <c r="L83" s="25"/>
+    </row>
+    <row r="84" spans="2:12">
+      <c r="B84" s="123"/>
+      <c r="C84" s="118" t="s">
+        <v>151</v>
+      </c>
+      <c r="D84" s="119">
         <v>2</v>
       </c>
-      <c r="E82" s="119">
+      <c r="E84" s="119">
         <f>15.42/3.281</f>
         <v>4.6997866504114594</v>
       </c>
-      <c r="F82" s="119"/>
-      <c r="G82" s="119">
-        <f>4.583/3.281</f>
-        <v>1.3968302346845474</v>
-      </c>
-      <c r="H82" s="116">
-        <f>D82*E82*G82</f>
-        <v>13.129608179723084</v>
-      </c>
-      <c r="I82" s="119"/>
-      <c r="J82" s="116"/>
-      <c r="K82" s="116"/>
-      <c r="L82" s="25"/>
-    </row>
-    <row r="83" spans="2:14">
-      <c r="B83" s="147"/>
-      <c r="C83" s="149"/>
-      <c r="D83" s="119">
+      <c r="F84" s="119"/>
+      <c r="G84" s="119">
+        <f>5.25/3.281</f>
+        <v>1.6001219140505942</v>
+      </c>
+      <c r="H84" s="116">
+        <f>D84*E84*G84</f>
+        <v>15.040463221371631</v>
+      </c>
+      <c r="I84" s="119"/>
+      <c r="J84" s="116"/>
+      <c r="K84" s="116"/>
+      <c r="L84" s="25"/>
+    </row>
+    <row r="85" spans="2:12">
+      <c r="B85" s="123"/>
+      <c r="C85" s="125"/>
+      <c r="D85" s="119">
         <v>2</v>
       </c>
-      <c r="E83" s="119">
+      <c r="E85" s="119">
         <f>10/3.281</f>
         <v>3.047851264858275</v>
       </c>
-      <c r="F83" s="119"/>
-      <c r="G83" s="119">
-        <f>4.583/3.281</f>
-        <v>1.3968302346845474</v>
-      </c>
-      <c r="H83" s="116">
-        <f>D83*E83*G83</f>
-        <v>8.5146615951511571</v>
-      </c>
-      <c r="I83" s="119"/>
-      <c r="J83" s="165"/>
-      <c r="K83" s="116"/>
-      <c r="L83" s="25"/>
-    </row>
-    <row r="84" spans="2:14">
-      <c r="B84" s="147"/>
-      <c r="C84" s="149"/>
-      <c r="D84" s="119"/>
-      <c r="E84" s="116"/>
-      <c r="F84" s="116"/>
-      <c r="G84" s="151"/>
-      <c r="H84" s="116">
-        <f>SUM(H82:H83)</f>
-        <v>21.644269774874239</v>
-      </c>
-      <c r="I84" s="119" t="s">
+      <c r="F85" s="119"/>
+      <c r="G85" s="119">
+        <f>5.25/3.281</f>
+        <v>1.6001219140505942</v>
+      </c>
+      <c r="H85" s="116">
+        <f>D85*E85*G85</f>
+        <v>9.7538671993330954</v>
+      </c>
+      <c r="I85" s="119"/>
+      <c r="J85" s="141"/>
+      <c r="K85" s="116"/>
+      <c r="L85" s="25"/>
+    </row>
+    <row r="86" spans="2:12" s="121" customFormat="1">
+      <c r="B86" s="123"/>
+      <c r="C86" s="137" t="str">
+        <f>C76</f>
+        <v>-at toilet of ward</v>
+      </c>
+      <c r="D86" s="119">
+        <f>D76</f>
+        <v>1</v>
+      </c>
+      <c r="E86" s="119">
+        <f>E76</f>
+        <v>1.6245047241694606</v>
+      </c>
+      <c r="F86" s="119"/>
+      <c r="G86" s="119">
+        <f>G76-4/3.281</f>
+        <v>1.4477293508076805</v>
+      </c>
+      <c r="H86" s="116">
+        <f>D86*E86*G86</f>
+        <v>2.3518431697058633</v>
+      </c>
+      <c r="I86" s="119"/>
+      <c r="J86" s="141"/>
+      <c r="K86" s="116"/>
+      <c r="L86" s="25"/>
+    </row>
+    <row r="87" spans="2:12" s="121" customFormat="1">
+      <c r="B87" s="123"/>
+      <c r="C87" s="137" t="str">
+        <f>C77</f>
+        <v>-deduction for opening</v>
+      </c>
+      <c r="D87" s="119">
+        <f>D77</f>
+        <v>-1</v>
+      </c>
+      <c r="E87" s="119">
+        <f>E77</f>
+        <v>0.76196281621456874</v>
+      </c>
+      <c r="F87" s="119"/>
+      <c r="G87" s="119">
+        <f>G77</f>
+        <v>1.9811033221578787</v>
+      </c>
+      <c r="H87" s="116">
+        <f>D87*E87*G87</f>
+        <v>-1.5095270665634553</v>
+      </c>
+      <c r="I87" s="119"/>
+      <c r="J87" s="141"/>
+      <c r="K87" s="116"/>
+      <c r="L87" s="25"/>
+    </row>
+    <row r="88" spans="2:12">
+      <c r="B88" s="123"/>
+      <c r="C88" s="125"/>
+      <c r="D88" s="119"/>
+      <c r="E88" s="116"/>
+      <c r="F88" s="116"/>
+      <c r="G88" s="127"/>
+      <c r="H88" s="116">
+        <f>SUM(H84:H87)</f>
+        <v>25.636646523847133</v>
+      </c>
+      <c r="I88" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="J84" s="116">
+      <c r="J88" s="116">
         <v>415.5</v>
       </c>
-      <c r="K84" s="116">
-        <f>H84*J84</f>
-        <v>8993.1940914602455</v>
-      </c>
-      <c r="L84" s="25"/>
-    </row>
-    <row r="85" spans="2:14">
-      <c r="B85" s="147"/>
-      <c r="C85" s="118" t="s">
+      <c r="K88" s="116">
+        <f>H88*J88</f>
+        <v>10652.026630658484</v>
+      </c>
+      <c r="L88" s="25"/>
+    </row>
+    <row r="89" spans="2:12">
+      <c r="B89" s="123"/>
+      <c r="C89" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="D85" s="119"/>
-      <c r="E85" s="116"/>
-      <c r="F85" s="116"/>
-      <c r="G85" s="151"/>
-      <c r="H85" s="116"/>
-      <c r="I85" s="119"/>
-      <c r="J85" s="165"/>
-      <c r="K85" s="116">
-        <f>0.13*H84*7010.67/100</f>
-        <v>197.26308261740283</v>
-      </c>
-      <c r="L85" s="25"/>
-    </row>
-    <row r="86" spans="2:14">
-      <c r="B86" s="147"/>
-      <c r="C86" s="118" t="s">
+      <c r="D89" s="119"/>
+      <c r="E89" s="116"/>
+      <c r="F89" s="116"/>
+      <c r="G89" s="127"/>
+      <c r="H89" s="116"/>
+      <c r="I89" s="119"/>
+      <c r="J89" s="141"/>
+      <c r="K89" s="116">
+        <f>0.13*H88*7010.67/100</f>
+        <v>233.64908929094122</v>
+      </c>
+      <c r="L89" s="25"/>
+    </row>
+    <row r="90" spans="2:12">
+      <c r="B90" s="123"/>
+      <c r="C90" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="D86" s="119"/>
-      <c r="E86" s="116"/>
-      <c r="F86" s="116"/>
-      <c r="G86" s="151"/>
-      <c r="H86" s="116"/>
-      <c r="I86" s="119"/>
-      <c r="J86" s="165"/>
-      <c r="K86" s="116">
-        <f>0.13*H84*4639.73/100</f>
-        <v>130.5506381433504</v>
-      </c>
-      <c r="L86" s="25"/>
-    </row>
-    <row r="87" spans="2:14">
-      <c r="B87" s="81"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="72"/>
-      <c r="E87" s="70"/>
-      <c r="F87" s="70"/>
-      <c r="G87" s="71"/>
-      <c r="H87" s="72"/>
-      <c r="I87" s="72"/>
-      <c r="J87" s="72"/>
-      <c r="K87" s="72"/>
-      <c r="L87" s="25"/>
-    </row>
-    <row r="88" spans="2:14" ht="35.1" customHeight="1">
-      <c r="B88" s="81">
-        <v>8</v>
-      </c>
-      <c r="C88" s="79" t="s">
+      <c r="D90" s="119"/>
+      <c r="E90" s="116"/>
+      <c r="F90" s="116"/>
+      <c r="G90" s="127"/>
+      <c r="H90" s="116"/>
+      <c r="I90" s="119"/>
+      <c r="J90" s="141"/>
+      <c r="K90" s="116">
+        <f>0.13*H88*4639.73/100</f>
+        <v>154.63125336891602</v>
+      </c>
+      <c r="L90" s="25"/>
+    </row>
+    <row r="91" spans="2:12" s="121" customFormat="1">
+      <c r="B91" s="123"/>
+      <c r="C91" s="118"/>
+      <c r="D91" s="119"/>
+      <c r="E91" s="116"/>
+      <c r="F91" s="116"/>
+      <c r="G91" s="127"/>
+      <c r="H91" s="116"/>
+      <c r="I91" s="119"/>
+      <c r="J91" s="141"/>
+      <c r="K91" s="116"/>
+      <c r="L91" s="25"/>
+    </row>
+    <row r="92" spans="2:12" s="121" customFormat="1" ht="78.599999999999994">
+      <c r="B92" s="123">
+        <v>11</v>
+      </c>
+      <c r="C92" s="169" t="s">
+        <v>153</v>
+      </c>
+      <c r="D92" s="169"/>
+      <c r="E92" s="116"/>
+      <c r="F92" s="116"/>
+      <c r="G92" s="127"/>
+      <c r="H92" s="116"/>
+      <c r="I92" s="119"/>
+      <c r="J92" s="141"/>
+      <c r="K92" s="116"/>
+      <c r="L92" s="25"/>
+    </row>
+    <row r="93" spans="2:12" s="121" customFormat="1">
+      <c r="B93" s="123"/>
+      <c r="C93" s="118" t="str">
+        <f>C86</f>
+        <v>-at toilet of ward</v>
+      </c>
+      <c r="D93" s="119">
+        <v>1</v>
+      </c>
+      <c r="E93" s="116">
+        <f>E86-2.5/3.281</f>
+        <v>0.86254190795489183</v>
+      </c>
+      <c r="F93" s="116"/>
+      <c r="G93" s="127">
+        <f>4/3.281</f>
+        <v>1.2191405059433098</v>
+      </c>
+      <c r="H93" s="116">
+        <f>D93*E93*G93</f>
+        <v>1.0515597780614345</v>
+      </c>
+      <c r="I93" s="119"/>
+      <c r="J93" s="141"/>
+      <c r="K93" s="116"/>
+      <c r="L93" s="25"/>
+    </row>
+    <row r="94" spans="2:12" s="121" customFormat="1">
+      <c r="B94" s="123"/>
+      <c r="C94" s="125"/>
+      <c r="D94" s="119"/>
+      <c r="E94" s="116"/>
+      <c r="F94" s="116"/>
+      <c r="G94" s="127"/>
+      <c r="H94" s="116">
+        <f>SUM(H93)</f>
+        <v>1.0515597780614345</v>
+      </c>
+      <c r="I94" s="119" t="s">
+        <v>40</v>
+      </c>
+      <c r="J94" s="116">
+        <v>415.5</v>
+      </c>
+      <c r="K94" s="116">
+        <f>H94*J94</f>
+        <v>436.92308778452605</v>
+      </c>
+      <c r="L94" s="25"/>
+    </row>
+    <row r="95" spans="2:12" s="121" customFormat="1">
+      <c r="B95" s="123"/>
+      <c r="C95" s="118" t="s">
+        <v>154</v>
+      </c>
+      <c r="D95" s="119"/>
+      <c r="E95" s="116"/>
+      <c r="F95" s="116"/>
+      <c r="G95" s="127"/>
+      <c r="H95" s="116"/>
+      <c r="I95" s="119"/>
+      <c r="J95" s="141"/>
+      <c r="K95" s="116">
+        <f>0.13*H94*6746.52/10</f>
+        <v>92.226797960531385</v>
+      </c>
+      <c r="L95" s="25"/>
+    </row>
+    <row r="96" spans="2:12" s="121" customFormat="1">
+      <c r="B96" s="123"/>
+      <c r="C96" s="118" t="s">
+        <v>30</v>
+      </c>
+      <c r="D96" s="119"/>
+      <c r="E96" s="116"/>
+      <c r="F96" s="116"/>
+      <c r="G96" s="127"/>
+      <c r="H96" s="116"/>
+      <c r="I96" s="119"/>
+      <c r="J96" s="141"/>
+      <c r="K96" s="116">
+        <f>0.13*H94*483.04/10</f>
+        <v>6.6032906575323391</v>
+      </c>
+      <c r="L96" s="25"/>
+    </row>
+    <row r="97" spans="2:12" s="121" customFormat="1">
+      <c r="B97" s="123"/>
+      <c r="C97" s="118" t="s">
+        <v>29</v>
+      </c>
+      <c r="D97" s="119"/>
+      <c r="E97" s="116"/>
+      <c r="F97" s="116"/>
+      <c r="G97" s="127"/>
+      <c r="H97" s="116"/>
+      <c r="I97" s="119"/>
+      <c r="J97" s="141"/>
+      <c r="K97" s="116">
+        <f>0.13*H94*729.73/10</f>
+        <v>9.9756113189820184</v>
+      </c>
+      <c r="L97" s="25"/>
+    </row>
+    <row r="98" spans="2:12" s="121" customFormat="1">
+      <c r="B98" s="123"/>
+      <c r="C98" s="118" t="s">
+        <v>155</v>
+      </c>
+      <c r="D98" s="119"/>
+      <c r="E98" s="116"/>
+      <c r="F98" s="116"/>
+      <c r="G98" s="127"/>
+      <c r="H98" s="116"/>
+      <c r="I98" s="119"/>
+      <c r="J98" s="141"/>
+      <c r="K98" s="116">
+        <f>0.13*H94*100.06/10</f>
+        <v>1.3678479281067528</v>
+      </c>
+      <c r="L98" s="25"/>
+    </row>
+    <row r="99" spans="2:12" s="121" customFormat="1">
+      <c r="B99" s="123"/>
+      <c r="C99" s="118"/>
+      <c r="D99" s="119"/>
+      <c r="E99" s="116"/>
+      <c r="F99" s="116"/>
+      <c r="G99" s="127"/>
+      <c r="H99" s="116"/>
+      <c r="I99" s="119"/>
+      <c r="J99" s="141"/>
+      <c r="K99" s="116"/>
+      <c r="L99" s="25"/>
+    </row>
+    <row r="100" spans="2:12" s="121" customFormat="1" ht="34.799999999999997">
+      <c r="B100" s="123">
+        <v>12</v>
+      </c>
+      <c r="C100" s="169" t="s">
+        <v>169</v>
+      </c>
+      <c r="D100" s="119"/>
+      <c r="E100" s="116"/>
+      <c r="F100" s="116"/>
+      <c r="G100" s="127"/>
+      <c r="H100" s="116"/>
+      <c r="I100" s="119"/>
+      <c r="J100" s="141"/>
+      <c r="K100" s="116"/>
+      <c r="L100" s="25"/>
+    </row>
+    <row r="101" spans="2:12" s="121" customFormat="1">
+      <c r="B101" s="123"/>
+      <c r="C101" s="118" t="str">
+        <f>C93</f>
+        <v>-at toilet of ward</v>
+      </c>
+      <c r="D101" s="119">
+        <f>D93</f>
+        <v>1</v>
+      </c>
+      <c r="E101" s="119">
+        <f>E86</f>
+        <v>1.6245047241694606</v>
+      </c>
+      <c r="F101" s="119"/>
+      <c r="G101" s="116">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="H101" s="119">
+        <f>PRODUCT(D101:G101)</f>
+        <v>3.9609990226625063</v>
+      </c>
+      <c r="I101" s="127"/>
+      <c r="J101" s="116"/>
+      <c r="K101" s="119"/>
+      <c r="L101" s="25"/>
+    </row>
+    <row r="102" spans="2:12" s="121" customFormat="1">
+      <c r="B102" s="123"/>
+      <c r="C102" s="118" t="str">
+        <f>C87</f>
+        <v>-deduction for opening</v>
+      </c>
+      <c r="D102" s="119">
+        <f>D87</f>
+        <v>-1</v>
+      </c>
+      <c r="E102" s="119">
+        <f>E87</f>
+        <v>0.76196281621456874</v>
+      </c>
+      <c r="F102" s="119"/>
+      <c r="G102" s="116">
+        <f>G87</f>
+        <v>1.9811033221578787</v>
+      </c>
+      <c r="H102" s="119">
+        <f>PRODUCT(D102:G102)</f>
+        <v>-1.5095270665634553</v>
+      </c>
+      <c r="I102" s="127"/>
+      <c r="J102" s="116"/>
+      <c r="K102" s="119"/>
+      <c r="L102" s="25"/>
+    </row>
+    <row r="103" spans="2:12" s="121" customFormat="1">
+      <c r="B103" s="123"/>
+      <c r="C103" s="118"/>
+      <c r="D103" s="119"/>
+      <c r="E103" s="119"/>
+      <c r="F103" s="119"/>
+      <c r="G103" s="116"/>
+      <c r="H103" s="119">
+        <f>SUM(H101:H102)</f>
+        <v>2.4514719560990512</v>
+      </c>
+      <c r="I103" s="127" t="s">
+        <v>23</v>
+      </c>
+      <c r="J103" s="116">
+        <v>57.76</v>
+      </c>
+      <c r="K103" s="119">
+        <f t="shared" ref="K103" si="10">H103*J103</f>
+        <v>141.59702018428121</v>
+      </c>
+      <c r="L103" s="25"/>
+    </row>
+    <row r="104" spans="2:12" s="121" customFormat="1">
+      <c r="B104" s="123"/>
+      <c r="C104" s="118" t="s">
+        <v>29</v>
+      </c>
+      <c r="D104" s="119"/>
+      <c r="E104" s="119"/>
+      <c r="F104" s="119"/>
+      <c r="G104" s="127"/>
+      <c r="H104" s="119"/>
+      <c r="I104" s="127"/>
+      <c r="J104" s="116"/>
+      <c r="K104" s="142">
+        <f>0.13*H103*20.7</f>
+        <v>6.5969110338625461</v>
+      </c>
+      <c r="L104" s="25"/>
+    </row>
+    <row r="105" spans="2:12">
+      <c r="B105" s="81"/>
+      <c r="C105" s="19"/>
+      <c r="D105" s="72"/>
+      <c r="E105" s="70"/>
+      <c r="F105" s="70"/>
+      <c r="G105" s="71"/>
+      <c r="H105" s="72"/>
+      <c r="I105" s="72"/>
+      <c r="J105" s="72"/>
+      <c r="K105" s="72"/>
+      <c r="L105" s="25"/>
+    </row>
+    <row r="106" spans="2:12" s="121" customFormat="1" ht="34.799999999999997">
+      <c r="B106" s="123">
+        <v>13</v>
+      </c>
+      <c r="C106" s="169" t="s">
+        <v>170</v>
+      </c>
+      <c r="D106" s="119"/>
+      <c r="E106" s="116"/>
+      <c r="F106" s="116"/>
+      <c r="G106" s="127"/>
+      <c r="H106" s="116"/>
+      <c r="I106" s="119"/>
+      <c r="J106" s="141"/>
+      <c r="K106" s="116"/>
+      <c r="L106" s="25"/>
+    </row>
+    <row r="107" spans="2:12" s="121" customFormat="1">
+      <c r="B107" s="123"/>
+      <c r="C107" s="118" t="str">
+        <f>C101</f>
+        <v>-at toilet of ward</v>
+      </c>
+      <c r="D107" s="119">
+        <f>D101</f>
+        <v>1</v>
+      </c>
+      <c r="E107" s="119">
+        <f>E101</f>
+        <v>1.6245047241694606</v>
+      </c>
+      <c r="F107" s="119"/>
+      <c r="G107" s="116">
+        <f>G101</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="H107" s="119">
+        <f>PRODUCT(D107:G107)</f>
+        <v>3.9609990226625063</v>
+      </c>
+      <c r="I107" s="127"/>
+      <c r="J107" s="116"/>
+      <c r="K107" s="119"/>
+      <c r="L107" s="25"/>
+    </row>
+    <row r="108" spans="2:12" s="121" customFormat="1">
+      <c r="B108" s="123"/>
+      <c r="C108" s="118" t="str">
+        <f>C102</f>
+        <v>-deduction for opening</v>
+      </c>
+      <c r="D108" s="119">
+        <f>D102</f>
+        <v>-1</v>
+      </c>
+      <c r="E108" s="119">
+        <f>E93</f>
+        <v>0.86254190795489183</v>
+      </c>
+      <c r="F108" s="119"/>
+      <c r="G108" s="116">
+        <f>G93</f>
+        <v>1.2191405059433098</v>
+      </c>
+      <c r="H108" s="119">
+        <f>PRODUCT(D108:G108)</f>
+        <v>-1.0515597780614345</v>
+      </c>
+      <c r="I108" s="127"/>
+      <c r="J108" s="116"/>
+      <c r="K108" s="119"/>
+      <c r="L108" s="25"/>
+    </row>
+    <row r="109" spans="2:12" s="121" customFormat="1">
+      <c r="B109" s="123"/>
+      <c r="C109" s="118"/>
+      <c r="D109" s="119">
+        <v>-1</v>
+      </c>
+      <c r="E109" s="119">
+        <f>2.5/3.81</f>
+        <v>0.65616797900262469</v>
+      </c>
+      <c r="F109" s="119"/>
+      <c r="G109" s="116">
+        <f>(6.5-4)/3.281</f>
+        <v>0.76196281621456874</v>
+      </c>
+      <c r="H109" s="119">
+        <f>PRODUCT(D109:G109)</f>
+        <v>-0.49997560119066192</v>
+      </c>
+      <c r="I109" s="127"/>
+      <c r="J109" s="116"/>
+      <c r="K109" s="119"/>
+      <c r="L109" s="25"/>
+    </row>
+    <row r="110" spans="2:12" s="121" customFormat="1">
+      <c r="B110" s="123"/>
+      <c r="C110" s="118"/>
+      <c r="D110" s="119"/>
+      <c r="E110" s="119"/>
+      <c r="F110" s="119"/>
+      <c r="G110" s="116"/>
+      <c r="H110" s="119">
+        <f>SUM(H107:H109)</f>
+        <v>2.40946364341041</v>
+      </c>
+      <c r="I110" s="127" t="s">
+        <v>23</v>
+      </c>
+      <c r="J110" s="116">
+        <v>334.57</v>
+      </c>
+      <c r="K110" s="119">
+        <f t="shared" ref="K110" si="11">H110*J110</f>
+        <v>806.13425117582085</v>
+      </c>
+      <c r="L110" s="25"/>
+    </row>
+    <row r="111" spans="2:12" s="121" customFormat="1">
+      <c r="B111" s="123"/>
+      <c r="C111" s="118" t="s">
+        <v>29</v>
+      </c>
+      <c r="D111" s="119"/>
+      <c r="E111" s="119"/>
+      <c r="F111" s="119"/>
+      <c r="G111" s="127"/>
+      <c r="H111" s="119"/>
+      <c r="I111" s="127"/>
+      <c r="J111" s="116"/>
+      <c r="K111" s="142">
+        <f>0.13*H110*110.368</f>
+        <v>34.570598841469618</v>
+      </c>
+      <c r="L111" s="25"/>
+    </row>
+    <row r="112" spans="2:12" s="121" customFormat="1">
+      <c r="B112" s="81"/>
+      <c r="C112" s="19"/>
+      <c r="D112" s="72"/>
+      <c r="E112" s="70"/>
+      <c r="F112" s="70"/>
+      <c r="G112" s="71"/>
+      <c r="H112" s="72"/>
+      <c r="I112" s="72"/>
+      <c r="J112" s="72"/>
+      <c r="K112" s="72"/>
+      <c r="L112" s="25"/>
+    </row>
+    <row r="113" spans="2:14" ht="35.1" customHeight="1">
+      <c r="B113" s="123">
+        <v>14</v>
+      </c>
+      <c r="C113" s="124" t="s">
+        <v>77</v>
+      </c>
+      <c r="D113" s="119"/>
+      <c r="E113" s="119"/>
+      <c r="F113" s="119"/>
+      <c r="G113" s="116"/>
+      <c r="H113" s="119"/>
+      <c r="I113" s="127"/>
+      <c r="J113" s="116"/>
+      <c r="K113" s="119"/>
+      <c r="L113" s="25"/>
+    </row>
+    <row r="114" spans="2:14">
+      <c r="B114" s="123"/>
+      <c r="C114" s="118" t="s">
+        <v>150</v>
+      </c>
+      <c r="D114" s="119">
+        <v>1</v>
+      </c>
+      <c r="E114" s="119">
+        <f>13.42/3.281</f>
+        <v>4.0902163974398045</v>
+      </c>
+      <c r="F114" s="119">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="G114" s="116"/>
+      <c r="H114" s="119">
+        <f>F114*E114*D114</f>
+        <v>9.9730969763847703</v>
+      </c>
+      <c r="I114" s="127" t="s">
+        <v>23</v>
+      </c>
+      <c r="J114" s="116">
+        <v>689.98</v>
+      </c>
+      <c r="K114" s="119">
+        <f>H114*J114</f>
+        <v>6881.2374517659637</v>
+      </c>
+      <c r="L114" s="25"/>
+    </row>
+    <row r="115" spans="2:14">
+      <c r="B115" s="123"/>
+      <c r="C115" s="118" t="s">
+        <v>29</v>
+      </c>
+      <c r="D115" s="119"/>
+      <c r="E115" s="119"/>
+      <c r="F115" s="119"/>
+      <c r="G115" s="127"/>
+      <c r="H115" s="119"/>
+      <c r="I115" s="127"/>
+      <c r="J115" s="116"/>
+      <c r="K115" s="142">
+        <f>0.13*H114*1694.03/10</f>
+        <v>219.63143112176621</v>
+      </c>
+      <c r="L115" s="25"/>
+    </row>
+    <row r="116" spans="2:14">
+      <c r="B116" s="123"/>
+      <c r="C116" s="118" t="s">
+        <v>30</v>
+      </c>
+      <c r="D116" s="119"/>
+      <c r="E116" s="119"/>
+      <c r="F116" s="119"/>
+      <c r="G116" s="127"/>
+      <c r="H116" s="119"/>
+      <c r="I116" s="127"/>
+      <c r="J116" s="116"/>
+      <c r="K116" s="142">
+        <f>0.13*H114*572.02/10</f>
+        <v>74.162542121611025</v>
+      </c>
+      <c r="L116" s="25"/>
+    </row>
+    <row r="117" spans="2:14">
+      <c r="B117" s="123"/>
+      <c r="C117" s="118" t="s">
+        <v>31</v>
+      </c>
+      <c r="D117" s="119"/>
+      <c r="E117" s="119"/>
+      <c r="F117" s="119"/>
+      <c r="G117" s="127"/>
+      <c r="H117" s="119"/>
+      <c r="I117" s="127"/>
+      <c r="J117" s="116"/>
+      <c r="K117" s="142">
+        <f>0.13*H114*1207.6/10</f>
+        <v>156.56565481286924</v>
+      </c>
+      <c r="L117" s="25"/>
+    </row>
+    <row r="118" spans="2:14" ht="18" customHeight="1">
+      <c r="B118" s="80"/>
+      <c r="C118" s="19"/>
+      <c r="D118" s="24"/>
+      <c r="E118" s="70"/>
+      <c r="F118" s="70"/>
+      <c r="G118" s="71"/>
+      <c r="H118" s="70"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="73"/>
+      <c r="K118" s="73"/>
+      <c r="L118" s="25"/>
+    </row>
+    <row r="119" spans="2:14" ht="35.1" customHeight="1">
+      <c r="B119" s="123">
+        <v>15</v>
+      </c>
+      <c r="C119" s="124" t="s">
         <v>79</v>
       </c>
-      <c r="D88" s="72"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="72"/>
-      <c r="G88" s="72"/>
-      <c r="H88" s="72"/>
-      <c r="I88" s="72"/>
-      <c r="J88" s="72"/>
-      <c r="K88" s="72"/>
-      <c r="L88" s="25"/>
-    </row>
-    <row r="89" spans="2:14">
-      <c r="B89" s="81"/>
-      <c r="C89" s="19" t="str">
-        <f>C82</f>
+      <c r="D119" s="119"/>
+      <c r="E119" s="119"/>
+      <c r="F119" s="119"/>
+      <c r="G119" s="119"/>
+      <c r="H119" s="119"/>
+      <c r="I119" s="119"/>
+      <c r="J119" s="119"/>
+      <c r="K119" s="119"/>
+      <c r="L119" s="25"/>
+    </row>
+    <row r="120" spans="2:14">
+      <c r="B120" s="123"/>
+      <c r="C120" s="118" t="str">
+        <f>C84</f>
         <v>-At shear wall</v>
       </c>
-      <c r="D89" s="72">
-        <f>D57</f>
+      <c r="D120" s="119">
+        <f>D64</f>
         <v>2</v>
       </c>
-      <c r="E89" s="72">
-        <f>E57</f>
-        <v>0</v>
-      </c>
-      <c r="F89" s="72"/>
-      <c r="G89" s="72">
-        <f>G57+0.3+0.3</f>
-        <v>1.8709539774459008</v>
-      </c>
-      <c r="H89" s="72">
-        <f t="shared" ref="H89:H90" si="6">D89*E89*G89</f>
-        <v>0</v>
-      </c>
-      <c r="I89" s="72"/>
-      <c r="J89" s="72"/>
-      <c r="K89" s="72"/>
-      <c r="L89" s="25"/>
-    </row>
-    <row r="90" spans="2:14">
-      <c r="B90" s="81"/>
-      <c r="C90" s="19"/>
-      <c r="D90" s="72">
-        <f>D58</f>
+      <c r="E120" s="119">
+        <f>E84</f>
+        <v>4.6997866504114594</v>
+      </c>
+      <c r="F120" s="119"/>
+      <c r="G120" s="119">
+        <f>G64+0.3+0.3</f>
+        <v>2.2001219140505941</v>
+      </c>
+      <c r="H120" s="116">
+        <f>PRODUCT(D120:G120)</f>
+        <v>20.680207201865382</v>
+      </c>
+      <c r="I120" s="119"/>
+      <c r="J120" s="119"/>
+      <c r="K120" s="119"/>
+      <c r="L120" s="25"/>
+    </row>
+    <row r="121" spans="2:14">
+      <c r="B121" s="123"/>
+      <c r="C121" s="118"/>
+      <c r="D121" s="119">
+        <f>D65</f>
         <v>2</v>
       </c>
-      <c r="E90" s="72">
-        <f>E58</f>
+      <c r="E121" s="119">
+        <f>E85</f>
         <v>3.047851264858275</v>
       </c>
-      <c r="F90" s="72"/>
-      <c r="G90" s="72">
-        <f>G58+0.3+0.3</f>
-        <v>1.8709539774459008</v>
-      </c>
-      <c r="H90" s="72">
-        <f t="shared" si="6"/>
-        <v>11.404778893300218</v>
-      </c>
-      <c r="I90" s="72"/>
-      <c r="J90" s="72"/>
-      <c r="K90" s="72"/>
-      <c r="L90" s="25"/>
-    </row>
-    <row r="91" spans="2:14">
-      <c r="B91" s="81"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="72"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="72"/>
-      <c r="G91" s="72"/>
-      <c r="H91" s="72">
-        <f>SUM(H88:H90)</f>
-        <v>11.404778893300218</v>
-      </c>
-      <c r="I91" s="24" t="s">
+      <c r="F121" s="119"/>
+      <c r="G121" s="119">
+        <f>G65+0.3+0.3</f>
+        <v>2.2001219140505941</v>
+      </c>
+      <c r="H121" s="116">
+        <f t="shared" ref="H121:H122" si="12">PRODUCT(D121:G121)</f>
+        <v>13.411288717163025</v>
+      </c>
+      <c r="I121" s="119"/>
+      <c r="J121" s="119"/>
+      <c r="K121" s="119"/>
+      <c r="L121" s="25"/>
+    </row>
+    <row r="122" spans="2:14" s="121" customFormat="1">
+      <c r="B122" s="123"/>
+      <c r="C122" s="136" t="s">
+        <v>152</v>
+      </c>
+      <c r="D122" s="119">
+        <v>1</v>
+      </c>
+      <c r="E122" s="119">
+        <f>E114</f>
+        <v>4.0902163974398045</v>
+      </c>
+      <c r="F122" s="119">
+        <f>F114</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="G122" s="119"/>
+      <c r="H122" s="116">
+        <f t="shared" si="12"/>
+        <v>9.9730969763847703</v>
+      </c>
+      <c r="I122" s="119"/>
+      <c r="J122" s="119"/>
+      <c r="K122" s="119"/>
+      <c r="L122" s="25"/>
+    </row>
+    <row r="123" spans="2:14">
+      <c r="B123" s="123"/>
+      <c r="C123" s="118"/>
+      <c r="D123" s="119"/>
+      <c r="E123" s="119"/>
+      <c r="F123" s="119"/>
+      <c r="G123" s="119"/>
+      <c r="H123" s="119">
+        <f>SUM(H120:H122)</f>
+        <v>44.06459289541317</v>
+      </c>
+      <c r="I123" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="J91" s="72">
-        <f>'[1]Table of Content 2'!$H$187</f>
-        <v>286.77</v>
-      </c>
-      <c r="K91" s="72">
-        <f>H91*J91</f>
-        <v>3270.5484432317035</v>
-      </c>
-      <c r="L91" s="25"/>
-    </row>
-    <row r="92" spans="2:14">
-      <c r="B92" s="81"/>
-      <c r="C92" s="19" t="s">
+      <c r="J123" s="119">
+        <v>287.32</v>
+      </c>
+      <c r="K123" s="119">
+        <f>H123*J123</f>
+        <v>12660.638830710112</v>
+      </c>
+      <c r="L123" s="25"/>
+    </row>
+    <row r="124" spans="2:14">
+      <c r="B124" s="123"/>
+      <c r="C124" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="D92" s="72"/>
-      <c r="E92" s="72"/>
-      <c r="F92" s="72"/>
-      <c r="G92" s="72"/>
-      <c r="H92" s="72"/>
-      <c r="I92" s="72"/>
-      <c r="J92" s="72"/>
-      <c r="K92" s="72">
-        <f>'[1]Update Descrip'!$H$2269/10*H91*0.13</f>
-        <v>113.82379907553776</v>
-      </c>
-      <c r="L92" s="25"/>
-    </row>
-    <row r="93" spans="2:14">
-      <c r="B93" s="81"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="72"/>
-      <c r="E93" s="72"/>
-      <c r="F93" s="72"/>
-      <c r="G93" s="72"/>
-      <c r="H93" s="72"/>
-      <c r="I93" s="72"/>
-      <c r="J93" s="72"/>
-      <c r="K93" s="72"/>
-      <c r="L93" s="25"/>
-    </row>
-    <row r="94" spans="2:14">
-      <c r="B94" s="81"/>
-      <c r="C94" s="19"/>
-      <c r="D94" s="72"/>
-      <c r="E94" s="72"/>
-      <c r="F94" s="72"/>
-      <c r="G94" s="72"/>
-      <c r="H94" s="72"/>
-      <c r="I94" s="72"/>
-      <c r="J94" s="72"/>
-      <c r="K94" s="72"/>
-      <c r="L94" s="25"/>
-    </row>
-    <row r="95" spans="2:14" ht="33" customHeight="1">
-      <c r="B95" s="80">
-        <v>9</v>
-      </c>
-      <c r="C95" s="21" t="s">
+      <c r="D124" s="119"/>
+      <c r="E124" s="119"/>
+      <c r="F124" s="119"/>
+      <c r="G124" s="119"/>
+      <c r="H124" s="119"/>
+      <c r="I124" s="119"/>
+      <c r="J124" s="119"/>
+      <c r="K124" s="119">
+        <f>0.13*H123*693.24/10</f>
+        <v>397.11539892461093</v>
+      </c>
+      <c r="L124" s="25"/>
+    </row>
+    <row r="125" spans="2:14">
+      <c r="B125" s="81"/>
+      <c r="C125" s="19"/>
+      <c r="D125" s="72"/>
+      <c r="E125" s="72"/>
+      <c r="F125" s="72"/>
+      <c r="G125" s="72"/>
+      <c r="H125" s="72"/>
+      <c r="I125" s="72"/>
+      <c r="J125" s="72"/>
+      <c r="K125" s="72"/>
+      <c r="L125" s="25"/>
+    </row>
+    <row r="126" spans="2:14">
+      <c r="B126" s="81"/>
+      <c r="C126" s="19"/>
+      <c r="D126" s="72"/>
+      <c r="E126" s="72"/>
+      <c r="F126" s="72"/>
+      <c r="G126" s="72"/>
+      <c r="H126" s="72"/>
+      <c r="I126" s="72"/>
+      <c r="J126" s="72"/>
+      <c r="K126" s="72"/>
+      <c r="L126" s="25"/>
+    </row>
+    <row r="127" spans="2:14" ht="33" customHeight="1">
+      <c r="B127" s="123">
+        <v>16</v>
+      </c>
+      <c r="C127" s="125" t="s">
         <v>87</v>
       </c>
-      <c r="D95" s="24">
+      <c r="D127" s="119">
         <v>1</v>
       </c>
-      <c r="E95" s="70"/>
-      <c r="F95" s="70"/>
-      <c r="G95" s="71"/>
-      <c r="H95" s="70">
-        <f>+D95</f>
+      <c r="E127" s="116"/>
+      <c r="F127" s="116"/>
+      <c r="G127" s="127"/>
+      <c r="H127" s="116">
+        <f>+D127</f>
         <v>1</v>
       </c>
-      <c r="I95" s="24" t="s">
+      <c r="I127" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="J95" s="73">
+      <c r="J127" s="116">
         <v>4659</v>
       </c>
-      <c r="K95" s="73">
-        <f>H95*J95</f>
+      <c r="K127" s="116">
+        <f>H127*J127</f>
         <v>4659</v>
       </c>
-      <c r="L95" s="25"/>
-      <c r="N95" s="1" t="s">
+      <c r="L127" s="25"/>
+      <c r="N127" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="96" spans="2:14">
-      <c r="B96" s="80"/>
-      <c r="C96" s="30" t="s">
+    <row r="128" spans="2:14">
+      <c r="B128" s="123"/>
+      <c r="C128" s="137" t="s">
         <v>88</v>
       </c>
-      <c r="D96" s="24"/>
-      <c r="E96" s="70"/>
-      <c r="F96" s="70"/>
-      <c r="G96" s="71"/>
-      <c r="H96" s="70"/>
-      <c r="I96" s="24"/>
-      <c r="J96" s="73"/>
-      <c r="K96" s="73">
-        <f>0.13*K95</f>
+      <c r="D128" s="119"/>
+      <c r="E128" s="116"/>
+      <c r="F128" s="116"/>
+      <c r="G128" s="127"/>
+      <c r="H128" s="116"/>
+      <c r="I128" s="119"/>
+      <c r="J128" s="116"/>
+      <c r="K128" s="116">
+        <f>0.13*K127</f>
         <v>605.67000000000007</v>
       </c>
-      <c r="L96" s="25"/>
-    </row>
-    <row r="97" spans="2:14">
-      <c r="B97" s="80"/>
-      <c r="C97" s="21"/>
-      <c r="D97" s="24"/>
-      <c r="E97" s="70"/>
-      <c r="F97" s="70"/>
-      <c r="G97" s="71"/>
-      <c r="H97" s="70"/>
-      <c r="I97" s="24"/>
-      <c r="J97" s="73"/>
-      <c r="K97" s="73"/>
-      <c r="L97" s="25"/>
-    </row>
-    <row r="98" spans="2:14" ht="33" customHeight="1">
-      <c r="B98" s="80">
-        <v>10</v>
-      </c>
-      <c r="C98" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D98" s="24"/>
-      <c r="E98" s="70"/>
-      <c r="F98" s="70"/>
-      <c r="G98" s="71"/>
-      <c r="H98" s="70">
+      <c r="L128" s="25"/>
+    </row>
+    <row r="129" spans="2:20">
+      <c r="B129" s="80"/>
+      <c r="C129" s="21"/>
+      <c r="D129" s="24"/>
+      <c r="E129" s="70"/>
+      <c r="F129" s="70"/>
+      <c r="G129" s="71"/>
+      <c r="H129" s="70"/>
+      <c r="I129" s="24"/>
+      <c r="J129" s="73"/>
+      <c r="K129" s="73"/>
+      <c r="L129" s="25"/>
+    </row>
+    <row r="130" spans="2:20" s="121" customFormat="1" ht="37.200000000000003">
+      <c r="B130" s="123">
+        <v>17</v>
+      </c>
+      <c r="C130" s="124" t="s">
+        <v>156</v>
+      </c>
+      <c r="D130" s="119"/>
+      <c r="E130" s="116"/>
+      <c r="F130" s="116"/>
+      <c r="G130" s="127"/>
+      <c r="H130" s="116"/>
+      <c r="I130" s="119"/>
+      <c r="J130" s="116"/>
+      <c r="K130" s="116"/>
+      <c r="L130" s="25"/>
+    </row>
+    <row r="131" spans="2:20" s="121" customFormat="1">
+      <c r="B131" s="123"/>
+      <c r="C131" s="138" t="s">
+        <v>157</v>
+      </c>
+      <c r="D131" s="119">
         <v>1</v>
       </c>
-      <c r="I98" s="24" t="s">
+      <c r="E131" s="116">
+        <f>1.75/3.281</f>
+        <v>0.53337397135019804</v>
+      </c>
+      <c r="F131" s="116"/>
+      <c r="G131" s="127">
+        <f>3.5/3.281</f>
+        <v>1.0667479427003961</v>
+      </c>
+      <c r="H131" s="116">
+        <f t="shared" ref="H131" si="13">PRODUCT(D131:G131)</f>
+        <v>0.56897558662776371</v>
+      </c>
+      <c r="I131" s="119"/>
+      <c r="J131" s="116"/>
+      <c r="K131" s="116"/>
+      <c r="L131" s="25"/>
+    </row>
+    <row r="132" spans="2:20" s="121" customFormat="1">
+      <c r="B132" s="123"/>
+      <c r="C132" s="118"/>
+      <c r="D132" s="119"/>
+      <c r="E132" s="119"/>
+      <c r="F132" s="119"/>
+      <c r="G132" s="119"/>
+      <c r="H132" s="119">
+        <f>SUM(H131)</f>
+        <v>0.56897558662776371</v>
+      </c>
+      <c r="I132" s="119" t="s">
+        <v>40</v>
+      </c>
+      <c r="J132" s="119">
+        <v>10663.63</v>
+      </c>
+      <c r="K132" s="119">
+        <f>H132*J132</f>
+        <v>6067.3451348314193</v>
+      </c>
+      <c r="L132" s="25"/>
+    </row>
+    <row r="133" spans="2:20" s="121" customFormat="1">
+      <c r="B133" s="123"/>
+      <c r="C133" s="118" t="s">
+        <v>158</v>
+      </c>
+      <c r="D133" s="119"/>
+      <c r="E133" s="119"/>
+      <c r="F133" s="119"/>
+      <c r="G133" s="119"/>
+      <c r="H133" s="119"/>
+      <c r="I133" s="119"/>
+      <c r="J133" s="119"/>
+      <c r="K133" s="119">
+        <f>0.13*H132*11733.39/2.23</f>
+        <v>389.1845827756519</v>
+      </c>
+      <c r="L133" s="25"/>
+    </row>
+    <row r="134" spans="2:20" s="121" customFormat="1">
+      <c r="B134" s="80"/>
+      <c r="C134" s="21"/>
+      <c r="D134" s="24"/>
+      <c r="E134" s="70"/>
+      <c r="F134" s="70"/>
+      <c r="G134" s="71"/>
+      <c r="H134" s="70"/>
+      <c r="I134" s="24"/>
+      <c r="J134" s="73"/>
+      <c r="K134" s="73"/>
+      <c r="L134" s="25"/>
+    </row>
+    <row r="135" spans="2:20" s="121" customFormat="1" ht="37.200000000000003">
+      <c r="B135" s="80">
+        <v>18</v>
+      </c>
+      <c r="C135" s="124" t="s">
+        <v>159</v>
+      </c>
+      <c r="D135" s="24"/>
+      <c r="E135" s="70"/>
+      <c r="F135" s="70"/>
+      <c r="G135" s="71"/>
+      <c r="H135" s="70"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="73"/>
+      <c r="K135" s="73"/>
+      <c r="L135" s="25"/>
+    </row>
+    <row r="136" spans="2:20" s="121" customFormat="1">
+      <c r="B136" s="123"/>
+      <c r="C136" s="138" t="s">
+        <v>160</v>
+      </c>
+      <c r="D136" s="119">
+        <v>3</v>
+      </c>
+      <c r="E136" s="116">
+        <f>1.42/3.281</f>
+        <v>0.43279487960987501</v>
+      </c>
+      <c r="F136" s="116"/>
+      <c r="G136" s="127">
+        <f>3.25/3.281</f>
+        <v>0.99055166107893933</v>
+      </c>
+      <c r="H136" s="116">
+        <f t="shared" ref="H136" si="14">PRODUCT(D136:G136)</f>
+        <v>1.2861170607120638</v>
+      </c>
+      <c r="I136" s="119"/>
+      <c r="J136" s="116"/>
+      <c r="K136" s="116"/>
+      <c r="L136" s="25"/>
+    </row>
+    <row r="137" spans="2:20" s="121" customFormat="1">
+      <c r="B137" s="123"/>
+      <c r="C137" s="118"/>
+      <c r="D137" s="119"/>
+      <c r="E137" s="119"/>
+      <c r="F137" s="119"/>
+      <c r="G137" s="119"/>
+      <c r="H137" s="119">
+        <f>SUM(H136)</f>
+        <v>1.2861170607120638</v>
+      </c>
+      <c r="I137" s="119" t="s">
+        <v>40</v>
+      </c>
+      <c r="J137" s="119">
+        <v>1063.57</v>
+      </c>
+      <c r="K137" s="119">
+        <f>H137*J137</f>
+        <v>1367.8755222615296</v>
+      </c>
+      <c r="L137" s="25"/>
+    </row>
+    <row r="138" spans="2:20" s="121" customFormat="1">
+      <c r="B138" s="123"/>
+      <c r="C138" s="118" t="s">
+        <v>158</v>
+      </c>
+      <c r="D138" s="119"/>
+      <c r="E138" s="119"/>
+      <c r="F138" s="119"/>
+      <c r="G138" s="119"/>
+      <c r="H138" s="119"/>
+      <c r="I138" s="119"/>
+      <c r="J138" s="119"/>
+      <c r="K138" s="119">
+        <f>0.13*H137*983.26</f>
+        <v>164.3963699450467</v>
+      </c>
+      <c r="L138" s="25"/>
+    </row>
+    <row r="139" spans="2:20" s="121" customFormat="1">
+      <c r="B139" s="123"/>
+      <c r="C139" s="118"/>
+      <c r="D139" s="119"/>
+      <c r="E139" s="119"/>
+      <c r="F139" s="119"/>
+      <c r="G139" s="119"/>
+      <c r="H139" s="119"/>
+      <c r="I139" s="119"/>
+      <c r="J139" s="119"/>
+      <c r="K139" s="119"/>
+      <c r="L139" s="25"/>
+    </row>
+    <row r="140" spans="2:20" s="121" customFormat="1" ht="167.4">
+      <c r="B140" s="123">
+        <v>19</v>
+      </c>
+      <c r="C140" s="124" t="s">
+        <v>163</v>
+      </c>
+      <c r="D140" s="119"/>
+      <c r="E140" s="119"/>
+      <c r="F140" s="119"/>
+      <c r="G140" s="119"/>
+      <c r="H140" s="119"/>
+      <c r="I140" s="119"/>
+      <c r="J140" s="119"/>
+      <c r="K140" s="119"/>
+      <c r="L140" s="25"/>
+    </row>
+    <row r="141" spans="2:20" s="121" customFormat="1">
+      <c r="B141" s="123"/>
+      <c r="C141" s="136" t="s">
+        <v>162</v>
+      </c>
+      <c r="D141" s="119">
+        <v>1</v>
+      </c>
+      <c r="E141" s="119">
+        <f>3/3.281</f>
+        <v>0.91435537945748246</v>
+      </c>
+      <c r="F141" s="119"/>
+      <c r="G141" s="119"/>
+      <c r="H141" s="116">
+        <f t="shared" ref="H141" si="15">PRODUCT(D141:G141)</f>
+        <v>0.91435537945748246</v>
+      </c>
+      <c r="I141" s="119"/>
+      <c r="J141" s="119"/>
+      <c r="K141" s="119"/>
+      <c r="L141" s="25"/>
+    </row>
+    <row r="142" spans="2:20" s="121" customFormat="1">
+      <c r="B142" s="123"/>
+      <c r="C142" s="118"/>
+      <c r="D142" s="119"/>
+      <c r="E142" s="119"/>
+      <c r="F142" s="119"/>
+      <c r="G142" s="119"/>
+      <c r="H142" s="119">
+        <f>SUM(H141)</f>
+        <v>0.91435537945748246</v>
+      </c>
+      <c r="I142" s="119" t="s">
+        <v>164</v>
+      </c>
+      <c r="J142" s="119">
+        <f>11197.91</f>
+        <v>11197.91</v>
+      </c>
+      <c r="K142" s="119">
+        <f>H142*J142</f>
+        <v>10238.869247180737</v>
+      </c>
+      <c r="L142" s="25"/>
+    </row>
+    <row r="143" spans="2:20" s="121" customFormat="1">
+      <c r="B143" s="123"/>
+      <c r="C143" s="118" t="s">
+        <v>158</v>
+      </c>
+      <c r="D143" s="119"/>
+      <c r="E143" s="119"/>
+      <c r="F143" s="119"/>
+      <c r="G143" s="119"/>
+      <c r="H143" s="119"/>
+      <c r="I143" s="119"/>
+      <c r="J143" s="119"/>
+      <c r="K143" s="119">
+        <f>0.13*K142</f>
+        <v>1331.053002133496</v>
+      </c>
+      <c r="L143" s="25"/>
+    </row>
+    <row r="144" spans="2:20" s="121" customFormat="1">
+      <c r="B144" s="123"/>
+      <c r="C144" s="118"/>
+      <c r="D144" s="119"/>
+      <c r="E144" s="119"/>
+      <c r="F144" s="119"/>
+      <c r="G144" s="119"/>
+      <c r="H144" s="119"/>
+      <c r="I144" s="119"/>
+      <c r="J144" s="119"/>
+      <c r="K144" s="119"/>
+      <c r="L144" s="25"/>
+      <c r="N144" s="1"/>
+      <c r="O144" s="1"/>
+      <c r="P144" s="1"/>
+      <c r="Q144" s="1"/>
+      <c r="R144" s="1"/>
+      <c r="S144" s="1"/>
+      <c r="T144" s="1"/>
+    </row>
+    <row r="145" spans="2:12" s="121" customFormat="1" ht="37.200000000000003">
+      <c r="B145" s="123">
+        <v>20</v>
+      </c>
+      <c r="C145" s="124" t="s">
+        <v>165</v>
+      </c>
+      <c r="D145" s="119"/>
+      <c r="E145" s="119"/>
+      <c r="F145" s="119"/>
+      <c r="G145" s="119"/>
+      <c r="H145" s="119"/>
+      <c r="I145" s="119"/>
+      <c r="J145" s="119"/>
+      <c r="K145" s="119"/>
+      <c r="L145" s="25"/>
+    </row>
+    <row r="146" spans="2:12" s="121" customFormat="1">
+      <c r="B146" s="123"/>
+      <c r="C146" s="136" t="s">
+        <v>150</v>
+      </c>
+      <c r="D146" s="119">
+        <v>1</v>
+      </c>
+      <c r="E146" s="119">
+        <f>(15.42*2+10*2)/3.281</f>
+        <v>15.49527583053947</v>
+      </c>
+      <c r="F146" s="119"/>
+      <c r="G146" s="119">
+        <f>5.25/3.281</f>
+        <v>1.6001219140505942</v>
+      </c>
+      <c r="H146" s="116">
+        <f t="shared" ref="H146:H147" si="16">PRODUCT(D146:G146)</f>
+        <v>24.794330420704728</v>
+      </c>
+      <c r="I146" s="119"/>
+      <c r="J146" s="119"/>
+      <c r="K146" s="119"/>
+      <c r="L146" s="25"/>
+    </row>
+    <row r="147" spans="2:12" s="121" customFormat="1">
+      <c r="B147" s="123"/>
+      <c r="C147" s="118"/>
+      <c r="D147" s="119">
+        <v>1</v>
+      </c>
+      <c r="E147" s="119">
+        <f>13.42/3.281</f>
+        <v>4.0902163974398045</v>
+      </c>
+      <c r="F147" s="119">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="G147" s="119"/>
+      <c r="H147" s="116">
+        <f t="shared" si="16"/>
+        <v>9.9730969763847703</v>
+      </c>
+      <c r="I147" s="119"/>
+      <c r="J147" s="119"/>
+      <c r="K147" s="119"/>
+      <c r="L147" s="25"/>
+    </row>
+    <row r="148" spans="2:12" s="121" customFormat="1">
+      <c r="B148" s="123"/>
+      <c r="C148" s="118"/>
+      <c r="D148" s="119"/>
+      <c r="E148" s="119"/>
+      <c r="F148" s="119"/>
+      <c r="G148" s="119"/>
+      <c r="H148" s="119">
+        <f>SUM(H146:H147)</f>
+        <v>34.767427397089499</v>
+      </c>
+      <c r="I148" s="119" t="s">
+        <v>23</v>
+      </c>
+      <c r="J148" s="119">
+        <f>11197.91</f>
+        <v>11197.91</v>
+      </c>
+      <c r="K148" s="119">
+        <f>H148*J148</f>
+        <v>389322.52292414248</v>
+      </c>
+      <c r="L148" s="25"/>
+    </row>
+    <row r="149" spans="2:12" s="121" customFormat="1">
+      <c r="B149" s="123"/>
+      <c r="C149" s="118" t="s">
+        <v>158</v>
+      </c>
+      <c r="D149" s="119"/>
+      <c r="E149" s="119"/>
+      <c r="F149" s="119"/>
+      <c r="G149" s="119"/>
+      <c r="H149" s="119"/>
+      <c r="I149" s="119"/>
+      <c r="J149" s="119"/>
+      <c r="K149" s="119">
+        <f>0.13*H148*2846.9/10</f>
+        <v>1286.7320577380633</v>
+      </c>
+      <c r="L149" s="25"/>
+    </row>
+    <row r="150" spans="2:12" s="121" customFormat="1">
+      <c r="B150" s="123"/>
+      <c r="C150" s="118"/>
+      <c r="D150" s="119"/>
+      <c r="E150" s="119"/>
+      <c r="F150" s="119"/>
+      <c r="G150" s="119"/>
+      <c r="H150" s="119"/>
+      <c r="I150" s="119"/>
+      <c r="J150" s="119"/>
+      <c r="K150" s="119"/>
+      <c r="L150" s="25"/>
+    </row>
+    <row r="151" spans="2:12" s="121" customFormat="1" ht="33" customHeight="1">
+      <c r="B151" s="81">
+        <v>21</v>
+      </c>
+      <c r="C151" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D151" s="24">
+        <v>1</v>
+      </c>
+      <c r="E151" s="24"/>
+      <c r="F151" s="24"/>
+      <c r="G151" s="24"/>
+      <c r="H151" s="24">
+        <v>1</v>
+      </c>
+      <c r="I151" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="J151" s="73">
+        <v>5000</v>
+      </c>
+      <c r="K151" s="73">
+        <f>H151*J151</f>
+        <v>5000</v>
+      </c>
+      <c r="L151" s="25"/>
+    </row>
+    <row r="152" spans="2:12">
+      <c r="B152" s="81"/>
+      <c r="C152" s="29"/>
+      <c r="D152" s="24"/>
+      <c r="E152" s="24"/>
+      <c r="F152" s="24"/>
+      <c r="G152" s="70"/>
+      <c r="H152" s="24"/>
+      <c r="I152" s="24"/>
+      <c r="J152" s="73"/>
+      <c r="K152" s="73"/>
+      <c r="L152" s="25"/>
+    </row>
+    <row r="153" spans="2:12" ht="33" customHeight="1">
+      <c r="B153" s="81">
+        <v>22</v>
+      </c>
+      <c r="C153" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D153" s="24">
+        <v>1</v>
+      </c>
+      <c r="E153" s="24"/>
+      <c r="F153" s="24"/>
+      <c r="G153" s="24"/>
+      <c r="H153" s="24">
+        <v>1</v>
+      </c>
+      <c r="I153" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="J98" s="73">
-        <v>9938</v>
-      </c>
-      <c r="K98" s="73">
-        <f>H98*J98</f>
-        <v>9938</v>
-      </c>
-      <c r="L98" s="25"/>
-      <c r="N98" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="99" spans="2:14">
-      <c r="B99" s="81"/>
-      <c r="C99" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="D99" s="24"/>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="70"/>
-      <c r="H99" s="24"/>
-      <c r="I99" s="24"/>
-      <c r="J99" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="K99" s="73">
-        <f>0.13*K98</f>
-        <v>1291.94</v>
-      </c>
-      <c r="L99" s="25"/>
-    </row>
-    <row r="100" spans="2:14">
-      <c r="B100" s="81"/>
-      <c r="C100" s="29"/>
-      <c r="D100" s="24"/>
-      <c r="E100" s="24"/>
-      <c r="F100" s="24"/>
-      <c r="G100" s="70"/>
-      <c r="H100" s="24"/>
-      <c r="I100" s="24"/>
-      <c r="J100" s="73"/>
-      <c r="K100" s="73"/>
-      <c r="L100" s="25"/>
-    </row>
-    <row r="101" spans="2:14">
-      <c r="B101" s="81"/>
-      <c r="C101" s="20"/>
-      <c r="D101" s="20"/>
-      <c r="E101" s="20"/>
-      <c r="F101" s="20"/>
-      <c r="G101" s="20"/>
-      <c r="H101" s="20"/>
-      <c r="I101" s="20"/>
-      <c r="J101" s="20"/>
-      <c r="K101" s="20"/>
-      <c r="L101" s="25"/>
-    </row>
-    <row r="102" spans="2:14" ht="18">
-      <c r="B102" s="81" t="s">
-        <v>97</v>
-      </c>
-      <c r="C102" s="82" t="s">
-        <v>96</v>
-      </c>
-      <c r="D102" s="24"/>
-      <c r="E102" s="24"/>
-      <c r="F102" s="24"/>
-      <c r="G102" s="70"/>
-      <c r="H102" s="24"/>
-      <c r="I102" s="24"/>
-      <c r="J102" s="73"/>
-      <c r="K102" s="73"/>
-      <c r="L102" s="25"/>
-    </row>
-    <row r="103" spans="2:14">
-      <c r="B103" s="81"/>
-      <c r="C103" s="29"/>
-      <c r="D103" s="24"/>
-      <c r="E103" s="24"/>
-      <c r="F103" s="24"/>
-      <c r="G103" s="70"/>
-      <c r="H103" s="24"/>
-      <c r="I103" s="24"/>
-      <c r="J103" s="73"/>
-      <c r="K103" s="73"/>
-      <c r="L103" s="25"/>
-    </row>
-    <row r="104" spans="2:14" ht="36">
-      <c r="B104" s="80">
-        <v>11</v>
-      </c>
-      <c r="C104" s="89" t="s">
-        <v>98</v>
-      </c>
-      <c r="D104" s="70">
+      <c r="J153" s="73">
+        <v>500</v>
+      </c>
+      <c r="K153" s="73">
+        <f>H153*J153</f>
+        <v>500</v>
+      </c>
+      <c r="L153" s="25"/>
+    </row>
+    <row r="154" spans="2:12" ht="17.399999999999999" thickBot="1">
+      <c r="B154" s="22"/>
+      <c r="C154" s="26"/>
+      <c r="D154" s="76"/>
+      <c r="E154" s="77"/>
+      <c r="F154" s="77"/>
+      <c r="G154" s="77"/>
+      <c r="H154" s="77"/>
+      <c r="I154" s="76"/>
+      <c r="J154" s="77"/>
+      <c r="K154" s="78">
+        <f>SUM(K12:K153)</f>
+        <v>877810.68270516139</v>
+      </c>
+      <c r="L154" s="23"/>
+    </row>
+    <row r="155" spans="2:12">
+      <c r="C155" s="9"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="10"/>
+      <c r="F155" s="10"/>
+      <c r="G155" s="10"/>
+      <c r="H155" s="10"/>
+      <c r="I155" s="10"/>
+      <c r="J155" s="10"/>
+      <c r="K155" s="11"/>
+      <c r="L155" s="8"/>
+    </row>
+    <row r="156" spans="2:12">
+      <c r="C156" s="5"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="H156" s="2"/>
+      <c r="I156" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="J156" s="65"/>
+      <c r="K156" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="L156" s="65" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="157" spans="2:12">
+      <c r="C157" s="5"/>
+      <c r="H157" s="64"/>
+      <c r="I157" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="J157" s="67"/>
+      <c r="K157" s="67">
+        <f>+K154</f>
+        <v>877810.68270516139</v>
+      </c>
+      <c r="L157" s="67"/>
+    </row>
+    <row r="158" spans="2:12">
+      <c r="C158" s="5"/>
+      <c r="H158" s="64"/>
+      <c r="I158" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="J158" s="68"/>
+      <c r="K158" s="67">
+        <v>200000</v>
+      </c>
+      <c r="L158" s="68">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" spans="2:12">
+      <c r="C159" s="5"/>
+      <c r="H159" s="64"/>
+      <c r="I159" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="J159" s="68"/>
+      <c r="K159" s="67">
+        <f>0.95*K158</f>
+        <v>190000</v>
+      </c>
+      <c r="L159" s="68">
+        <f>K159/K157*100</f>
+        <v>21.644758231293604</v>
+      </c>
+    </row>
+    <row r="160" spans="2:12">
+      <c r="C160" s="5"/>
+      <c r="H160" s="64"/>
+      <c r="I160" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="J160" s="68"/>
+      <c r="K160" s="67">
+        <f>K157-K159</f>
+        <v>687810.68270516139</v>
+      </c>
+      <c r="L160" s="68">
+        <f>K160/K158*100</f>
+        <v>343.90534135258071</v>
+      </c>
+    </row>
+    <row r="161" spans="3:12">
+      <c r="C161" s="5"/>
+      <c r="H161" s="64"/>
+      <c r="I161" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="J161" s="68"/>
+      <c r="K161" s="67">
+        <f>L161*K158/100</f>
+        <v>4000</v>
+      </c>
+      <c r="L161" s="68">
         <v>2</v>
       </c>
-      <c r="E104" s="70">
-        <f>25/3.28</f>
-        <v>7.6219512195121952</v>
-      </c>
-      <c r="F104" s="70">
-        <f>17/3.28</f>
-        <v>5.1829268292682933</v>
-      </c>
-      <c r="G104" s="70"/>
-      <c r="H104" s="70">
-        <f>F104*E104*D104</f>
-        <v>79.008030933967888</v>
-      </c>
-      <c r="I104" s="70" t="s">
-        <v>90</v>
-      </c>
-      <c r="J104" s="70">
-        <f>'[2]Table of Content 2'!$H$329</f>
-        <v>68.400000000000006</v>
-      </c>
-      <c r="K104" s="70">
-        <f>H104*J104</f>
-        <v>5404.1493158834037</v>
-      </c>
-      <c r="L104" s="25"/>
-    </row>
-    <row r="105" spans="2:14">
-      <c r="B105" s="81"/>
-      <c r="C105" s="29"/>
-      <c r="D105" s="24"/>
-      <c r="E105" s="24"/>
-      <c r="F105" s="24"/>
-      <c r="G105" s="70"/>
-      <c r="H105" s="24"/>
-      <c r="I105" s="24"/>
-      <c r="J105" s="73"/>
-      <c r="K105" s="73"/>
-      <c r="L105" s="25"/>
-    </row>
-    <row r="106" spans="2:14" ht="36">
-      <c r="B106" s="81">
-        <v>12</v>
-      </c>
-      <c r="C106" s="89" t="s">
-        <v>99</v>
-      </c>
-      <c r="D106" s="24">
-        <v>2</v>
-      </c>
-      <c r="E106" s="24">
-        <f>E104</f>
-        <v>7.6219512195121952</v>
-      </c>
-      <c r="F106" s="24">
-        <f>F104</f>
-        <v>5.1829268292682933</v>
-      </c>
-      <c r="G106" s="70"/>
-      <c r="H106" s="70">
-        <f>F106*E106*D106</f>
-        <v>79.008030933967888</v>
-      </c>
-      <c r="I106" s="70" t="s">
-        <v>90</v>
-      </c>
-      <c r="J106" s="73">
-        <v>369.1</v>
-      </c>
-      <c r="K106" s="73">
-        <f>H106*J106</f>
-        <v>29161.864217727551</v>
-      </c>
-      <c r="L106" s="25"/>
-    </row>
-    <row r="107" spans="2:14">
-      <c r="B107" s="81"/>
-      <c r="C107" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D107" s="24"/>
-      <c r="E107" s="24"/>
-      <c r="F107" s="24"/>
-      <c r="G107" s="70"/>
-      <c r="H107" s="70"/>
-      <c r="I107" s="70"/>
-      <c r="J107" s="73"/>
-      <c r="K107" s="73">
-        <f>124.6*H106*0.13</f>
-        <v>1279.772085068412</v>
-      </c>
-      <c r="L107" s="25"/>
-    </row>
-    <row r="108" spans="2:14" ht="72">
-      <c r="B108" s="81">
-        <v>13</v>
-      </c>
-      <c r="C108" s="89" t="s">
-        <v>92</v>
-      </c>
-      <c r="D108" s="24">
-        <v>1</v>
-      </c>
-      <c r="E108" s="24">
-        <f>E106</f>
-        <v>7.6219512195121952</v>
-      </c>
-      <c r="F108" s="24"/>
-      <c r="G108" s="70"/>
-      <c r="H108" s="24">
-        <f>E108</f>
-        <v>7.6219512195121952</v>
-      </c>
-      <c r="I108" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="J108" s="73">
-        <f>'[1]Table of Content 2'!$H$412</f>
-        <v>2761</v>
-      </c>
-      <c r="K108" s="73">
-        <f>H108*J108</f>
-        <v>21044.207317073171</v>
-      </c>
-      <c r="L108" s="25"/>
-    </row>
-    <row r="109" spans="2:14">
-      <c r="B109" s="81"/>
-      <c r="C109" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D109" s="24"/>
-      <c r="E109" s="24"/>
-      <c r="F109" s="24"/>
-      <c r="G109" s="70"/>
-      <c r="H109" s="24"/>
-      <c r="I109" s="24"/>
-      <c r="J109" s="73"/>
-      <c r="K109" s="73">
-        <f>2491*H108*0.13</f>
-        <v>2468.2164634146343</v>
-      </c>
-      <c r="L109" s="25"/>
-      <c r="N109" s="1">
-        <f>17/3.28</f>
-        <v>5.1829268292682933</v>
-      </c>
-    </row>
-    <row r="110" spans="2:14">
-      <c r="B110" s="81"/>
-      <c r="C110" s="29"/>
-      <c r="D110" s="24"/>
-      <c r="E110" s="24"/>
-      <c r="F110" s="24"/>
-      <c r="G110" s="70"/>
-      <c r="H110" s="24"/>
-      <c r="I110" s="24"/>
-      <c r="J110" s="73"/>
-      <c r="K110" s="73"/>
-      <c r="L110" s="25"/>
-      <c r="N110" s="1" t="e">
-        <f>#REF!*N109*2*68.4</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="111" spans="2:14" ht="33" customHeight="1">
-      <c r="B111" s="81">
-        <v>14</v>
-      </c>
-      <c r="C111" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D111" s="24">
-        <v>1</v>
-      </c>
-      <c r="E111" s="24"/>
-      <c r="F111" s="24"/>
-      <c r="G111" s="24"/>
-      <c r="H111" s="24">
-        <v>1</v>
-      </c>
-      <c r="I111" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="J111" s="73">
-        <v>1000</v>
-      </c>
-      <c r="K111" s="73">
-        <f>H111*J111</f>
-        <v>1000</v>
-      </c>
-      <c r="L111" s="25"/>
-    </row>
-    <row r="112" spans="2:14" ht="17.25" thickBot="1">
-      <c r="B112" s="22"/>
-      <c r="C112" s="26"/>
-      <c r="D112" s="76"/>
-      <c r="E112" s="77"/>
-      <c r="F112" s="77"/>
-      <c r="G112" s="77"/>
-      <c r="H112" s="77"/>
-      <c r="I112" s="76"/>
-      <c r="J112" s="77"/>
-      <c r="K112" s="78">
-        <f>SUM(K8:K111)</f>
-        <v>461715.70282650145</v>
-      </c>
-      <c r="L112" s="23"/>
-    </row>
-    <row r="113" spans="3:12">
-      <c r="C113" s="9"/>
-      <c r="D113" s="10"/>
-      <c r="E113" s="10"/>
-      <c r="F113" s="10"/>
-      <c r="G113" s="10"/>
-      <c r="H113" s="10"/>
-      <c r="I113" s="10"/>
-      <c r="J113" s="10"/>
-      <c r="K113" s="11"/>
-      <c r="L113" s="8"/>
-    </row>
-    <row r="114" spans="3:12">
-      <c r="C114" s="5"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="J114" s="65"/>
-      <c r="K114" s="65" t="s">
-        <v>71</v>
-      </c>
-      <c r="L114" s="65" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="115" spans="3:12">
-      <c r="C115" s="5"/>
-      <c r="H115" s="64"/>
-      <c r="I115" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="J115" s="67"/>
-      <c r="K115" s="67">
-        <f>+K112</f>
-        <v>461715.70282650145</v>
-      </c>
-      <c r="L115" s="67"/>
-    </row>
-    <row r="116" spans="3:12">
-      <c r="C116" s="5"/>
-      <c r="H116" s="64"/>
-      <c r="I116" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="J116" s="68"/>
-      <c r="K116" s="67">
-        <v>200000</v>
-      </c>
-      <c r="L116" s="68">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="117" spans="3:12">
-      <c r="C117" s="5"/>
-      <c r="H117" s="64"/>
-      <c r="I117" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="J117" s="68"/>
-      <c r="K117" s="67">
-        <f>0.95*K116</f>
-        <v>190000</v>
-      </c>
-      <c r="L117" s="68">
-        <f>K117/K115*100</f>
-        <v>41.150863797109402</v>
-      </c>
-    </row>
-    <row r="118" spans="3:12">
-      <c r="C118" s="5"/>
-      <c r="H118" s="64"/>
-      <c r="I118" s="66" t="s">
-        <v>15</v>
-      </c>
-      <c r="J118" s="68"/>
-      <c r="K118" s="67">
-        <f>K115-K117</f>
-        <v>271715.70282650145</v>
-      </c>
-      <c r="L118" s="68">
-        <f>K118/K116*100</f>
-        <v>135.85785141325073</v>
-      </c>
-    </row>
-    <row r="119" spans="3:12">
-      <c r="C119" s="5"/>
-      <c r="H119" s="64"/>
-      <c r="I119" s="66" t="s">
-        <v>20</v>
-      </c>
-      <c r="J119" s="68"/>
-      <c r="K119" s="67">
-        <f>L119*K116/100</f>
-        <v>4000</v>
-      </c>
-      <c r="L119" s="68">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" spans="3:12">
-      <c r="C120" s="5"/>
-      <c r="H120" s="63"/>
-      <c r="I120" s="66" t="s">
+    </row>
+    <row r="162" spans="3:12">
+      <c r="C162" s="5"/>
+      <c r="H162" s="63"/>
+      <c r="I162" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="J120" s="68"/>
-      <c r="K120" s="68">
-        <f>L120*K116/100</f>
+      <c r="J162" s="68"/>
+      <c r="K162" s="68">
+        <f>L162*K158/100</f>
         <v>6000</v>
       </c>
-      <c r="L120" s="68">
+      <c r="L162" s="68">
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="3:12">
-      <c r="G121" s="62"/>
+    <row r="163" spans="3:12">
+      <c r="G163" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -9815,55 +10819,55 @@
     <oddHeader>&amp;RPage &amp;P of &amp;N</oddHeader>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="74" max="11" man="1"/>
     <brk id="112" max="11" man="1"/>
+    <brk id="154" max="11" man="1"/>
   </rowBreaks>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="3" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <col min="2" max="3" width="13.88671875" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5">
+    <row r="1" spans="1:8" ht="21">
       <c r="A1" s="91">
         <v>152</v>
       </c>
-      <c r="B1" s="138" t="s">
+      <c r="B1" s="160" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75">
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="162" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-    </row>
-    <row r="3" spans="1:8" ht="31.5">
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+    </row>
+    <row r="3" spans="1:8" ht="32.4">
       <c r="A3" s="93"/>
       <c r="B3" s="94" t="s">
         <v>112</v>
@@ -9887,9 +10891,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16.5">
+    <row r="4" spans="1:8" ht="16.8">
       <c r="A4" s="93"/>
-      <c r="B4" s="142" t="s">
+      <c r="B4" s="164" t="s">
         <v>119</v>
       </c>
       <c r="C4" s="95" t="s">
@@ -9910,9 +10914,9 @@
       </c>
       <c r="H4" s="99"/>
     </row>
-    <row r="5" spans="1:8" ht="16.5">
+    <row r="5" spans="1:8" ht="18">
       <c r="A5" s="93"/>
-      <c r="B5" s="143"/>
+      <c r="B5" s="165"/>
       <c r="C5" s="100" t="s">
         <v>122</v>
       </c>
@@ -9934,9 +10938,9 @@
         <v>1557.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5">
+    <row r="6" spans="1:8" ht="18">
       <c r="A6" s="93"/>
-      <c r="B6" s="144" t="s">
+      <c r="B6" s="166" t="s">
         <v>123</v>
       </c>
       <c r="C6" s="97" t="s">
@@ -9958,9 +10962,9 @@
       </c>
       <c r="H6" s="99"/>
     </row>
-    <row r="7" spans="1:8" ht="16.5">
+    <row r="7" spans="1:8" ht="18">
       <c r="A7" s="93"/>
-      <c r="B7" s="145"/>
+      <c r="B7" s="167"/>
       <c r="C7" s="100" t="s">
         <v>126</v>
       </c>
@@ -9983,7 +10987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16.5">
+    <row r="8" spans="1:8" ht="20.399999999999999">
       <c r="A8" s="93"/>
       <c r="B8" s="93"/>
       <c r="C8" s="93"/>
@@ -9998,7 +11002,7 @@
         <v>1557.5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.5">
+    <row r="9" spans="1:8" ht="20.399999999999999">
       <c r="A9" s="93"/>
       <c r="B9" s="93" t="s">
         <v>129</v>
@@ -10015,7 +11019,7 @@
         <v>233.62</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="16.5">
+    <row r="10" spans="1:8" ht="20.399999999999999">
       <c r="A10" s="110"/>
       <c r="B10" s="111">
         <f>+H10</f>
@@ -10040,7 +11044,7 @@
         <v>1791.12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75">
+    <row r="11" spans="1:8" ht="16.8">
       <c r="A11" s="93"/>
       <c r="B11" s="113">
         <v>10</v>

--- a/बजेट माग estimate/Swasthya chauki/water tank 2082_2083.xlsx
+++ b/बजेट माग estimate/Swasthya chauki/water tank 2082_2083.xlsx
@@ -23,7 +23,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">ESTIMATE!$A$1:$L$71</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">me!$A$1:$L$154</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">me!$A$1:$L$162</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">ESTIMATE!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">me!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">WCR!$1:$11</definedName>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="171">
   <si>
     <t>S.N.</t>
   </si>
@@ -474,12 +474,6 @@
     <t>Date: 2081/02/21</t>
   </si>
   <si>
-    <t>gfªn]ef/] :jf:yo rf}sL kfgL 6\ofÍL dd{t tyf cGo lalaw dd{t</t>
-  </si>
-  <si>
-    <t>Date: 2082/08/17</t>
-  </si>
-  <si>
     <t>F.Y.:-2082/083</t>
   </si>
   <si>
@@ -490,9 +484,6 @@
   </si>
   <si>
     <t>;'Vvf O{6f RofK6f] 5fKg] sfd</t>
-  </si>
-  <si>
-    <t>g/d k|sf/sf] Sn] / l;N6L df6f]df ;j} lsl;dsf] vGg] sfd ===============================================================================</t>
   </si>
   <si>
     <t xml:space="preserve">;fx|f] k|sf/sf] Sn], g/d d'/d 9'+uf -#) ;]=dL=;Dd_ ld;]sf] df6f]df ;j} lsl;dsf] vGg] sfd </t>
@@ -717,6 +708,31 @@
   </si>
   <si>
     <t xml:space="preserve">b'O{ sf]6 Knfli6s O{dNzg k]G6 nufpg] sfd -k|fOd/ ;lxt_ </t>
+  </si>
+  <si>
+    <t>Date: 2082/08/19</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Project:-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>gfªn]ef/] :jf:yo rf}sL kfgL 6\ofÍL dd{t tyf cGo lalaw dd{t</t>
+    </r>
+  </si>
+  <si>
+    <t>Remark</t>
   </si>
 </sst>
 </file>
@@ -746,7 +762,7 @@
     <numFmt numFmtId="182" formatCode="_ &quot;\&quot;* #,##0.00_ ;_ &quot;\&quot;* \-#,##0.00_ ;_ &quot;\&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="183" formatCode="0.0"/>
   </numFmts>
-  <fonts count="87">
+  <fonts count="88">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1251,8 +1267,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1421,14 +1443,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="42">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1940,45 +1956,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="759">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2798,7 +2775,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3007,7 +2984,6 @@
     <xf numFmtId="0" fontId="70" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="78" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3069,85 +3045,6 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="51" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="183" fontId="51" fillId="33" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="51" fillId="33" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="52" fillId="33" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="183" fontId="52" fillId="33" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="52" fillId="33" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="33" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="justify"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="33" borderId="23" xfId="734" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="51" fillId="33" borderId="23" xfId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3164,6 +3061,21 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3182,21 +3094,6 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3221,11 +3118,159 @@
     <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="51" fillId="33" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="51" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="52" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="183" fontId="52" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="52" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="51" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="justify"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="19" xfId="734" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="0" borderId="19" xfId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="49" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="759">
@@ -4604,68 +4649,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
     </row>
     <row r="2" spans="1:18" ht="20.399999999999999">
-      <c r="A2" s="146" t="s">
+      <c r="A2" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="145" t="s">
+      <c r="A3" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="145"/>
-      <c r="C3" s="145"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="145"/>
-      <c r="H3" s="145"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="145"/>
-      <c r="K3" s="145"/>
-      <c r="L3" s="145"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="147" t="s">
+      <c r="A4" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="147"/>
-      <c r="L4" s="147"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
     </row>
     <row r="5" spans="1:18" ht="19.8">
       <c r="A5" s="6"/>
@@ -4676,33 +4721,33 @@
         <v>93</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="148" t="s">
+      <c r="K5" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="148"/>
+      <c r="L5" s="118"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="B6" s="144" t="s">
+      <c r="B6" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="144"/>
-      <c r="D6" s="144"/>
-      <c r="E6" s="144"/>
-      <c r="F6" s="144"/>
-      <c r="G6" s="144"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="114"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="143" t="s">
+      <c r="I6" s="113" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="143"/>
-      <c r="K6" s="143"/>
-      <c r="L6" s="143"/>
-      <c r="O6" s="143" t="s">
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="113"/>
+      <c r="O6" s="113" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="143"/>
-      <c r="Q6" s="143"/>
-      <c r="R6" s="143"/>
+      <c r="P6" s="113"/>
+      <c r="Q6" s="113"/>
+      <c r="R6" s="113"/>
     </row>
     <row r="7" spans="1:18" ht="17.399999999999999" thickBot="1">
       <c r="C7" s="5"/>
@@ -6272,60 +6317,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
     </row>
     <row r="2" spans="1:10" ht="24.6">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="125" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="150"/>
-      <c r="H2" s="150"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="150"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
     </row>
     <row r="3" spans="1:10" ht="18">
-      <c r="A3" s="151" t="s">
+      <c r="A3" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="151"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="151"/>
-      <c r="F3" s="151"/>
-      <c r="G3" s="151"/>
-      <c r="H3" s="151"/>
-      <c r="I3" s="151"/>
-      <c r="J3" s="151"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="152"/>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="152"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="127"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="37"/>
@@ -6344,33 +6389,33 @@
         <v>55</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="153" t="e">
+      <c r="C6" s="128" t="e">
         <f>E51</f>
         <v>#REF!</v>
       </c>
-      <c r="D6" s="154"/>
+      <c r="D6" s="129"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
         <v>56</v>
       </c>
       <c r="H6" s="31"/>
-      <c r="I6" s="153" t="e">
+      <c r="I6" s="128" t="e">
         <f>H51</f>
         <v>#REF!</v>
       </c>
-      <c r="J6" s="154"/>
+      <c r="J6" s="129"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="32"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="156"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="119"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="120"/>
     </row>
     <row r="8" spans="1:10" ht="16.8">
       <c r="A8" t="s">
@@ -6397,32 +6442,32 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="157" t="s">
+      <c r="A10" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="157" t="s">
+      <c r="B10" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="159" t="s">
+      <c r="C10" s="123" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="159"/>
-      <c r="E10" s="159"/>
-      <c r="F10" s="159" t="s">
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="159"/>
-      <c r="H10" s="159"/>
-      <c r="I10" s="157" t="s">
+      <c r="G10" s="123"/>
+      <c r="H10" s="123"/>
+      <c r="I10" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="157" t="s">
+      <c r="J10" s="121" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="158"/>
-      <c r="B11" s="158"/>
+      <c r="A11" s="122"/>
+      <c r="B11" s="122"/>
       <c r="C11" s="39" t="s">
         <v>64</v>
       </c>
@@ -6441,8 +6486,8 @@
       <c r="H11" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="158"/>
-      <c r="J11" s="158"/>
+      <c r="I11" s="122"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="15.6">
       <c r="A12" s="47">
@@ -7369,6 +7414,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:J7"/>
@@ -7378,12 +7429,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="J10:J11"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -7401,3409 +7446,3376 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:T163"/>
+  <dimension ref="A1:L163"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" style="1"/>
-    <col min="14" max="14" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="1"/>
-    <col min="16" max="16" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="3.6640625" style="139" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" style="143" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" style="152" customWidth="1"/>
+    <col min="4" max="4" width="7.109375" style="139" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="139" customWidth="1"/>
+    <col min="6" max="6" width="10" style="139" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="139" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" style="139" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" style="139" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" style="145" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" style="139" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" style="139" customWidth="1"/>
+    <col min="13" max="16384" width="9.109375" style="139"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="145" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="138" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-    </row>
-    <row r="2" spans="1:18" ht="20.399999999999999">
-      <c r="A2" s="146" t="s">
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="138"/>
+    </row>
+    <row r="2" spans="1:12" ht="20.399999999999999">
+      <c r="A2" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="145" t="s">
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="145"/>
-      <c r="C3" s="145"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="145"/>
-      <c r="H3" s="145"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="145"/>
-      <c r="K3" s="145"/>
-      <c r="L3" s="145"/>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="147" t="s">
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="147"/>
-      <c r="L4" s="147"/>
-    </row>
-    <row r="5" spans="1:18" ht="19.8">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="28" t="s">
+      <c r="B4" s="141"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="141"/>
+      <c r="J4" s="141"/>
+      <c r="K4" s="141"/>
+      <c r="L4" s="141"/>
+    </row>
+    <row r="5" spans="1:12" ht="20.399999999999999">
+      <c r="A5" s="142"/>
+      <c r="B5" s="144" t="s">
+        <v>169</v>
+      </c>
+      <c r="H5" s="142"/>
+      <c r="K5" s="146" t="s">
         <v>101</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="K5" s="148" t="s">
+      <c r="L5" s="146"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6" s="147" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="147"/>
+      <c r="D6" s="147"/>
+      <c r="E6" s="147"/>
+      <c r="F6" s="147"/>
+      <c r="G6" s="147"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="149" t="s">
+        <v>168</v>
+      </c>
+      <c r="J6" s="149"/>
+      <c r="K6" s="149"/>
+      <c r="L6" s="149"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="C7" s="150"/>
+      <c r="D7" s="142"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="148"/>
+      <c r="J7" s="151"/>
+      <c r="K7" s="148"/>
+      <c r="L7" s="152"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="145"/>
+      <c r="B8" s="162" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="163" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="165" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="165" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="165" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="199" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="166" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="165" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="165" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="167" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="18">
+      <c r="A9" s="145"/>
+      <c r="B9" s="162" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="168" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="164"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="165"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="166"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
+      <c r="L9" s="167"/>
+    </row>
+    <row r="10" spans="1:12" ht="35.1" customHeight="1">
+      <c r="B10" s="169">
+        <v>1</v>
+      </c>
+      <c r="C10" s="170" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="148"/>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="B6" s="144" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="144"/>
-      <c r="D6" s="144"/>
-      <c r="E6" s="144"/>
-      <c r="F6" s="144"/>
-      <c r="G6" s="144"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="143" t="s">
-        <v>102</v>
-      </c>
-      <c r="J6" s="143"/>
-      <c r="K6" s="143"/>
-      <c r="L6" s="143"/>
-      <c r="O6" s="143" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" s="143"/>
-      <c r="Q6" s="143"/>
-      <c r="R6" s="143"/>
-    </row>
-    <row r="7" spans="1:18" ht="17.399999999999999" thickBot="1">
-      <c r="C7" s="5"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="1:18" ht="17.399999999999999" thickBot="1">
-      <c r="A8" s="2"/>
-      <c r="B8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="D10" s="171">
         <v>1</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="14" t="s">
+      <c r="E10" s="172">
         <v>5</v>
       </c>
-      <c r="H8" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="18">
-      <c r="A9" s="2"/>
-      <c r="B9" s="83" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="84" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="85"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="88"/>
-    </row>
-    <row r="10" spans="1:18" ht="35.1" customHeight="1">
-      <c r="B10" s="123">
-        <v>1</v>
-      </c>
-      <c r="C10" s="124" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" s="119">
-        <v>1</v>
-      </c>
-      <c r="E10" s="116">
-        <v>5</v>
-      </c>
-      <c r="F10" s="116">
+      <c r="F10" s="172">
         <f>11/3.281</f>
         <v>3.3526363913441024</v>
       </c>
-      <c r="G10" s="116">
+      <c r="G10" s="172">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="H10" s="116">
+      <c r="H10" s="172">
         <f>D10*E10*F10*G10</f>
         <v>1.2572386467540384</v>
       </c>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="25"/>
-    </row>
-    <row r="11" spans="1:18" s="121" customFormat="1">
-      <c r="B11" s="123"/>
-      <c r="C11" s="138" t="s">
-        <v>157</v>
-      </c>
-      <c r="D11" s="119">
+      <c r="I10" s="171"/>
+      <c r="J10" s="171"/>
+      <c r="K10" s="171"/>
+      <c r="L10" s="173"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11" s="169"/>
+      <c r="C11" s="174" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="171">
         <v>1</v>
       </c>
-      <c r="E11" s="116">
+      <c r="E11" s="172">
         <f>5.17/3.281</f>
         <v>1.5757391039317281</v>
       </c>
-      <c r="F11" s="116">
+      <c r="F11" s="172">
         <f>2/3.281</f>
         <v>0.6095702529716549</v>
       </c>
-      <c r="G11" s="116">
+      <c r="G11" s="172">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="H11" s="116">
+      <c r="H11" s="172">
         <f t="shared" ref="H11" si="0">D11*E11*F11*G11</f>
         <v>7.2039276315074424E-2</v>
       </c>
-      <c r="I11" s="119"/>
-      <c r="J11" s="119"/>
-      <c r="K11" s="119"/>
-      <c r="L11" s="25"/>
-    </row>
-    <row r="12" spans="1:18" s="121" customFormat="1">
-      <c r="B12" s="123"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="116"/>
-      <c r="G12" s="116"/>
-      <c r="H12" s="116">
+      <c r="I11" s="171"/>
+      <c r="J11" s="171"/>
+      <c r="K11" s="171"/>
+      <c r="L11" s="173"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12" s="169"/>
+      <c r="C12" s="174"/>
+      <c r="D12" s="171"/>
+      <c r="E12" s="172"/>
+      <c r="F12" s="172"/>
+      <c r="G12" s="172"/>
+      <c r="H12" s="172">
         <f>SUM(H10:H11)</f>
         <v>1.3292779230691127</v>
       </c>
-      <c r="I12" s="119" t="s">
+      <c r="I12" s="171" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="119">
+      <c r="J12" s="171">
         <v>3740</v>
       </c>
-      <c r="K12" s="119">
+      <c r="K12" s="171">
         <f>H12*J12</f>
         <v>4971.4994322784814</v>
       </c>
-      <c r="L12" s="25"/>
-    </row>
-    <row r="13" spans="1:18" ht="18.600000000000001">
-      <c r="B13" s="80"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="70"/>
-      <c r="L13" s="25"/>
-    </row>
-    <row r="14" spans="1:18" ht="55.8">
-      <c r="B14" s="123">
+      <c r="L12" s="173"/>
+    </row>
+    <row r="13" spans="1:12" ht="18.600000000000001">
+      <c r="B13" s="169"/>
+      <c r="C13" s="170"/>
+      <c r="D13" s="171"/>
+      <c r="E13" s="172"/>
+      <c r="F13" s="172"/>
+      <c r="G13" s="172"/>
+      <c r="H13" s="172"/>
+      <c r="I13" s="171"/>
+      <c r="J13" s="172"/>
+      <c r="K13" s="172"/>
+      <c r="L13" s="173"/>
+    </row>
+    <row r="14" spans="1:12" ht="55.8">
+      <c r="B14" s="169">
         <v>2</v>
       </c>
-      <c r="C14" s="124" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" s="119">
+      <c r="C14" s="170" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="171">
         <v>2</v>
       </c>
-      <c r="E14" s="116">
+      <c r="E14" s="172">
         <f>E10</f>
         <v>5</v>
       </c>
-      <c r="F14" s="116">
+      <c r="F14" s="172">
         <v>0.23</v>
       </c>
-      <c r="G14" s="116">
+      <c r="G14" s="172">
         <v>1.4</v>
       </c>
-      <c r="H14" s="116">
+      <c r="H14" s="172">
         <f>D14*E14*G14</f>
         <v>14</v>
       </c>
-      <c r="I14" s="116"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="116"/>
-      <c r="L14" s="25"/>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="B15" s="123"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="119">
+      <c r="I14" s="172"/>
+      <c r="J14" s="172"/>
+      <c r="K14" s="172"/>
+      <c r="L14" s="173"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15" s="169"/>
+      <c r="C15" s="175"/>
+      <c r="D15" s="171">
         <v>2</v>
       </c>
-      <c r="E15" s="116">
+      <c r="E15" s="172">
         <f>F10-0.23*2</f>
         <v>2.8926363913441024</v>
       </c>
-      <c r="F15" s="116">
+      <c r="F15" s="172">
         <v>0.23</v>
       </c>
-      <c r="G15" s="116">
+      <c r="G15" s="172">
         <v>1.4</v>
       </c>
-      <c r="H15" s="116">
+      <c r="H15" s="172">
         <f>D15*E15*G15</f>
         <v>8.0993818957634858</v>
       </c>
-      <c r="I15" s="116"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="116"/>
-      <c r="L15" s="25"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="B16" s="123"/>
-      <c r="C16" s="137"/>
-      <c r="D16" s="119">
+      <c r="I15" s="172"/>
+      <c r="J15" s="172"/>
+      <c r="K15" s="172"/>
+      <c r="L15" s="173"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="B16" s="169"/>
+      <c r="C16" s="175"/>
+      <c r="D16" s="171">
         <v>1</v>
       </c>
-      <c r="E16" s="116">
+      <c r="E16" s="172">
         <f>E10</f>
         <v>5</v>
       </c>
-      <c r="F16" s="116">
+      <c r="F16" s="172">
         <v>0.23</v>
       </c>
-      <c r="G16" s="116">
+      <c r="G16" s="172">
         <v>0.45</v>
       </c>
-      <c r="H16" s="116">
+      <c r="H16" s="172">
         <f>D16*E16*G16</f>
         <v>2.25</v>
       </c>
-      <c r="I16" s="116"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="116"/>
-      <c r="L16" s="25"/>
-    </row>
-    <row r="17" spans="2:14" s="121" customFormat="1">
-      <c r="B17" s="123"/>
-      <c r="C17" s="138" t="s">
-        <v>161</v>
-      </c>
-      <c r="D17" s="119">
+      <c r="I16" s="172"/>
+      <c r="J16" s="172"/>
+      <c r="K16" s="172"/>
+      <c r="L16" s="173"/>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" s="169"/>
+      <c r="C17" s="174" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="171">
         <v>1</v>
       </c>
-      <c r="E17" s="116">
+      <c r="E17" s="172">
         <f>3.75/3.281</f>
         <v>1.1429442243218531</v>
       </c>
-      <c r="F17" s="116">
+      <c r="F17" s="172">
         <v>0.23</v>
       </c>
-      <c r="G17" s="116">
+      <c r="G17" s="172">
         <f>2/3.281</f>
         <v>0.6095702529716549</v>
       </c>
-      <c r="H17" s="116">
+      <c r="H17" s="172">
         <f>D17*E17*G17</f>
         <v>0.6967047999523639</v>
       </c>
-      <c r="I17" s="116"/>
-      <c r="J17" s="116"/>
-      <c r="K17" s="116"/>
-      <c r="L17" s="25"/>
-    </row>
-    <row r="18" spans="2:14" s="121" customFormat="1">
-      <c r="B18" s="123"/>
-      <c r="C18" s="138" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="119">
+      <c r="I17" s="172"/>
+      <c r="J17" s="172"/>
+      <c r="K17" s="172"/>
+      <c r="L17" s="173"/>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="B18" s="169"/>
+      <c r="C18" s="174" t="s">
+        <v>154</v>
+      </c>
+      <c r="D18" s="171">
         <v>1</v>
       </c>
-      <c r="E18" s="116">
+      <c r="E18" s="172">
         <f>2/3.281</f>
         <v>0.6095702529716549</v>
       </c>
-      <c r="F18" s="116">
+      <c r="F18" s="172">
         <v>0.1</v>
       </c>
-      <c r="G18" s="116">
+      <c r="G18" s="172">
         <f>25/12/3.281</f>
         <v>0.63496901351214063</v>
       </c>
-      <c r="H18" s="116">
+      <c r="H18" s="172">
         <f t="shared" ref="H18" si="1">D18*E18*F18*G18</f>
         <v>3.8705822219575775E-2</v>
       </c>
-      <c r="I18" s="119"/>
-      <c r="J18" s="119"/>
-      <c r="K18" s="119"/>
-      <c r="L18" s="25"/>
-    </row>
-    <row r="19" spans="2:14">
-      <c r="B19" s="123"/>
-      <c r="C19" s="138" t="s">
-        <v>148</v>
-      </c>
-      <c r="D19" s="119">
+      <c r="I18" s="171"/>
+      <c r="J18" s="171"/>
+      <c r="K18" s="171"/>
+      <c r="L18" s="173"/>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="169"/>
+      <c r="C19" s="174" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="171">
         <v>1</v>
       </c>
-      <c r="E19" s="116">
+      <c r="E19" s="172">
         <f>(5.25/3.281)</f>
         <v>1.6001219140505942</v>
       </c>
-      <c r="F19" s="116">
+      <c r="F19" s="172">
         <v>0.23</v>
       </c>
-      <c r="G19" s="116">
+      <c r="G19" s="172">
         <f>((5.33+8)/2)/3.281</f>
         <v>2.03139286802804</v>
       </c>
-      <c r="H19" s="116">
+      <c r="H19" s="172">
         <f t="shared" ref="H19:H21" si="2">D19*E19*G19</f>
         <v>3.2504762441777535</v>
       </c>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="25"/>
-    </row>
-    <row r="20" spans="2:14">
-      <c r="B20" s="123"/>
-      <c r="C20" s="137"/>
-      <c r="D20" s="119">
+      <c r="I19" s="172"/>
+      <c r="J19" s="172"/>
+      <c r="K19" s="172"/>
+      <c r="L19" s="173"/>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="169"/>
+      <c r="C20" s="175"/>
+      <c r="D20" s="171">
         <v>1</v>
       </c>
-      <c r="E20" s="116">
+      <c r="E20" s="172">
         <f>4.5/3.281</f>
         <v>1.3715330691862238</v>
       </c>
-      <c r="F20" s="116">
+      <c r="F20" s="172">
         <v>0.23</v>
       </c>
-      <c r="G20" s="116">
+      <c r="G20" s="172">
         <f>8/3.281</f>
         <v>2.4382810118866196</v>
       </c>
-      <c r="H20" s="116">
+      <c r="H20" s="172">
         <f t="shared" si="2"/>
         <v>3.3441830397713468</v>
       </c>
-      <c r="I20" s="116"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="25"/>
-    </row>
-    <row r="21" spans="2:14">
-      <c r="B21" s="123"/>
-      <c r="C21" s="138" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" s="119">
+      <c r="I20" s="172"/>
+      <c r="J20" s="172"/>
+      <c r="K20" s="172"/>
+      <c r="L20" s="173"/>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="B21" s="169"/>
+      <c r="C21" s="174" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="171">
         <v>-1</v>
       </c>
-      <c r="E21" s="116">
+      <c r="E21" s="172">
         <f>2.5/3.281</f>
         <v>0.76196281621456874</v>
       </c>
-      <c r="F21" s="116">
+      <c r="F21" s="172">
         <v>0.23</v>
       </c>
-      <c r="G21" s="116">
+      <c r="G21" s="172">
         <f>6.5/3.281</f>
         <v>1.9811033221578787</v>
       </c>
-      <c r="H21" s="116">
+      <c r="H21" s="172">
         <f t="shared" si="2"/>
         <v>-1.5095270665634553</v>
       </c>
-      <c r="I21" s="116"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="25"/>
-    </row>
-    <row r="22" spans="2:14">
-      <c r="B22" s="123"/>
-      <c r="C22" s="126"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="116">
+      <c r="I21" s="172"/>
+      <c r="J21" s="172"/>
+      <c r="K21" s="172"/>
+      <c r="L21" s="173"/>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="B22" s="169"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="171"/>
+      <c r="E22" s="172"/>
+      <c r="F22" s="172"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="172">
         <f>SUM(H14:H21)</f>
         <v>30.169924735321075</v>
       </c>
-      <c r="I22" s="119" t="s">
+      <c r="I22" s="171" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="116">
+      <c r="J22" s="172">
         <v>1982.2</v>
       </c>
-      <c r="K22" s="116">
+      <c r="K22" s="172">
         <f>H22*J22</f>
         <v>59802.824810353435</v>
       </c>
-      <c r="L22" s="25"/>
-    </row>
-    <row r="23" spans="2:14">
-      <c r="B23" s="80"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="70"/>
-      <c r="K23" s="70"/>
-      <c r="L23" s="25"/>
-    </row>
-    <row r="24" spans="2:14" ht="55.8">
-      <c r="B24" s="123">
+      <c r="L22" s="173"/>
+    </row>
+    <row r="23" spans="2:12">
+      <c r="B23" s="169"/>
+      <c r="C23" s="178"/>
+      <c r="D23" s="171"/>
+      <c r="E23" s="172"/>
+      <c r="F23" s="172"/>
+      <c r="G23" s="177"/>
+      <c r="H23" s="172"/>
+      <c r="I23" s="171"/>
+      <c r="J23" s="172"/>
+      <c r="K23" s="172"/>
+      <c r="L23" s="173"/>
+    </row>
+    <row r="24" spans="2:12" ht="55.8">
+      <c r="B24" s="169">
         <v>3</v>
       </c>
-      <c r="C24" s="128" t="s">
-        <v>108</v>
-      </c>
-      <c r="D24" s="119"/>
-      <c r="E24" s="116"/>
-      <c r="F24" s="116"/>
-      <c r="G24" s="127"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="119"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="116"/>
-      <c r="L24" s="25"/>
-      <c r="N24" s="90" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14">
-      <c r="B25" s="123"/>
-      <c r="C25" s="129"/>
-      <c r="D25" s="119">
+      <c r="C24" s="153" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="171"/>
+      <c r="E24" s="172"/>
+      <c r="F24" s="172"/>
+      <c r="G24" s="177"/>
+      <c r="H24" s="172"/>
+      <c r="I24" s="171"/>
+      <c r="J24" s="172"/>
+      <c r="K24" s="172"/>
+      <c r="L24" s="173"/>
+    </row>
+    <row r="25" spans="2:12">
+      <c r="B25" s="169"/>
+      <c r="C25" s="178"/>
+      <c r="D25" s="171">
         <f>D10</f>
         <v>1</v>
       </c>
-      <c r="E25" s="116">
+      <c r="E25" s="172">
         <f>E10</f>
         <v>5</v>
       </c>
-      <c r="F25" s="116">
+      <c r="F25" s="172">
         <f>F10</f>
         <v>3.3526363913441024</v>
       </c>
-      <c r="G25" s="127">
+      <c r="G25" s="177">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="H25" s="116">
+      <c r="H25" s="172">
         <f>D25*E25*F25*G25</f>
         <v>1.2572386467540384</v>
       </c>
-      <c r="I25" s="119"/>
-      <c r="J25" s="116"/>
-      <c r="K25" s="116"/>
-      <c r="L25" s="25"/>
-    </row>
-    <row r="26" spans="2:14">
-      <c r="B26" s="123"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="127"/>
-      <c r="H26" s="116">
+      <c r="I25" s="171"/>
+      <c r="J25" s="172"/>
+      <c r="K25" s="172"/>
+      <c r="L25" s="173"/>
+    </row>
+    <row r="26" spans="2:12">
+      <c r="B26" s="169"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="172"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="177"/>
+      <c r="H26" s="172">
         <f>SUM(H25)</f>
         <v>1.2572386467540384</v>
       </c>
-      <c r="I26" s="119" t="s">
+      <c r="I26" s="171" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="116">
+      <c r="J26" s="172">
         <v>770.43</v>
       </c>
-      <c r="K26" s="116">
+      <c r="K26" s="172">
         <f>H26*J26</f>
         <v>968.61437061871379</v>
       </c>
-      <c r="L26" s="25"/>
-    </row>
-    <row r="27" spans="2:14">
-      <c r="B27" s="80"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="70"/>
-      <c r="K27" s="70"/>
-      <c r="L27" s="25"/>
-    </row>
-    <row r="28" spans="2:14" ht="18.600000000000001">
-      <c r="B28" s="130">
+      <c r="L26" s="173"/>
+    </row>
+    <row r="27" spans="2:12">
+      <c r="B27" s="169"/>
+      <c r="C27" s="176"/>
+      <c r="D27" s="171"/>
+      <c r="E27" s="172"/>
+      <c r="F27" s="172"/>
+      <c r="G27" s="177"/>
+      <c r="H27" s="172"/>
+      <c r="I27" s="171"/>
+      <c r="J27" s="172"/>
+      <c r="K27" s="172"/>
+      <c r="L27" s="173"/>
+    </row>
+    <row r="28" spans="2:12" ht="18.600000000000001">
+      <c r="B28" s="179">
         <v>4</v>
       </c>
-      <c r="C28" s="131" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="127"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="127"/>
-      <c r="H28" s="132"/>
-      <c r="I28" s="127"/>
-      <c r="J28" s="132"/>
-      <c r="K28" s="132"/>
-      <c r="L28" s="25"/>
-    </row>
-    <row r="29" spans="2:14">
-      <c r="B29" s="130"/>
-      <c r="C29" s="133" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" s="127">
+      <c r="C28" s="154" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="177"/>
+      <c r="E28" s="180"/>
+      <c r="F28" s="180"/>
+      <c r="G28" s="177"/>
+      <c r="H28" s="180"/>
+      <c r="I28" s="177"/>
+      <c r="J28" s="180"/>
+      <c r="K28" s="180"/>
+      <c r="L28" s="173"/>
+    </row>
+    <row r="29" spans="2:12">
+      <c r="B29" s="179"/>
+      <c r="C29" s="181" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="177">
         <f>D16</f>
         <v>1</v>
       </c>
-      <c r="E29" s="132">
+      <c r="E29" s="180">
         <f>E16</f>
         <v>5</v>
       </c>
-      <c r="F29" s="132">
+      <c r="F29" s="180">
         <f>F25</f>
         <v>3.3526363913441024</v>
       </c>
-      <c r="G29" s="127"/>
-      <c r="H29" s="132">
+      <c r="G29" s="177"/>
+      <c r="H29" s="180">
         <f>PRODUCT(D29:G29)</f>
         <v>16.763181956720512</v>
       </c>
-      <c r="I29" s="127"/>
-      <c r="J29" s="132"/>
-      <c r="K29" s="132"/>
-      <c r="L29" s="25"/>
-    </row>
-    <row r="30" spans="2:14">
-      <c r="B30" s="130"/>
-      <c r="C30" s="134"/>
-      <c r="D30" s="127"/>
-      <c r="E30" s="132"/>
-      <c r="F30" s="132"/>
-      <c r="G30" s="127"/>
-      <c r="H30" s="132">
+      <c r="I29" s="177"/>
+      <c r="J29" s="180"/>
+      <c r="K29" s="180"/>
+      <c r="L29" s="173"/>
+    </row>
+    <row r="30" spans="2:12">
+      <c r="B30" s="179"/>
+      <c r="C30" s="173"/>
+      <c r="D30" s="177"/>
+      <c r="E30" s="180"/>
+      <c r="F30" s="180"/>
+      <c r="G30" s="177"/>
+      <c r="H30" s="180">
         <f>SUM(H29)</f>
         <v>16.763181956720512</v>
       </c>
-      <c r="I30" s="127" t="s">
+      <c r="I30" s="177" t="s">
         <v>23</v>
       </c>
-      <c r="J30" s="132">
+      <c r="J30" s="180">
         <f>Sheet1!H8/10</f>
         <v>155.75</v>
       </c>
-      <c r="K30" s="132">
+      <c r="K30" s="180">
         <f>H30*J30</f>
         <v>2610.8655897592198</v>
       </c>
-      <c r="L30" s="25"/>
-    </row>
-    <row r="31" spans="2:14">
-      <c r="B31" s="80"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="70"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="25"/>
-    </row>
-    <row r="32" spans="2:14" ht="35.1" customHeight="1">
-      <c r="B32" s="123">
+      <c r="L30" s="173"/>
+    </row>
+    <row r="31" spans="2:12">
+      <c r="B31" s="169"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="171"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="172"/>
+      <c r="G31" s="177"/>
+      <c r="H31" s="172"/>
+      <c r="I31" s="171"/>
+      <c r="J31" s="172"/>
+      <c r="K31" s="172"/>
+      <c r="L31" s="173"/>
+    </row>
+    <row r="32" spans="2:12" ht="35.1" customHeight="1">
+      <c r="B32" s="169">
         <v>5</v>
       </c>
-      <c r="C32" s="124" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="119"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="116"/>
-      <c r="G32" s="116"/>
-      <c r="H32" s="116"/>
-      <c r="I32" s="119"/>
-      <c r="J32" s="116"/>
-      <c r="K32" s="116"/>
-      <c r="L32" s="25"/>
+      <c r="C32" s="170" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="171"/>
+      <c r="E32" s="172"/>
+      <c r="F32" s="172"/>
+      <c r="G32" s="172"/>
+      <c r="H32" s="172"/>
+      <c r="I32" s="171"/>
+      <c r="J32" s="172"/>
+      <c r="K32" s="172"/>
+      <c r="L32" s="173"/>
     </row>
     <row r="33" spans="2:12">
-      <c r="B33" s="123"/>
-      <c r="C33" s="118" t="str">
+      <c r="B33" s="169"/>
+      <c r="C33" s="182" t="str">
         <f>C29</f>
         <v>-for flooring</v>
       </c>
-      <c r="D33" s="119">
+      <c r="D33" s="171">
         <f>D29</f>
         <v>1</v>
       </c>
-      <c r="E33" s="116">
+      <c r="E33" s="172">
         <f>E29</f>
         <v>5</v>
       </c>
-      <c r="F33" s="116">
+      <c r="F33" s="172">
         <f>F29</f>
         <v>3.3526363913441024</v>
       </c>
-      <c r="G33" s="116">
+      <c r="G33" s="172">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="H33" s="116">
+      <c r="H33" s="172">
         <f>D33*E33*F33*G33</f>
         <v>1.2572386467540384</v>
       </c>
-      <c r="I33" s="119"/>
-      <c r="J33" s="116"/>
-      <c r="K33" s="116"/>
-      <c r="L33" s="25"/>
+      <c r="I33" s="171"/>
+      <c r="J33" s="172"/>
+      <c r="K33" s="172"/>
+      <c r="L33" s="173"/>
     </row>
     <row r="34" spans="2:12">
-      <c r="B34" s="123"/>
-      <c r="C34" s="135"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="116" t="s">
+      <c r="B34" s="169"/>
+      <c r="C34" s="183"/>
+      <c r="D34" s="171"/>
+      <c r="E34" s="172"/>
+      <c r="F34" s="172" t="s">
         <v>32</v>
       </c>
-      <c r="G34" s="116"/>
-      <c r="H34" s="116">
+      <c r="G34" s="172"/>
+      <c r="H34" s="172">
         <f>SUM(H33)</f>
         <v>1.2572386467540384</v>
       </c>
-      <c r="I34" s="119" t="s">
+      <c r="I34" s="171" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="116">
+      <c r="J34" s="172">
         <v>13351.1</v>
       </c>
-      <c r="K34" s="116">
+      <c r="K34" s="172">
         <f>H34*J34</f>
         <v>16785.518896677844</v>
       </c>
-      <c r="L34" s="25"/>
+      <c r="L34" s="173"/>
     </row>
     <row r="35" spans="2:12">
-      <c r="B35" s="123"/>
-      <c r="C35" s="118" t="s">
+      <c r="B35" s="169"/>
+      <c r="C35" s="182" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="119"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="116"/>
-      <c r="H35" s="116"/>
-      <c r="I35" s="119"/>
-      <c r="J35" s="116"/>
-      <c r="K35" s="116">
+      <c r="D35" s="171"/>
+      <c r="E35" s="172"/>
+      <c r="F35" s="172"/>
+      <c r="G35" s="172"/>
+      <c r="H35" s="172"/>
+      <c r="I35" s="171"/>
+      <c r="J35" s="172"/>
+      <c r="K35" s="172">
         <f>0.13*H34*4169.92</f>
         <v>681.53599512343794</v>
       </c>
-      <c r="L35" s="25"/>
+      <c r="L35" s="173"/>
     </row>
     <row r="36" spans="2:12">
-      <c r="B36" s="123"/>
-      <c r="C36" s="118" t="s">
+      <c r="B36" s="169"/>
+      <c r="C36" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="119"/>
-      <c r="E36" s="116"/>
-      <c r="F36" s="116"/>
-      <c r="G36" s="116"/>
-      <c r="H36" s="116"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="116"/>
-      <c r="K36" s="116">
+      <c r="D36" s="171"/>
+      <c r="E36" s="172"/>
+      <c r="F36" s="172"/>
+      <c r="G36" s="172"/>
+      <c r="H36" s="172"/>
+      <c r="I36" s="171"/>
+      <c r="J36" s="172"/>
+      <c r="K36" s="172">
         <f>0.13*H34*1414.16</f>
         <v>231.13175861017984</v>
       </c>
-      <c r="L36" s="25"/>
+      <c r="L36" s="173"/>
     </row>
     <row r="37" spans="2:12">
-      <c r="B37" s="123"/>
-      <c r="C37" s="118" t="s">
+      <c r="B37" s="169"/>
+      <c r="C37" s="182" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="119"/>
-      <c r="E37" s="116"/>
-      <c r="F37" s="116"/>
-      <c r="G37" s="116"/>
-      <c r="H37" s="116"/>
-      <c r="I37" s="119"/>
-      <c r="J37" s="116"/>
-      <c r="K37" s="116">
+      <c r="D37" s="171"/>
+      <c r="E37" s="172"/>
+      <c r="F37" s="172"/>
+      <c r="G37" s="172"/>
+      <c r="H37" s="172"/>
+      <c r="I37" s="171"/>
+      <c r="J37" s="172"/>
+      <c r="K37" s="172">
         <f>0.13*H34*(1652.5+737.97+349.56)</f>
         <v>447.83330920451084</v>
       </c>
-      <c r="L37" s="25"/>
+      <c r="L37" s="173"/>
     </row>
     <row r="38" spans="2:12" ht="18.600000000000001">
-      <c r="B38" s="80"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="73"/>
-      <c r="K38" s="73"/>
-      <c r="L38" s="25"/>
+      <c r="B38" s="169"/>
+      <c r="C38" s="170"/>
+      <c r="D38" s="171"/>
+      <c r="E38" s="172"/>
+      <c r="F38" s="172"/>
+      <c r="G38" s="172"/>
+      <c r="H38" s="172"/>
+      <c r="I38" s="171"/>
+      <c r="J38" s="172"/>
+      <c r="K38" s="172"/>
+      <c r="L38" s="173"/>
     </row>
     <row r="39" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B39" s="122">
+      <c r="B39" s="169">
         <v>6</v>
       </c>
-      <c r="C39" s="124" t="s">
+      <c r="C39" s="170" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="119"/>
-      <c r="E39" s="116"/>
-      <c r="F39" s="116"/>
-      <c r="G39" s="116"/>
-      <c r="H39" s="116"/>
-      <c r="I39" s="119"/>
-      <c r="J39" s="120"/>
-      <c r="K39" s="116"/>
-      <c r="L39" s="25"/>
+      <c r="D39" s="171"/>
+      <c r="E39" s="172"/>
+      <c r="F39" s="172"/>
+      <c r="G39" s="172"/>
+      <c r="H39" s="172"/>
+      <c r="I39" s="171"/>
+      <c r="J39" s="172"/>
+      <c r="K39" s="172"/>
+      <c r="L39" s="173"/>
     </row>
     <row r="40" spans="2:12">
-      <c r="B40" s="122"/>
-      <c r="C40" s="136" t="s">
-        <v>136</v>
-      </c>
-      <c r="D40" s="119">
+      <c r="B40" s="169"/>
+      <c r="C40" s="184" t="s">
+        <v>133</v>
+      </c>
+      <c r="D40" s="171">
         <v>33</v>
       </c>
-      <c r="E40" s="116">
+      <c r="E40" s="172">
         <f>(2+5.917+16.17+5.917+2)/3.281</f>
         <v>9.7543431880524238</v>
       </c>
-      <c r="F40" s="116"/>
-      <c r="G40" s="116">
+      <c r="F40" s="172"/>
+      <c r="G40" s="172">
         <f>10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
-      <c r="H40" s="116">
+      <c r="H40" s="172">
         <f>D40*E40*G40</f>
         <v>198.69958346032715</v>
       </c>
-      <c r="I40" s="119"/>
-      <c r="J40" s="120"/>
-      <c r="K40" s="116"/>
-      <c r="L40" s="25"/>
+      <c r="I40" s="171"/>
+      <c r="J40" s="172"/>
+      <c r="K40" s="172"/>
+      <c r="L40" s="173"/>
     </row>
     <row r="41" spans="2:12">
-      <c r="B41" s="122"/>
-      <c r="C41" s="118"/>
-      <c r="D41" s="119">
+      <c r="B41" s="169"/>
+      <c r="C41" s="182"/>
+      <c r="D41" s="171">
         <v>32</v>
       </c>
-      <c r="E41" s="116">
+      <c r="E41" s="172">
         <f>(2+5.5+15.667+5.5+2)/3.281</f>
         <v>9.3468454739408724</v>
       </c>
-      <c r="F41" s="116"/>
-      <c r="G41" s="116">
+      <c r="F41" s="172"/>
+      <c r="G41" s="172">
         <f>10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
-      <c r="H41" s="116">
+      <c r="H41" s="172">
         <f t="shared" ref="H41" si="3">D41*E41*G41</f>
         <v>184.62904639883203</v>
       </c>
-      <c r="I41" s="119"/>
-      <c r="J41" s="120"/>
-      <c r="K41" s="116"/>
-      <c r="L41" s="25"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="172"/>
+      <c r="K41" s="172"/>
+      <c r="L41" s="173"/>
     </row>
     <row r="42" spans="2:12">
-      <c r="B42" s="122"/>
-      <c r="C42" s="136" t="s">
-        <v>136</v>
-      </c>
-      <c r="D42" s="119">
+      <c r="B42" s="169"/>
+      <c r="C42" s="184" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" s="171">
         <v>23</v>
       </c>
-      <c r="E42" s="116">
+      <c r="E42" s="172">
         <f>(2+5.917+10.75+5.917+2)/3.281</f>
         <v>8.1024078024992381</v>
       </c>
-      <c r="F42" s="116"/>
-      <c r="G42" s="116">
+      <c r="F42" s="172"/>
+      <c r="G42" s="172">
         <f>10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
-      <c r="H42" s="116">
+      <c r="H42" s="172">
         <f>D42*E42*G42</f>
         <v>115.03418485029782</v>
       </c>
-      <c r="I42" s="119"/>
-      <c r="J42" s="120"/>
-      <c r="K42" s="116"/>
-      <c r="L42" s="25"/>
+      <c r="I42" s="171"/>
+      <c r="J42" s="172"/>
+      <c r="K42" s="172"/>
+      <c r="L42" s="173"/>
     </row>
     <row r="43" spans="2:12">
-      <c r="B43" s="122"/>
-      <c r="C43" s="118"/>
-      <c r="D43" s="119">
+      <c r="B43" s="169"/>
+      <c r="C43" s="182"/>
+      <c r="D43" s="171">
         <v>22</v>
       </c>
-      <c r="E43" s="116">
+      <c r="E43" s="172">
         <f>(2+5.5+10.25+5.5+2)/3.281</f>
         <v>7.6958244437671439</v>
       </c>
-      <c r="F43" s="116"/>
-      <c r="G43" s="116">
+      <c r="F43" s="172"/>
+      <c r="G43" s="172">
         <f>10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
-      <c r="H43" s="116">
+      <c r="H43" s="172">
         <f t="shared" ref="H43" si="4">D43*E43*G43</f>
         <v>104.51119614992416</v>
       </c>
-      <c r="I43" s="119"/>
-      <c r="J43" s="120"/>
-      <c r="K43" s="116"/>
-      <c r="L43" s="25"/>
+      <c r="I43" s="171"/>
+      <c r="J43" s="172"/>
+      <c r="K43" s="172"/>
+      <c r="L43" s="173"/>
     </row>
     <row r="44" spans="2:12">
-      <c r="B44" s="122"/>
-      <c r="C44" s="135"/>
-      <c r="D44" s="119">
+      <c r="B44" s="169"/>
+      <c r="C44" s="183"/>
+      <c r="D44" s="171">
         <v>12</v>
       </c>
-      <c r="E44" s="116">
+      <c r="E44" s="172">
         <f>(16.17+10.75+16.17+10.75)/3.281</f>
         <v>16.409631209996952</v>
       </c>
-      <c r="F44" s="116"/>
-      <c r="G44" s="116">
+      <c r="F44" s="172"/>
+      <c r="G44" s="172">
         <f>8*8/162</f>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H44" s="116">
+      <c r="H44" s="172">
         <f>D44*E44*G44</f>
         <v>77.79380721776333</v>
       </c>
-      <c r="I44" s="119"/>
-      <c r="J44" s="120"/>
-      <c r="K44" s="116"/>
-      <c r="L44" s="25"/>
+      <c r="I44" s="171"/>
+      <c r="J44" s="172"/>
+      <c r="K44" s="172"/>
+      <c r="L44" s="173"/>
     </row>
     <row r="45" spans="2:12">
-      <c r="B45" s="122"/>
-      <c r="C45" s="118"/>
-      <c r="D45" s="119">
+      <c r="B45" s="169"/>
+      <c r="C45" s="182"/>
+      <c r="D45" s="171">
         <v>11</v>
       </c>
-      <c r="E45" s="116">
+      <c r="E45" s="172">
         <f>(15.667+10.25+15.667+10.25)/3.281</f>
         <v>15.798232246266382</v>
       </c>
-      <c r="F45" s="116"/>
-      <c r="G45" s="116">
+      <c r="F45" s="172"/>
+      <c r="G45" s="172">
         <f>8*8/162</f>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H45" s="116">
+      <c r="H45" s="172">
         <f>D45*E45*G45</f>
         <v>68.654046304762545</v>
       </c>
-      <c r="I45" s="119"/>
-      <c r="J45" s="120"/>
-      <c r="K45" s="116"/>
-      <c r="L45" s="25"/>
+      <c r="I45" s="171"/>
+      <c r="J45" s="172"/>
+      <c r="K45" s="172"/>
+      <c r="L45" s="173"/>
     </row>
     <row r="46" spans="2:12">
-      <c r="B46" s="122"/>
-      <c r="C46" s="136" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" s="119">
+      <c r="B46" s="169"/>
+      <c r="C46" s="184" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46" s="171">
         <f>2*TRUNC((E47/0.15),0)</f>
         <v>42</v>
       </c>
-      <c r="E46" s="116">
+      <c r="E46" s="172">
         <f>(16.17/3.281)</f>
         <v>4.928375495275831</v>
       </c>
-      <c r="F46" s="116"/>
-      <c r="G46" s="116">
+      <c r="F46" s="172"/>
+      <c r="G46" s="172">
         <f t="shared" ref="G46:G50" si="5">8*8/162</f>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H46" s="116">
+      <c r="H46" s="172">
         <f t="shared" ref="H46:H47" si="6">D46*E46*G46</f>
         <v>81.774526736428598</v>
       </c>
-      <c r="I46" s="119"/>
-      <c r="J46" s="120"/>
-      <c r="K46" s="116"/>
-      <c r="L46" s="25"/>
+      <c r="I46" s="171"/>
+      <c r="J46" s="172"/>
+      <c r="K46" s="172"/>
+      <c r="L46" s="173"/>
     </row>
     <row r="47" spans="2:12">
-      <c r="B47" s="122"/>
-      <c r="C47" s="118"/>
-      <c r="D47" s="119">
+      <c r="B47" s="169"/>
+      <c r="C47" s="182"/>
+      <c r="D47" s="171">
         <f>2*TRUNC((E46/0.15),0)</f>
         <v>64</v>
       </c>
-      <c r="E47" s="116">
+      <c r="E47" s="172">
         <f>10.75/3.281</f>
         <v>3.2764401097226452</v>
       </c>
-      <c r="F47" s="116"/>
-      <c r="G47" s="116">
+      <c r="F47" s="172"/>
+      <c r="G47" s="172">
         <f t="shared" si="5"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H47" s="116">
+      <c r="H47" s="172">
         <f t="shared" si="6"/>
         <v>82.841349934715765</v>
       </c>
-      <c r="I47" s="119"/>
-      <c r="J47" s="120"/>
-      <c r="K47" s="116"/>
-      <c r="L47" s="25"/>
-    </row>
-    <row r="48" spans="2:12" s="121" customFormat="1">
-      <c r="B48" s="123"/>
-      <c r="C48" s="136" t="s">
-        <v>149</v>
-      </c>
-      <c r="D48" s="119">
+      <c r="I47" s="171"/>
+      <c r="J47" s="172"/>
+      <c r="K47" s="172"/>
+      <c r="L47" s="173"/>
+    </row>
+    <row r="48" spans="2:12">
+      <c r="B48" s="169"/>
+      <c r="C48" s="184" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48" s="171">
         <f>-2*5</f>
         <v>-10</v>
       </c>
-      <c r="E48" s="116">
+      <c r="E48" s="172">
         <v>0.6</v>
       </c>
-      <c r="F48" s="116"/>
-      <c r="G48" s="116">
+      <c r="F48" s="172"/>
+      <c r="G48" s="172">
         <f t="shared" si="5"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H48" s="116">
+      <c r="H48" s="172">
         <f t="shared" ref="H48:H49" si="7">PRODUCT(D48:G48)</f>
         <v>-2.3703703703703702</v>
       </c>
-      <c r="I48" s="119"/>
-      <c r="J48" s="116"/>
-      <c r="K48" s="116"/>
-      <c r="L48" s="25"/>
-    </row>
-    <row r="49" spans="2:12" s="121" customFormat="1">
-      <c r="B49" s="122"/>
-      <c r="C49" s="136"/>
-      <c r="D49" s="119">
+      <c r="I48" s="171"/>
+      <c r="J48" s="172"/>
+      <c r="K48" s="172"/>
+      <c r="L48" s="173"/>
+    </row>
+    <row r="49" spans="2:12">
+      <c r="B49" s="169"/>
+      <c r="C49" s="184"/>
+      <c r="D49" s="171">
         <f>-2*5</f>
         <v>-10</v>
       </c>
-      <c r="E49" s="116">
+      <c r="E49" s="172">
         <v>0.6</v>
       </c>
-      <c r="F49" s="116"/>
-      <c r="G49" s="116">
+      <c r="F49" s="172"/>
+      <c r="G49" s="172">
         <f t="shared" si="5"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H49" s="116">
+      <c r="H49" s="172">
         <f t="shared" si="7"/>
         <v>-2.3703703703703702</v>
       </c>
-      <c r="I49" s="119"/>
-      <c r="J49" s="120"/>
-      <c r="K49" s="116"/>
-      <c r="L49" s="25"/>
+      <c r="I49" s="171"/>
+      <c r="J49" s="172"/>
+      <c r="K49" s="172"/>
+      <c r="L49" s="173"/>
     </row>
     <row r="50" spans="2:12">
-      <c r="B50" s="122"/>
-      <c r="C50" s="136" t="s">
-        <v>144</v>
-      </c>
-      <c r="D50" s="168">
+      <c r="B50" s="169"/>
+      <c r="C50" s="184" t="s">
+        <v>141</v>
+      </c>
+      <c r="D50" s="185">
         <f>28*2+17*2</f>
         <v>90</v>
       </c>
-      <c r="E50" s="116">
+      <c r="E50" s="172">
         <f>(1+1.42+1)/3.281</f>
         <v>1.04236513258153</v>
       </c>
-      <c r="F50" s="116"/>
-      <c r="G50" s="116">
+      <c r="F50" s="172"/>
+      <c r="G50" s="172">
         <f t="shared" si="5"/>
         <v>0.39506172839506171</v>
       </c>
-      <c r="H50" s="116">
+      <c r="H50" s="172">
         <f t="shared" ref="H50" si="8">D50*E50*G50</f>
         <v>37.061871380676621</v>
       </c>
-      <c r="I50" s="119"/>
-      <c r="J50" s="120"/>
-      <c r="K50" s="116"/>
-      <c r="L50" s="25"/>
+      <c r="I50" s="171"/>
+      <c r="J50" s="172"/>
+      <c r="K50" s="172"/>
+      <c r="L50" s="173"/>
     </row>
     <row r="51" spans="2:12">
-      <c r="B51" s="122"/>
-      <c r="C51" s="118"/>
-      <c r="D51" s="119"/>
-      <c r="E51" s="116"/>
-      <c r="F51" s="116"/>
-      <c r="G51" s="116"/>
-      <c r="H51" s="116">
+      <c r="B51" s="169"/>
+      <c r="C51" s="182"/>
+      <c r="D51" s="171"/>
+      <c r="E51" s="172"/>
+      <c r="F51" s="172"/>
+      <c r="G51" s="172"/>
+      <c r="H51" s="172">
         <f>SUM(H40:H50)</f>
         <v>946.25887169298721</v>
       </c>
-      <c r="I51" s="119" t="s">
+      <c r="I51" s="171" t="s">
         <v>18</v>
       </c>
-      <c r="J51" s="120">
+      <c r="J51" s="172">
         <f>132360/1000</f>
         <v>132.36000000000001</v>
       </c>
-      <c r="K51" s="116">
+      <c r="K51" s="172">
         <f>H51*J51</f>
         <v>125246.82425728381</v>
       </c>
-      <c r="L51" s="25"/>
+      <c r="L51" s="173"/>
     </row>
     <row r="52" spans="2:12">
-      <c r="B52" s="122"/>
-      <c r="C52" s="118" t="s">
+      <c r="B52" s="169"/>
+      <c r="C52" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="119"/>
-      <c r="E52" s="116"/>
-      <c r="F52" s="116"/>
-      <c r="G52" s="116"/>
-      <c r="H52" s="116"/>
-      <c r="I52" s="119"/>
-      <c r="J52" s="120"/>
-      <c r="K52" s="116">
+      <c r="D52" s="171"/>
+      <c r="E52" s="172"/>
+      <c r="F52" s="172"/>
+      <c r="G52" s="172"/>
+      <c r="H52" s="172"/>
+      <c r="I52" s="171"/>
+      <c r="J52" s="172"/>
+      <c r="K52" s="172">
         <f>0.13*H51*106200/1000</f>
         <v>13064.049982593382</v>
       </c>
-      <c r="L52" s="25"/>
+      <c r="L52" s="173"/>
     </row>
     <row r="53" spans="2:12">
-      <c r="B53" s="114"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="70"/>
-      <c r="F53" s="70"/>
-      <c r="G53" s="70"/>
-      <c r="H53" s="70"/>
-      <c r="I53" s="24"/>
-      <c r="J53" s="115"/>
-      <c r="K53" s="117"/>
-      <c r="L53" s="25"/>
+      <c r="B53" s="169"/>
+      <c r="C53" s="182"/>
+      <c r="D53" s="171"/>
+      <c r="E53" s="172"/>
+      <c r="F53" s="172"/>
+      <c r="G53" s="172"/>
+      <c r="H53" s="172"/>
+      <c r="I53" s="171"/>
+      <c r="J53" s="172"/>
+      <c r="K53" s="172"/>
+      <c r="L53" s="173"/>
     </row>
     <row r="54" spans="2:12" ht="37.200000000000003">
-      <c r="B54" s="122">
+      <c r="B54" s="169">
         <v>7</v>
       </c>
-      <c r="C54" s="124" t="s">
-        <v>138</v>
-      </c>
-      <c r="D54" s="119"/>
-      <c r="E54" s="116"/>
-      <c r="F54" s="116"/>
-      <c r="G54" s="116"/>
-      <c r="H54" s="116"/>
-      <c r="I54" s="119"/>
-      <c r="J54" s="120"/>
-      <c r="K54" s="116"/>
-      <c r="L54" s="25"/>
+      <c r="C54" s="170" t="s">
+        <v>135</v>
+      </c>
+      <c r="D54" s="171"/>
+      <c r="E54" s="172"/>
+      <c r="F54" s="172"/>
+      <c r="G54" s="172"/>
+      <c r="H54" s="172"/>
+      <c r="I54" s="171"/>
+      <c r="J54" s="172"/>
+      <c r="K54" s="172"/>
+      <c r="L54" s="173"/>
     </row>
     <row r="55" spans="2:12">
-      <c r="B55" s="122"/>
-      <c r="C55" s="136" t="s">
-        <v>139</v>
-      </c>
-      <c r="D55" s="119">
+      <c r="B55" s="169"/>
+      <c r="C55" s="184" t="s">
+        <v>136</v>
+      </c>
+      <c r="D55" s="171">
         <v>1</v>
       </c>
-      <c r="E55" s="116">
+      <c r="E55" s="172">
         <f>((16.42+11)*2)/3.281</f>
         <v>16.714416336482781</v>
       </c>
-      <c r="F55" s="116"/>
-      <c r="G55" s="116">
+      <c r="F55" s="172"/>
+      <c r="G55" s="172">
         <f>4.583/3.281</f>
         <v>1.3968302346845474</v>
       </c>
-      <c r="H55" s="116">
+      <c r="H55" s="172">
         <f>PRODUCT(D55:G55)</f>
         <v>23.347202093904475</v>
       </c>
-      <c r="I55" s="119"/>
-      <c r="J55" s="120"/>
-      <c r="K55" s="116"/>
-      <c r="L55" s="25"/>
+      <c r="I55" s="171"/>
+      <c r="J55" s="172"/>
+      <c r="K55" s="172"/>
+      <c r="L55" s="173"/>
     </row>
     <row r="56" spans="2:12">
-      <c r="B56" s="122"/>
-      <c r="C56" s="118"/>
-      <c r="D56" s="119">
+      <c r="B56" s="169"/>
+      <c r="C56" s="182"/>
+      <c r="D56" s="171">
         <v>1</v>
       </c>
-      <c r="E56" s="116">
+      <c r="E56" s="172">
         <f>((15.42+10)*2)/3.281</f>
         <v>15.49527583053947</v>
       </c>
-      <c r="F56" s="116"/>
-      <c r="G56" s="116">
+      <c r="F56" s="172"/>
+      <c r="G56" s="172">
         <f>4.17/3.281</f>
         <v>1.2709539774459007</v>
       </c>
-      <c r="H56" s="116">
+      <c r="H56" s="172">
         <f t="shared" ref="H56:H58" si="9">PRODUCT(D56:G56)</f>
         <v>19.693782448445472</v>
       </c>
-      <c r="I56" s="119"/>
-      <c r="J56" s="120"/>
-      <c r="K56" s="116"/>
-      <c r="L56" s="25"/>
+      <c r="I56" s="171"/>
+      <c r="J56" s="172"/>
+      <c r="K56" s="172"/>
+      <c r="L56" s="173"/>
     </row>
     <row r="57" spans="2:12">
-      <c r="B57" s="122"/>
-      <c r="C57" s="136" t="s">
-        <v>140</v>
-      </c>
-      <c r="D57" s="119">
+      <c r="B57" s="169"/>
+      <c r="C57" s="184" t="s">
+        <v>137</v>
+      </c>
+      <c r="D57" s="171">
         <v>1</v>
       </c>
-      <c r="E57" s="116">
+      <c r="E57" s="172">
         <f>(15.42/3.281)</f>
         <v>4.6997866504114594</v>
       </c>
-      <c r="F57" s="116">
+      <c r="F57" s="172">
         <f>10/3.281</f>
         <v>3.047851264858275</v>
       </c>
-      <c r="G57" s="116"/>
-      <c r="H57" s="116">
+      <c r="G57" s="172"/>
+      <c r="H57" s="172">
         <f t="shared" si="9"/>
         <v>14.324250687020601</v>
       </c>
-      <c r="I57" s="119"/>
-      <c r="J57" s="120"/>
-      <c r="K57" s="116"/>
-      <c r="L57" s="25"/>
-    </row>
-    <row r="58" spans="2:12" s="121" customFormat="1">
-      <c r="B58" s="123"/>
-      <c r="C58" s="136" t="s">
-        <v>149</v>
-      </c>
-      <c r="D58" s="119">
+      <c r="I57" s="171"/>
+      <c r="J57" s="172"/>
+      <c r="K57" s="172"/>
+      <c r="L57" s="173"/>
+    </row>
+    <row r="58" spans="2:12">
+      <c r="B58" s="169"/>
+      <c r="C58" s="184" t="s">
+        <v>146</v>
+      </c>
+      <c r="D58" s="171">
         <v>-1</v>
       </c>
-      <c r="E58" s="116">
+      <c r="E58" s="172">
         <v>0.6</v>
       </c>
-      <c r="F58" s="116">
+      <c r="F58" s="172">
         <v>0.6</v>
       </c>
-      <c r="G58" s="116"/>
-      <c r="H58" s="116">
+      <c r="G58" s="172"/>
+      <c r="H58" s="172">
         <f t="shared" si="9"/>
         <v>-0.36</v>
       </c>
-      <c r="I58" s="119"/>
-      <c r="J58" s="116"/>
-      <c r="K58" s="116"/>
-      <c r="L58" s="25"/>
+      <c r="I58" s="171"/>
+      <c r="J58" s="172"/>
+      <c r="K58" s="172"/>
+      <c r="L58" s="173"/>
     </row>
     <row r="59" spans="2:12">
-      <c r="B59" s="122"/>
-      <c r="C59" s="118"/>
-      <c r="D59" s="119"/>
-      <c r="E59" s="116"/>
-      <c r="F59" s="116"/>
-      <c r="G59" s="116"/>
-      <c r="H59" s="116">
+      <c r="B59" s="169"/>
+      <c r="C59" s="182"/>
+      <c r="D59" s="171"/>
+      <c r="E59" s="172"/>
+      <c r="F59" s="172"/>
+      <c r="G59" s="172"/>
+      <c r="H59" s="172">
         <f>SUM(H55:H58)</f>
         <v>57.005235229370548</v>
       </c>
-      <c r="I59" s="119" t="s">
+      <c r="I59" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="J59" s="120">
+      <c r="J59" s="172">
         <v>922.71</v>
       </c>
-      <c r="K59" s="116">
+      <c r="K59" s="172">
         <f>H59*J59</f>
         <v>52599.300598492504</v>
       </c>
-      <c r="L59" s="25"/>
+      <c r="L59" s="173"/>
     </row>
     <row r="60" spans="2:12">
-      <c r="B60" s="122"/>
-      <c r="C60" s="118" t="s">
+      <c r="B60" s="169"/>
+      <c r="C60" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="119"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="119"/>
-      <c r="J60" s="120"/>
-      <c r="K60" s="116">
+      <c r="D60" s="171"/>
+      <c r="E60" s="172"/>
+      <c r="F60" s="172"/>
+      <c r="G60" s="172"/>
+      <c r="H60" s="172"/>
+      <c r="I60" s="171"/>
+      <c r="J60" s="172"/>
+      <c r="K60" s="172">
         <f>0.13*H59*46827.87/100</f>
         <v>3470.2638680324994</v>
       </c>
-      <c r="L60" s="25"/>
+      <c r="L60" s="173"/>
     </row>
     <row r="61" spans="2:12">
-      <c r="B61" s="114"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="70"/>
-      <c r="H61" s="70"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="115"/>
-      <c r="K61" s="117"/>
-      <c r="L61" s="25"/>
+      <c r="B61" s="169"/>
+      <c r="C61" s="182"/>
+      <c r="D61" s="171"/>
+      <c r="E61" s="172"/>
+      <c r="F61" s="172"/>
+      <c r="G61" s="172"/>
+      <c r="H61" s="172"/>
+      <c r="I61" s="171"/>
+      <c r="J61" s="172"/>
+      <c r="K61" s="172"/>
+      <c r="L61" s="173"/>
     </row>
     <row r="62" spans="2:12" ht="55.8">
-      <c r="B62" s="123">
+      <c r="B62" s="169">
         <v>8</v>
       </c>
-      <c r="C62" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="D62" s="119"/>
-      <c r="E62" s="116"/>
-      <c r="F62" s="116"/>
-      <c r="G62" s="116"/>
-      <c r="H62" s="116"/>
-      <c r="I62" s="119"/>
-      <c r="J62" s="116"/>
-      <c r="K62" s="116"/>
-      <c r="L62" s="25"/>
+      <c r="C62" s="170" t="s">
+        <v>142</v>
+      </c>
+      <c r="D62" s="171"/>
+      <c r="E62" s="172"/>
+      <c r="F62" s="172"/>
+      <c r="G62" s="172"/>
+      <c r="H62" s="172"/>
+      <c r="I62" s="171"/>
+      <c r="J62" s="172"/>
+      <c r="K62" s="172"/>
+      <c r="L62" s="173"/>
     </row>
     <row r="63" spans="2:12">
-      <c r="B63" s="123"/>
-      <c r="C63" s="136" t="s">
-        <v>143</v>
-      </c>
-      <c r="D63" s="119">
+      <c r="B63" s="169"/>
+      <c r="C63" s="184" t="s">
+        <v>140</v>
+      </c>
+      <c r="D63" s="171">
         <v>2</v>
       </c>
-      <c r="E63" s="116">
+      <c r="E63" s="172">
         <f>E29</f>
         <v>5</v>
       </c>
-      <c r="F63" s="116">
+      <c r="F63" s="172">
         <f>F29</f>
         <v>3.3526363913441024</v>
       </c>
-      <c r="G63" s="116">
+      <c r="G63" s="172">
         <f>0.42/3.281</f>
         <v>0.12800975312404753</v>
       </c>
-      <c r="H63" s="116">
+      <c r="H63" s="172">
         <f>D63*E63*F63*G63</f>
         <v>4.2917015677065615</v>
       </c>
-      <c r="I63" s="119"/>
-      <c r="J63" s="116"/>
-      <c r="K63" s="116"/>
-      <c r="L63" s="25"/>
+      <c r="I63" s="171"/>
+      <c r="J63" s="172"/>
+      <c r="K63" s="172"/>
+      <c r="L63" s="173"/>
     </row>
     <row r="64" spans="2:12">
-      <c r="B64" s="123"/>
-      <c r="C64" s="136" t="s">
-        <v>142</v>
-      </c>
-      <c r="D64" s="119">
+      <c r="B64" s="169"/>
+      <c r="C64" s="184" t="s">
+        <v>139</v>
+      </c>
+      <c r="D64" s="171">
         <v>2</v>
       </c>
-      <c r="E64" s="116">
+      <c r="E64" s="172">
         <f>E63</f>
         <v>5</v>
       </c>
-      <c r="F64" s="116">
+      <c r="F64" s="172">
         <v>0.15</v>
       </c>
-      <c r="G64" s="116">
+      <c r="G64" s="172">
         <f>5.25/3.281</f>
         <v>1.6001219140505942</v>
       </c>
-      <c r="H64" s="116">
+      <c r="H64" s="172">
         <f>D64*E64*F64*G64</f>
         <v>2.4001828710758915</v>
       </c>
-      <c r="I64" s="119"/>
-      <c r="J64" s="116"/>
-      <c r="K64" s="116"/>
-      <c r="L64" s="25"/>
+      <c r="I64" s="171"/>
+      <c r="J64" s="172"/>
+      <c r="K64" s="172"/>
+      <c r="L64" s="173"/>
     </row>
     <row r="65" spans="2:12">
-      <c r="B65" s="123"/>
-      <c r="C65" s="135"/>
-      <c r="D65" s="119">
+      <c r="B65" s="169"/>
+      <c r="C65" s="183"/>
+      <c r="D65" s="171">
         <v>2</v>
       </c>
-      <c r="E65" s="116">
+      <c r="E65" s="172">
         <f>10/3.281</f>
         <v>3.047851264858275</v>
       </c>
-      <c r="F65" s="116">
+      <c r="F65" s="172">
         <v>0.15</v>
       </c>
-      <c r="G65" s="116">
+      <c r="G65" s="172">
         <f>5.25/3.281</f>
         <v>1.6001219140505942</v>
       </c>
-      <c r="H65" s="116">
+      <c r="H65" s="172">
         <f>D65*E65*F65*G65</f>
         <v>1.4630800798999641</v>
       </c>
-      <c r="I65" s="119"/>
-      <c r="J65" s="116"/>
-      <c r="K65" s="116"/>
-      <c r="L65" s="25"/>
+      <c r="I65" s="171"/>
+      <c r="J65" s="172"/>
+      <c r="K65" s="172"/>
+      <c r="L65" s="173"/>
     </row>
     <row r="66" spans="2:12">
-      <c r="B66" s="123"/>
-      <c r="C66" s="136" t="s">
-        <v>141</v>
-      </c>
-      <c r="D66" s="119">
+      <c r="B66" s="169"/>
+      <c r="C66" s="184" t="s">
+        <v>138</v>
+      </c>
+      <c r="D66" s="171">
         <v>0.5</v>
       </c>
-      <c r="E66" s="116">
+      <c r="E66" s="172">
         <f>(13.42*2+8*2)/3.281</f>
         <v>13.05699481865285</v>
       </c>
-      <c r="F66" s="116">
+      <c r="F66" s="172">
         <f>1/3.281</f>
         <v>0.30478512648582745</v>
       </c>
-      <c r="G66" s="116">
+      <c r="G66" s="172">
         <f>1/3.281</f>
         <v>0.30478512648582745</v>
       </c>
-      <c r="H66" s="116">
+      <c r="H66" s="172">
         <f>D66*E66*F66*G66</f>
         <v>0.60645806420723891</v>
       </c>
-      <c r="I66" s="119"/>
-      <c r="J66" s="116"/>
-      <c r="K66" s="116"/>
-      <c r="L66" s="25"/>
-    </row>
-    <row r="67" spans="2:12" s="121" customFormat="1">
-      <c r="B67" s="123"/>
-      <c r="C67" s="136" t="s">
-        <v>149</v>
-      </c>
-      <c r="D67" s="119">
+      <c r="I66" s="171"/>
+      <c r="J66" s="172"/>
+      <c r="K66" s="172"/>
+      <c r="L66" s="173"/>
+    </row>
+    <row r="67" spans="2:12">
+      <c r="B67" s="169"/>
+      <c r="C67" s="184" t="s">
+        <v>146</v>
+      </c>
+      <c r="D67" s="171">
         <v>-1</v>
       </c>
-      <c r="E67" s="116">
+      <c r="E67" s="172">
         <v>0.6</v>
       </c>
-      <c r="F67" s="116">
+      <c r="F67" s="172">
         <v>0.6</v>
       </c>
-      <c r="G67" s="116">
+      <c r="G67" s="172">
         <f>0.42/3.281</f>
         <v>0.12800975312404753</v>
       </c>
-      <c r="H67" s="116">
+      <c r="H67" s="172">
         <f>D67*E67*F67*G67</f>
         <v>-4.6083511124657105E-2</v>
       </c>
-      <c r="I67" s="119"/>
-      <c r="J67" s="116"/>
-      <c r="K67" s="116"/>
-      <c r="L67" s="25"/>
+      <c r="I67" s="171"/>
+      <c r="J67" s="172"/>
+      <c r="K67" s="172"/>
+      <c r="L67" s="173"/>
     </row>
     <row r="68" spans="2:12">
-      <c r="B68" s="123"/>
-      <c r="C68" s="136"/>
-      <c r="D68" s="119"/>
-      <c r="E68" s="116"/>
-      <c r="F68" s="116" t="s">
+      <c r="B68" s="169"/>
+      <c r="C68" s="184"/>
+      <c r="D68" s="171"/>
+      <c r="E68" s="172"/>
+      <c r="F68" s="172" t="s">
         <v>32</v>
       </c>
-      <c r="G68" s="116"/>
-      <c r="H68" s="116">
+      <c r="G68" s="172"/>
+      <c r="H68" s="172">
         <f>SUM(H63:H67)</f>
         <v>8.7153390717649994</v>
       </c>
-      <c r="I68" s="119" t="s">
+      <c r="I68" s="171" t="s">
         <v>24</v>
       </c>
-      <c r="J68" s="116">
+      <c r="J68" s="172">
         <v>13957.29</v>
       </c>
-      <c r="K68" s="116">
+      <c r="K68" s="172">
         <f>H68*J68</f>
         <v>121642.51487295491</v>
       </c>
-      <c r="L68" s="25"/>
+      <c r="L68" s="173"/>
     </row>
     <row r="69" spans="2:12">
-      <c r="B69" s="123"/>
-      <c r="C69" s="118" t="s">
+      <c r="B69" s="169"/>
+      <c r="C69" s="182" t="s">
         <v>29</v>
       </c>
-      <c r="D69" s="119"/>
-      <c r="E69" s="116"/>
-      <c r="F69" s="116"/>
-      <c r="G69" s="116"/>
-      <c r="H69" s="116"/>
-      <c r="I69" s="119"/>
-      <c r="J69" s="116"/>
-      <c r="K69" s="116">
+      <c r="D69" s="171"/>
+      <c r="E69" s="172"/>
+      <c r="F69" s="172"/>
+      <c r="G69" s="172"/>
+      <c r="H69" s="172"/>
+      <c r="I69" s="171"/>
+      <c r="J69" s="172"/>
+      <c r="K69" s="172">
         <f>0.13*H68*5212.4</f>
         <v>5905.6183390968245</v>
       </c>
-      <c r="L69" s="25"/>
+      <c r="L69" s="173"/>
     </row>
     <row r="70" spans="2:12">
-      <c r="B70" s="123"/>
-      <c r="C70" s="118" t="s">
+      <c r="B70" s="169"/>
+      <c r="C70" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="D70" s="119"/>
-      <c r="E70" s="116"/>
-      <c r="F70" s="116"/>
-      <c r="G70" s="116"/>
-      <c r="H70" s="116"/>
-      <c r="I70" s="119"/>
-      <c r="J70" s="116"/>
-      <c r="K70" s="116">
+      <c r="D70" s="171"/>
+      <c r="E70" s="172"/>
+      <c r="F70" s="172"/>
+      <c r="G70" s="172"/>
+      <c r="H70" s="172"/>
+      <c r="I70" s="171"/>
+      <c r="J70" s="172"/>
+      <c r="K70" s="172">
         <f>0.13*H68*1350.6</f>
         <v>1530.221803542355</v>
       </c>
-      <c r="L70" s="25"/>
+      <c r="L70" s="173"/>
     </row>
     <row r="71" spans="2:12">
-      <c r="B71" s="123"/>
-      <c r="C71" s="118" t="s">
+      <c r="B71" s="169"/>
+      <c r="C71" s="182" t="s">
         <v>31</v>
       </c>
-      <c r="D71" s="119"/>
-      <c r="E71" s="116"/>
-      <c r="F71" s="116"/>
-      <c r="G71" s="116"/>
-      <c r="H71" s="116"/>
-      <c r="I71" s="119"/>
-      <c r="J71" s="116"/>
-      <c r="K71" s="116">
+      <c r="D71" s="171"/>
+      <c r="E71" s="172"/>
+      <c r="F71" s="172"/>
+      <c r="G71" s="172"/>
+      <c r="H71" s="172"/>
+      <c r="I71" s="171"/>
+      <c r="J71" s="172"/>
+      <c r="K71" s="172">
         <f>0.13*H68*(1912.03+921.59)</f>
         <v>3210.4746830695158</v>
       </c>
-      <c r="L71" s="25"/>
+      <c r="L71" s="173"/>
     </row>
     <row r="72" spans="2:12">
-      <c r="B72" s="123"/>
-      <c r="C72" s="118" t="s">
-        <v>146</v>
-      </c>
-      <c r="D72" s="119"/>
-      <c r="E72" s="116"/>
-      <c r="F72" s="116"/>
-      <c r="G72" s="116"/>
-      <c r="H72" s="116"/>
-      <c r="I72" s="119"/>
-      <c r="J72" s="116"/>
-      <c r="K72" s="116">
+      <c r="B72" s="169"/>
+      <c r="C72" s="182" t="s">
+        <v>143</v>
+      </c>
+      <c r="D72" s="171"/>
+      <c r="E72" s="172"/>
+      <c r="F72" s="172"/>
+      <c r="G72" s="172"/>
+      <c r="H72" s="172"/>
+      <c r="I72" s="171"/>
+      <c r="J72" s="172"/>
+      <c r="K72" s="172">
         <f>0.13*H68*392.92</f>
         <v>445.17603365012752</v>
       </c>
-      <c r="L72" s="25"/>
+      <c r="L72" s="173"/>
     </row>
     <row r="73" spans="2:12">
-      <c r="B73" s="122"/>
-      <c r="C73" s="118" t="s">
-        <v>147</v>
-      </c>
-      <c r="D73" s="119"/>
-      <c r="E73" s="116"/>
-      <c r="F73" s="116"/>
-      <c r="G73" s="116"/>
-      <c r="H73" s="116"/>
-      <c r="I73" s="119"/>
-      <c r="J73" s="116"/>
-      <c r="K73" s="116">
+      <c r="B73" s="169"/>
+      <c r="C73" s="182" t="s">
+        <v>144</v>
+      </c>
+      <c r="D73" s="171"/>
+      <c r="E73" s="172"/>
+      <c r="F73" s="172"/>
+      <c r="G73" s="172"/>
+      <c r="H73" s="172"/>
+      <c r="I73" s="171"/>
+      <c r="J73" s="172"/>
+      <c r="K73" s="172">
         <f>0.13*H68*14.15</f>
         <v>16.031866222511717</v>
       </c>
-      <c r="L73" s="25"/>
+      <c r="L73" s="173"/>
     </row>
     <row r="74" spans="2:12">
-      <c r="B74" s="114"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="70"/>
-      <c r="F74" s="70"/>
-      <c r="G74" s="70"/>
-      <c r="H74" s="70"/>
-      <c r="I74" s="24"/>
-      <c r="J74" s="115"/>
-      <c r="K74" s="117"/>
-      <c r="L74" s="25"/>
+      <c r="B74" s="169"/>
+      <c r="C74" s="182"/>
+      <c r="D74" s="171"/>
+      <c r="E74" s="172"/>
+      <c r="F74" s="172"/>
+      <c r="G74" s="172"/>
+      <c r="H74" s="172"/>
+      <c r="I74" s="171"/>
+      <c r="J74" s="172"/>
+      <c r="K74" s="172"/>
+      <c r="L74" s="173"/>
     </row>
     <row r="75" spans="2:12" ht="52.8">
-      <c r="B75" s="122">
+      <c r="B75" s="169">
         <v>9</v>
       </c>
-      <c r="C75" s="124" t="s">
-        <v>168</v>
-      </c>
-      <c r="D75" s="119"/>
-      <c r="E75" s="116"/>
-      <c r="F75" s="116"/>
-      <c r="G75" s="116"/>
-      <c r="H75" s="116"/>
-      <c r="I75" s="119"/>
-      <c r="J75" s="120"/>
-      <c r="K75" s="116"/>
-      <c r="L75" s="25"/>
+      <c r="C75" s="170" t="s">
+        <v>165</v>
+      </c>
+      <c r="D75" s="171"/>
+      <c r="E75" s="172"/>
+      <c r="F75" s="172"/>
+      <c r="G75" s="172"/>
+      <c r="H75" s="172"/>
+      <c r="I75" s="171"/>
+      <c r="J75" s="172"/>
+      <c r="K75" s="172"/>
+      <c r="L75" s="173"/>
     </row>
     <row r="76" spans="2:12">
-      <c r="B76" s="123"/>
-      <c r="C76" s="118" t="str">
+      <c r="B76" s="169"/>
+      <c r="C76" s="182" t="str">
         <f>C19</f>
         <v>-at toilet of ward</v>
       </c>
-      <c r="D76" s="139">
+      <c r="D76" s="171">
         <v>1</v>
       </c>
-      <c r="E76" s="140">
+      <c r="E76" s="172">
         <f>5.33/3.281</f>
         <v>1.6245047241694606</v>
       </c>
-      <c r="F76" s="140">
+      <c r="F76" s="172">
         <v>0.23</v>
       </c>
-      <c r="G76" s="140">
+      <c r="G76" s="172">
         <f>8.75/3.281</f>
         <v>2.6668698567509903</v>
       </c>
-      <c r="H76" s="140">
+      <c r="H76" s="172">
         <f>D76*E76*F76*G76</f>
         <v>0.99643881663853684</v>
       </c>
-      <c r="I76" s="139"/>
-      <c r="J76" s="119"/>
-      <c r="K76" s="119"/>
-      <c r="L76" s="25"/>
+      <c r="I76" s="171"/>
+      <c r="J76" s="171"/>
+      <c r="K76" s="171"/>
+      <c r="L76" s="173"/>
     </row>
     <row r="77" spans="2:12">
-      <c r="B77" s="123"/>
-      <c r="C77" s="118" t="s">
-        <v>149</v>
-      </c>
-      <c r="D77" s="119">
+      <c r="B77" s="169"/>
+      <c r="C77" s="182" t="s">
+        <v>146</v>
+      </c>
+      <c r="D77" s="171">
         <v>-1</v>
       </c>
-      <c r="E77" s="116">
+      <c r="E77" s="172">
         <f>2.5/3.281</f>
         <v>0.76196281621456874</v>
       </c>
-      <c r="F77" s="116">
+      <c r="F77" s="172">
         <v>0.23</v>
       </c>
-      <c r="G77" s="116">
+      <c r="G77" s="172">
         <f>6.5/3.281</f>
         <v>1.9811033221578787</v>
       </c>
-      <c r="H77" s="140">
+      <c r="H77" s="172">
         <f>D77*E77*F77*G77</f>
         <v>-0.34719122530959468</v>
       </c>
-      <c r="I77" s="119"/>
-      <c r="J77" s="119"/>
-      <c r="K77" s="119"/>
-      <c r="L77" s="25"/>
+      <c r="I77" s="171"/>
+      <c r="J77" s="171"/>
+      <c r="K77" s="171"/>
+      <c r="L77" s="173"/>
     </row>
     <row r="78" spans="2:12">
-      <c r="B78" s="123"/>
-      <c r="C78" s="118"/>
-      <c r="D78" s="119"/>
-      <c r="E78" s="116"/>
-      <c r="F78" s="116"/>
-      <c r="G78" s="127"/>
-      <c r="H78" s="116">
+      <c r="B78" s="169"/>
+      <c r="C78" s="182"/>
+      <c r="D78" s="171"/>
+      <c r="E78" s="172"/>
+      <c r="F78" s="172"/>
+      <c r="G78" s="177"/>
+      <c r="H78" s="172">
         <f>SUM(H76:H77)</f>
         <v>0.64924759132894216</v>
       </c>
-      <c r="I78" s="119" t="s">
+      <c r="I78" s="171" t="s">
         <v>35</v>
       </c>
-      <c r="J78" s="116">
+      <c r="J78" s="172">
         <v>14491.84</v>
       </c>
-      <c r="K78" s="116">
+      <c r="K78" s="172">
         <f>H78*J78</f>
         <v>9408.7922139244165</v>
       </c>
-      <c r="L78" s="25"/>
+      <c r="L78" s="173"/>
     </row>
     <row r="79" spans="2:12">
-      <c r="B79" s="123"/>
-      <c r="C79" s="118" t="s">
+      <c r="B79" s="169"/>
+      <c r="C79" s="182" t="s">
         <v>29</v>
       </c>
-      <c r="D79" s="119"/>
-      <c r="E79" s="116"/>
-      <c r="F79" s="116"/>
-      <c r="G79" s="127"/>
-      <c r="H79" s="119"/>
-      <c r="I79" s="119"/>
-      <c r="J79" s="116"/>
-      <c r="K79" s="116">
+      <c r="D79" s="171"/>
+      <c r="E79" s="172"/>
+      <c r="F79" s="172"/>
+      <c r="G79" s="177"/>
+      <c r="H79" s="171"/>
+      <c r="I79" s="171"/>
+      <c r="J79" s="172"/>
+      <c r="K79" s="172">
         <f>0.13*H78*912.17</f>
         <v>76.989142799727745</v>
       </c>
-      <c r="L79" s="25"/>
+      <c r="L79" s="173"/>
     </row>
     <row r="80" spans="2:12">
-      <c r="B80" s="123"/>
-      <c r="C80" s="118" t="s">
+      <c r="B80" s="169"/>
+      <c r="C80" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="D80" s="119"/>
-      <c r="E80" s="119"/>
-      <c r="F80" s="119"/>
-      <c r="G80" s="119"/>
-      <c r="H80" s="119"/>
-      <c r="I80" s="119"/>
-      <c r="J80" s="116"/>
-      <c r="K80" s="116">
+      <c r="D80" s="171"/>
+      <c r="E80" s="171"/>
+      <c r="F80" s="171"/>
+      <c r="G80" s="171"/>
+      <c r="H80" s="171"/>
+      <c r="I80" s="171"/>
+      <c r="J80" s="172"/>
+      <c r="K80" s="172">
         <f>0.13*H78*953.37</f>
         <v>80.466512898885568</v>
       </c>
-      <c r="L80" s="25"/>
+      <c r="L80" s="173"/>
     </row>
     <row r="81" spans="2:12">
-      <c r="B81" s="123"/>
-      <c r="C81" s="118" t="s">
+      <c r="B81" s="169"/>
+      <c r="C81" s="182" t="s">
         <v>38</v>
       </c>
-      <c r="D81" s="119"/>
-      <c r="E81" s="116"/>
-      <c r="F81" s="116"/>
-      <c r="G81" s="127"/>
-      <c r="H81" s="116"/>
-      <c r="I81" s="119"/>
-      <c r="J81" s="116"/>
-      <c r="K81" s="116">
+      <c r="D81" s="171"/>
+      <c r="E81" s="172"/>
+      <c r="F81" s="172"/>
+      <c r="G81" s="177"/>
+      <c r="H81" s="172"/>
+      <c r="I81" s="171"/>
+      <c r="J81" s="172"/>
+      <c r="K81" s="172">
         <f>0.13*H78*8481.2</f>
         <v>715.83182730527324</v>
       </c>
-      <c r="L81" s="25"/>
+      <c r="L81" s="173"/>
     </row>
     <row r="82" spans="2:12">
-      <c r="B82" s="80"/>
-      <c r="C82" s="20"/>
-      <c r="D82" s="24"/>
-      <c r="E82" s="70"/>
-      <c r="F82" s="70"/>
-      <c r="G82" s="71"/>
-      <c r="H82" s="70"/>
-      <c r="I82" s="24"/>
-      <c r="J82" s="73"/>
-      <c r="K82" s="73"/>
-      <c r="L82" s="25"/>
+      <c r="B82" s="169"/>
+      <c r="C82" s="176"/>
+      <c r="D82" s="171"/>
+      <c r="E82" s="172"/>
+      <c r="F82" s="172"/>
+      <c r="G82" s="177"/>
+      <c r="H82" s="172"/>
+      <c r="I82" s="171"/>
+      <c r="J82" s="172"/>
+      <c r="K82" s="172"/>
+      <c r="L82" s="173"/>
     </row>
     <row r="83" spans="2:12" ht="35.1" customHeight="1">
-      <c r="B83" s="123">
+      <c r="B83" s="169">
         <v>10</v>
       </c>
-      <c r="C83" s="124" t="s">
+      <c r="C83" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="D83" s="119"/>
-      <c r="E83" s="119"/>
-      <c r="F83" s="119"/>
-      <c r="G83" s="119"/>
-      <c r="H83" s="116"/>
-      <c r="I83" s="119"/>
-      <c r="J83" s="116"/>
-      <c r="K83" s="116"/>
-      <c r="L83" s="25"/>
+      <c r="D83" s="171"/>
+      <c r="E83" s="171"/>
+      <c r="F83" s="171"/>
+      <c r="G83" s="171"/>
+      <c r="H83" s="172"/>
+      <c r="I83" s="171"/>
+      <c r="J83" s="172"/>
+      <c r="K83" s="172"/>
+      <c r="L83" s="173"/>
     </row>
     <row r="84" spans="2:12">
-      <c r="B84" s="123"/>
-      <c r="C84" s="118" t="s">
-        <v>151</v>
-      </c>
-      <c r="D84" s="119">
+      <c r="B84" s="169"/>
+      <c r="C84" s="182" t="s">
+        <v>148</v>
+      </c>
+      <c r="D84" s="171">
         <v>2</v>
       </c>
-      <c r="E84" s="119">
+      <c r="E84" s="171">
         <f>15.42/3.281</f>
         <v>4.6997866504114594</v>
       </c>
-      <c r="F84" s="119"/>
-      <c r="G84" s="119">
+      <c r="F84" s="171"/>
+      <c r="G84" s="171">
         <f>5.25/3.281</f>
         <v>1.6001219140505942</v>
       </c>
-      <c r="H84" s="116">
+      <c r="H84" s="172">
         <f>D84*E84*G84</f>
         <v>15.040463221371631</v>
       </c>
-      <c r="I84" s="119"/>
-      <c r="J84" s="116"/>
-      <c r="K84" s="116"/>
-      <c r="L84" s="25"/>
+      <c r="I84" s="171"/>
+      <c r="J84" s="172"/>
+      <c r="K84" s="172"/>
+      <c r="L84" s="173"/>
     </row>
     <row r="85" spans="2:12">
-      <c r="B85" s="123"/>
-      <c r="C85" s="125"/>
-      <c r="D85" s="119">
+      <c r="B85" s="169"/>
+      <c r="C85" s="186"/>
+      <c r="D85" s="171">
         <v>2</v>
       </c>
-      <c r="E85" s="119">
+      <c r="E85" s="171">
         <f>10/3.281</f>
         <v>3.047851264858275</v>
       </c>
-      <c r="F85" s="119"/>
-      <c r="G85" s="119">
+      <c r="F85" s="171"/>
+      <c r="G85" s="171">
         <f>5.25/3.281</f>
         <v>1.6001219140505942</v>
       </c>
-      <c r="H85" s="116">
+      <c r="H85" s="172">
         <f>D85*E85*G85</f>
         <v>9.7538671993330954</v>
       </c>
-      <c r="I85" s="119"/>
-      <c r="J85" s="141"/>
-      <c r="K85" s="116"/>
-      <c r="L85" s="25"/>
-    </row>
-    <row r="86" spans="2:12" s="121" customFormat="1">
-      <c r="B86" s="123"/>
-      <c r="C86" s="137" t="str">
-        <f>C76</f>
+      <c r="I85" s="171"/>
+      <c r="J85" s="187"/>
+      <c r="K85" s="172"/>
+      <c r="L85" s="173"/>
+    </row>
+    <row r="86" spans="2:12">
+      <c r="B86" s="169"/>
+      <c r="C86" s="175" t="str">
+        <f t="shared" ref="C86:E87" si="10">C76</f>
         <v>-at toilet of ward</v>
       </c>
-      <c r="D86" s="119">
-        <f>D76</f>
+      <c r="D86" s="171">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="E86" s="119">
-        <f>E76</f>
+      <c r="E86" s="171">
+        <f t="shared" si="10"/>
         <v>1.6245047241694606</v>
       </c>
-      <c r="F86" s="119"/>
-      <c r="G86" s="119">
+      <c r="F86" s="171"/>
+      <c r="G86" s="171">
         <f>G76-4/3.281</f>
         <v>1.4477293508076805</v>
       </c>
-      <c r="H86" s="116">
+      <c r="H86" s="172">
         <f>D86*E86*G86</f>
         <v>2.3518431697058633</v>
       </c>
-      <c r="I86" s="119"/>
-      <c r="J86" s="141"/>
-      <c r="K86" s="116"/>
-      <c r="L86" s="25"/>
-    </row>
-    <row r="87" spans="2:12" s="121" customFormat="1">
-      <c r="B87" s="123"/>
-      <c r="C87" s="137" t="str">
-        <f>C77</f>
+      <c r="I86" s="171"/>
+      <c r="J86" s="187"/>
+      <c r="K86" s="172"/>
+      <c r="L86" s="173"/>
+    </row>
+    <row r="87" spans="2:12">
+      <c r="B87" s="169"/>
+      <c r="C87" s="175" t="str">
+        <f t="shared" si="10"/>
         <v>-deduction for opening</v>
       </c>
-      <c r="D87" s="119">
-        <f>D77</f>
+      <c r="D87" s="171">
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
-      <c r="E87" s="119">
-        <f>E77</f>
+      <c r="E87" s="171">
+        <f t="shared" si="10"/>
         <v>0.76196281621456874</v>
       </c>
-      <c r="F87" s="119"/>
-      <c r="G87" s="119">
+      <c r="F87" s="171"/>
+      <c r="G87" s="171">
         <f>G77</f>
         <v>1.9811033221578787</v>
       </c>
-      <c r="H87" s="116">
+      <c r="H87" s="172">
         <f>D87*E87*G87</f>
         <v>-1.5095270665634553</v>
       </c>
-      <c r="I87" s="119"/>
-      <c r="J87" s="141"/>
-      <c r="K87" s="116"/>
-      <c r="L87" s="25"/>
+      <c r="I87" s="171"/>
+      <c r="J87" s="187"/>
+      <c r="K87" s="172"/>
+      <c r="L87" s="173"/>
     </row>
     <row r="88" spans="2:12">
-      <c r="B88" s="123"/>
-      <c r="C88" s="125"/>
-      <c r="D88" s="119"/>
-      <c r="E88" s="116"/>
-      <c r="F88" s="116"/>
-      <c r="G88" s="127"/>
-      <c r="H88" s="116">
+      <c r="B88" s="169"/>
+      <c r="C88" s="186"/>
+      <c r="D88" s="171"/>
+      <c r="E88" s="172"/>
+      <c r="F88" s="172"/>
+      <c r="G88" s="177"/>
+      <c r="H88" s="172">
         <f>SUM(H84:H87)</f>
         <v>25.636646523847133</v>
       </c>
-      <c r="I88" s="119" t="s">
+      <c r="I88" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="J88" s="116">
+      <c r="J88" s="172">
         <v>415.5</v>
       </c>
-      <c r="K88" s="116">
+      <c r="K88" s="172">
         <f>H88*J88</f>
         <v>10652.026630658484</v>
       </c>
-      <c r="L88" s="25"/>
+      <c r="L88" s="173"/>
     </row>
     <row r="89" spans="2:12">
-      <c r="B89" s="123"/>
-      <c r="C89" s="118" t="s">
+      <c r="B89" s="169"/>
+      <c r="C89" s="182" t="s">
         <v>29</v>
       </c>
-      <c r="D89" s="119"/>
-      <c r="E89" s="116"/>
-      <c r="F89" s="116"/>
-      <c r="G89" s="127"/>
-      <c r="H89" s="116"/>
-      <c r="I89" s="119"/>
-      <c r="J89" s="141"/>
-      <c r="K89" s="116">
+      <c r="D89" s="171"/>
+      <c r="E89" s="172"/>
+      <c r="F89" s="172"/>
+      <c r="G89" s="177"/>
+      <c r="H89" s="172"/>
+      <c r="I89" s="171"/>
+      <c r="J89" s="187"/>
+      <c r="K89" s="172">
         <f>0.13*H88*7010.67/100</f>
         <v>233.64908929094122</v>
       </c>
-      <c r="L89" s="25"/>
+      <c r="L89" s="173"/>
     </row>
     <row r="90" spans="2:12">
-      <c r="B90" s="123"/>
-      <c r="C90" s="118" t="s">
+      <c r="B90" s="169"/>
+      <c r="C90" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="D90" s="119"/>
-      <c r="E90" s="116"/>
-      <c r="F90" s="116"/>
-      <c r="G90" s="127"/>
-      <c r="H90" s="116"/>
-      <c r="I90" s="119"/>
-      <c r="J90" s="141"/>
-      <c r="K90" s="116">
+      <c r="D90" s="171"/>
+      <c r="E90" s="172"/>
+      <c r="F90" s="172"/>
+      <c r="G90" s="177"/>
+      <c r="H90" s="172"/>
+      <c r="I90" s="171"/>
+      <c r="J90" s="187"/>
+      <c r="K90" s="172">
         <f>0.13*H88*4639.73/100</f>
         <v>154.63125336891602</v>
       </c>
-      <c r="L90" s="25"/>
-    </row>
-    <row r="91" spans="2:12" s="121" customFormat="1">
-      <c r="B91" s="123"/>
-      <c r="C91" s="118"/>
-      <c r="D91" s="119"/>
-      <c r="E91" s="116"/>
-      <c r="F91" s="116"/>
-      <c r="G91" s="127"/>
-      <c r="H91" s="116"/>
-      <c r="I91" s="119"/>
-      <c r="J91" s="141"/>
-      <c r="K91" s="116"/>
-      <c r="L91" s="25"/>
-    </row>
-    <row r="92" spans="2:12" s="121" customFormat="1" ht="78.599999999999994">
-      <c r="B92" s="123">
+      <c r="L90" s="173"/>
+    </row>
+    <row r="91" spans="2:12">
+      <c r="B91" s="169"/>
+      <c r="C91" s="182"/>
+      <c r="D91" s="171"/>
+      <c r="E91" s="172"/>
+      <c r="F91" s="172"/>
+      <c r="G91" s="177"/>
+      <c r="H91" s="172"/>
+      <c r="I91" s="171"/>
+      <c r="J91" s="187"/>
+      <c r="K91" s="172"/>
+      <c r="L91" s="173"/>
+    </row>
+    <row r="92" spans="2:12" ht="65.400000000000006">
+      <c r="B92" s="169">
         <v>11</v>
       </c>
-      <c r="C92" s="169" t="s">
-        <v>153</v>
-      </c>
-      <c r="D92" s="169"/>
-      <c r="E92" s="116"/>
-      <c r="F92" s="116"/>
-      <c r="G92" s="127"/>
-      <c r="H92" s="116"/>
-      <c r="I92" s="119"/>
-      <c r="J92" s="141"/>
-      <c r="K92" s="116"/>
-      <c r="L92" s="25"/>
-    </row>
-    <row r="93" spans="2:12" s="121" customFormat="1">
-      <c r="B93" s="123"/>
-      <c r="C93" s="118" t="str">
+      <c r="C92" s="155" t="s">
+        <v>150</v>
+      </c>
+      <c r="D92" s="155"/>
+      <c r="E92" s="172"/>
+      <c r="F92" s="172"/>
+      <c r="G92" s="177"/>
+      <c r="H92" s="172"/>
+      <c r="I92" s="171"/>
+      <c r="J92" s="187"/>
+      <c r="K92" s="172"/>
+      <c r="L92" s="173"/>
+    </row>
+    <row r="93" spans="2:12">
+      <c r="B93" s="169"/>
+      <c r="C93" s="182" t="str">
         <f>C86</f>
         <v>-at toilet of ward</v>
       </c>
-      <c r="D93" s="119">
+      <c r="D93" s="171">
         <v>1</v>
       </c>
-      <c r="E93" s="116">
+      <c r="E93" s="172">
         <f>E86-2.5/3.281</f>
         <v>0.86254190795489183</v>
       </c>
-      <c r="F93" s="116"/>
-      <c r="G93" s="127">
+      <c r="F93" s="172"/>
+      <c r="G93" s="177">
         <f>4/3.281</f>
         <v>1.2191405059433098</v>
       </c>
-      <c r="H93" s="116">
+      <c r="H93" s="172">
         <f>D93*E93*G93</f>
         <v>1.0515597780614345</v>
       </c>
-      <c r="I93" s="119"/>
-      <c r="J93" s="141"/>
-      <c r="K93" s="116"/>
-      <c r="L93" s="25"/>
-    </row>
-    <row r="94" spans="2:12" s="121" customFormat="1">
-      <c r="B94" s="123"/>
-      <c r="C94" s="125"/>
-      <c r="D94" s="119"/>
-      <c r="E94" s="116"/>
-      <c r="F94" s="116"/>
-      <c r="G94" s="127"/>
-      <c r="H94" s="116">
+      <c r="I93" s="171"/>
+      <c r="J93" s="187"/>
+      <c r="K93" s="172"/>
+      <c r="L93" s="173"/>
+    </row>
+    <row r="94" spans="2:12">
+      <c r="B94" s="169"/>
+      <c r="C94" s="186"/>
+      <c r="D94" s="171"/>
+      <c r="E94" s="172"/>
+      <c r="F94" s="172"/>
+      <c r="G94" s="177"/>
+      <c r="H94" s="172">
         <f>SUM(H93)</f>
         <v>1.0515597780614345</v>
       </c>
-      <c r="I94" s="119" t="s">
+      <c r="I94" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="J94" s="116">
+      <c r="J94" s="172">
         <v>415.5</v>
       </c>
-      <c r="K94" s="116">
+      <c r="K94" s="172">
         <f>H94*J94</f>
         <v>436.92308778452605</v>
       </c>
-      <c r="L94" s="25"/>
-    </row>
-    <row r="95" spans="2:12" s="121" customFormat="1">
-      <c r="B95" s="123"/>
-      <c r="C95" s="118" t="s">
-        <v>154</v>
-      </c>
-      <c r="D95" s="119"/>
-      <c r="E95" s="116"/>
-      <c r="F95" s="116"/>
-      <c r="G95" s="127"/>
-      <c r="H95" s="116"/>
-      <c r="I95" s="119"/>
-      <c r="J95" s="141"/>
-      <c r="K95" s="116">
+      <c r="L94" s="173"/>
+    </row>
+    <row r="95" spans="2:12">
+      <c r="B95" s="169"/>
+      <c r="C95" s="182" t="s">
+        <v>151</v>
+      </c>
+      <c r="D95" s="171"/>
+      <c r="E95" s="172"/>
+      <c r="F95" s="172"/>
+      <c r="G95" s="177"/>
+      <c r="H95" s="172"/>
+      <c r="I95" s="171"/>
+      <c r="J95" s="187"/>
+      <c r="K95" s="172">
         <f>0.13*H94*6746.52/10</f>
         <v>92.226797960531385</v>
       </c>
-      <c r="L95" s="25"/>
-    </row>
-    <row r="96" spans="2:12" s="121" customFormat="1">
-      <c r="B96" s="123"/>
-      <c r="C96" s="118" t="s">
+      <c r="L95" s="173"/>
+    </row>
+    <row r="96" spans="2:12">
+      <c r="B96" s="169"/>
+      <c r="C96" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="D96" s="119"/>
-      <c r="E96" s="116"/>
-      <c r="F96" s="116"/>
-      <c r="G96" s="127"/>
-      <c r="H96" s="116"/>
-      <c r="I96" s="119"/>
-      <c r="J96" s="141"/>
-      <c r="K96" s="116">
+      <c r="D96" s="171"/>
+      <c r="E96" s="172"/>
+      <c r="F96" s="172"/>
+      <c r="G96" s="177"/>
+      <c r="H96" s="172"/>
+      <c r="I96" s="171"/>
+      <c r="J96" s="187"/>
+      <c r="K96" s="172">
         <f>0.13*H94*483.04/10</f>
         <v>6.6032906575323391</v>
       </c>
-      <c r="L96" s="25"/>
-    </row>
-    <row r="97" spans="2:12" s="121" customFormat="1">
-      <c r="B97" s="123"/>
-      <c r="C97" s="118" t="s">
+      <c r="L96" s="173"/>
+    </row>
+    <row r="97" spans="2:12">
+      <c r="B97" s="169"/>
+      <c r="C97" s="182" t="s">
         <v>29</v>
       </c>
-      <c r="D97" s="119"/>
-      <c r="E97" s="116"/>
-      <c r="F97" s="116"/>
-      <c r="G97" s="127"/>
-      <c r="H97" s="116"/>
-      <c r="I97" s="119"/>
-      <c r="J97" s="141"/>
-      <c r="K97" s="116">
+      <c r="D97" s="171"/>
+      <c r="E97" s="172"/>
+      <c r="F97" s="172"/>
+      <c r="G97" s="177"/>
+      <c r="H97" s="172"/>
+      <c r="I97" s="171"/>
+      <c r="J97" s="187"/>
+      <c r="K97" s="172">
         <f>0.13*H94*729.73/10</f>
         <v>9.9756113189820184</v>
       </c>
-      <c r="L97" s="25"/>
-    </row>
-    <row r="98" spans="2:12" s="121" customFormat="1">
-      <c r="B98" s="123"/>
-      <c r="C98" s="118" t="s">
-        <v>155</v>
-      </c>
-      <c r="D98" s="119"/>
-      <c r="E98" s="116"/>
-      <c r="F98" s="116"/>
-      <c r="G98" s="127"/>
-      <c r="H98" s="116"/>
-      <c r="I98" s="119"/>
-      <c r="J98" s="141"/>
-      <c r="K98" s="116">
+      <c r="L97" s="173"/>
+    </row>
+    <row r="98" spans="2:12">
+      <c r="B98" s="169"/>
+      <c r="C98" s="182" t="s">
+        <v>152</v>
+      </c>
+      <c r="D98" s="171"/>
+      <c r="E98" s="172"/>
+      <c r="F98" s="172"/>
+      <c r="G98" s="177"/>
+      <c r="H98" s="172"/>
+      <c r="I98" s="171"/>
+      <c r="J98" s="187"/>
+      <c r="K98" s="172">
         <f>0.13*H94*100.06/10</f>
         <v>1.3678479281067528</v>
       </c>
-      <c r="L98" s="25"/>
-    </row>
-    <row r="99" spans="2:12" s="121" customFormat="1">
-      <c r="B99" s="123"/>
-      <c r="C99" s="118"/>
-      <c r="D99" s="119"/>
-      <c r="E99" s="116"/>
-      <c r="F99" s="116"/>
-      <c r="G99" s="127"/>
-      <c r="H99" s="116"/>
-      <c r="I99" s="119"/>
-      <c r="J99" s="141"/>
-      <c r="K99" s="116"/>
-      <c r="L99" s="25"/>
-    </row>
-    <row r="100" spans="2:12" s="121" customFormat="1" ht="34.799999999999997">
-      <c r="B100" s="123">
+      <c r="L98" s="173"/>
+    </row>
+    <row r="99" spans="2:12">
+      <c r="B99" s="169"/>
+      <c r="C99" s="182"/>
+      <c r="D99" s="171"/>
+      <c r="E99" s="172"/>
+      <c r="F99" s="172"/>
+      <c r="G99" s="177"/>
+      <c r="H99" s="172"/>
+      <c r="I99" s="171"/>
+      <c r="J99" s="187"/>
+      <c r="K99" s="172"/>
+      <c r="L99" s="173"/>
+    </row>
+    <row r="100" spans="2:12" ht="34.799999999999997">
+      <c r="B100" s="169">
         <v>12</v>
       </c>
-      <c r="C100" s="169" t="s">
-        <v>169</v>
-      </c>
-      <c r="D100" s="119"/>
-      <c r="E100" s="116"/>
-      <c r="F100" s="116"/>
-      <c r="G100" s="127"/>
-      <c r="H100" s="116"/>
-      <c r="I100" s="119"/>
-      <c r="J100" s="141"/>
-      <c r="K100" s="116"/>
-      <c r="L100" s="25"/>
-    </row>
-    <row r="101" spans="2:12" s="121" customFormat="1">
-      <c r="B101" s="123"/>
-      <c r="C101" s="118" t="str">
+      <c r="C100" s="155" t="s">
+        <v>166</v>
+      </c>
+      <c r="D100" s="171"/>
+      <c r="E100" s="172"/>
+      <c r="F100" s="172"/>
+      <c r="G100" s="177"/>
+      <c r="H100" s="172"/>
+      <c r="I100" s="171"/>
+      <c r="J100" s="187"/>
+      <c r="K100" s="172"/>
+      <c r="L100" s="173"/>
+    </row>
+    <row r="101" spans="2:12">
+      <c r="B101" s="169"/>
+      <c r="C101" s="182" t="str">
         <f>C93</f>
         <v>-at toilet of ward</v>
       </c>
-      <c r="D101" s="119">
+      <c r="D101" s="171">
         <f>D93</f>
         <v>1</v>
       </c>
-      <c r="E101" s="119">
+      <c r="E101" s="171">
         <f>E86</f>
         <v>1.6245047241694606</v>
       </c>
-      <c r="F101" s="119"/>
-      <c r="G101" s="116">
+      <c r="F101" s="171"/>
+      <c r="G101" s="172">
         <f>8/3.281</f>
         <v>2.4382810118866196</v>
       </c>
-      <c r="H101" s="119">
+      <c r="H101" s="171">
         <f>PRODUCT(D101:G101)</f>
         <v>3.9609990226625063</v>
       </c>
-      <c r="I101" s="127"/>
-      <c r="J101" s="116"/>
-      <c r="K101" s="119"/>
-      <c r="L101" s="25"/>
-    </row>
-    <row r="102" spans="2:12" s="121" customFormat="1">
-      <c r="B102" s="123"/>
-      <c r="C102" s="118" t="str">
+      <c r="I101" s="177"/>
+      <c r="J101" s="172"/>
+      <c r="K101" s="171"/>
+      <c r="L101" s="173"/>
+    </row>
+    <row r="102" spans="2:12">
+      <c r="B102" s="169"/>
+      <c r="C102" s="182" t="str">
         <f>C87</f>
         <v>-deduction for opening</v>
       </c>
-      <c r="D102" s="119">
+      <c r="D102" s="171">
         <f>D87</f>
         <v>-1</v>
       </c>
-      <c r="E102" s="119">
+      <c r="E102" s="171">
         <f>E87</f>
         <v>0.76196281621456874</v>
       </c>
-      <c r="F102" s="119"/>
-      <c r="G102" s="116">
+      <c r="F102" s="171"/>
+      <c r="G102" s="172">
         <f>G87</f>
         <v>1.9811033221578787</v>
       </c>
-      <c r="H102" s="119">
+      <c r="H102" s="171">
         <f>PRODUCT(D102:G102)</f>
         <v>-1.5095270665634553</v>
       </c>
-      <c r="I102" s="127"/>
-      <c r="J102" s="116"/>
-      <c r="K102" s="119"/>
-      <c r="L102" s="25"/>
-    </row>
-    <row r="103" spans="2:12" s="121" customFormat="1">
-      <c r="B103" s="123"/>
-      <c r="C103" s="118"/>
-      <c r="D103" s="119"/>
-      <c r="E103" s="119"/>
-      <c r="F103" s="119"/>
-      <c r="G103" s="116"/>
-      <c r="H103" s="119">
+      <c r="I102" s="177"/>
+      <c r="J102" s="172"/>
+      <c r="K102" s="171"/>
+      <c r="L102" s="173"/>
+    </row>
+    <row r="103" spans="2:12">
+      <c r="B103" s="169"/>
+      <c r="C103" s="182"/>
+      <c r="D103" s="171"/>
+      <c r="E103" s="171"/>
+      <c r="F103" s="171"/>
+      <c r="G103" s="172"/>
+      <c r="H103" s="171">
         <f>SUM(H101:H102)</f>
         <v>2.4514719560990512</v>
       </c>
-      <c r="I103" s="127" t="s">
+      <c r="I103" s="177" t="s">
         <v>23</v>
       </c>
-      <c r="J103" s="116">
+      <c r="J103" s="172">
         <v>57.76</v>
       </c>
-      <c r="K103" s="119">
-        <f t="shared" ref="K103" si="10">H103*J103</f>
+      <c r="K103" s="171">
+        <f t="shared" ref="K103" si="11">H103*J103</f>
         <v>141.59702018428121</v>
       </c>
-      <c r="L103" s="25"/>
-    </row>
-    <row r="104" spans="2:12" s="121" customFormat="1">
-      <c r="B104" s="123"/>
-      <c r="C104" s="118" t="s">
+      <c r="L103" s="173"/>
+    </row>
+    <row r="104" spans="2:12">
+      <c r="B104" s="169"/>
+      <c r="C104" s="182" t="s">
         <v>29</v>
       </c>
-      <c r="D104" s="119"/>
-      <c r="E104" s="119"/>
-      <c r="F104" s="119"/>
-      <c r="G104" s="127"/>
-      <c r="H104" s="119"/>
-      <c r="I104" s="127"/>
-      <c r="J104" s="116"/>
-      <c r="K104" s="142">
+      <c r="D104" s="171"/>
+      <c r="E104" s="171"/>
+      <c r="F104" s="171"/>
+      <c r="G104" s="177"/>
+      <c r="H104" s="171"/>
+      <c r="I104" s="177"/>
+      <c r="J104" s="172"/>
+      <c r="K104" s="188">
         <f>0.13*H103*20.7</f>
         <v>6.5969110338625461</v>
       </c>
-      <c r="L104" s="25"/>
+      <c r="L104" s="173"/>
     </row>
     <row r="105" spans="2:12">
-      <c r="B105" s="81"/>
-      <c r="C105" s="19"/>
-      <c r="D105" s="72"/>
-      <c r="E105" s="70"/>
-      <c r="F105" s="70"/>
-      <c r="G105" s="71"/>
-      <c r="H105" s="72"/>
-      <c r="I105" s="72"/>
-      <c r="J105" s="72"/>
-      <c r="K105" s="72"/>
-      <c r="L105" s="25"/>
-    </row>
-    <row r="106" spans="2:12" s="121" customFormat="1" ht="34.799999999999997">
-      <c r="B106" s="123">
+      <c r="B105" s="169"/>
+      <c r="C105" s="182"/>
+      <c r="D105" s="171"/>
+      <c r="E105" s="172"/>
+      <c r="F105" s="172"/>
+      <c r="G105" s="177"/>
+      <c r="H105" s="171"/>
+      <c r="I105" s="171"/>
+      <c r="J105" s="171"/>
+      <c r="K105" s="171"/>
+      <c r="L105" s="173"/>
+    </row>
+    <row r="106" spans="2:12" ht="34.799999999999997">
+      <c r="B106" s="169">
         <v>13</v>
       </c>
-      <c r="C106" s="169" t="s">
-        <v>170</v>
-      </c>
-      <c r="D106" s="119"/>
-      <c r="E106" s="116"/>
-      <c r="F106" s="116"/>
-      <c r="G106" s="127"/>
-      <c r="H106" s="116"/>
-      <c r="I106" s="119"/>
-      <c r="J106" s="141"/>
-      <c r="K106" s="116"/>
-      <c r="L106" s="25"/>
-    </row>
-    <row r="107" spans="2:12" s="121" customFormat="1">
-      <c r="B107" s="123"/>
-      <c r="C107" s="118" t="str">
+      <c r="C106" s="155" t="s">
+        <v>167</v>
+      </c>
+      <c r="D106" s="171"/>
+      <c r="E106" s="172"/>
+      <c r="F106" s="172"/>
+      <c r="G106" s="177"/>
+      <c r="H106" s="172"/>
+      <c r="I106" s="171"/>
+      <c r="J106" s="187"/>
+      <c r="K106" s="172"/>
+      <c r="L106" s="173"/>
+    </row>
+    <row r="107" spans="2:12">
+      <c r="B107" s="169"/>
+      <c r="C107" s="182" t="str">
         <f>C101</f>
         <v>-at toilet of ward</v>
       </c>
-      <c r="D107" s="119">
+      <c r="D107" s="171">
         <f>D101</f>
         <v>1</v>
       </c>
-      <c r="E107" s="119">
+      <c r="E107" s="171">
         <f>E101</f>
         <v>1.6245047241694606</v>
       </c>
-      <c r="F107" s="119"/>
-      <c r="G107" s="116">
+      <c r="F107" s="171"/>
+      <c r="G107" s="172">
         <f>G101</f>
         <v>2.4382810118866196</v>
       </c>
-      <c r="H107" s="119">
+      <c r="H107" s="171">
         <f>PRODUCT(D107:G107)</f>
         <v>3.9609990226625063</v>
       </c>
-      <c r="I107" s="127"/>
-      <c r="J107" s="116"/>
-      <c r="K107" s="119"/>
-      <c r="L107" s="25"/>
-    </row>
-    <row r="108" spans="2:12" s="121" customFormat="1">
-      <c r="B108" s="123"/>
-      <c r="C108" s="118" t="str">
+      <c r="I107" s="177"/>
+      <c r="J107" s="172"/>
+      <c r="K107" s="171"/>
+      <c r="L107" s="173"/>
+    </row>
+    <row r="108" spans="2:12">
+      <c r="B108" s="169"/>
+      <c r="C108" s="182" t="str">
         <f>C102</f>
         <v>-deduction for opening</v>
       </c>
-      <c r="D108" s="119">
+      <c r="D108" s="171">
         <f>D102</f>
         <v>-1</v>
       </c>
-      <c r="E108" s="119">
+      <c r="E108" s="171">
         <f>E93</f>
         <v>0.86254190795489183</v>
       </c>
-      <c r="F108" s="119"/>
-      <c r="G108" s="116">
+      <c r="F108" s="171"/>
+      <c r="G108" s="172">
         <f>G93</f>
         <v>1.2191405059433098</v>
       </c>
-      <c r="H108" s="119">
+      <c r="H108" s="171">
         <f>PRODUCT(D108:G108)</f>
         <v>-1.0515597780614345</v>
       </c>
-      <c r="I108" s="127"/>
-      <c r="J108" s="116"/>
-      <c r="K108" s="119"/>
-      <c r="L108" s="25"/>
-    </row>
-    <row r="109" spans="2:12" s="121" customFormat="1">
-      <c r="B109" s="123"/>
-      <c r="C109" s="118"/>
-      <c r="D109" s="119">
+      <c r="I108" s="177"/>
+      <c r="J108" s="172"/>
+      <c r="K108" s="171"/>
+      <c r="L108" s="173"/>
+    </row>
+    <row r="109" spans="2:12">
+      <c r="B109" s="169"/>
+      <c r="C109" s="182"/>
+      <c r="D109" s="171">
         <v>-1</v>
       </c>
-      <c r="E109" s="119">
+      <c r="E109" s="171">
         <f>2.5/3.81</f>
         <v>0.65616797900262469</v>
       </c>
-      <c r="F109" s="119"/>
-      <c r="G109" s="116">
+      <c r="F109" s="171"/>
+      <c r="G109" s="172">
         <f>(6.5-4)/3.281</f>
         <v>0.76196281621456874</v>
       </c>
-      <c r="H109" s="119">
+      <c r="H109" s="171">
         <f>PRODUCT(D109:G109)</f>
         <v>-0.49997560119066192</v>
       </c>
-      <c r="I109" s="127"/>
-      <c r="J109" s="116"/>
-      <c r="K109" s="119"/>
-      <c r="L109" s="25"/>
-    </row>
-    <row r="110" spans="2:12" s="121" customFormat="1">
-      <c r="B110" s="123"/>
-      <c r="C110" s="118"/>
-      <c r="D110" s="119"/>
-      <c r="E110" s="119"/>
-      <c r="F110" s="119"/>
-      <c r="G110" s="116"/>
-      <c r="H110" s="119">
+      <c r="I109" s="177"/>
+      <c r="J109" s="172"/>
+      <c r="K109" s="171"/>
+      <c r="L109" s="173"/>
+    </row>
+    <row r="110" spans="2:12">
+      <c r="B110" s="169"/>
+      <c r="C110" s="182"/>
+      <c r="D110" s="171"/>
+      <c r="E110" s="171"/>
+      <c r="F110" s="171"/>
+      <c r="G110" s="172"/>
+      <c r="H110" s="171">
         <f>SUM(H107:H109)</f>
         <v>2.40946364341041</v>
       </c>
-      <c r="I110" s="127" t="s">
+      <c r="I110" s="177" t="s">
         <v>23</v>
       </c>
-      <c r="J110" s="116">
+      <c r="J110" s="172">
         <v>334.57</v>
       </c>
-      <c r="K110" s="119">
-        <f t="shared" ref="K110" si="11">H110*J110</f>
+      <c r="K110" s="171">
+        <f t="shared" ref="K110" si="12">H110*J110</f>
         <v>806.13425117582085</v>
       </c>
-      <c r="L110" s="25"/>
-    </row>
-    <row r="111" spans="2:12" s="121" customFormat="1">
-      <c r="B111" s="123"/>
-      <c r="C111" s="118" t="s">
+      <c r="L110" s="173"/>
+    </row>
+    <row r="111" spans="2:12">
+      <c r="B111" s="169"/>
+      <c r="C111" s="182" t="s">
         <v>29</v>
       </c>
-      <c r="D111" s="119"/>
-      <c r="E111" s="119"/>
-      <c r="F111" s="119"/>
-      <c r="G111" s="127"/>
-      <c r="H111" s="119"/>
-      <c r="I111" s="127"/>
-      <c r="J111" s="116"/>
-      <c r="K111" s="142">
+      <c r="D111" s="171"/>
+      <c r="E111" s="171"/>
+      <c r="F111" s="171"/>
+      <c r="G111" s="177"/>
+      <c r="H111" s="171"/>
+      <c r="I111" s="177"/>
+      <c r="J111" s="172"/>
+      <c r="K111" s="188">
         <f>0.13*H110*110.368</f>
         <v>34.570598841469618</v>
       </c>
-      <c r="L111" s="25"/>
-    </row>
-    <row r="112" spans="2:12" s="121" customFormat="1">
-      <c r="B112" s="81"/>
-      <c r="C112" s="19"/>
-      <c r="D112" s="72"/>
-      <c r="E112" s="70"/>
-      <c r="F112" s="70"/>
-      <c r="G112" s="71"/>
-      <c r="H112" s="72"/>
-      <c r="I112" s="72"/>
-      <c r="J112" s="72"/>
-      <c r="K112" s="72"/>
-      <c r="L112" s="25"/>
-    </row>
-    <row r="113" spans="2:14" ht="35.1" customHeight="1">
-      <c r="B113" s="123">
+      <c r="L111" s="173"/>
+    </row>
+    <row r="112" spans="2:12">
+      <c r="B112" s="169"/>
+      <c r="C112" s="182"/>
+      <c r="D112" s="171"/>
+      <c r="E112" s="172"/>
+      <c r="F112" s="172"/>
+      <c r="G112" s="177"/>
+      <c r="H112" s="171"/>
+      <c r="I112" s="171"/>
+      <c r="J112" s="171"/>
+      <c r="K112" s="171"/>
+      <c r="L112" s="173"/>
+    </row>
+    <row r="113" spans="2:12" ht="35.1" customHeight="1">
+      <c r="B113" s="169">
         <v>14</v>
       </c>
-      <c r="C113" s="124" t="s">
+      <c r="C113" s="170" t="s">
         <v>77</v>
       </c>
-      <c r="D113" s="119"/>
-      <c r="E113" s="119"/>
-      <c r="F113" s="119"/>
-      <c r="G113" s="116"/>
-      <c r="H113" s="119"/>
-      <c r="I113" s="127"/>
-      <c r="J113" s="116"/>
-      <c r="K113" s="119"/>
-      <c r="L113" s="25"/>
-    </row>
-    <row r="114" spans="2:14">
-      <c r="B114" s="123"/>
-      <c r="C114" s="118" t="s">
-        <v>150</v>
-      </c>
-      <c r="D114" s="119">
+      <c r="D113" s="171"/>
+      <c r="E113" s="171"/>
+      <c r="F113" s="171"/>
+      <c r="G113" s="172"/>
+      <c r="H113" s="171"/>
+      <c r="I113" s="177"/>
+      <c r="J113" s="172"/>
+      <c r="K113" s="171"/>
+      <c r="L113" s="173"/>
+    </row>
+    <row r="114" spans="2:12">
+      <c r="B114" s="169"/>
+      <c r="C114" s="182" t="s">
+        <v>147</v>
+      </c>
+      <c r="D114" s="171">
         <v>1</v>
       </c>
-      <c r="E114" s="119">
+      <c r="E114" s="171">
         <f>13.42/3.281</f>
         <v>4.0902163974398045</v>
       </c>
-      <c r="F114" s="119">
+      <c r="F114" s="171">
         <f>8/3.281</f>
         <v>2.4382810118866196</v>
       </c>
-      <c r="G114" s="116"/>
-      <c r="H114" s="119">
+      <c r="G114" s="172"/>
+      <c r="H114" s="171">
         <f>F114*E114*D114</f>
         <v>9.9730969763847703</v>
       </c>
-      <c r="I114" s="127" t="s">
+      <c r="I114" s="177" t="s">
         <v>23</v>
       </c>
-      <c r="J114" s="116">
+      <c r="J114" s="172">
         <v>689.98</v>
       </c>
-      <c r="K114" s="119">
+      <c r="K114" s="171">
         <f>H114*J114</f>
         <v>6881.2374517659637</v>
       </c>
-      <c r="L114" s="25"/>
-    </row>
-    <row r="115" spans="2:14">
-      <c r="B115" s="123"/>
-      <c r="C115" s="118" t="s">
+      <c r="L114" s="173"/>
+    </row>
+    <row r="115" spans="2:12">
+      <c r="B115" s="169"/>
+      <c r="C115" s="182" t="s">
         <v>29</v>
       </c>
-      <c r="D115" s="119"/>
-      <c r="E115" s="119"/>
-      <c r="F115" s="119"/>
-      <c r="G115" s="127"/>
-      <c r="H115" s="119"/>
-      <c r="I115" s="127"/>
-      <c r="J115" s="116"/>
-      <c r="K115" s="142">
+      <c r="D115" s="171"/>
+      <c r="E115" s="171"/>
+      <c r="F115" s="171"/>
+      <c r="G115" s="177"/>
+      <c r="H115" s="171"/>
+      <c r="I115" s="177"/>
+      <c r="J115" s="172"/>
+      <c r="K115" s="188">
         <f>0.13*H114*1694.03/10</f>
         <v>219.63143112176621</v>
       </c>
-      <c r="L115" s="25"/>
-    </row>
-    <row r="116" spans="2:14">
-      <c r="B116" s="123"/>
-      <c r="C116" s="118" t="s">
+      <c r="L115" s="173"/>
+    </row>
+    <row r="116" spans="2:12">
+      <c r="B116" s="169"/>
+      <c r="C116" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="D116" s="119"/>
-      <c r="E116" s="119"/>
-      <c r="F116" s="119"/>
-      <c r="G116" s="127"/>
-      <c r="H116" s="119"/>
-      <c r="I116" s="127"/>
-      <c r="J116" s="116"/>
-      <c r="K116" s="142">
+      <c r="D116" s="171"/>
+      <c r="E116" s="171"/>
+      <c r="F116" s="171"/>
+      <c r="G116" s="177"/>
+      <c r="H116" s="171"/>
+      <c r="I116" s="177"/>
+      <c r="J116" s="172"/>
+      <c r="K116" s="188">
         <f>0.13*H114*572.02/10</f>
         <v>74.162542121611025</v>
       </c>
-      <c r="L116" s="25"/>
-    </row>
-    <row r="117" spans="2:14">
-      <c r="B117" s="123"/>
-      <c r="C117" s="118" t="s">
+      <c r="L116" s="173"/>
+    </row>
+    <row r="117" spans="2:12">
+      <c r="B117" s="169"/>
+      <c r="C117" s="182" t="s">
         <v>31</v>
       </c>
-      <c r="D117" s="119"/>
-      <c r="E117" s="119"/>
-      <c r="F117" s="119"/>
-      <c r="G117" s="127"/>
-      <c r="H117" s="119"/>
-      <c r="I117" s="127"/>
-      <c r="J117" s="116"/>
-      <c r="K117" s="142">
+      <c r="D117" s="171"/>
+      <c r="E117" s="171"/>
+      <c r="F117" s="171"/>
+      <c r="G117" s="177"/>
+      <c r="H117" s="171"/>
+      <c r="I117" s="177"/>
+      <c r="J117" s="172"/>
+      <c r="K117" s="188">
         <f>0.13*H114*1207.6/10</f>
         <v>156.56565481286924</v>
       </c>
-      <c r="L117" s="25"/>
-    </row>
-    <row r="118" spans="2:14" ht="18" customHeight="1">
-      <c r="B118" s="80"/>
-      <c r="C118" s="19"/>
-      <c r="D118" s="24"/>
-      <c r="E118" s="70"/>
-      <c r="F118" s="70"/>
-      <c r="G118" s="71"/>
-      <c r="H118" s="70"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="73"/>
-      <c r="K118" s="73"/>
-      <c r="L118" s="25"/>
-    </row>
-    <row r="119" spans="2:14" ht="35.1" customHeight="1">
-      <c r="B119" s="123">
+      <c r="L117" s="173"/>
+    </row>
+    <row r="118" spans="2:12" ht="18" customHeight="1">
+      <c r="B118" s="169"/>
+      <c r="C118" s="182"/>
+      <c r="D118" s="171"/>
+      <c r="E118" s="172"/>
+      <c r="F118" s="172"/>
+      <c r="G118" s="177"/>
+      <c r="H118" s="172"/>
+      <c r="I118" s="171"/>
+      <c r="J118" s="172"/>
+      <c r="K118" s="172"/>
+      <c r="L118" s="173"/>
+    </row>
+    <row r="119" spans="2:12" ht="35.1" customHeight="1">
+      <c r="B119" s="169">
         <v>15</v>
       </c>
-      <c r="C119" s="124" t="s">
+      <c r="C119" s="170" t="s">
         <v>79</v>
       </c>
-      <c r="D119" s="119"/>
-      <c r="E119" s="119"/>
-      <c r="F119" s="119"/>
-      <c r="G119" s="119"/>
-      <c r="H119" s="119"/>
-      <c r="I119" s="119"/>
-      <c r="J119" s="119"/>
-      <c r="K119" s="119"/>
-      <c r="L119" s="25"/>
-    </row>
-    <row r="120" spans="2:14">
-      <c r="B120" s="123"/>
-      <c r="C120" s="118" t="str">
+      <c r="D119" s="171"/>
+      <c r="E119" s="171"/>
+      <c r="F119" s="171"/>
+      <c r="G119" s="171"/>
+      <c r="H119" s="171"/>
+      <c r="I119" s="171"/>
+      <c r="J119" s="171"/>
+      <c r="K119" s="171"/>
+      <c r="L119" s="173"/>
+    </row>
+    <row r="120" spans="2:12">
+      <c r="B120" s="169"/>
+      <c r="C120" s="182" t="str">
         <f>C84</f>
         <v>-At shear wall</v>
       </c>
-      <c r="D120" s="119">
+      <c r="D120" s="171">
         <f>D64</f>
         <v>2</v>
       </c>
-      <c r="E120" s="119">
+      <c r="E120" s="171">
         <f>E84</f>
         <v>4.6997866504114594</v>
       </c>
-      <c r="F120" s="119"/>
-      <c r="G120" s="119">
+      <c r="F120" s="171"/>
+      <c r="G120" s="171">
         <f>G64+0.3+0.3</f>
         <v>2.2001219140505941</v>
       </c>
-      <c r="H120" s="116">
+      <c r="H120" s="172">
         <f>PRODUCT(D120:G120)</f>
         <v>20.680207201865382</v>
       </c>
-      <c r="I120" s="119"/>
-      <c r="J120" s="119"/>
-      <c r="K120" s="119"/>
-      <c r="L120" s="25"/>
-    </row>
-    <row r="121" spans="2:14">
-      <c r="B121" s="123"/>
-      <c r="C121" s="118"/>
-      <c r="D121" s="119">
+      <c r="I120" s="171"/>
+      <c r="J120" s="171"/>
+      <c r="K120" s="171"/>
+      <c r="L120" s="173"/>
+    </row>
+    <row r="121" spans="2:12">
+      <c r="B121" s="169"/>
+      <c r="C121" s="182"/>
+      <c r="D121" s="171">
         <f>D65</f>
         <v>2</v>
       </c>
-      <c r="E121" s="119">
+      <c r="E121" s="171">
         <f>E85</f>
         <v>3.047851264858275</v>
       </c>
-      <c r="F121" s="119"/>
-      <c r="G121" s="119">
+      <c r="F121" s="171"/>
+      <c r="G121" s="171">
         <f>G65+0.3+0.3</f>
         <v>2.2001219140505941</v>
       </c>
-      <c r="H121" s="116">
-        <f t="shared" ref="H121:H122" si="12">PRODUCT(D121:G121)</f>
+      <c r="H121" s="172">
+        <f t="shared" ref="H121:H122" si="13">PRODUCT(D121:G121)</f>
         <v>13.411288717163025</v>
       </c>
-      <c r="I121" s="119"/>
-      <c r="J121" s="119"/>
-      <c r="K121" s="119"/>
-      <c r="L121" s="25"/>
-    </row>
-    <row r="122" spans="2:14" s="121" customFormat="1">
-      <c r="B122" s="123"/>
-      <c r="C122" s="136" t="s">
-        <v>152</v>
-      </c>
-      <c r="D122" s="119">
+      <c r="I121" s="171"/>
+      <c r="J121" s="171"/>
+      <c r="K121" s="171"/>
+      <c r="L121" s="173"/>
+    </row>
+    <row r="122" spans="2:12">
+      <c r="B122" s="169"/>
+      <c r="C122" s="184" t="s">
+        <v>149</v>
+      </c>
+      <c r="D122" s="171">
         <v>1</v>
       </c>
-      <c r="E122" s="119">
+      <c r="E122" s="171">
         <f>E114</f>
         <v>4.0902163974398045</v>
       </c>
-      <c r="F122" s="119">
+      <c r="F122" s="171">
         <f>F114</f>
         <v>2.4382810118866196</v>
       </c>
-      <c r="G122" s="119"/>
-      <c r="H122" s="116">
-        <f t="shared" si="12"/>
+      <c r="G122" s="171"/>
+      <c r="H122" s="172">
+        <f t="shared" si="13"/>
         <v>9.9730969763847703</v>
       </c>
-      <c r="I122" s="119"/>
-      <c r="J122" s="119"/>
-      <c r="K122" s="119"/>
-      <c r="L122" s="25"/>
-    </row>
-    <row r="123" spans="2:14">
-      <c r="B123" s="123"/>
-      <c r="C123" s="118"/>
-      <c r="D123" s="119"/>
-      <c r="E123" s="119"/>
-      <c r="F123" s="119"/>
-      <c r="G123" s="119"/>
-      <c r="H123" s="119">
+      <c r="I122" s="171"/>
+      <c r="J122" s="171"/>
+      <c r="K122" s="171"/>
+      <c r="L122" s="173"/>
+    </row>
+    <row r="123" spans="2:12">
+      <c r="B123" s="169"/>
+      <c r="C123" s="182"/>
+      <c r="D123" s="171"/>
+      <c r="E123" s="171"/>
+      <c r="F123" s="171"/>
+      <c r="G123" s="171"/>
+      <c r="H123" s="171">
         <f>SUM(H120:H122)</f>
         <v>44.06459289541317</v>
       </c>
-      <c r="I123" s="119" t="s">
+      <c r="I123" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="J123" s="119">
+      <c r="J123" s="171">
         <v>287.32</v>
       </c>
-      <c r="K123" s="119">
+      <c r="K123" s="171">
         <f>H123*J123</f>
         <v>12660.638830710112</v>
       </c>
-      <c r="L123" s="25"/>
-    </row>
-    <row r="124" spans="2:14">
-      <c r="B124" s="123"/>
-      <c r="C124" s="118" t="s">
+      <c r="L123" s="173"/>
+    </row>
+    <row r="124" spans="2:12">
+      <c r="B124" s="169"/>
+      <c r="C124" s="182" t="s">
         <v>29</v>
       </c>
-      <c r="D124" s="119"/>
-      <c r="E124" s="119"/>
-      <c r="F124" s="119"/>
-      <c r="G124" s="119"/>
-      <c r="H124" s="119"/>
-      <c r="I124" s="119"/>
-      <c r="J124" s="119"/>
-      <c r="K124" s="119">
+      <c r="D124" s="171"/>
+      <c r="E124" s="171"/>
+      <c r="F124" s="171"/>
+      <c r="G124" s="171"/>
+      <c r="H124" s="171"/>
+      <c r="I124" s="171"/>
+      <c r="J124" s="171"/>
+      <c r="K124" s="171">
         <f>0.13*H123*693.24/10</f>
         <v>397.11539892461093</v>
       </c>
-      <c r="L124" s="25"/>
-    </row>
-    <row r="125" spans="2:14">
-      <c r="B125" s="81"/>
-      <c r="C125" s="19"/>
-      <c r="D125" s="72"/>
-      <c r="E125" s="72"/>
-      <c r="F125" s="72"/>
-      <c r="G125" s="72"/>
-      <c r="H125" s="72"/>
-      <c r="I125" s="72"/>
-      <c r="J125" s="72"/>
-      <c r="K125" s="72"/>
-      <c r="L125" s="25"/>
-    </row>
-    <row r="126" spans="2:14">
-      <c r="B126" s="81"/>
-      <c r="C126" s="19"/>
-      <c r="D126" s="72"/>
-      <c r="E126" s="72"/>
-      <c r="F126" s="72"/>
-      <c r="G126" s="72"/>
-      <c r="H126" s="72"/>
-      <c r="I126" s="72"/>
-      <c r="J126" s="72"/>
-      <c r="K126" s="72"/>
-      <c r="L126" s="25"/>
-    </row>
-    <row r="127" spans="2:14" ht="33" customHeight="1">
-      <c r="B127" s="123">
+      <c r="L124" s="173"/>
+    </row>
+    <row r="125" spans="2:12">
+      <c r="B125" s="169"/>
+      <c r="C125" s="182"/>
+      <c r="D125" s="171"/>
+      <c r="E125" s="171"/>
+      <c r="F125" s="171"/>
+      <c r="G125" s="171"/>
+      <c r="H125" s="171"/>
+      <c r="I125" s="171"/>
+      <c r="J125" s="171"/>
+      <c r="K125" s="171"/>
+      <c r="L125" s="173"/>
+    </row>
+    <row r="126" spans="2:12">
+      <c r="B126" s="169"/>
+      <c r="C126" s="182"/>
+      <c r="D126" s="171"/>
+      <c r="E126" s="171"/>
+      <c r="F126" s="171"/>
+      <c r="G126" s="171"/>
+      <c r="H126" s="171"/>
+      <c r="I126" s="171"/>
+      <c r="J126" s="171"/>
+      <c r="K126" s="171"/>
+      <c r="L126" s="173"/>
+    </row>
+    <row r="127" spans="2:12" ht="33" customHeight="1">
+      <c r="B127" s="169">
         <v>16</v>
       </c>
-      <c r="C127" s="125" t="s">
+      <c r="C127" s="186" t="s">
         <v>87</v>
       </c>
-      <c r="D127" s="119">
+      <c r="D127" s="171">
         <v>1</v>
       </c>
-      <c r="E127" s="116"/>
-      <c r="F127" s="116"/>
-      <c r="G127" s="127"/>
-      <c r="H127" s="116">
+      <c r="E127" s="172"/>
+      <c r="F127" s="172"/>
+      <c r="G127" s="177"/>
+      <c r="H127" s="172">
         <f>+D127</f>
         <v>1</v>
       </c>
-      <c r="I127" s="119" t="s">
+      <c r="I127" s="171" t="s">
         <v>34</v>
       </c>
-      <c r="J127" s="116">
+      <c r="J127" s="172">
         <v>4659</v>
       </c>
-      <c r="K127" s="116">
+      <c r="K127" s="172">
         <f>H127*J127</f>
         <v>4659</v>
       </c>
-      <c r="L127" s="25"/>
-      <c r="N127" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="128" spans="2:14">
-      <c r="B128" s="123"/>
-      <c r="C128" s="137" t="s">
+      <c r="L127" s="173"/>
+    </row>
+    <row r="128" spans="2:12">
+      <c r="B128" s="169"/>
+      <c r="C128" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="D128" s="119"/>
-      <c r="E128" s="116"/>
-      <c r="F128" s="116"/>
-      <c r="G128" s="127"/>
-      <c r="H128" s="116"/>
-      <c r="I128" s="119"/>
-      <c r="J128" s="116"/>
-      <c r="K128" s="116">
+      <c r="D128" s="171"/>
+      <c r="E128" s="172"/>
+      <c r="F128" s="172"/>
+      <c r="G128" s="177"/>
+      <c r="H128" s="172"/>
+      <c r="I128" s="171"/>
+      <c r="J128" s="172"/>
+      <c r="K128" s="172">
         <f>0.13*K127</f>
         <v>605.67000000000007</v>
       </c>
-      <c r="L128" s="25"/>
-    </row>
-    <row r="129" spans="2:20">
-      <c r="B129" s="80"/>
-      <c r="C129" s="21"/>
-      <c r="D129" s="24"/>
-      <c r="E129" s="70"/>
-      <c r="F129" s="70"/>
-      <c r="G129" s="71"/>
-      <c r="H129" s="70"/>
-      <c r="I129" s="24"/>
-      <c r="J129" s="73"/>
-      <c r="K129" s="73"/>
-      <c r="L129" s="25"/>
-    </row>
-    <row r="130" spans="2:20" s="121" customFormat="1" ht="37.200000000000003">
-      <c r="B130" s="123">
+      <c r="L128" s="173"/>
+    </row>
+    <row r="129" spans="2:12">
+      <c r="B129" s="169"/>
+      <c r="C129" s="186"/>
+      <c r="D129" s="171"/>
+      <c r="E129" s="172"/>
+      <c r="F129" s="172"/>
+      <c r="G129" s="177"/>
+      <c r="H129" s="172"/>
+      <c r="I129" s="171"/>
+      <c r="J129" s="172"/>
+      <c r="K129" s="172"/>
+      <c r="L129" s="173"/>
+    </row>
+    <row r="130" spans="2:12" ht="37.200000000000003">
+      <c r="B130" s="169">
         <v>17</v>
       </c>
-      <c r="C130" s="124" t="s">
-        <v>156</v>
-      </c>
-      <c r="D130" s="119"/>
-      <c r="E130" s="116"/>
-      <c r="F130" s="116"/>
-      <c r="G130" s="127"/>
-      <c r="H130" s="116"/>
-      <c r="I130" s="119"/>
-      <c r="J130" s="116"/>
-      <c r="K130" s="116"/>
-      <c r="L130" s="25"/>
-    </row>
-    <row r="131" spans="2:20" s="121" customFormat="1">
-      <c r="B131" s="123"/>
-      <c r="C131" s="138" t="s">
-        <v>157</v>
-      </c>
-      <c r="D131" s="119">
+      <c r="C130" s="170" t="s">
+        <v>153</v>
+      </c>
+      <c r="D130" s="171"/>
+      <c r="E130" s="172"/>
+      <c r="F130" s="172"/>
+      <c r="G130" s="177"/>
+      <c r="H130" s="172"/>
+      <c r="I130" s="171"/>
+      <c r="J130" s="172"/>
+      <c r="K130" s="172"/>
+      <c r="L130" s="173"/>
+    </row>
+    <row r="131" spans="2:12">
+      <c r="B131" s="169"/>
+      <c r="C131" s="174" t="s">
+        <v>154</v>
+      </c>
+      <c r="D131" s="171">
         <v>1</v>
       </c>
-      <c r="E131" s="116">
+      <c r="E131" s="172">
         <f>1.75/3.281</f>
         <v>0.53337397135019804</v>
       </c>
-      <c r="F131" s="116"/>
-      <c r="G131" s="127">
+      <c r="F131" s="172"/>
+      <c r="G131" s="177">
         <f>3.5/3.281</f>
         <v>1.0667479427003961</v>
       </c>
-      <c r="H131" s="116">
-        <f t="shared" ref="H131" si="13">PRODUCT(D131:G131)</f>
+      <c r="H131" s="172">
+        <f t="shared" ref="H131" si="14">PRODUCT(D131:G131)</f>
         <v>0.56897558662776371</v>
       </c>
-      <c r="I131" s="119"/>
-      <c r="J131" s="116"/>
-      <c r="K131" s="116"/>
-      <c r="L131" s="25"/>
-    </row>
-    <row r="132" spans="2:20" s="121" customFormat="1">
-      <c r="B132" s="123"/>
-      <c r="C132" s="118"/>
-      <c r="D132" s="119"/>
-      <c r="E132" s="119"/>
-      <c r="F132" s="119"/>
-      <c r="G132" s="119"/>
-      <c r="H132" s="119">
+      <c r="I131" s="171"/>
+      <c r="J131" s="172"/>
+      <c r="K131" s="172"/>
+      <c r="L131" s="173"/>
+    </row>
+    <row r="132" spans="2:12">
+      <c r="B132" s="169"/>
+      <c r="C132" s="182"/>
+      <c r="D132" s="171"/>
+      <c r="E132" s="171"/>
+      <c r="F132" s="171"/>
+      <c r="G132" s="171"/>
+      <c r="H132" s="171">
         <f>SUM(H131)</f>
         <v>0.56897558662776371</v>
       </c>
-      <c r="I132" s="119" t="s">
+      <c r="I132" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="J132" s="119">
+      <c r="J132" s="171">
         <v>10663.63</v>
       </c>
-      <c r="K132" s="119">
+      <c r="K132" s="171">
         <f>H132*J132</f>
         <v>6067.3451348314193</v>
       </c>
-      <c r="L132" s="25"/>
-    </row>
-    <row r="133" spans="2:20" s="121" customFormat="1">
-      <c r="B133" s="123"/>
-      <c r="C133" s="118" t="s">
-        <v>158</v>
-      </c>
-      <c r="D133" s="119"/>
-      <c r="E133" s="119"/>
-      <c r="F133" s="119"/>
-      <c r="G133" s="119"/>
-      <c r="H133" s="119"/>
-      <c r="I133" s="119"/>
-      <c r="J133" s="119"/>
-      <c r="K133" s="119">
+      <c r="L132" s="173"/>
+    </row>
+    <row r="133" spans="2:12">
+      <c r="B133" s="169"/>
+      <c r="C133" s="182" t="s">
+        <v>155</v>
+      </c>
+      <c r="D133" s="171"/>
+      <c r="E133" s="171"/>
+      <c r="F133" s="171"/>
+      <c r="G133" s="171"/>
+      <c r="H133" s="171"/>
+      <c r="I133" s="171"/>
+      <c r="J133" s="171"/>
+      <c r="K133" s="171">
         <f>0.13*H132*11733.39/2.23</f>
         <v>389.1845827756519</v>
       </c>
-      <c r="L133" s="25"/>
-    </row>
-    <row r="134" spans="2:20" s="121" customFormat="1">
-      <c r="B134" s="80"/>
-      <c r="C134" s="21"/>
-      <c r="D134" s="24"/>
-      <c r="E134" s="70"/>
-      <c r="F134" s="70"/>
-      <c r="G134" s="71"/>
-      <c r="H134" s="70"/>
-      <c r="I134" s="24"/>
-      <c r="J134" s="73"/>
-      <c r="K134" s="73"/>
-      <c r="L134" s="25"/>
-    </row>
-    <row r="135" spans="2:20" s="121" customFormat="1" ht="37.200000000000003">
-      <c r="B135" s="80">
+      <c r="L133" s="173"/>
+    </row>
+    <row r="134" spans="2:12">
+      <c r="B134" s="169"/>
+      <c r="C134" s="186"/>
+      <c r="D134" s="171"/>
+      <c r="E134" s="172"/>
+      <c r="F134" s="172"/>
+      <c r="G134" s="177"/>
+      <c r="H134" s="172"/>
+      <c r="I134" s="171"/>
+      <c r="J134" s="172"/>
+      <c r="K134" s="172"/>
+      <c r="L134" s="173"/>
+    </row>
+    <row r="135" spans="2:12" ht="37.200000000000003">
+      <c r="B135" s="169">
         <v>18</v>
       </c>
-      <c r="C135" s="124" t="s">
-        <v>159</v>
-      </c>
-      <c r="D135" s="24"/>
-      <c r="E135" s="70"/>
-      <c r="F135" s="70"/>
-      <c r="G135" s="71"/>
-      <c r="H135" s="70"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="73"/>
-      <c r="K135" s="73"/>
-      <c r="L135" s="25"/>
-    </row>
-    <row r="136" spans="2:20" s="121" customFormat="1">
-      <c r="B136" s="123"/>
-      <c r="C136" s="138" t="s">
-        <v>160</v>
-      </c>
-      <c r="D136" s="119">
+      <c r="C135" s="170" t="s">
+        <v>156</v>
+      </c>
+      <c r="D135" s="171"/>
+      <c r="E135" s="172"/>
+      <c r="F135" s="172"/>
+      <c r="G135" s="177"/>
+      <c r="H135" s="172"/>
+      <c r="I135" s="171"/>
+      <c r="J135" s="172"/>
+      <c r="K135" s="172"/>
+      <c r="L135" s="173"/>
+    </row>
+    <row r="136" spans="2:12">
+      <c r="B136" s="169"/>
+      <c r="C136" s="174" t="s">
+        <v>157</v>
+      </c>
+      <c r="D136" s="171">
         <v>3</v>
       </c>
-      <c r="E136" s="116">
+      <c r="E136" s="172">
         <f>1.42/3.281</f>
         <v>0.43279487960987501</v>
       </c>
-      <c r="F136" s="116"/>
-      <c r="G136" s="127">
+      <c r="F136" s="172"/>
+      <c r="G136" s="177">
         <f>3.25/3.281</f>
         <v>0.99055166107893933</v>
       </c>
-      <c r="H136" s="116">
-        <f t="shared" ref="H136" si="14">PRODUCT(D136:G136)</f>
+      <c r="H136" s="172">
+        <f t="shared" ref="H136" si="15">PRODUCT(D136:G136)</f>
         <v>1.2861170607120638</v>
       </c>
-      <c r="I136" s="119"/>
-      <c r="J136" s="116"/>
-      <c r="K136" s="116"/>
-      <c r="L136" s="25"/>
-    </row>
-    <row r="137" spans="2:20" s="121" customFormat="1">
-      <c r="B137" s="123"/>
-      <c r="C137" s="118"/>
-      <c r="D137" s="119"/>
-      <c r="E137" s="119"/>
-      <c r="F137" s="119"/>
-      <c r="G137" s="119"/>
-      <c r="H137" s="119">
+      <c r="I136" s="171"/>
+      <c r="J136" s="172"/>
+      <c r="K136" s="172"/>
+      <c r="L136" s="173"/>
+    </row>
+    <row r="137" spans="2:12">
+      <c r="B137" s="169"/>
+      <c r="C137" s="182"/>
+      <c r="D137" s="171"/>
+      <c r="E137" s="171"/>
+      <c r="F137" s="171"/>
+      <c r="G137" s="171"/>
+      <c r="H137" s="171">
         <f>SUM(H136)</f>
         <v>1.2861170607120638</v>
       </c>
-      <c r="I137" s="119" t="s">
+      <c r="I137" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="J137" s="119">
+      <c r="J137" s="171">
         <v>1063.57</v>
       </c>
-      <c r="K137" s="119">
+      <c r="K137" s="171">
         <f>H137*J137</f>
         <v>1367.8755222615296</v>
       </c>
-      <c r="L137" s="25"/>
-    </row>
-    <row r="138" spans="2:20" s="121" customFormat="1">
-      <c r="B138" s="123"/>
-      <c r="C138" s="118" t="s">
-        <v>158</v>
-      </c>
-      <c r="D138" s="119"/>
-      <c r="E138" s="119"/>
-      <c r="F138" s="119"/>
-      <c r="G138" s="119"/>
-      <c r="H138" s="119"/>
-      <c r="I138" s="119"/>
-      <c r="J138" s="119"/>
-      <c r="K138" s="119">
+      <c r="L137" s="173"/>
+    </row>
+    <row r="138" spans="2:12">
+      <c r="B138" s="169"/>
+      <c r="C138" s="182" t="s">
+        <v>155</v>
+      </c>
+      <c r="D138" s="171"/>
+      <c r="E138" s="171"/>
+      <c r="F138" s="171"/>
+      <c r="G138" s="171"/>
+      <c r="H138" s="171"/>
+      <c r="I138" s="171"/>
+      <c r="J138" s="171"/>
+      <c r="K138" s="171">
         <f>0.13*H137*983.26</f>
         <v>164.3963699450467</v>
       </c>
-      <c r="L138" s="25"/>
-    </row>
-    <row r="139" spans="2:20" s="121" customFormat="1">
-      <c r="B139" s="123"/>
-      <c r="C139" s="118"/>
-      <c r="D139" s="119"/>
-      <c r="E139" s="119"/>
-      <c r="F139" s="119"/>
-      <c r="G139" s="119"/>
-      <c r="H139" s="119"/>
-      <c r="I139" s="119"/>
-      <c r="J139" s="119"/>
-      <c r="K139" s="119"/>
-      <c r="L139" s="25"/>
-    </row>
-    <row r="140" spans="2:20" s="121" customFormat="1" ht="167.4">
-      <c r="B140" s="123">
+      <c r="L138" s="173"/>
+    </row>
+    <row r="139" spans="2:12">
+      <c r="B139" s="169"/>
+      <c r="C139" s="182"/>
+      <c r="D139" s="171"/>
+      <c r="E139" s="171"/>
+      <c r="F139" s="171"/>
+      <c r="G139" s="171"/>
+      <c r="H139" s="171"/>
+      <c r="I139" s="171"/>
+      <c r="J139" s="171"/>
+      <c r="K139" s="171"/>
+      <c r="L139" s="173"/>
+    </row>
+    <row r="140" spans="2:12" ht="148.80000000000001">
+      <c r="B140" s="169">
         <v>19</v>
       </c>
-      <c r="C140" s="124" t="s">
-        <v>163</v>
-      </c>
-      <c r="D140" s="119"/>
-      <c r="E140" s="119"/>
-      <c r="F140" s="119"/>
-      <c r="G140" s="119"/>
-      <c r="H140" s="119"/>
-      <c r="I140" s="119"/>
-      <c r="J140" s="119"/>
-      <c r="K140" s="119"/>
-      <c r="L140" s="25"/>
-    </row>
-    <row r="141" spans="2:20" s="121" customFormat="1">
-      <c r="B141" s="123"/>
-      <c r="C141" s="136" t="s">
-        <v>162</v>
-      </c>
-      <c r="D141" s="119">
+      <c r="C140" s="170" t="s">
+        <v>160</v>
+      </c>
+      <c r="D140" s="171"/>
+      <c r="E140" s="171"/>
+      <c r="F140" s="171"/>
+      <c r="G140" s="171"/>
+      <c r="H140" s="171"/>
+      <c r="I140" s="171"/>
+      <c r="J140" s="171"/>
+      <c r="K140" s="171"/>
+      <c r="L140" s="173"/>
+    </row>
+    <row r="141" spans="2:12">
+      <c r="B141" s="169"/>
+      <c r="C141" s="184" t="s">
+        <v>159</v>
+      </c>
+      <c r="D141" s="171">
         <v>1</v>
       </c>
-      <c r="E141" s="119">
+      <c r="E141" s="171">
         <f>3/3.281</f>
         <v>0.91435537945748246</v>
       </c>
-      <c r="F141" s="119"/>
-      <c r="G141" s="119"/>
-      <c r="H141" s="116">
-        <f t="shared" ref="H141" si="15">PRODUCT(D141:G141)</f>
+      <c r="F141" s="171"/>
+      <c r="G141" s="171"/>
+      <c r="H141" s="172">
+        <f t="shared" ref="H141" si="16">PRODUCT(D141:G141)</f>
         <v>0.91435537945748246</v>
       </c>
-      <c r="I141" s="119"/>
-      <c r="J141" s="119"/>
-      <c r="K141" s="119"/>
-      <c r="L141" s="25"/>
-    </row>
-    <row r="142" spans="2:20" s="121" customFormat="1">
-      <c r="B142" s="123"/>
-      <c r="C142" s="118"/>
-      <c r="D142" s="119"/>
-      <c r="E142" s="119"/>
-      <c r="F142" s="119"/>
-      <c r="G142" s="119"/>
-      <c r="H142" s="119">
+      <c r="I141" s="171"/>
+      <c r="J141" s="171"/>
+      <c r="K141" s="171"/>
+      <c r="L141" s="173"/>
+    </row>
+    <row r="142" spans="2:12">
+      <c r="B142" s="169"/>
+      <c r="C142" s="182"/>
+      <c r="D142" s="171"/>
+      <c r="E142" s="171"/>
+      <c r="F142" s="171"/>
+      <c r="G142" s="171"/>
+      <c r="H142" s="171">
         <f>SUM(H141)</f>
         <v>0.91435537945748246</v>
       </c>
-      <c r="I142" s="119" t="s">
-        <v>164</v>
-      </c>
-      <c r="J142" s="119">
+      <c r="I142" s="171" t="s">
+        <v>161</v>
+      </c>
+      <c r="J142" s="171">
         <f>11197.91</f>
         <v>11197.91</v>
       </c>
-      <c r="K142" s="119">
+      <c r="K142" s="171">
         <f>H142*J142</f>
         <v>10238.869247180737</v>
       </c>
-      <c r="L142" s="25"/>
-    </row>
-    <row r="143" spans="2:20" s="121" customFormat="1">
-      <c r="B143" s="123"/>
-      <c r="C143" s="118" t="s">
-        <v>158</v>
-      </c>
-      <c r="D143" s="119"/>
-      <c r="E143" s="119"/>
-      <c r="F143" s="119"/>
-      <c r="G143" s="119"/>
-      <c r="H143" s="119"/>
-      <c r="I143" s="119"/>
-      <c r="J143" s="119"/>
-      <c r="K143" s="119">
+      <c r="L142" s="173"/>
+    </row>
+    <row r="143" spans="2:12">
+      <c r="B143" s="169"/>
+      <c r="C143" s="182" t="s">
+        <v>155</v>
+      </c>
+      <c r="D143" s="171"/>
+      <c r="E143" s="171"/>
+      <c r="F143" s="171"/>
+      <c r="G143" s="171"/>
+      <c r="H143" s="171"/>
+      <c r="I143" s="171"/>
+      <c r="J143" s="171"/>
+      <c r="K143" s="171">
         <f>0.13*K142</f>
         <v>1331.053002133496</v>
       </c>
-      <c r="L143" s="25"/>
-    </row>
-    <row r="144" spans="2:20" s="121" customFormat="1">
-      <c r="B144" s="123"/>
-      <c r="C144" s="118"/>
-      <c r="D144" s="119"/>
-      <c r="E144" s="119"/>
-      <c r="F144" s="119"/>
-      <c r="G144" s="119"/>
-      <c r="H144" s="119"/>
-      <c r="I144" s="119"/>
-      <c r="J144" s="119"/>
-      <c r="K144" s="119"/>
-      <c r="L144" s="25"/>
-      <c r="N144" s="1"/>
-      <c r="O144" s="1"/>
-      <c r="P144" s="1"/>
-      <c r="Q144" s="1"/>
-      <c r="R144" s="1"/>
-      <c r="S144" s="1"/>
-      <c r="T144" s="1"/>
-    </row>
-    <row r="145" spans="2:12" s="121" customFormat="1" ht="37.200000000000003">
-      <c r="B145" s="123">
+      <c r="L143" s="173"/>
+    </row>
+    <row r="144" spans="2:12">
+      <c r="B144" s="169"/>
+      <c r="C144" s="182"/>
+      <c r="D144" s="171"/>
+      <c r="E144" s="171"/>
+      <c r="F144" s="171"/>
+      <c r="G144" s="171"/>
+      <c r="H144" s="171"/>
+      <c r="I144" s="171"/>
+      <c r="J144" s="171"/>
+      <c r="K144" s="171"/>
+      <c r="L144" s="173"/>
+    </row>
+    <row r="145" spans="2:12" ht="37.200000000000003">
+      <c r="B145" s="169">
         <v>20</v>
       </c>
-      <c r="C145" s="124" t="s">
-        <v>165</v>
-      </c>
-      <c r="D145" s="119"/>
-      <c r="E145" s="119"/>
-      <c r="F145" s="119"/>
-      <c r="G145" s="119"/>
-      <c r="H145" s="119"/>
-      <c r="I145" s="119"/>
-      <c r="J145" s="119"/>
-      <c r="K145" s="119"/>
-      <c r="L145" s="25"/>
-    </row>
-    <row r="146" spans="2:12" s="121" customFormat="1">
-      <c r="B146" s="123"/>
-      <c r="C146" s="136" t="s">
-        <v>150</v>
-      </c>
-      <c r="D146" s="119">
+      <c r="C145" s="170" t="s">
+        <v>162</v>
+      </c>
+      <c r="D145" s="171"/>
+      <c r="E145" s="171"/>
+      <c r="F145" s="171"/>
+      <c r="G145" s="171"/>
+      <c r="H145" s="171"/>
+      <c r="I145" s="171"/>
+      <c r="J145" s="171"/>
+      <c r="K145" s="171"/>
+      <c r="L145" s="173"/>
+    </row>
+    <row r="146" spans="2:12">
+      <c r="B146" s="169"/>
+      <c r="C146" s="184" t="s">
+        <v>147</v>
+      </c>
+      <c r="D146" s="171">
         <v>1</v>
       </c>
-      <c r="E146" s="119">
+      <c r="E146" s="171">
         <f>(15.42*2+10*2)/3.281</f>
         <v>15.49527583053947</v>
       </c>
-      <c r="F146" s="119"/>
-      <c r="G146" s="119">
+      <c r="F146" s="171"/>
+      <c r="G146" s="171">
         <f>5.25/3.281</f>
         <v>1.6001219140505942</v>
       </c>
-      <c r="H146" s="116">
-        <f t="shared" ref="H146:H147" si="16">PRODUCT(D146:G146)</f>
+      <c r="H146" s="172">
+        <f t="shared" ref="H146:H147" si="17">PRODUCT(D146:G146)</f>
         <v>24.794330420704728</v>
       </c>
-      <c r="I146" s="119"/>
-      <c r="J146" s="119"/>
-      <c r="K146" s="119"/>
-      <c r="L146" s="25"/>
-    </row>
-    <row r="147" spans="2:12" s="121" customFormat="1">
-      <c r="B147" s="123"/>
-      <c r="C147" s="118"/>
-      <c r="D147" s="119">
+      <c r="I146" s="171"/>
+      <c r="J146" s="171"/>
+      <c r="K146" s="171"/>
+      <c r="L146" s="173"/>
+    </row>
+    <row r="147" spans="2:12">
+      <c r="B147" s="169"/>
+      <c r="C147" s="182"/>
+      <c r="D147" s="171">
         <v>1</v>
       </c>
-      <c r="E147" s="119">
+      <c r="E147" s="171">
         <f>13.42/3.281</f>
         <v>4.0902163974398045</v>
       </c>
-      <c r="F147" s="119">
+      <c r="F147" s="171">
         <f>8/3.281</f>
         <v>2.4382810118866196</v>
       </c>
-      <c r="G147" s="119"/>
-      <c r="H147" s="116">
-        <f t="shared" si="16"/>
+      <c r="G147" s="171"/>
+      <c r="H147" s="172">
+        <f t="shared" si="17"/>
         <v>9.9730969763847703</v>
       </c>
-      <c r="I147" s="119"/>
-      <c r="J147" s="119"/>
-      <c r="K147" s="119"/>
-      <c r="L147" s="25"/>
-    </row>
-    <row r="148" spans="2:12" s="121" customFormat="1">
-      <c r="B148" s="123"/>
-      <c r="C148" s="118"/>
-      <c r="D148" s="119"/>
-      <c r="E148" s="119"/>
-      <c r="F148" s="119"/>
-      <c r="G148" s="119"/>
-      <c r="H148" s="119">
+      <c r="I147" s="171"/>
+      <c r="J147" s="171"/>
+      <c r="K147" s="171"/>
+      <c r="L147" s="173"/>
+    </row>
+    <row r="148" spans="2:12">
+      <c r="B148" s="169"/>
+      <c r="C148" s="182"/>
+      <c r="D148" s="171"/>
+      <c r="E148" s="171"/>
+      <c r="F148" s="171"/>
+      <c r="G148" s="171"/>
+      <c r="H148" s="171">
         <f>SUM(H146:H147)</f>
         <v>34.767427397089499</v>
       </c>
-      <c r="I148" s="119" t="s">
+      <c r="I148" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="J148" s="119">
+      <c r="J148" s="171">
         <f>11197.91</f>
         <v>11197.91</v>
       </c>
-      <c r="K148" s="119">
+      <c r="K148" s="171">
         <f>H148*J148</f>
         <v>389322.52292414248</v>
       </c>
-      <c r="L148" s="25"/>
-    </row>
-    <row r="149" spans="2:12" s="121" customFormat="1">
-      <c r="B149" s="123"/>
-      <c r="C149" s="118" t="s">
-        <v>158</v>
-      </c>
-      <c r="D149" s="119"/>
-      <c r="E149" s="119"/>
-      <c r="F149" s="119"/>
-      <c r="G149" s="119"/>
-      <c r="H149" s="119"/>
-      <c r="I149" s="119"/>
-      <c r="J149" s="119"/>
-      <c r="K149" s="119">
+      <c r="L148" s="173"/>
+    </row>
+    <row r="149" spans="2:12">
+      <c r="B149" s="169"/>
+      <c r="C149" s="182" t="s">
+        <v>155</v>
+      </c>
+      <c r="D149" s="171"/>
+      <c r="E149" s="171"/>
+      <c r="F149" s="171"/>
+      <c r="G149" s="171"/>
+      <c r="H149" s="171"/>
+      <c r="I149" s="171"/>
+      <c r="J149" s="171"/>
+      <c r="K149" s="171">
         <f>0.13*H148*2846.9/10</f>
         <v>1286.7320577380633</v>
       </c>
-      <c r="L149" s="25"/>
-    </row>
-    <row r="150" spans="2:12" s="121" customFormat="1">
-      <c r="B150" s="123"/>
-      <c r="C150" s="118"/>
-      <c r="D150" s="119"/>
-      <c r="E150" s="119"/>
-      <c r="F150" s="119"/>
-      <c r="G150" s="119"/>
-      <c r="H150" s="119"/>
-      <c r="I150" s="119"/>
-      <c r="J150" s="119"/>
-      <c r="K150" s="119"/>
-      <c r="L150" s="25"/>
-    </row>
-    <row r="151" spans="2:12" s="121" customFormat="1" ht="33" customHeight="1">
-      <c r="B151" s="81">
+      <c r="L149" s="173"/>
+    </row>
+    <row r="150" spans="2:12">
+      <c r="B150" s="169"/>
+      <c r="C150" s="182"/>
+      <c r="D150" s="171"/>
+      <c r="E150" s="171"/>
+      <c r="F150" s="171"/>
+      <c r="G150" s="171"/>
+      <c r="H150" s="171"/>
+      <c r="I150" s="171"/>
+      <c r="J150" s="171"/>
+      <c r="K150" s="171"/>
+      <c r="L150" s="173"/>
+    </row>
+    <row r="151" spans="2:12" ht="33" customHeight="1">
+      <c r="B151" s="169">
         <v>21</v>
       </c>
-      <c r="C151" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="D151" s="24">
+      <c r="C151" s="183" t="s">
+        <v>163</v>
+      </c>
+      <c r="D151" s="171">
         <v>1</v>
       </c>
-      <c r="E151" s="24"/>
-      <c r="F151" s="24"/>
-      <c r="G151" s="24"/>
-      <c r="H151" s="24">
+      <c r="E151" s="171"/>
+      <c r="F151" s="171"/>
+      <c r="G151" s="171"/>
+      <c r="H151" s="171">
         <v>1</v>
       </c>
-      <c r="I151" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="J151" s="73">
+      <c r="I151" s="171" t="s">
+        <v>164</v>
+      </c>
+      <c r="J151" s="172">
         <v>5000</v>
       </c>
-      <c r="K151" s="73">
+      <c r="K151" s="172">
         <f>H151*J151</f>
         <v>5000</v>
       </c>
-      <c r="L151" s="25"/>
+      <c r="L151" s="173"/>
     </row>
     <row r="152" spans="2:12">
-      <c r="B152" s="81"/>
-      <c r="C152" s="29"/>
-      <c r="D152" s="24"/>
-      <c r="E152" s="24"/>
-      <c r="F152" s="24"/>
-      <c r="G152" s="70"/>
-      <c r="H152" s="24"/>
-      <c r="I152" s="24"/>
-      <c r="J152" s="73"/>
-      <c r="K152" s="73"/>
-      <c r="L152" s="25"/>
+      <c r="B152" s="169"/>
+      <c r="C152" s="189"/>
+      <c r="D152" s="171"/>
+      <c r="E152" s="171"/>
+      <c r="F152" s="171"/>
+      <c r="G152" s="172"/>
+      <c r="H152" s="171"/>
+      <c r="I152" s="171"/>
+      <c r="J152" s="172"/>
+      <c r="K152" s="172"/>
+      <c r="L152" s="173"/>
     </row>
     <row r="153" spans="2:12" ht="33" customHeight="1">
-      <c r="B153" s="81">
+      <c r="B153" s="169">
         <v>22</v>
       </c>
-      <c r="C153" s="18" t="s">
+      <c r="C153" s="183" t="s">
         <v>89</v>
       </c>
-      <c r="D153" s="24">
+      <c r="D153" s="171">
         <v>1</v>
       </c>
-      <c r="E153" s="24"/>
-      <c r="F153" s="24"/>
-      <c r="G153" s="24"/>
-      <c r="H153" s="24">
+      <c r="E153" s="171"/>
+      <c r="F153" s="171"/>
+      <c r="G153" s="171"/>
+      <c r="H153" s="171">
         <v>1</v>
       </c>
-      <c r="I153" s="24" t="s">
+      <c r="I153" s="171" t="s">
         <v>34</v>
       </c>
-      <c r="J153" s="73">
+      <c r="J153" s="172">
         <v>500</v>
       </c>
-      <c r="K153" s="73">
+      <c r="K153" s="172">
         <f>H153*J153</f>
         <v>500</v>
       </c>
-      <c r="L153" s="25"/>
-    </row>
-    <row r="154" spans="2:12" ht="17.399999999999999" thickBot="1">
-      <c r="B154" s="22"/>
-      <c r="C154" s="26"/>
-      <c r="D154" s="76"/>
-      <c r="E154" s="77"/>
-      <c r="F154" s="77"/>
-      <c r="G154" s="77"/>
-      <c r="H154" s="77"/>
-      <c r="I154" s="76"/>
-      <c r="J154" s="77"/>
-      <c r="K154" s="78">
+      <c r="L153" s="173"/>
+    </row>
+    <row r="154" spans="2:12">
+      <c r="B154" s="190"/>
+      <c r="C154" s="191"/>
+      <c r="D154" s="171"/>
+      <c r="E154" s="172"/>
+      <c r="F154" s="172"/>
+      <c r="G154" s="172"/>
+      <c r="H154" s="172"/>
+      <c r="I154" s="171"/>
+      <c r="J154" s="172"/>
+      <c r="K154" s="192">
         <f>SUM(K12:K153)</f>
         <v>877810.68270516139</v>
       </c>
-      <c r="L154" s="23"/>
+      <c r="L154" s="193"/>
     </row>
     <row r="155" spans="2:12">
-      <c r="C155" s="9"/>
-      <c r="D155" s="10"/>
-      <c r="E155" s="10"/>
-      <c r="F155" s="10"/>
-      <c r="G155" s="10"/>
-      <c r="H155" s="10"/>
-      <c r="I155" s="10"/>
-      <c r="J155" s="10"/>
-      <c r="K155" s="11"/>
-      <c r="L155" s="8"/>
+      <c r="C155" s="156"/>
+      <c r="D155" s="157"/>
+      <c r="E155" s="157"/>
+      <c r="F155" s="157"/>
+      <c r="G155" s="157"/>
+      <c r="H155" s="157"/>
+      <c r="I155" s="157"/>
+      <c r="J155" s="157"/>
+      <c r="K155" s="158"/>
+      <c r="L155" s="152"/>
     </row>
     <row r="156" spans="2:12">
-      <c r="C156" s="5"/>
-      <c r="E156" s="2"/>
-      <c r="F156" s="2"/>
-      <c r="H156" s="2"/>
-      <c r="I156" s="65" t="s">
+      <c r="C156" s="166" t="s">
         <v>12</v>
       </c>
-      <c r="J156" s="65"/>
-      <c r="K156" s="65" t="s">
+      <c r="D156" s="194" t="s">
         <v>71</v>
       </c>
-      <c r="L156" s="65" t="s">
+      <c r="E156" s="194"/>
+      <c r="F156" s="166" t="s">
         <v>72</v>
       </c>
+      <c r="H156" s="145"/>
     </row>
     <row r="157" spans="2:12">
-      <c r="C157" s="5"/>
-      <c r="H157" s="64"/>
-      <c r="I157" s="66" t="s">
+      <c r="C157" s="176" t="s">
         <v>13</v>
       </c>
-      <c r="J157" s="67"/>
-      <c r="K157" s="67">
+      <c r="D157" s="195">
         <f>+K154</f>
         <v>877810.68270516139</v>
       </c>
-      <c r="L157" s="67"/>
+      <c r="E157" s="195"/>
+      <c r="F157" s="196"/>
+      <c r="H157" s="159"/>
     </row>
     <row r="158" spans="2:12">
-      <c r="C158" s="5"/>
-      <c r="H158" s="64"/>
-      <c r="I158" s="66" t="s">
+      <c r="C158" s="176" t="s">
         <v>14</v>
       </c>
-      <c r="J158" s="68"/>
-      <c r="K158" s="67">
+      <c r="D158" s="195">
         <v>200000</v>
       </c>
-      <c r="L158" s="68">
+      <c r="E158" s="195"/>
+      <c r="F158" s="197">
         <v>100</v>
       </c>
+      <c r="H158" s="159"/>
     </row>
     <row r="159" spans="2:12">
-      <c r="C159" s="5"/>
-      <c r="H159" s="64"/>
-      <c r="I159" s="66" t="s">
+      <c r="C159" s="176" t="s">
         <v>19</v>
       </c>
-      <c r="J159" s="68"/>
-      <c r="K159" s="67">
-        <f>0.95*K158</f>
+      <c r="D159" s="195">
+        <f>0.95*D158</f>
         <v>190000</v>
       </c>
-      <c r="L159" s="68">
-        <f>K159/K157*100</f>
+      <c r="E159" s="195"/>
+      <c r="F159" s="197">
+        <f>D159/D157*100</f>
         <v>21.644758231293604</v>
       </c>
+      <c r="H159" s="159"/>
     </row>
     <row r="160" spans="2:12">
-      <c r="C160" s="5"/>
-      <c r="H160" s="64"/>
-      <c r="I160" s="66" t="s">
+      <c r="C160" s="176" t="s">
         <v>15</v>
       </c>
-      <c r="J160" s="68"/>
-      <c r="K160" s="67">
-        <f>K157-K159</f>
+      <c r="D160" s="195">
+        <f>D157-D159</f>
         <v>687810.68270516139</v>
       </c>
-      <c r="L160" s="68">
-        <f>K160/K158*100</f>
+      <c r="E160" s="195"/>
+      <c r="F160" s="197">
+        <f>D160/D158*100</f>
         <v>343.90534135258071</v>
       </c>
-    </row>
-    <row r="161" spans="3:12">
-      <c r="C161" s="5"/>
-      <c r="H161" s="64"/>
-      <c r="I161" s="66" t="s">
+      <c r="H160" s="159"/>
+    </row>
+    <row r="161" spans="3:8">
+      <c r="C161" s="176" t="s">
         <v>20</v>
       </c>
-      <c r="J161" s="68"/>
-      <c r="K161" s="67">
-        <f>L161*K158/100</f>
+      <c r="D161" s="195">
+        <f>F161*D158/100</f>
         <v>4000</v>
       </c>
-      <c r="L161" s="68">
+      <c r="E161" s="195"/>
+      <c r="F161" s="197">
         <v>2</v>
       </c>
-    </row>
-    <row r="162" spans="3:12">
-      <c r="C162" s="5"/>
-      <c r="H162" s="63"/>
-      <c r="I162" s="66" t="s">
+      <c r="H161" s="159"/>
+    </row>
+    <row r="162" spans="3:8">
+      <c r="C162" s="176" t="s">
         <v>21</v>
       </c>
-      <c r="J162" s="68"/>
-      <c r="K162" s="68">
-        <f>L162*K158/100</f>
+      <c r="D162" s="198">
+        <f>F162*D158/100</f>
         <v>6000</v>
       </c>
-      <c r="L162" s="68">
+      <c r="E162" s="198"/>
+      <c r="F162" s="197">
         <v>3</v>
       </c>
-    </row>
-    <row r="163" spans="3:12">
-      <c r="G163" s="62"/>
+      <c r="H162" s="160"/>
+    </row>
+    <row r="163" spans="3:8">
+      <c r="G163" s="161"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="O6:R6"/>
+  <mergeCells count="14">
+    <mergeCell ref="D161:E161"/>
+    <mergeCell ref="D162:E162"/>
+    <mergeCell ref="D156:E156"/>
+    <mergeCell ref="D157:E157"/>
+    <mergeCell ref="D158:E158"/>
+    <mergeCell ref="D159:E159"/>
+    <mergeCell ref="D160:E160"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
@@ -10813,15 +10825,11 @@
     <mergeCell ref="I6:L6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.38" bottom="0.7" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup scale="70" fitToHeight="2" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.70866141732283472" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="76" fitToHeight="2" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;RPage &amp;P of &amp;N</oddHeader>
   </headerFooter>
-  <rowBreaks count="2" manualBreakCount="2">
-    <brk id="112" max="11" man="1"/>
-    <brk id="154" max="11" man="1"/>
-  </rowBreaks>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -10840,221 +10848,221 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">
-      <c r="A1" s="91">
+      <c r="A1" s="90">
         <v>152</v>
       </c>
-      <c r="B1" s="160" t="s">
+      <c r="B1" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.6">
+      <c r="A2" s="91" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+    </row>
+    <row r="3" spans="1:8" ht="32.4">
+      <c r="A3" s="92"/>
+      <c r="B3" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.6">
-      <c r="A2" s="92" t="s">
+      <c r="C3" s="93" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="162" t="s">
+      <c r="D3" s="93" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-    </row>
-    <row r="3" spans="1:8" ht="32.4">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94" t="s">
+      <c r="E3" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="94" t="s">
+      <c r="F3" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="94" t="s">
+      <c r="G3" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="94" t="s">
+      <c r="H3" s="93" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="94" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="16.8">
+      <c r="A4" s="92"/>
+      <c r="B4" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="94" t="s">
+      <c r="C4" s="94" t="s">
         <v>117</v>
       </c>
-      <c r="H3" s="94" t="s">
+      <c r="D4" s="95">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="96" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="16.8">
-      <c r="A4" s="93"/>
-      <c r="B4" s="164" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="95" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" s="96">
-        <v>0.5</v>
-      </c>
-      <c r="E4" s="97" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" s="98">
+      <c r="F4" s="97">
         <v>1245</v>
       </c>
-      <c r="G4" s="98">
+      <c r="G4" s="97">
         <f>FLOOR(D4*F4,0.01)</f>
         <v>622.5</v>
       </c>
-      <c r="H4" s="99"/>
+      <c r="H4" s="98"/>
     </row>
     <row r="5" spans="1:8" ht="18">
-      <c r="A5" s="93"/>
-      <c r="B5" s="165"/>
-      <c r="C5" s="100" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="101">
+      <c r="A5" s="92"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="99" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="100">
         <v>1</v>
       </c>
-      <c r="E5" s="100" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="102">
+      <c r="E5" s="99" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="101">
         <v>935</v>
       </c>
-      <c r="G5" s="102">
+      <c r="G5" s="101">
         <f>FLOOR(D5*F5,0.01)</f>
         <v>935</v>
       </c>
-      <c r="H5" s="103">
+      <c r="H5" s="102">
         <f>SUM(G4+G5)</f>
         <v>1557.5</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18">
-      <c r="A6" s="93"/>
-      <c r="B6" s="166" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="96">
+      <c r="A6" s="92"/>
+      <c r="B6" s="136" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="96" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="95">
         <f>420*0</f>
         <v>0</v>
       </c>
-      <c r="E6" s="97" t="s">
-        <v>125</v>
-      </c>
-      <c r="F6" s="104">
+      <c r="E6" s="96" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="103">
         <v>15.145</v>
       </c>
-      <c r="G6" s="105">
+      <c r="G6" s="104">
         <f>FLOOR(D6*F6,0.01)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="99"/>
+      <c r="H6" s="98"/>
     </row>
     <row r="7" spans="1:8" ht="18">
-      <c r="A7" s="93"/>
-      <c r="B7" s="167"/>
-      <c r="C7" s="100" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="101">
+      <c r="A7" s="92"/>
+      <c r="B7" s="137"/>
+      <c r="C7" s="99" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="100">
         <f>0.71*0</f>
         <v>0</v>
       </c>
-      <c r="E7" s="100" t="s">
-        <v>127</v>
-      </c>
-      <c r="F7" s="102">
+      <c r="E7" s="99" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="101">
         <v>3177.9</v>
       </c>
-      <c r="G7" s="102">
+      <c r="G7" s="101">
         <f>FLOOR(D7*F7,0.01)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="106">
+      <c r="H7" s="105">
         <f>SUM(G6:G7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.399999999999999">
-      <c r="A8" s="93"/>
-      <c r="B8" s="93"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="107" t="s">
-        <v>128</v>
-      </c>
-      <c r="G8" s="108"/>
-      <c r="H8" s="102">
+      <c r="A8" s="92"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="106" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="107"/>
+      <c r="H8" s="101">
         <f>SUM(H7,H5)</f>
         <v>1557.5</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.399999999999999">
-      <c r="A9" s="93"/>
-      <c r="B9" s="93" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" s="108"/>
-      <c r="H9" s="109">
+      <c r="A9" s="92"/>
+      <c r="B9" s="92" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="106" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="107"/>
+      <c r="H9" s="108">
         <f>FLOOR(H8*0.15,0.01)</f>
         <v>233.62</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.399999999999999">
-      <c r="A10" s="110"/>
-      <c r="B10" s="111">
+      <c r="A10" s="109"/>
+      <c r="B10" s="110">
         <f>+H10</f>
         <v>1791.12</v>
       </c>
-      <c r="C10" s="112" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="109">
+      <c r="C10" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="108">
         <f>INT(B10/B11*100)/100</f>
         <v>179.11</v>
       </c>
-      <c r="E10" s="93" t="s">
-        <v>132</v>
-      </c>
-      <c r="F10" s="107" t="s">
-        <v>133</v>
-      </c>
-      <c r="G10" s="108"/>
-      <c r="H10" s="109">
+      <c r="E10" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="106" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" s="107"/>
+      <c r="H10" s="108">
         <f>SUM(H8:H9)</f>
         <v>1791.12</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.8">
-      <c r="A11" s="93"/>
-      <c r="B11" s="113">
+      <c r="A11" s="92"/>
+      <c r="B11" s="112">
         <v>10</v>
       </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="4">
